--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -6510,10 +6510,10 @@
         <v>880</v>
       </c>
       <c r="N144" t="n">
-        <v>169.22033898305</v>
+        <v>156</v>
       </c>
       <c r="O144" t="n">
-        <v>148913.898305084</v>
+        <v>137280</v>
       </c>
       <c r="P144" t="n">
         <v>195</v>
@@ -7446,10 +7446,10 @@
         <v>73</v>
       </c>
       <c r="N165" t="n">
-        <v>6470.8036363636</v>
+        <v>6441.03</v>
       </c>
       <c r="O165" t="n">
-        <v>472368.6654545428</v>
+        <v>470195.19</v>
       </c>
       <c r="P165" t="n">
         <v>10500</v>
@@ -10755,10 +10755,10 @@
         <v>1</v>
       </c>
       <c r="N241" t="n">
-        <v>2109.2758108108</v>
+        <v>2081.1521621622</v>
       </c>
       <c r="O241" t="n">
-        <v>2109.2758108108</v>
+        <v>2081.1521621622</v>
       </c>
       <c r="P241" t="n">
         <v>3000</v>
@@ -13013,10 +13013,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4254.3242335766</v>
+        <v>4163.1601459854</v>
       </c>
       <c r="O293" t="n">
-        <v>293548.3721167854</v>
+        <v>287258.0500729926</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13197,10 +13197,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O297" t="n">
-        <v>2088542.891382522</v>
+        <v>2082050.012494819</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13565,10 +13565,10 @@
         <v>193</v>
       </c>
       <c r="N305" t="n">
-        <v>1821.7243939394</v>
+        <v>1812.57</v>
       </c>
       <c r="O305" t="n">
-        <v>351592.8080303042</v>
+        <v>349826.01</v>
       </c>
       <c r="P305" t="n">
         <v>2900</v>
@@ -13749,10 +13749,10 @@
         <v>90</v>
       </c>
       <c r="N309" t="n">
-        <v>15692.208588957</v>
+        <v>15502</v>
       </c>
       <c r="O309" t="n">
-        <v>1412298.77300613</v>
+        <v>1395180</v>
       </c>
       <c r="P309" t="n">
         <v>25900</v>
@@ -19222,10 +19222,10 @@
         <v>266</v>
       </c>
       <c r="N428" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O428" t="n">
-        <v>761062.1196162726</v>
+        <v>760020.5199999999</v>
       </c>
       <c r="P428" t="n">
         <v>4900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -603,10 +603,10 @@
         <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.40686747</v>
+        <v>96741.40695121999</v>
       </c>
       <c r="O5" t="n">
-        <v>5611001.59831326</v>
+        <v>5611001.60317076</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
@@ -968,10 +968,10 @@
         <v>1080</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3036050799</v>
+        <v>1811.3037351443</v>
       </c>
       <c r="O14" t="n">
-        <v>1956207.893486292</v>
+        <v>1956208.033955844</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1085,10 +1085,10 @@
         <v>343</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.7465222073</v>
+        <v>3376.746520334</v>
       </c>
       <c r="O17" t="n">
-        <v>1158224.057117104</v>
+        <v>1158224.056474562</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.0011709602</v>
+        <v>2413.0011723329</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.617096025</v>
+        <v>1271651.617819438</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.966415094</v>
+        <v>15711.966317829</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.581886768</v>
+        <v>1131261.574883688</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -2764,10 +2764,10 @@
         <v>60</v>
       </c>
       <c r="N59" t="n">
-        <v>30238.812222222</v>
+        <v>30238.812278481</v>
       </c>
       <c r="O59" t="n">
-        <v>1814328.73333332</v>
+        <v>1814328.73670886</v>
       </c>
       <c r="P59" t="n">
         <v>51100</v>
@@ -3056,10 +3056,10 @@
         <v>12</v>
       </c>
       <c r="N66" t="n">
-        <v>36306.262857143</v>
+        <v>36306.276</v>
       </c>
       <c r="O66" t="n">
-        <v>435675.154285716</v>
+        <v>435675.312</v>
       </c>
       <c r="P66" t="n">
         <v>64900</v>
@@ -3103,10 +3103,10 @@
         <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>56906.799135802</v>
+        <v>56906.800422535</v>
       </c>
       <c r="O67" t="n">
-        <v>2276271.96543208</v>
+        <v>2276272.0169014</v>
       </c>
       <c r="P67" t="n">
         <v>95900</v>
@@ -3244,10 +3244,10 @@
         <v>112</v>
       </c>
       <c r="N70" t="n">
-        <v>141416.8844164</v>
+        <v>141416.8844586</v>
       </c>
       <c r="O70" t="n">
-        <v>15838691.0546368</v>
+        <v>15838691.0593632</v>
       </c>
       <c r="P70" t="n">
         <v>251900</v>
@@ -3286,10 +3286,10 @@
         <v>39</v>
       </c>
       <c r="N71" t="n">
-        <v>200072.19889655</v>
+        <v>200072.19902098</v>
       </c>
       <c r="O71" t="n">
-        <v>7802815.75696545</v>
+        <v>7802815.761818221</v>
       </c>
       <c r="P71" t="n">
         <v>312000</v>
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="N72" t="n">
-        <v>174389.78511628</v>
+        <v>174389.78625</v>
       </c>
       <c r="O72" t="n">
-        <v>2441456.99162792</v>
+        <v>2441457.0075</v>
       </c>
       <c r="P72" t="n">
         <v>368200</v>
@@ -3469,10 +3469,10 @@
         <v>14</v>
       </c>
       <c r="N75" t="n">
-        <v>263530.18</v>
+        <v>263530.179</v>
       </c>
       <c r="O75" t="n">
-        <v>3689422.52</v>
+        <v>3689422.506</v>
       </c>
       <c r="P75" t="n">
         <v>402900</v>
@@ -3731,10 +3731,10 @@
         <v>97</v>
       </c>
       <c r="N81" t="n">
-        <v>61666.873832487</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O81" t="n">
-        <v>5981686.761751239</v>
+        <v>5981686.762697184</v>
       </c>
       <c r="P81" t="n">
         <v>98900</v>
@@ -4117,10 +4117,10 @@
         <v>1440</v>
       </c>
       <c r="N90" t="n">
-        <v>1950.2152617329</v>
+        <v>1950.2152574526</v>
       </c>
       <c r="O90" t="n">
-        <v>2808309.976895376</v>
+        <v>2808309.970731744</v>
       </c>
       <c r="P90" t="n">
         <v>2900</v>
@@ -5366,10 +5366,10 @@
         <v>6298</v>
       </c>
       <c r="N119" t="n">
-        <v>3158.8608123465</v>
+        <v>3158.860813208</v>
       </c>
       <c r="O119" t="n">
-        <v>19894505.39615826</v>
+        <v>19894505.40158398</v>
       </c>
       <c r="P119" t="n">
         <v>5600</v>
@@ -5458,10 +5458,10 @@
         <v>144</v>
       </c>
       <c r="N121" t="n">
-        <v>3841.6246596357</v>
+        <v>3841.6246641075</v>
       </c>
       <c r="O121" t="n">
-        <v>553193.9509875408</v>
+        <v>553193.95163148</v>
       </c>
       <c r="P121" t="n">
         <v>6900</v>
@@ -5916,10 +5916,10 @@
         <v>3024</v>
       </c>
       <c r="N131" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070299</v>
       </c>
       <c r="O131" t="n">
-        <v>11478227.06125449</v>
+        <v>11478227.06125842</v>
       </c>
       <c r="P131" t="n">
         <v>6200</v>
@@ -6733,10 +6733,10 @@
         <v>264</v>
       </c>
       <c r="N149" t="n">
-        <v>3594.2542686567</v>
+        <v>3594.2542583732</v>
       </c>
       <c r="O149" t="n">
-        <v>948883.1269253688</v>
+        <v>948883.1242105248</v>
       </c>
       <c r="P149" t="n">
         <v>6500</v>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>2723</v>
+        <v>2243</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6997,19 +6997,19 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>2723</v>
+        <v>2243</v>
       </c>
       <c r="N155" t="n">
         <v>2090.85</v>
       </c>
       <c r="O155" t="n">
-        <v>5693384.55</v>
+        <v>4689776.55</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
       </c>
       <c r="Q155" t="n">
-        <v>7896700</v>
+        <v>6504700</v>
       </c>
     </row>
     <row r="156">
@@ -7315,10 +7315,10 @@
         <v>78</v>
       </c>
       <c r="N162" t="n">
-        <v>3041.6600119617</v>
+        <v>3041.6600120048</v>
       </c>
       <c r="O162" t="n">
-        <v>237249.4809330126</v>
+        <v>237249.4809363744</v>
       </c>
       <c r="P162" t="n">
         <v>5500</v>
@@ -8637,10 +8637,10 @@
         <v>1152</v>
       </c>
       <c r="N192" t="n">
-        <v>1630.9228476208</v>
+        <v>1630.9229073724</v>
       </c>
       <c r="O192" t="n">
-        <v>1878823.120459162</v>
+        <v>1878823.189293005</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8683,10 +8683,10 @@
         <v>1152</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.604715</v>
+        <v>1690.6040282132</v>
       </c>
       <c r="O193" t="n">
-        <v>1947576.63168</v>
+        <v>1947575.840501606</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8729,10 +8729,10 @@
         <v>5472</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1927793589</v>
+        <v>1550.1928456407</v>
       </c>
       <c r="O194" t="n">
-        <v>8482654.8886519</v>
+        <v>8482655.25134591</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8775,10 +8775,10 @@
         <v>2016</v>
       </c>
       <c r="N195" t="n">
-        <v>2403.5096714419</v>
+        <v>2403.5097473321</v>
       </c>
       <c r="O195" t="n">
-        <v>4845475.497626871</v>
+        <v>4845475.650621513</v>
       </c>
       <c r="P195" t="n">
         <v>3500</v>
@@ -10235,10 +10235,10 @@
         <v>122</v>
       </c>
       <c r="N229" t="n">
-        <v>22485.695964126</v>
+        <v>22485.695955056</v>
       </c>
       <c r="O229" t="n">
-        <v>2743254.907623372</v>
+        <v>2743254.906516832</v>
       </c>
       <c r="P229" t="n">
         <v>36500</v>
@@ -10366,10 +10366,10 @@
         <v>381</v>
       </c>
       <c r="N232" t="n">
-        <v>2680.739700672</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O232" t="n">
-        <v>1021361.825956032</v>
+        <v>1021361.825886309</v>
       </c>
       <c r="P232" t="n">
         <v>4900</v>
@@ -10407,10 +10407,10 @@
         <v>1254</v>
       </c>
       <c r="N233" t="n">
-        <v>880.32913152496</v>
+        <v>880.32918386061</v>
       </c>
       <c r="O233" t="n">
-        <v>1103932.7309323</v>
+        <v>1103932.796561205</v>
       </c>
       <c r="P233" t="n">
         <v>1200</v>
@@ -10714,10 +10714,10 @@
         <v>523</v>
       </c>
       <c r="N240" t="n">
-        <v>998.76125748503</v>
+        <v>998.76125816993</v>
       </c>
       <c r="O240" t="n">
-        <v>522352.1376646707</v>
+        <v>522352.1380228734</v>
       </c>
       <c r="P240" t="n">
         <v>1600</v>
@@ -10891,10 +10891,10 @@
         <v>390</v>
       </c>
       <c r="N244" t="n">
-        <v>4285.1951469098</v>
+        <v>4285.1951678535</v>
       </c>
       <c r="O244" t="n">
-        <v>1671226.107294822</v>
+        <v>1671226.115462865</v>
       </c>
       <c r="P244" t="n">
         <v>6900</v>
@@ -12220,10 +12220,10 @@
         <v>34</v>
       </c>
       <c r="N275" t="n">
-        <v>27123.765285451</v>
+        <v>27123.765268022</v>
       </c>
       <c r="O275" t="n">
-        <v>922208.0197053341</v>
+        <v>922208.0191127481</v>
       </c>
       <c r="P275" t="n">
         <v>44500</v>
@@ -12829,10 +12829,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3113.890023175</v>
+        <v>3113.8900237812</v>
       </c>
       <c r="O289" t="n">
-        <v>1348314.380034775</v>
+        <v>1348314.38029726</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13013,10 +13013,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4163.1601459854</v>
+        <v>4163.1601515152</v>
       </c>
       <c r="O293" t="n">
-        <v>287258.0500729926</v>
+        <v>287258.0504545488</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13197,10 +13197,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5218.1704573805</v>
+        <v>5218.1704631579</v>
       </c>
       <c r="O297" t="n">
-        <v>2082050.012494819</v>
+        <v>2082050.014800002</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13243,10 +13243,10 @@
         <v>206</v>
       </c>
       <c r="N298" t="n">
-        <v>1595.0095696489</v>
+        <v>1595.009520202</v>
       </c>
       <c r="O298" t="n">
-        <v>328571.9713476734</v>
+        <v>328571.961161612</v>
       </c>
       <c r="P298" t="n">
         <v>2600</v>
@@ -13289,10 +13289,10 @@
         <v>601</v>
       </c>
       <c r="N299" t="n">
-        <v>3610.6500224972</v>
+        <v>3610.6500229095</v>
       </c>
       <c r="O299" t="n">
-        <v>2170000.663520817</v>
+        <v>2170000.66376861</v>
       </c>
       <c r="P299" t="n">
         <v>5800</v>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13424,19 +13424,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="N302" t="n">
         <v>3965.02</v>
       </c>
       <c r="O302" t="n">
-        <v>1494812.54</v>
+        <v>1256911.34</v>
       </c>
       <c r="P302" t="n">
         <v>6500</v>
       </c>
       <c r="Q302" t="n">
-        <v>2450500</v>
+        <v>2060500</v>
       </c>
     </row>
     <row r="303">
@@ -13703,10 +13703,10 @@
         <v>384</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.362204192</v>
+        <v>1664.3618458274</v>
       </c>
       <c r="O308" t="n">
-        <v>639115.086409728</v>
+        <v>639114.9487977216</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -14393,10 +14393,10 @@
         <v>1145</v>
       </c>
       <c r="N323" t="n">
-        <v>1778.4724989266</v>
+        <v>1778.4725014327</v>
       </c>
       <c r="O323" t="n">
-        <v>2036351.011270957</v>
+        <v>2036351.014140442</v>
       </c>
       <c r="P323" t="n">
         <v>4900</v>
@@ -16134,10 +16134,10 @@
         <v>216</v>
       </c>
       <c r="N361" t="n">
-        <v>5869.1728258706</v>
+        <v>5869.1727972028</v>
       </c>
       <c r="O361" t="n">
-        <v>1267741.33038805</v>
+        <v>1267741.324195805</v>
       </c>
       <c r="P361" t="n">
         <v>9500</v>
@@ -18064,10 +18064,10 @@
         <v>4224</v>
       </c>
       <c r="N403" t="n">
-        <v>1516.0388192979</v>
+        <v>1516.038818618</v>
       </c>
       <c r="O403" t="n">
-        <v>6403747.97271433</v>
+        <v>6403747.969842432</v>
       </c>
       <c r="P403" t="n">
         <v>2300</v>
@@ -18110,10 +18110,10 @@
         <v>1152</v>
       </c>
       <c r="N404" t="n">
-        <v>2458.5136620146</v>
+        <v>2458.5136155257</v>
       </c>
       <c r="O404" t="n">
-        <v>2832207.738640819</v>
+        <v>2832207.685085606</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -18156,10 +18156,10 @@
         <v>480</v>
       </c>
       <c r="N405" t="n">
-        <v>1907.3946349467</v>
+        <v>1907.3946039604</v>
       </c>
       <c r="O405" t="n">
-        <v>915549.424774416</v>
+        <v>915549.4099009919</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18202,10 +18202,10 @@
         <v>576</v>
       </c>
       <c r="N406" t="n">
-        <v>1771.0915140845</v>
+        <v>1771.0914991182</v>
       </c>
       <c r="O406" t="n">
-        <v>1020148.712112672</v>
+        <v>1020148.703492083</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18248,10 +18248,10 @@
         <v>960</v>
       </c>
       <c r="N407" t="n">
-        <v>2079.3843256997</v>
+        <v>2079.3842820513</v>
       </c>
       <c r="O407" t="n">
-        <v>1996208.952671712</v>
+        <v>1996208.910769248</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -18294,10 +18294,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1803.0147949081</v>
+        <v>1803.0148044218</v>
       </c>
       <c r="O408" t="n">
-        <v>2423251.884356486</v>
+        <v>2423251.897142899</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18340,10 +18340,10 @@
         <v>144</v>
       </c>
       <c r="N409" t="n">
-        <v>3306.5955223881</v>
+        <v>3306.595494368</v>
       </c>
       <c r="O409" t="n">
-        <v>476149.7552238864</v>
+        <v>476149.751188992</v>
       </c>
       <c r="P409" t="n">
         <v>4900</v>
@@ -18432,10 +18432,10 @@
         <v>612</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7893319081</v>
+        <v>2108.7893820527</v>
       </c>
       <c r="O411" t="n">
-        <v>1290579.071127757</v>
+        <v>1290579.101816253</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18524,10 +18524,10 @@
         <v>714</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.5675847458</v>
+        <v>3224.5676430401</v>
       </c>
       <c r="O413" t="n">
-        <v>2302341.255508501</v>
+        <v>2302341.297130631</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18570,10 +18570,10 @@
         <v>1152</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.9315412844</v>
+        <v>1655.9314708603</v>
       </c>
       <c r="O414" t="n">
-        <v>1907633.135559629</v>
+        <v>1907633.054431065</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -18985,10 +18985,10 @@
         <v>8400</v>
       </c>
       <c r="N423" t="n">
-        <v>1955.2371193049</v>
+        <v>1955.2371191444</v>
       </c>
       <c r="O423" t="n">
-        <v>16423991.80216116</v>
+        <v>16423991.80081296</v>
       </c>
       <c r="P423" t="n">
         <v>3000</v>
@@ -19683,10 +19683,10 @@
         <v>912</v>
       </c>
       <c r="N438" t="n">
-        <v>2286.1662851537</v>
+        <v>2286.1661853593</v>
       </c>
       <c r="O438" t="n">
-        <v>2084983.652060174</v>
+        <v>2084983.561047682</v>
       </c>
       <c r="P438" t="n">
         <v>3000</v>
@@ -20039,10 +20039,10 @@
         <v>7572</v>
       </c>
       <c r="N446" t="n">
-        <v>517.28716412902</v>
+        <v>517.28728171896</v>
       </c>
       <c r="O446" t="n">
-        <v>3916898.406784939</v>
+        <v>3916899.297175965</v>
       </c>
       <c r="P446" t="n">
         <v>900</v>
@@ -20088,10 +20088,10 @@
         <v>1008</v>
       </c>
       <c r="N447" t="n">
-        <v>3110.8436976288</v>
+        <v>3110.8435374771</v>
       </c>
       <c r="O447" t="n">
-        <v>3135730.44720983</v>
+        <v>3135730.285776917</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
@@ -20220,10 +20220,10 @@
         <v>19400</v>
       </c>
       <c r="N450" t="n">
-        <v>703.79553051727</v>
+        <v>703.79547499887</v>
       </c>
       <c r="O450" t="n">
-        <v>13653633.29203504</v>
+        <v>13653632.21497808</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
@@ -20797,10 +20797,10 @@
         <v>2569</v>
       </c>
       <c r="N463" t="n">
-        <v>1595.5195815035</v>
+        <v>1595.5194396439</v>
       </c>
       <c r="O463" t="n">
-        <v>4098889.804882491</v>
+        <v>4098889.440445179</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -21302,10 +21302,10 @@
         <v>4</v>
       </c>
       <c r="N474" t="n">
-        <v>1783.7988883868</v>
+        <v>1783.7988878843</v>
       </c>
       <c r="O474" t="n">
-        <v>7135.1955535472</v>
+        <v>7135.1955515372</v>
       </c>
       <c r="P474" t="n">
         <v>1500</v>
@@ -21444,10 +21444,10 @@
         <v>50</v>
       </c>
       <c r="N477" t="n">
-        <v>4159.0002836879</v>
+        <v>4159.0002846975</v>
       </c>
       <c r="O477" t="n">
-        <v>207950.014184395</v>
+        <v>207950.014234875</v>
       </c>
       <c r="P477" t="n">
         <v>8900</v>
@@ -21674,10 +21674,10 @@
         <v>1976</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.9398308668</v>
+        <v>7046.939830831</v>
       </c>
       <c r="O482" t="n">
-        <v>13924753.1057928</v>
+        <v>13924753.10572206</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
@@ -23804,10 +23804,10 @@
         <v>69</v>
       </c>
       <c r="N531" t="n">
-        <v>4985.4043478261</v>
+        <v>4985.4044444444</v>
       </c>
       <c r="O531" t="n">
-        <v>343992.9000000009</v>
+        <v>343992.9066666636</v>
       </c>
       <c r="P531" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -650,10 +650,10 @@
         <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>66707.977073171</v>
+        <v>66707.97725</v>
       </c>
       <c r="O6" t="n">
-        <v>1400867.518536591</v>
+        <v>1400867.52225</v>
       </c>
       <c r="P6" t="n">
         <v>125900</v>
@@ -968,10 +968,10 @@
         <v>1080</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3037351443</v>
+        <v>1811.3037703513</v>
       </c>
       <c r="O14" t="n">
-        <v>1956208.033955844</v>
+        <v>1956208.071979404</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1007,10 +1007,10 @@
         <v>48</v>
       </c>
       <c r="N15" t="n">
-        <v>27000</v>
+        <v>27225.941422594</v>
       </c>
       <c r="O15" t="n">
-        <v>1296000</v>
+        <v>1306845.188284512</v>
       </c>
       <c r="P15" t="n">
         <v>30000</v>
@@ -1085,10 +1085,10 @@
         <v>343</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.746520334</v>
+        <v>3376.7465175202</v>
       </c>
       <c r="O17" t="n">
-        <v>1158224.056474562</v>
+        <v>1158224.055509429</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -1163,10 +1163,10 @@
         <v>162</v>
       </c>
       <c r="N19" t="n">
-        <v>5758.9597797357</v>
+        <v>5784.4419026549</v>
       </c>
       <c r="O19" t="n">
-        <v>932951.4843171834</v>
+        <v>937079.5882300938</v>
       </c>
       <c r="P19" t="n">
         <v>16900</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8539724138</v>
+        <v>6272.8541142857</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.458041381</v>
+        <v>1354936.488685711</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.0011723329</v>
+        <v>2421.5176470588</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.617819438</v>
+        <v>1276139.799999987</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2123,10 +2123,10 @@
         <v>144</v>
       </c>
       <c r="N43" t="n">
-        <v>3716.3301863354</v>
+        <v>3716.330188383</v>
       </c>
       <c r="O43" t="n">
-        <v>535151.5468322976</v>
+        <v>535151.547127152</v>
       </c>
       <c r="P43" t="n">
         <v>9500</v>
@@ -2396,10 +2396,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="n">
-        <v>21333.69</v>
+        <v>21510.733070539</v>
       </c>
       <c r="O50" t="n">
-        <v>640010.7</v>
+        <v>645321.99211617</v>
       </c>
       <c r="P50" t="n">
         <v>30000</v>
@@ -2513,10 +2513,10 @@
         <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>14857.62306383</v>
+        <v>14857.623171806</v>
       </c>
       <c r="O53" t="n">
-        <v>356582.95353192</v>
+        <v>356582.956123344</v>
       </c>
       <c r="P53" t="n">
         <v>34900</v>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3910.628317757</v>
+        <v>3910.628245614</v>
       </c>
       <c r="O54" t="n">
-        <v>594415.5042990639</v>
+        <v>594415.493333328</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -2594,10 +2594,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>10994.352121212</v>
+        <v>10994.352244898</v>
       </c>
       <c r="O55" t="n">
-        <v>527728.901818176</v>
+        <v>527728.907755104</v>
       </c>
       <c r="P55" t="n">
         <v>16900</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.966317829</v>
+        <v>15834.716054688</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.574883688</v>
+        <v>1140099.555937536</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -3286,10 +3286,10 @@
         <v>39</v>
       </c>
       <c r="N71" t="n">
-        <v>200072.19902098</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O71" t="n">
-        <v>7802815.761818221</v>
+        <v>7802815.766808661</v>
       </c>
       <c r="P71" t="n">
         <v>312000</v>
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="N72" t="n">
-        <v>174389.78625</v>
+        <v>174389.78666667</v>
       </c>
       <c r="O72" t="n">
-        <v>2441457.0075</v>
+        <v>2441457.01333338</v>
       </c>
       <c r="P72" t="n">
         <v>368200</v>
@@ -3375,10 +3375,10 @@
         <v>18</v>
       </c>
       <c r="N73" t="n">
-        <v>251809.29411765</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O73" t="n">
-        <v>4532567.294117699</v>
+        <v>4532567.29090902</v>
       </c>
       <c r="P73" t="n">
         <v>584000</v>
@@ -3775,10 +3775,10 @@
         <v>54</v>
       </c>
       <c r="N82" t="n">
-        <v>27000</v>
+        <v>27232.75862069</v>
       </c>
       <c r="O82" t="n">
-        <v>1458000</v>
+        <v>1470568.96551726</v>
       </c>
       <c r="P82" t="n">
         <v>20000</v>
@@ -4035,10 +4035,10 @@
         <v>72</v>
       </c>
       <c r="N88" t="n">
-        <v>2563.34</v>
+        <v>2576.9026455026</v>
       </c>
       <c r="O88" t="n">
-        <v>184560.48</v>
+        <v>185536.9904761872</v>
       </c>
       <c r="P88" t="n">
         <v>4700</v>
@@ -5366,10 +5366,10 @@
         <v>6298</v>
       </c>
       <c r="N119" t="n">
-        <v>3158.860813208</v>
+        <v>3158.8608137572</v>
       </c>
       <c r="O119" t="n">
-        <v>19894505.40158398</v>
+        <v>19894505.40504285</v>
       </c>
       <c r="P119" t="n">
         <v>5600</v>
@@ -5458,10 +5458,10 @@
         <v>144</v>
       </c>
       <c r="N121" t="n">
-        <v>3841.6246641075</v>
+        <v>3841.6246911197</v>
       </c>
       <c r="O121" t="n">
-        <v>553193.95163148</v>
+        <v>553193.9555212368</v>
       </c>
       <c r="P121" t="n">
         <v>6900</v>
@@ -5596,10 +5596,10 @@
         <v>224</v>
       </c>
       <c r="N124" t="n">
-        <v>2694.8235409253</v>
+        <v>2694.8235120643</v>
       </c>
       <c r="O124" t="n">
-        <v>603640.4731672673</v>
+        <v>603640.4667024032</v>
       </c>
       <c r="P124" t="n">
         <v>4900</v>
@@ -6054,10 +6054,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>4890.9300453515</v>
+        <v>4890.9300454545</v>
       </c>
       <c r="O134" t="n">
-        <v>313019.522902496</v>
+        <v>313019.522909088</v>
       </c>
       <c r="P134" t="n">
         <v>8200</v>
@@ -6377,10 +6377,10 @@
         <v>24</v>
       </c>
       <c r="N141" t="n">
-        <v>2267.0481966544</v>
+        <v>2289.4664730119</v>
       </c>
       <c r="O141" t="n">
-        <v>54409.1567197056</v>
+        <v>54947.19535228559</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
@@ -6866,10 +6866,10 @@
         <v>599</v>
       </c>
       <c r="N152" t="n">
-        <v>4891</v>
+        <v>4898.3218562874</v>
       </c>
       <c r="O152" t="n">
-        <v>2929709</v>
+        <v>2934094.791916152</v>
       </c>
       <c r="P152" t="n">
         <v>8200</v>
@@ -7315,10 +7315,10 @@
         <v>78</v>
       </c>
       <c r="N162" t="n">
-        <v>3041.6600120048</v>
+        <v>3041.6600123153</v>
       </c>
       <c r="O162" t="n">
-        <v>237249.4809363744</v>
+        <v>237249.4809605934</v>
       </c>
       <c r="P162" t="n">
         <v>5500</v>
@@ -8229,10 +8229,10 @@
         <v>403</v>
       </c>
       <c r="N183" t="n">
-        <v>2204</v>
+        <v>2225.439688716</v>
       </c>
       <c r="O183" t="n">
-        <v>888212</v>
+        <v>896852.194552548</v>
       </c>
       <c r="P183" t="n">
         <v>1500</v>
@@ -8637,10 +8637,10 @@
         <v>1152</v>
       </c>
       <c r="N192" t="n">
-        <v>1630.9229073724</v>
+        <v>1630.9229356747</v>
       </c>
       <c r="O192" t="n">
-        <v>1878823.189293005</v>
+        <v>1878823.221897254</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8683,10 +8683,10 @@
         <v>1152</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.6040282132</v>
+        <v>1690.6038424947</v>
       </c>
       <c r="O193" t="n">
-        <v>1947575.840501606</v>
+        <v>1947575.626553894</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8729,10 +8729,10 @@
         <v>5472</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1928456407</v>
+        <v>1550.192872291</v>
       </c>
       <c r="O194" t="n">
-        <v>8482655.25134591</v>
+        <v>8482655.397176351</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8775,10 +8775,10 @@
         <v>2016</v>
       </c>
       <c r="N195" t="n">
-        <v>2403.5097473321</v>
+        <v>2403.5098964308</v>
       </c>
       <c r="O195" t="n">
-        <v>4845475.650621513</v>
+        <v>4845475.951204493</v>
       </c>
       <c r="P195" t="n">
         <v>3500</v>
@@ -9697,10 +9697,10 @@
         <v>384</v>
       </c>
       <c r="N216" t="n">
-        <v>2661.82</v>
+        <v>2667.5690712743</v>
       </c>
       <c r="O216" t="n">
-        <v>1022138.88</v>
+        <v>1024346.523369331</v>
       </c>
       <c r="P216" t="n">
         <v>3200</v>
@@ -9738,10 +9738,10 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>4488</v>
+        <v>4508.1255605381</v>
       </c>
       <c r="O217" t="n">
-        <v>4488</v>
+        <v>4508.1255605381</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -9779,10 +9779,10 @@
         <v>481</v>
       </c>
       <c r="N218" t="n">
-        <v>2610</v>
+        <v>2613.7446197991</v>
       </c>
       <c r="O218" t="n">
-        <v>1255410</v>
+        <v>1257211.162123367</v>
       </c>
       <c r="P218" t="n">
         <v>3200</v>
@@ -9902,10 +9902,10 @@
         <v>158</v>
       </c>
       <c r="N221" t="n">
-        <v>2286.55</v>
+        <v>2306.01</v>
       </c>
       <c r="O221" t="n">
-        <v>361274.9</v>
+        <v>364349.58</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10232,19 +10232,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="N229" t="n">
-        <v>22485.695955056</v>
+        <v>22485.695945946</v>
       </c>
       <c r="O229" t="n">
-        <v>2743254.906516832</v>
+        <v>2023712.63513514</v>
       </c>
       <c r="P229" t="n">
         <v>36500</v>
       </c>
       <c r="Q229" t="n">
-        <v>4453000</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="230">
@@ -10407,10 +10407,10 @@
         <v>1254</v>
       </c>
       <c r="N233" t="n">
-        <v>880.32918386061</v>
+        <v>880.32919651056</v>
       </c>
       <c r="O233" t="n">
-        <v>1103932.796561205</v>
+        <v>1103932.812424242</v>
       </c>
       <c r="P233" t="n">
         <v>1200</v>
@@ -10891,10 +10891,10 @@
         <v>390</v>
       </c>
       <c r="N244" t="n">
-        <v>4285.1951678535</v>
+        <v>4285.1952156057</v>
       </c>
       <c r="O244" t="n">
-        <v>1671226.115462865</v>
+        <v>1671226.134086223</v>
       </c>
       <c r="P244" t="n">
         <v>6900</v>
@@ -12220,10 +12220,10 @@
         <v>34</v>
       </c>
       <c r="N275" t="n">
-        <v>27123.765268022</v>
+        <v>27123.765259259</v>
       </c>
       <c r="O275" t="n">
-        <v>922208.0191127481</v>
+        <v>922208.0188148059</v>
       </c>
       <c r="P275" t="n">
         <v>44500</v>
@@ -12435,10 +12435,10 @@
         <v>1</v>
       </c>
       <c r="N280" t="n">
-        <v>6518</v>
+        <v>9777</v>
       </c>
       <c r="O280" t="n">
-        <v>6518</v>
+        <v>9777</v>
       </c>
       <c r="P280" t="n">
         <v>10900</v>
@@ -12655,10 +12655,10 @@
         <v>84</v>
       </c>
       <c r="N285" t="n">
-        <v>13878.97</v>
+        <v>13971.496466667</v>
       </c>
       <c r="O285" t="n">
-        <v>1165833.48</v>
+        <v>1173605.703200028</v>
       </c>
       <c r="P285" t="n">
         <v>21900</v>
@@ -12829,10 +12829,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3113.8900237812</v>
+        <v>3117.5970357143</v>
       </c>
       <c r="O289" t="n">
-        <v>1348314.38029726</v>
+        <v>1349919.516464292</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13013,10 +13013,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4163.1601515152</v>
+        <v>4163.16016</v>
       </c>
       <c r="O293" t="n">
-        <v>287258.0504545488</v>
+        <v>287258.05104</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13059,10 +13059,10 @@
         <v>3</v>
       </c>
       <c r="N294" t="n">
-        <v>8878.450000000001</v>
+        <v>9099.032608695699</v>
       </c>
       <c r="O294" t="n">
-        <v>26635.35</v>
+        <v>27297.0978260871</v>
       </c>
       <c r="P294" t="n">
         <v>14100</v>
@@ -13105,10 +13105,10 @@
         <v>334</v>
       </c>
       <c r="N295" t="n">
-        <v>2495.98</v>
+        <v>2498.7228351648</v>
       </c>
       <c r="O295" t="n">
-        <v>833657.3199999999</v>
+        <v>834573.4269450433</v>
       </c>
       <c r="P295" t="n">
         <v>4100</v>
@@ -13197,10 +13197,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5218.1704631579</v>
+        <v>5218.1704646251</v>
       </c>
       <c r="O297" t="n">
-        <v>2082050.014800002</v>
+        <v>2082050.015385415</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13243,10 +13243,10 @@
         <v>206</v>
       </c>
       <c r="N298" t="n">
-        <v>1595.009520202</v>
+        <v>1595.0095153061</v>
       </c>
       <c r="O298" t="n">
-        <v>328571.961161612</v>
+        <v>328571.9601530566</v>
       </c>
       <c r="P298" t="n">
         <v>2600</v>
@@ -13289,10 +13289,10 @@
         <v>601</v>
       </c>
       <c r="N299" t="n">
-        <v>3610.6500229095</v>
+        <v>3610.650023015</v>
       </c>
       <c r="O299" t="n">
-        <v>2170000.66376861</v>
+        <v>2170000.663832015</v>
       </c>
       <c r="P299" t="n">
         <v>5800</v>
@@ -13427,10 +13427,10 @@
         <v>317</v>
       </c>
       <c r="N302" t="n">
-        <v>3965.02</v>
+        <v>3969.9272029703</v>
       </c>
       <c r="O302" t="n">
-        <v>1256911.34</v>
+        <v>1258466.923341585</v>
       </c>
       <c r="P302" t="n">
         <v>6500</v>
@@ -13473,10 +13473,10 @@
         <v>228</v>
       </c>
       <c r="N303" t="n">
-        <v>5791.05</v>
+        <v>5844.4237327189</v>
       </c>
       <c r="O303" t="n">
-        <v>1320359.4</v>
+        <v>1332528.611059909</v>
       </c>
       <c r="P303" t="n">
         <v>9300</v>
@@ -13565,10 +13565,10 @@
         <v>193</v>
       </c>
       <c r="N305" t="n">
-        <v>1812.57</v>
+        <v>1817.3525065963</v>
       </c>
       <c r="O305" t="n">
-        <v>349826.01</v>
+        <v>350749.0337730859</v>
       </c>
       <c r="P305" t="n">
         <v>2900</v>
@@ -13703,10 +13703,10 @@
         <v>384</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.3618458274</v>
+        <v>1664.3615095729</v>
       </c>
       <c r="O308" t="n">
-        <v>639114.9487977216</v>
+        <v>639114.8196759936</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -14393,10 +14393,10 @@
         <v>1145</v>
       </c>
       <c r="N323" t="n">
-        <v>1778.4725014327</v>
+        <v>1778.4725043029</v>
       </c>
       <c r="O323" t="n">
-        <v>2036351.014140442</v>
+        <v>2036351.01742682</v>
       </c>
       <c r="P323" t="n">
         <v>4900</v>
@@ -14485,10 +14485,10 @@
         <v>672</v>
       </c>
       <c r="N325" t="n">
-        <v>22739</v>
+        <v>22795.894912427</v>
       </c>
       <c r="O325" t="n">
-        <v>15280608</v>
+        <v>15318841.38115094</v>
       </c>
       <c r="P325" t="n">
         <v>36900</v>
@@ -14577,10 +14577,10 @@
         <v>720</v>
       </c>
       <c r="N327" t="n">
-        <v>16058</v>
+        <v>16092.045229682</v>
       </c>
       <c r="O327" t="n">
-        <v>11561760</v>
+        <v>11586272.56537104</v>
       </c>
       <c r="P327" t="n">
         <v>25900</v>
@@ -15221,10 +15221,10 @@
         <v>28</v>
       </c>
       <c r="N341" t="n">
-        <v>2252.2960914286</v>
+        <v>2252.2962193699</v>
       </c>
       <c r="O341" t="n">
-        <v>63064.2905600008</v>
+        <v>63064.2941423572</v>
       </c>
       <c r="P341" t="n">
         <v>3900</v>
@@ -15403,10 +15403,10 @@
         <v>864</v>
       </c>
       <c r="N345" t="n">
-        <v>2328.11876101</v>
+        <v>2328.1187566293</v>
       </c>
       <c r="O345" t="n">
-        <v>2011494.60951264</v>
+        <v>2011494.605727715</v>
       </c>
       <c r="P345" t="n">
         <v>4500</v>
@@ -15449,10 +15449,10 @@
         <v>322</v>
       </c>
       <c r="N346" t="n">
-        <v>21676</v>
+        <v>21748.414253898</v>
       </c>
       <c r="O346" t="n">
-        <v>6979672</v>
+        <v>7002989.389755157</v>
       </c>
       <c r="P346" t="n">
         <v>34900</v>
@@ -16134,10 +16134,10 @@
         <v>216</v>
       </c>
       <c r="N361" t="n">
-        <v>5869.1727972028</v>
+        <v>5869.1727755511</v>
       </c>
       <c r="O361" t="n">
-        <v>1267741.324195805</v>
+        <v>1267741.319519038</v>
       </c>
       <c r="P361" t="n">
         <v>9500</v>
@@ -16594,10 +16594,10 @@
         <v>480</v>
       </c>
       <c r="N371" t="n">
-        <v>3898</v>
+        <v>3903.9739463602</v>
       </c>
       <c r="O371" t="n">
-        <v>1871040</v>
+        <v>1873907.494252896</v>
       </c>
       <c r="P371" t="n">
         <v>6900</v>
@@ -16640,10 +16640,10 @@
         <v>425</v>
       </c>
       <c r="N372" t="n">
-        <v>13565</v>
+        <v>13585.460030166</v>
       </c>
       <c r="O372" t="n">
-        <v>5765125</v>
+        <v>5773820.512820549</v>
       </c>
       <c r="P372" t="n">
         <v>22500</v>
@@ -17650,10 +17650,10 @@
         <v>103</v>
       </c>
       <c r="N394" t="n">
-        <v>21762</v>
+        <v>21937.5</v>
       </c>
       <c r="O394" t="n">
-        <v>2241486</v>
+        <v>2259562.5</v>
       </c>
       <c r="P394" t="n">
         <v>35900</v>
@@ -18064,10 +18064,10 @@
         <v>4224</v>
       </c>
       <c r="N403" t="n">
-        <v>1516.038818618</v>
+        <v>1516.0388180509</v>
       </c>
       <c r="O403" t="n">
-        <v>6403747.969842432</v>
+        <v>6403747.967447002</v>
       </c>
       <c r="P403" t="n">
         <v>2300</v>
@@ -18110,10 +18110,10 @@
         <v>1152</v>
       </c>
       <c r="N404" t="n">
-        <v>2458.5136155257</v>
+        <v>2458.5135821813</v>
       </c>
       <c r="O404" t="n">
-        <v>2832207.685085606</v>
+        <v>2832207.646672858</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -18156,10 +18156,10 @@
         <v>480</v>
       </c>
       <c r="N405" t="n">
-        <v>1907.3946039604</v>
+        <v>1907.3945816073</v>
       </c>
       <c r="O405" t="n">
-        <v>915549.4099009919</v>
+        <v>915549.3991715041</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18202,10 +18202,10 @@
         <v>576</v>
       </c>
       <c r="N406" t="n">
-        <v>1771.0914991182</v>
+        <v>1771.0914183976</v>
       </c>
       <c r="O406" t="n">
-        <v>1020148.703492083</v>
+        <v>1020148.656997018</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18248,10 +18248,10 @@
         <v>960</v>
       </c>
       <c r="N407" t="n">
-        <v>2079.3842820513</v>
+        <v>2079.384280218</v>
       </c>
       <c r="O407" t="n">
-        <v>1996208.910769248</v>
+        <v>1996208.90900928</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -18294,10 +18294,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1803.0148044218</v>
+        <v>1803.0149016773</v>
       </c>
       <c r="O408" t="n">
-        <v>2423251.897142899</v>
+        <v>2423252.027854291</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18340,10 +18340,10 @@
         <v>144</v>
       </c>
       <c r="N409" t="n">
-        <v>3306.595494368</v>
+        <v>3306.5954716981</v>
       </c>
       <c r="O409" t="n">
-        <v>476149.751188992</v>
+        <v>476149.7479245264</v>
       </c>
       <c r="P409" t="n">
         <v>4900</v>
@@ -18386,10 +18386,10 @@
         <v>1440</v>
       </c>
       <c r="N410" t="n">
-        <v>2122.1641906742</v>
+        <v>2122.1641716329</v>
       </c>
       <c r="O410" t="n">
-        <v>3055916.434570848</v>
+        <v>3055916.407151376</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18432,10 +18432,10 @@
         <v>612</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7893820527</v>
+        <v>2108.7895881384</v>
       </c>
       <c r="O411" t="n">
-        <v>1290579.101816253</v>
+        <v>1290579.227940701</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18478,10 +18478,10 @@
         <v>864</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.0840312319</v>
+        <v>2056.0839842611</v>
       </c>
       <c r="O412" t="n">
-        <v>1776456.602984362</v>
+        <v>1776456.56240159</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18524,10 +18524,10 @@
         <v>714</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.5676430401</v>
+        <v>3224.5678063672</v>
       </c>
       <c r="O413" t="n">
-        <v>2302341.297130631</v>
+        <v>2302341.41374618</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18570,10 +18570,10 @@
         <v>1152</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.9314708603</v>
+        <v>1655.9314682295</v>
       </c>
       <c r="O414" t="n">
-        <v>1907633.054431065</v>
+        <v>1907633.051400384</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -18985,10 +18985,10 @@
         <v>8400</v>
       </c>
       <c r="N423" t="n">
-        <v>1955.2371191444</v>
+        <v>1955.2371159315</v>
       </c>
       <c r="O423" t="n">
-        <v>16423991.80081296</v>
+        <v>16423991.7738246</v>
       </c>
       <c r="P423" t="n">
         <v>3000</v>
@@ -19369,10 +19369,10 @@
         <v>2</v>
       </c>
       <c r="N431" t="n">
-        <v>1530.4499206349</v>
+        <v>1530.4499204455</v>
       </c>
       <c r="O431" t="n">
-        <v>3060.8998412698</v>
+        <v>3060.899840891</v>
       </c>
       <c r="P431" t="n">
         <v>2600</v>
@@ -20039,10 +20039,10 @@
         <v>7572</v>
       </c>
       <c r="N446" t="n">
-        <v>517.28728171896</v>
+        <v>517.28742027978</v>
       </c>
       <c r="O446" t="n">
-        <v>3916899.297175965</v>
+        <v>3916900.346358494</v>
       </c>
       <c r="P446" t="n">
         <v>900</v>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20085,19 +20085,19 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="N447" t="n">
-        <v>3110.8435374771</v>
+        <v>3110.8434146796</v>
       </c>
       <c r="O447" t="n">
-        <v>3135730.285776917</v>
+        <v>1567865.080998518</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
       </c>
       <c r="Q447" t="n">
-        <v>4536000</v>
+        <v>2268000</v>
       </c>
     </row>
     <row r="448">
@@ -20208,7 +20208,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>19400</v>
+        <v>18248</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -20217,19 +20217,19 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>19400</v>
+        <v>18248</v>
       </c>
       <c r="N450" t="n">
-        <v>703.79547499887</v>
+        <v>703.79546441605</v>
       </c>
       <c r="O450" t="n">
-        <v>13653632.21497808</v>
+        <v>12842859.63466408</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
       </c>
       <c r="Q450" t="n">
-        <v>17460000</v>
+        <v>16423200</v>
       </c>
     </row>
     <row r="451">
@@ -20269,10 +20269,10 @@
         <v>127</v>
       </c>
       <c r="N451" t="n">
-        <v>3182.2510752688</v>
+        <v>3182.2510791367</v>
       </c>
       <c r="O451" t="n">
-        <v>404145.8865591376</v>
+        <v>404145.8870503609</v>
       </c>
       <c r="P451" t="n">
         <v>6900</v>
@@ -20797,10 +20797,10 @@
         <v>2569</v>
       </c>
       <c r="N463" t="n">
-        <v>1595.5194396439</v>
+        <v>1595.5193419662</v>
       </c>
       <c r="O463" t="n">
-        <v>4098889.440445179</v>
+        <v>4098889.189511168</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -20831,7 +20831,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>360</v>
+        <v>241</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -20840,19 +20840,19 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>360</v>
+        <v>241</v>
       </c>
       <c r="N464" t="n">
         <v>1567.02</v>
       </c>
       <c r="O464" t="n">
-        <v>564127.2</v>
+        <v>377651.82</v>
       </c>
       <c r="P464" t="n">
         <v>2900</v>
       </c>
       <c r="Q464" t="n">
-        <v>1044000</v>
+        <v>698900</v>
       </c>
     </row>
     <row r="465">
@@ -21444,10 +21444,10 @@
         <v>50</v>
       </c>
       <c r="N477" t="n">
-        <v>4159.0002846975</v>
+        <v>4159.0002867384</v>
       </c>
       <c r="O477" t="n">
-        <v>207950.014234875</v>
+        <v>207950.01433692</v>
       </c>
       <c r="P477" t="n">
         <v>8900</v>
@@ -21674,10 +21674,10 @@
         <v>1976</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.939830831</v>
+        <v>7046.9398307595</v>
       </c>
       <c r="O482" t="n">
-        <v>13924753.10572206</v>
+        <v>13924753.10558077</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
@@ -21888,7 +21888,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21897,19 +21897,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N487" t="n">
         <v>44113.603675676</v>
       </c>
       <c r="O487" t="n">
-        <v>2293907.391135152</v>
+        <v>1764544.14702704</v>
       </c>
       <c r="P487" t="n">
         <v>71900</v>
       </c>
       <c r="Q487" t="n">
-        <v>3738800</v>
+        <v>2876000</v>
       </c>
     </row>
     <row r="488">
@@ -23253,10 +23253,10 @@
         <v>68</v>
       </c>
       <c r="N518" t="n">
-        <v>2830.2246883469</v>
+        <v>2830.224701087</v>
       </c>
       <c r="O518" t="n">
-        <v>192455.2788075892</v>
+        <v>192455.279673916</v>
       </c>
       <c r="P518" t="n">
         <v>2400</v>
@@ -23804,10 +23804,10 @@
         <v>69</v>
       </c>
       <c r="N531" t="n">
-        <v>4985.4044444444</v>
+        <v>4985.404494382</v>
       </c>
       <c r="O531" t="n">
-        <v>343992.9066666636</v>
+        <v>343992.910112358</v>
       </c>
       <c r="P531" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -1007,10 +1007,10 @@
         <v>48</v>
       </c>
       <c r="N15" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>1306845.188284512</v>
+        <v>1296000</v>
       </c>
       <c r="P15" t="n">
         <v>30000</v>
@@ -1163,10 +1163,10 @@
         <v>162</v>
       </c>
       <c r="N19" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O19" t="n">
-        <v>937079.5882300938</v>
+        <v>932951.4841592982</v>
       </c>
       <c r="P19" t="n">
         <v>16900</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O41" t="n">
-        <v>1276139.799999987</v>
+        <v>1271651.620000006</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2396,10 +2396,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O50" t="n">
-        <v>645321.99211617</v>
+        <v>640010.7</v>
       </c>
       <c r="P50" t="n">
         <v>30000</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O58" t="n">
-        <v>1140099.555937536</v>
+        <v>1131261.572812536</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -3775,10 +3775,10 @@
         <v>54</v>
       </c>
       <c r="N82" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O82" t="n">
-        <v>1470568.96551726</v>
+        <v>1458000</v>
       </c>
       <c r="P82" t="n">
         <v>20000</v>
@@ -4035,10 +4035,10 @@
         <v>72</v>
       </c>
       <c r="N88" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O88" t="n">
-        <v>185536.9904761872</v>
+        <v>184560.48</v>
       </c>
       <c r="P88" t="n">
         <v>4700</v>
@@ -6377,10 +6377,10 @@
         <v>24</v>
       </c>
       <c r="N141" t="n">
-        <v>2289.4664730119</v>
+        <v>2267.0481788216</v>
       </c>
       <c r="O141" t="n">
-        <v>54947.19535228559</v>
+        <v>54409.15629171839</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
@@ -6866,10 +6866,10 @@
         <v>599</v>
       </c>
       <c r="N152" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O152" t="n">
-        <v>2934094.791916152</v>
+        <v>2929709</v>
       </c>
       <c r="P152" t="n">
         <v>8200</v>
@@ -8229,10 +8229,10 @@
         <v>403</v>
       </c>
       <c r="N183" t="n">
-        <v>2225.439688716</v>
+        <v>2204</v>
       </c>
       <c r="O183" t="n">
-        <v>896852.194552548</v>
+        <v>888212</v>
       </c>
       <c r="P183" t="n">
         <v>1500</v>
@@ -9697,10 +9697,10 @@
         <v>384</v>
       </c>
       <c r="N216" t="n">
-        <v>2667.5690712743</v>
+        <v>2661.82</v>
       </c>
       <c r="O216" t="n">
-        <v>1024346.523369331</v>
+        <v>1022138.88</v>
       </c>
       <c r="P216" t="n">
         <v>3200</v>
@@ -9738,10 +9738,10 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O217" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -9779,10 +9779,10 @@
         <v>481</v>
       </c>
       <c r="N218" t="n">
-        <v>2613.7446197991</v>
+        <v>2610</v>
       </c>
       <c r="O218" t="n">
-        <v>1257211.162123367</v>
+        <v>1255410</v>
       </c>
       <c r="P218" t="n">
         <v>3200</v>
@@ -9902,10 +9902,10 @@
         <v>158</v>
       </c>
       <c r="N221" t="n">
-        <v>2306.01</v>
+        <v>2286.55</v>
       </c>
       <c r="O221" t="n">
-        <v>364349.58</v>
+        <v>361274.9</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
@@ -12435,10 +12435,10 @@
         <v>1</v>
       </c>
       <c r="N280" t="n">
-        <v>9777</v>
+        <v>6518</v>
       </c>
       <c r="O280" t="n">
-        <v>9777</v>
+        <v>6518</v>
       </c>
       <c r="P280" t="n">
         <v>10900</v>
@@ -12655,10 +12655,10 @@
         <v>84</v>
       </c>
       <c r="N285" t="n">
-        <v>13971.496466667</v>
+        <v>13878.97</v>
       </c>
       <c r="O285" t="n">
-        <v>1173605.703200028</v>
+        <v>1165833.48</v>
       </c>
       <c r="P285" t="n">
         <v>21900</v>
@@ -12829,10 +12829,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O289" t="n">
-        <v>1349919.516464292</v>
+        <v>1348314.380309513</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13059,10 +13059,10 @@
         <v>3</v>
       </c>
       <c r="N294" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O294" t="n">
-        <v>27297.0978260871</v>
+        <v>26635.35</v>
       </c>
       <c r="P294" t="n">
         <v>14100</v>
@@ -13105,10 +13105,10 @@
         <v>334</v>
       </c>
       <c r="N295" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O295" t="n">
-        <v>834573.4269450433</v>
+        <v>833657.3199999999</v>
       </c>
       <c r="P295" t="n">
         <v>4100</v>
@@ -13427,10 +13427,10 @@
         <v>317</v>
       </c>
       <c r="N302" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O302" t="n">
-        <v>1258466.923341585</v>
+        <v>1256911.34</v>
       </c>
       <c r="P302" t="n">
         <v>6500</v>
@@ -13473,10 +13473,10 @@
         <v>228</v>
       </c>
       <c r="N303" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O303" t="n">
-        <v>1332528.611059909</v>
+        <v>1320359.4</v>
       </c>
       <c r="P303" t="n">
         <v>9300</v>
@@ -13565,10 +13565,10 @@
         <v>193</v>
       </c>
       <c r="N305" t="n">
-        <v>1817.3525065963</v>
+        <v>1812.57</v>
       </c>
       <c r="O305" t="n">
-        <v>350749.0337730859</v>
+        <v>349826.01</v>
       </c>
       <c r="P305" t="n">
         <v>2900</v>
@@ -14485,10 +14485,10 @@
         <v>672</v>
       </c>
       <c r="N325" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O325" t="n">
-        <v>15318841.38115094</v>
+        <v>15280608</v>
       </c>
       <c r="P325" t="n">
         <v>36900</v>
@@ -14577,10 +14577,10 @@
         <v>720</v>
       </c>
       <c r="N327" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O327" t="n">
-        <v>11586272.56537104</v>
+        <v>11561760</v>
       </c>
       <c r="P327" t="n">
         <v>25900</v>
@@ -15449,10 +15449,10 @@
         <v>322</v>
       </c>
       <c r="N346" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O346" t="n">
-        <v>7002989.389755157</v>
+        <v>6979672</v>
       </c>
       <c r="P346" t="n">
         <v>34900</v>
@@ -16594,10 +16594,10 @@
         <v>480</v>
       </c>
       <c r="N371" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O371" t="n">
-        <v>1873907.494252896</v>
+        <v>1871040</v>
       </c>
       <c r="P371" t="n">
         <v>6900</v>
@@ -16640,10 +16640,10 @@
         <v>425</v>
       </c>
       <c r="N372" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O372" t="n">
-        <v>5773820.512820549</v>
+        <v>5765125</v>
       </c>
       <c r="P372" t="n">
         <v>22500</v>
@@ -17650,10 +17650,10 @@
         <v>103</v>
       </c>
       <c r="N394" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O394" t="n">
-        <v>2259562.5</v>
+        <v>2241486</v>
       </c>
       <c r="P394" t="n">
         <v>35900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -603,10 +603,10 @@
         <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.40695121999</v>
+        <v>96741.407037037</v>
       </c>
       <c r="O5" t="n">
-        <v>5611001.60317076</v>
+        <v>5611001.608148146</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1080</v>
+        <v>860</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -965,19 +965,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1080</v>
+        <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3037703513</v>
+        <v>1815.9962867012</v>
       </c>
       <c r="O14" t="n">
-        <v>1956208.071979404</v>
+        <v>1561756.806563032</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>2808000</v>
+        <v>2236000</v>
       </c>
     </row>
     <row r="15">
@@ -1046,10 +1046,10 @@
         <v>112</v>
       </c>
       <c r="N16" t="n">
-        <v>1990.0436380597</v>
+        <v>2001.2446341463</v>
       </c>
       <c r="O16" t="n">
-        <v>222884.8874626864</v>
+        <v>224139.3990243856</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8541142857</v>
+        <v>6300.2067296512</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.488685711</v>
+        <v>1360844.653604659</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -1920,10 +1920,10 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>3926.8371340839</v>
+        <v>3926.8371326165</v>
       </c>
       <c r="O38" t="n">
-        <v>2548517.300020451</v>
+        <v>2548517.299068109</v>
       </c>
       <c r="P38" t="n">
         <v>4800</v>
@@ -2636,10 +2636,10 @@
         <v>60</v>
       </c>
       <c r="N56" t="n">
-        <v>16486.41027027</v>
+        <v>16486.410204082</v>
       </c>
       <c r="O56" t="n">
-        <v>989184.6162162001</v>
+        <v>989184.61224492</v>
       </c>
       <c r="P56" t="n">
         <v>30500</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.966289063</v>
+        <v>15711.966215139</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.572812536</v>
+        <v>1131261.567490008</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -2942,19 +2942,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>52637</v>
-      </c>
-      <c r="B64" t="n">
-        <v>6941607352212</v>
+        <v>53069</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>53069 JUEGO DE PISCINA GRANDE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2963,7 +2955,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2972,28 +2964,31 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>22267.551785714</v>
+        <v>137679.73</v>
       </c>
       <c r="O64" t="n">
-        <v>178140.414285712</v>
+        <v>550718.92</v>
       </c>
       <c r="P64" t="n">
-        <v>46300</v>
+        <v>209900</v>
       </c>
       <c r="Q64" t="n">
-        <v>370400</v>
+        <v>839600</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>53069</v>
+        <v>55030</v>
+      </c>
+      <c r="B65" t="n">
+        <v>6942138913774</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>53069 JUEGO DE PISCINA GRANDE</t>
+          <t>55030 PISCINA ACUARIO 183 X 38CM</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3002,7 +2997,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3011,31 +3006,36 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>137679.73</v>
+        <v>36306.276</v>
       </c>
       <c r="O65" t="n">
-        <v>550718.92</v>
+        <v>435675.312</v>
       </c>
       <c r="P65" t="n">
-        <v>209900</v>
+        <v>64900</v>
       </c>
       <c r="Q65" t="n">
-        <v>839600</v>
+        <v>778800</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55030</v>
+        <v>55031</v>
       </c>
       <c r="B66" t="n">
-        <v>6942138913774</v>
+        <v>6942138913781</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>55030 PISCINA ACUARIO 183 X 38CM</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3053,31 +3053,31 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="N66" t="n">
-        <v>36306.276</v>
+        <v>56906.800422535</v>
       </c>
       <c r="O66" t="n">
-        <v>435675.312</v>
+        <v>2276272.0169014</v>
       </c>
       <c r="P66" t="n">
-        <v>64900</v>
+        <v>95900</v>
       </c>
       <c r="Q66" t="n">
-        <v>778800</v>
+        <v>3836000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55031</v>
+        <v>56217</v>
       </c>
       <c r="B67" t="n">
-        <v>6942138913781</v>
+        <v>6941607344613</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+          <t>BESTWAY 48 X 48 X 121.22M X 1.22M X 30.5CM MY FIRST FRAME POOL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3100,31 +3100,31 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="N67" t="n">
-        <v>56906.800422535</v>
+        <v>62349.659444444</v>
       </c>
       <c r="O67" t="n">
-        <v>2276272.0169014</v>
+        <v>561146.934999996</v>
       </c>
       <c r="P67" t="n">
-        <v>95900</v>
+        <v>109900</v>
       </c>
       <c r="Q67" t="n">
-        <v>3836000</v>
+        <v>989100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56217</v>
+        <v>56283</v>
       </c>
       <c r="B68" t="n">
-        <v>6941607344613</v>
+        <v>6941607344606</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BESTWAY 48 X 48 X 121.22M X 1.22M X 30.5CM MY FIRST FRAME POOL</t>
+          <t>BESTWAY 5 X 151.52M X 38CM MY FIRST FRAME POOL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="N68" t="n">
-        <v>62349.660526316</v>
+        <v>77455.73771929801</v>
       </c>
       <c r="O68" t="n">
-        <v>561146.944736844</v>
+        <v>7900485.247368396</v>
       </c>
       <c r="P68" t="n">
-        <v>109900</v>
+        <v>122900</v>
       </c>
       <c r="Q68" t="n">
-        <v>989100</v>
+        <v>12535800</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>56283</v>
+        <v>56401</v>
       </c>
       <c r="B69" t="n">
-        <v>6941607344606</v>
+        <v>6941607327951</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BESTWAY 5 X 151.52M X 38CM MY FIRST FRAME POOL</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3194,45 +3194,40 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N69" t="n">
-        <v>77455.73765217399</v>
+        <v>141416.88447284</v>
       </c>
       <c r="O69" t="n">
-        <v>7900485.240521748</v>
+        <v>15838691.06095808</v>
       </c>
       <c r="P69" t="n">
-        <v>122900</v>
+        <v>251900</v>
       </c>
       <c r="Q69" t="n">
-        <v>12535800</v>
+        <v>28212800</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56401</v>
+        <v>56403</v>
       </c>
       <c r="B70" t="n">
-        <v>6941607327951</v>
+        <v>6941607327982</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3241,40 +3236,40 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="N70" t="n">
-        <v>141416.8844586</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O70" t="n">
-        <v>15838691.0593632</v>
+        <v>7802815.766808661</v>
       </c>
       <c r="P70" t="n">
-        <v>251900</v>
+        <v>312000</v>
       </c>
       <c r="Q70" t="n">
-        <v>28212800</v>
+        <v>12168000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56403</v>
+        <v>56404</v>
       </c>
       <c r="B71" t="n">
-        <v>6941607327982</v>
+        <v>6941607327999</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3283,40 +3278,45 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="N71" t="n">
-        <v>200072.19914894</v>
+        <v>174389.78756757</v>
       </c>
       <c r="O71" t="n">
-        <v>7802815.766808661</v>
+        <v>2441457.02594598</v>
       </c>
       <c r="P71" t="n">
-        <v>312000</v>
+        <v>368200</v>
       </c>
       <c r="Q71" t="n">
-        <v>12168000</v>
+        <v>5154800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56404</v>
+        <v>56405</v>
       </c>
       <c r="B72" t="n">
-        <v>6941607327999</v>
+        <v>6941607328002</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3325,31 +3325,31 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N72" t="n">
-        <v>174389.78666667</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O72" t="n">
-        <v>2441457.01333338</v>
+        <v>4532567.29090902</v>
       </c>
       <c r="P72" t="n">
-        <v>368200</v>
+        <v>584000</v>
       </c>
       <c r="Q72" t="n">
-        <v>5154800</v>
+        <v>10512000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56405</v>
+        <v>56417</v>
       </c>
       <c r="B73" t="n">
-        <v>6941607328002</v>
+        <v>6942138981902</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3372,31 +3372,31 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N73" t="n">
-        <v>251809.29393939</v>
+        <v>344599.17881356</v>
       </c>
       <c r="O73" t="n">
-        <v>4532567.29090902</v>
+        <v>7581181.933898319</v>
       </c>
       <c r="P73" t="n">
-        <v>584000</v>
+        <v>532900</v>
       </c>
       <c r="Q73" t="n">
-        <v>10512000</v>
+        <v>11723800</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>56417</v>
+        <v>56706</v>
       </c>
       <c r="B74" t="n">
-        <v>6942138981902</v>
+        <v>6941607329344</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm 56706</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3419,31 +3419,33 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N74" t="n">
-        <v>344599.17885246</v>
+        <v>263530.179</v>
       </c>
       <c r="O74" t="n">
-        <v>7581181.93475412</v>
+        <v>3689422.506</v>
       </c>
       <c r="P74" t="n">
-        <v>532900</v>
+        <v>402900</v>
       </c>
       <c r="Q74" t="n">
-        <v>11723800</v>
+        <v>5640600</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>56706</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6001Y</t>
+        </is>
       </c>
       <c r="B75" t="n">
-        <v>6941607329344</v>
+        <v>6941607375976</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm 56706</t>
+          <t>saluspa 77 x 26/1.96m x 66cm miami energysense airjet 6 dark  green round</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3457,7 +3459,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3466,33 +3468,31 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>263530.179</v>
+        <v>1395300</v>
       </c>
       <c r="O75" t="n">
-        <v>3689422.506</v>
+        <v>1395300</v>
       </c>
       <c r="P75" t="n">
-        <v>402900</v>
+        <v>2200000</v>
       </c>
       <c r="Q75" t="n">
-        <v>5640600</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>6001Y</t>
-        </is>
+      <c r="A76" t="n">
+        <v>60120</v>
       </c>
       <c r="B76" t="n">
-        <v>6941607375976</v>
+        <v>6941607370421</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>saluspa 77 x 26/1.96m x 66cm miami energysense airjet 6 dark  green round</t>
+          <t>Hydrojet smart 1,96m x71cm 60120</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3518,42 +3518,42 @@
         <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>1395300</v>
+        <v>1779420</v>
       </c>
       <c r="O76" t="n">
-        <v>1395300</v>
+        <v>1779420</v>
       </c>
       <c r="P76" t="n">
-        <v>2200000</v>
+        <v>2900000</v>
       </c>
       <c r="Q76" t="n">
-        <v>2200000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>60120</v>
+        <v>6027378</v>
       </c>
       <c r="B77" t="n">
-        <v>6941607370421</v>
+        <v>5985458545219</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hydrojet smart 1,96m x71cm 60120</t>
+          <t>TIBURON MANIA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>JUEGOS DE MESA</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3562,36 +3562,30 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="N77" t="n">
-        <v>1779420</v>
+        <v>27000</v>
       </c>
       <c r="O77" t="n">
-        <v>1779420</v>
+        <v>1782000</v>
       </c>
       <c r="P77" t="n">
-        <v>2900000</v>
+        <v>20000</v>
       </c>
       <c r="Q77" t="n">
-        <v>2900000</v>
+        <v>1320000</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>6027378</v>
-      </c>
-      <c r="B78" t="n">
-        <v>5985458545219</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>63167-1</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TIBURON MANIA</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>JUEGOS DE MESA</t>
+          <t>DISPENSADOR DE COMIDA Y BEBIDA PARA PERROS</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3600,7 +3594,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3609,30 +3603,28 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="N78" t="n">
-        <v>27000</v>
+        <v>44538.46</v>
       </c>
       <c r="O78" t="n">
-        <v>1782000</v>
+        <v>356307.68</v>
       </c>
       <c r="P78" t="n">
-        <v>20000</v>
+        <v>57900</v>
       </c>
       <c r="Q78" t="n">
-        <v>1320000</v>
+        <v>463200</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>63167-1</t>
-        </is>
+      <c r="A79" t="n">
+        <v>67223</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DISPENSADOR DE COMIDA Y BEBIDA PARA PERROS</t>
+          <t>bestway 73 x 30 x 11/1.85m x 76cm x 28cm aeroluxe air mattress jr.twin built-in foot pump 6PCS</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3641,7 +3633,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3650,28 +3642,28 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N79" t="n">
-        <v>44538.46</v>
+        <v>29510.75</v>
       </c>
       <c r="O79" t="n">
-        <v>356307.68</v>
+        <v>177064.5</v>
       </c>
       <c r="P79" t="n">
-        <v>57900</v>
+        <v>58000</v>
       </c>
       <c r="Q79" t="n">
-        <v>463200</v>
+        <v>348000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>67223</v>
+        <v>67374</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>bestway 73 x 30 x 11/1.85m x 76cm x 28cm aeroluxe air mattress jr.twin built-in foot pump 6PCS</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3680,7 +3672,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3689,28 +3681,33 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="N80" t="n">
-        <v>29510.75</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O80" t="n">
-        <v>177064.5</v>
+        <v>5981686.762697184</v>
       </c>
       <c r="P80" t="n">
-        <v>58000</v>
+        <v>98900</v>
       </c>
       <c r="Q80" t="n">
-        <v>348000</v>
+        <v>9593300</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>67374</v>
+        <v>88400</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>DIGIBIRD CASA DE LA DIVERSION 2 ASSORTED</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3719,7 +3716,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3728,33 +3725,28 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="N81" t="n">
-        <v>61666.873842239</v>
+        <v>27000</v>
       </c>
       <c r="O81" t="n">
-        <v>5981686.762697184</v>
+        <v>1458000</v>
       </c>
       <c r="P81" t="n">
-        <v>98900</v>
+        <v>20000</v>
       </c>
       <c r="Q81" t="n">
-        <v>9593300</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>88400</v>
+        <v>91004</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DIGIBIRD CASA DE LA DIVERSION 2 ASSORTED</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3763,7 +3755,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3772,28 +3764,35 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="N82" t="n">
-        <v>27000</v>
+        <v>3872.3234767642</v>
       </c>
       <c r="O82" t="n">
-        <v>1458000</v>
+        <v>1165569.366506024</v>
       </c>
       <c r="P82" t="n">
-        <v>20000</v>
+        <v>5500</v>
       </c>
       <c r="Q82" t="n">
-        <v>1080000</v>
+        <v>1655500</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>91004</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9102O</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>9102O GAFA ACUATICA PRINCESS DISNEY</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3802,7 +3801,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>301</v>
+        <v>131</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3811,30 +3810,30 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>301</v>
+        <v>131</v>
       </c>
       <c r="N83" t="n">
-        <v>3865.67</v>
+        <v>2589.9594489247</v>
       </c>
       <c r="O83" t="n">
-        <v>1163566.67</v>
+        <v>339284.6878091357</v>
       </c>
       <c r="P83" t="n">
-        <v>5500</v>
+        <v>4700</v>
       </c>
       <c r="Q83" t="n">
-        <v>1655500</v>
+        <v>615700</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9102O</t>
+          <t>9102X</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9102O GAFA ACUATICA PRINCESS DISNEY</t>
+          <t>9102X CARETA ACUATICA DISNEY PRINCESS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3848,7 +3847,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3857,30 +3856,30 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="N84" t="n">
-        <v>2572.67</v>
+        <v>11528</v>
       </c>
       <c r="O84" t="n">
-        <v>337019.77</v>
+        <v>2075040</v>
       </c>
       <c r="P84" t="n">
-        <v>4700</v>
+        <v>17900</v>
       </c>
       <c r="Q84" t="n">
-        <v>615700</v>
+        <v>3222000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9102X</t>
+          <t>9102Z</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9102X CARETA ACUATICA DISNEY PRINCESS</t>
+          <t>9102Z GAFA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3894,7 +3893,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3903,35 +3902,28 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="N85" t="n">
-        <v>11528</v>
+        <v>2597.4440764331</v>
       </c>
       <c r="O85" t="n">
-        <v>2075040</v>
+        <v>174028.7531210177</v>
       </c>
       <c r="P85" t="n">
-        <v>17900</v>
+        <v>4700</v>
       </c>
       <c r="Q85" t="n">
-        <v>3222000</v>
+        <v>314900</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>9102Z</t>
-        </is>
+      <c r="A86" t="n">
+        <v>91040</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9102Z GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3940,7 +3932,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3949,28 +3941,33 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="N86" t="n">
-        <v>2570.16</v>
+        <v>3126.0967950311</v>
       </c>
       <c r="O86" t="n">
-        <v>172200.72</v>
+        <v>103161.1942360263</v>
       </c>
       <c r="P86" t="n">
-        <v>4700</v>
+        <v>5500</v>
       </c>
       <c r="Q86" t="n">
-        <v>314900</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>91040</v>
+        <v>98019</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>98019 GAFA ACUATICA SPIDERMAN BESTWAY</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3979,7 +3976,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3988,33 +3985,30 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="N87" t="n">
-        <v>3114.49</v>
+        <v>2597.7011260054</v>
       </c>
       <c r="O87" t="n">
-        <v>102778.17</v>
+        <v>187034.4810723888</v>
       </c>
       <c r="P87" t="n">
-        <v>5500</v>
+        <v>4700</v>
       </c>
       <c r="Q87" t="n">
-        <v>181500</v>
+        <v>338400</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>98019</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>A-668</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>98019 GAFA ACUATICA SPIDERMAN BESTWAY</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RAYADOR</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4023,7 +4017,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4032,30 +4026,30 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="N88" t="n">
-        <v>2563.34</v>
+        <v>27450.51804878</v>
       </c>
       <c r="O88" t="n">
-        <v>184560.48</v>
+        <v>850966.0595121799</v>
       </c>
       <c r="P88" t="n">
-        <v>4700</v>
+        <v>40900</v>
       </c>
       <c r="Q88" t="n">
-        <v>338400</v>
+        <v>1267900</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A-668</t>
+          <t>C1011</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RAYADOR</t>
+          <t>BOLITRON DEGRADE CON LUZ</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4064,7 +4058,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>31</v>
+        <v>1440</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4073,30 +4067,30 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>31</v>
+        <v>1440</v>
       </c>
       <c r="N89" t="n">
-        <v>27450.51804878</v>
+        <v>1950.2152574526</v>
       </c>
       <c r="O89" t="n">
-        <v>850966.0595121799</v>
+        <v>2808309.970731744</v>
       </c>
       <c r="P89" t="n">
-        <v>40900</v>
+        <v>2900</v>
       </c>
       <c r="Q89" t="n">
-        <v>1267900</v>
+        <v>4176000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C1011</t>
+          <t>C1017</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BOLITRON DEGRADE CON LUZ</t>
+          <t>SOLDADO ARRASTRA</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4105,7 +4099,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1440</v>
+        <v>2130</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4114,30 +4108,30 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1440</v>
+        <v>2130</v>
       </c>
       <c r="N90" t="n">
-        <v>1950.2152574526</v>
+        <v>2837.5718128026</v>
       </c>
       <c r="O90" t="n">
-        <v>2808309.970731744</v>
+        <v>6044027.961269538</v>
       </c>
       <c r="P90" t="n">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="Q90" t="n">
-        <v>4176000</v>
+        <v>7455000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C1017</t>
+          <t>C1020</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SOLDADO ARRASTRA</t>
+          <t>INFLABLE VARA ANIMALES</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4146,7 +4140,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2130</v>
+        <v>12735</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4155,30 +4149,35 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2130</v>
+        <v>12735</v>
       </c>
       <c r="N91" t="n">
-        <v>2833</v>
+        <v>1726.32</v>
       </c>
       <c r="O91" t="n">
-        <v>6034290</v>
+        <v>21984685.2</v>
       </c>
       <c r="P91" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="Q91" t="n">
-        <v>7455000</v>
+        <v>19102500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C1020</t>
+          <t>C1027</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>INFLABLE VARA ANIMALES</t>
+          <t>BALON #5 CAUCHO</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4187,7 +4186,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>13035</v>
+        <v>200</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4196,30 +4195,30 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>13035</v>
+        <v>200</v>
       </c>
       <c r="N92" t="n">
-        <v>1726.32</v>
+        <v>4937.3101595359</v>
       </c>
       <c r="O92" t="n">
-        <v>22502581.2</v>
+        <v>987462.0319071801</v>
       </c>
       <c r="P92" t="n">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="Q92" t="n">
-        <v>19552500</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C1027</t>
+          <t>C1037</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BALON #5 CAUCHO</t>
+          <t>LANZA CHORRO DOBLE61cm C1037</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4229,11 +4228,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4242,30 +4241,30 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="N93" t="n">
-        <v>4937.3101589595</v>
+        <v>6513</v>
       </c>
       <c r="O93" t="n">
-        <v>987462.0317918999</v>
+        <v>390780</v>
       </c>
       <c r="P93" t="n">
-        <v>7500</v>
+        <v>11500</v>
       </c>
       <c r="Q93" t="n">
-        <v>1500000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C1037</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LANZA CHORRO DOBLE61cm C1037</t>
+          <t>SCOOTER COLORES</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4275,11 +4274,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4288,35 +4287,30 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="N94" t="n">
-        <v>6513</v>
+        <v>39171.85</v>
       </c>
       <c r="O94" t="n">
-        <v>390780</v>
+        <v>2781201.35</v>
       </c>
       <c r="P94" t="n">
-        <v>11500</v>
+        <v>68900</v>
       </c>
       <c r="Q94" t="n">
-        <v>690000</v>
+        <v>4891900</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1095</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>POP IT DADOS GRNDE</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4325,7 +4319,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>71</v>
+        <v>613</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4334,30 +4328,30 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>71</v>
+        <v>613</v>
       </c>
       <c r="N95" t="n">
-        <v>39171.85</v>
+        <v>12608</v>
       </c>
       <c r="O95" t="n">
-        <v>2781201.35</v>
+        <v>7728704</v>
       </c>
       <c r="P95" t="n">
-        <v>68900</v>
+        <v>10900</v>
       </c>
       <c r="Q95" t="n">
-        <v>4891900</v>
+        <v>6681700</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C1095</t>
+          <t>C1097</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>POP IT DADOS GRNDE</t>
+          <t>POP IT REDONDO GRND</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4366,7 +4360,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>613</v>
+        <v>318</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4375,30 +4369,35 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>613</v>
+        <v>318</v>
       </c>
       <c r="N96" t="n">
-        <v>12608</v>
+        <v>32420</v>
       </c>
       <c r="O96" t="n">
-        <v>7728704</v>
+        <v>10309560</v>
       </c>
       <c r="P96" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="Q96" t="n">
-        <v>6681700</v>
+        <v>5374200</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C1097</t>
+          <t>C1108</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>POP IT REDONDO GRND</t>
+          <t>PATINES INFANTILES</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4407,7 +4406,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4416,35 +4415,30 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>32420</v>
+        <v>61675.37</v>
       </c>
       <c r="O97" t="n">
-        <v>10309560</v>
+        <v>308376.85</v>
       </c>
       <c r="P97" t="n">
-        <v>16900</v>
+        <v>80000</v>
       </c>
       <c r="Q97" t="n">
-        <v>5374200</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C1108</t>
+          <t>C1110</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PATINES INFANTILES</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TERMO PELUCHE</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4453,7 +4447,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4462,30 +4456,30 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="N98" t="n">
-        <v>61675.37</v>
+        <v>21084.771455026</v>
       </c>
       <c r="O98" t="n">
-        <v>308376.85</v>
+        <v>5144684.235026344</v>
       </c>
       <c r="P98" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="Q98" t="n">
-        <v>400000</v>
+        <v>7320000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C1110</t>
+          <t>C1111</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TERMO PELUCHE</t>
+          <t>TERMO ANIMALES SILICONA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4494,7 +4488,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4503,25 +4497,25 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="N99" t="n">
-        <v>21084.771455026</v>
+        <v>31409.101333333</v>
       </c>
       <c r="O99" t="n">
-        <v>5144684.235026344</v>
+        <v>3769092.15999996</v>
       </c>
       <c r="P99" t="n">
-        <v>30000</v>
+        <v>49900</v>
       </c>
       <c r="Q99" t="n">
-        <v>7320000</v>
+        <v>5988000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C1111</t>
+          <t>C1112</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4535,7 +4529,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4544,30 +4538,30 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="N100" t="n">
-        <v>31409.101333333</v>
+        <v>31233.611787072</v>
       </c>
       <c r="O100" t="n">
-        <v>3769092.15999996</v>
+        <v>4903677.050570305</v>
       </c>
       <c r="P100" t="n">
-        <v>49900</v>
+        <v>45500</v>
       </c>
       <c r="Q100" t="n">
-        <v>5988000</v>
+        <v>7143500</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C1112</t>
+          <t>C1128</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TERMO ANIMALES SILICONA</t>
+          <t>BOLSA METALIZADA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4576,7 +4570,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>157</v>
+        <v>954</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4585,25 +4579,25 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>157</v>
+        <v>954</v>
       </c>
       <c r="N101" t="n">
-        <v>31233.611787072</v>
+        <v>1062</v>
       </c>
       <c r="O101" t="n">
-        <v>4903677.050570305</v>
+        <v>1013148</v>
       </c>
       <c r="P101" t="n">
-        <v>45500</v>
+        <v>1600</v>
       </c>
       <c r="Q101" t="n">
-        <v>7143500</v>
+        <v>1526400</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C1128</t>
+          <t>C1129</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4617,7 +4611,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>954</v>
+        <v>505</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4626,30 +4620,30 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>954</v>
+        <v>505</v>
       </c>
       <c r="N102" t="n">
-        <v>1062</v>
+        <v>1332</v>
       </c>
       <c r="O102" t="n">
-        <v>1013148</v>
+        <v>672660</v>
       </c>
       <c r="P102" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="Q102" t="n">
-        <v>1526400</v>
+        <v>1010000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C1129</t>
+          <t>C1139L</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BOLSA METALIZADA</t>
+          <t>BOLSA DE REGALO ANIMALES</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4658,7 +4652,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>505</v>
+        <v>217</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4667,30 +4661,30 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>505</v>
+        <v>217</v>
       </c>
       <c r="N103" t="n">
-        <v>1332</v>
+        <v>2331</v>
       </c>
       <c r="O103" t="n">
-        <v>672660</v>
+        <v>505827</v>
       </c>
       <c r="P103" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="Q103" t="n">
-        <v>1010000</v>
+        <v>759500</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C1139L</t>
+          <t>C1142L</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO ANIMALES</t>
+          <t>BOLSA DE REGALO HAPPY VERDAY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4699,7 +4693,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4708,30 +4702,30 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="N104" t="n">
         <v>2331</v>
       </c>
       <c r="O104" t="n">
-        <v>505827</v>
+        <v>531468</v>
       </c>
       <c r="P104" t="n">
         <v>3500</v>
       </c>
       <c r="Q104" t="n">
-        <v>759500</v>
+        <v>798000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C1142L</t>
+          <t>C1143L</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO HAPPY VERDAY</t>
+          <t>BOLSA DE REGALO FELICIDADES</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4740,7 +4734,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4749,39 +4743,44 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="N105" t="n">
         <v>2331</v>
       </c>
       <c r="O105" t="n">
-        <v>531468</v>
+        <v>391608</v>
       </c>
       <c r="P105" t="n">
         <v>3500</v>
       </c>
       <c r="Q105" t="n">
-        <v>798000</v>
+        <v>588000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C1143L</t>
+          <t>C1153</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO FELICIDADES</t>
+          <t>LANZA CHORROS 60cm C1153</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>168</v>
+        <v>2</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4790,44 +4789,39 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>168</v>
+        <v>2</v>
       </c>
       <c r="N106" t="n">
-        <v>2331</v>
+        <v>2613</v>
       </c>
       <c r="O106" t="n">
-        <v>391608</v>
+        <v>5226</v>
       </c>
       <c r="P106" t="n">
-        <v>3500</v>
+        <v>5100</v>
       </c>
       <c r="Q106" t="n">
-        <v>588000</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C1153</t>
+          <t>C1172</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LANZA CHORROS 60cm C1153</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS SET</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4836,30 +4830,35 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="N107" t="n">
-        <v>2613</v>
+        <v>28561.915454545</v>
       </c>
       <c r="O107" t="n">
-        <v>5226</v>
+        <v>6569240.55454535</v>
       </c>
       <c r="P107" t="n">
-        <v>5100</v>
+        <v>29000</v>
       </c>
       <c r="Q107" t="n">
-        <v>10200</v>
+        <v>6670000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C1172</t>
+          <t>C1182</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GLOBOS SET</t>
+          <t>MUÑECA CON OREJITAS QUE ALUMBRA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4868,7 +4867,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4877,35 +4876,30 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>28561.915454545</v>
+        <v>12114.32</v>
       </c>
       <c r="O108" t="n">
-        <v>6569240.55454535</v>
+        <v>12114.32</v>
       </c>
       <c r="P108" t="n">
-        <v>29000</v>
+        <v>20900</v>
       </c>
       <c r="Q108" t="n">
-        <v>6670000</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C1182</t>
+          <t>C1188</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MUÑECA CON OREJITAS QUE ALUMBRA</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MUNECA CRY BABY OJO DE VIDRIO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4914,7 +4908,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4923,30 +4917,30 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="N109" t="n">
-        <v>12114.32</v>
+        <v>17207.41</v>
       </c>
       <c r="O109" t="n">
-        <v>12114.32</v>
+        <v>1737948.41</v>
       </c>
       <c r="P109" t="n">
-        <v>20900</v>
+        <v>20000</v>
       </c>
       <c r="Q109" t="n">
-        <v>20900</v>
+        <v>2020000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C1188</t>
+          <t>C1199</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MUNECA CRY BABY OJO DE VIDRIO</t>
+          <t>C1199 BEBE HERNANDITO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4955,7 +4949,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4964,30 +4958,30 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="N110" t="n">
-        <v>17207.41</v>
+        <v>18694.410088692</v>
       </c>
       <c r="O110" t="n">
-        <v>1737948.41</v>
+        <v>635609.9430155279</v>
       </c>
       <c r="P110" t="n">
-        <v>20000</v>
+        <v>29900</v>
       </c>
       <c r="Q110" t="n">
-        <v>2020000</v>
+        <v>1016600</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C1199</t>
+          <t>C1207</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C1199 BEBE HERNANDITO</t>
+          <t>TROMPO ESPIRAL</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -4996,7 +4990,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5005,30 +4999,35 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="N111" t="n">
-        <v>18694.410088692</v>
+        <v>2913</v>
       </c>
       <c r="O111" t="n">
-        <v>635609.9430155279</v>
+        <v>14565</v>
       </c>
       <c r="P111" t="n">
-        <v>29900</v>
+        <v>4950</v>
       </c>
       <c r="Q111" t="n">
-        <v>1016600</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C1207</t>
+          <t>C1210</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TROMPO ESPIRAL</t>
+          <t>TROMPO STD</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5037,7 +5036,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>5</v>
+        <v>708</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -5046,30 +5045,30 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>5</v>
+        <v>708</v>
       </c>
       <c r="N112" t="n">
-        <v>2913</v>
+        <v>2804.33</v>
       </c>
       <c r="O112" t="n">
-        <v>14565</v>
+        <v>1985465.64</v>
       </c>
       <c r="P112" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="Q112" t="n">
-        <v>24750</v>
+        <v>3469200</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C1210</t>
+          <t>C1243</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TROMPO STD</t>
+          <t>MUÑECAS CON ACCESORIOS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5083,7 +5082,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>708</v>
+        <v>468</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5092,30 +5091,30 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>708</v>
+        <v>468</v>
       </c>
       <c r="N113" t="n">
-        <v>2804.33</v>
+        <v>3247</v>
       </c>
       <c r="O113" t="n">
-        <v>1985465.64</v>
+        <v>1519596</v>
       </c>
       <c r="P113" t="n">
-        <v>4900</v>
+        <v>5200</v>
       </c>
       <c r="Q113" t="n">
-        <v>3469200</v>
+        <v>2433600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C1243</t>
+          <t>C1244</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MUÑECAS CON ACCESORIOS</t>
+          <t>SIRENA DE CUERDA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5129,7 +5128,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>468</v>
+        <v>1080</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -5138,30 +5137,30 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>468</v>
+        <v>1080</v>
       </c>
       <c r="N114" t="n">
-        <v>3247</v>
+        <v>2588.3559055118</v>
       </c>
       <c r="O114" t="n">
-        <v>1519596</v>
+        <v>2795424.377952744</v>
       </c>
       <c r="P114" t="n">
-        <v>5200</v>
+        <v>4500</v>
       </c>
       <c r="Q114" t="n">
-        <v>2433600</v>
+        <v>4860000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C1244</t>
+          <t>C1246</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SIRENA DE CUERDA</t>
+          <t>BALON DE FUTBOL # 5 CON RECUBRIMIENTO C1246</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5171,11 +5170,11 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>1080</v>
+        <v>3379</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5184,30 +5183,30 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>1080</v>
+        <v>3379</v>
       </c>
       <c r="N115" t="n">
-        <v>2344</v>
+        <v>10600</v>
       </c>
       <c r="O115" t="n">
-        <v>2531520</v>
+        <v>35817400</v>
       </c>
       <c r="P115" t="n">
-        <v>4200</v>
+        <v>17200</v>
       </c>
       <c r="Q115" t="n">
-        <v>4536000</v>
+        <v>58118800</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C1246</t>
+          <t>C1247</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BALON DE FUTBOL # 5 CON RECUBRIMIENTO C1246</t>
+          <t>MUÑECA PEQUEÑA CON ACCESORIOS CUATRO MODELOS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5217,11 +5216,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>3379</v>
+        <v>2160</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5230,19 +5229,19 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3379</v>
+        <v>2160</v>
       </c>
       <c r="N116" t="n">
-        <v>10600</v>
+        <v>5216.8959875629</v>
       </c>
       <c r="O116" t="n">
-        <v>35817400</v>
+        <v>11268495.33313586</v>
       </c>
       <c r="P116" t="n">
-        <v>17200</v>
+        <v>8500</v>
       </c>
       <c r="Q116" t="n">
-        <v>58118800</v>
+        <v>18360000</v>
       </c>
     </row>
     <row r="117">
@@ -5320,10 +5319,10 @@
         <v>75</v>
       </c>
       <c r="N118" t="n">
-        <v>6713.08</v>
+        <v>6816.3581538462</v>
       </c>
       <c r="O118" t="n">
-        <v>503481</v>
+        <v>511226.861538465</v>
       </c>
       <c r="P118" t="n">
         <v>9900</v>
@@ -5734,10 +5733,10 @@
         <v>360</v>
       </c>
       <c r="N127" t="n">
-        <v>7507.39</v>
+        <v>7538.62740638</v>
       </c>
       <c r="O127" t="n">
-        <v>2702660.4</v>
+        <v>2713905.8662968</v>
       </c>
       <c r="P127" t="n">
         <v>13500</v>
@@ -5783,10 +5782,10 @@
         <v>220</v>
       </c>
       <c r="N128" t="n">
-        <v>8796</v>
+        <v>8907.908396946599</v>
       </c>
       <c r="O128" t="n">
-        <v>1935120</v>
+        <v>1959739.847328252</v>
       </c>
       <c r="P128" t="n">
         <v>14900</v>
@@ -5916,10 +5915,10 @@
         <v>3024</v>
       </c>
       <c r="N131" t="n">
-        <v>3795.7100070299</v>
+        <v>3801.7317574476</v>
       </c>
       <c r="O131" t="n">
-        <v>11478227.06125842</v>
+        <v>11496436.83452154</v>
       </c>
       <c r="P131" t="n">
         <v>6200</v>
@@ -5962,10 +5961,10 @@
         <v>1303</v>
       </c>
       <c r="N132" t="n">
-        <v>3684</v>
+        <v>3695.2967632027</v>
       </c>
       <c r="O132" t="n">
-        <v>4800252</v>
+        <v>4814971.682453118</v>
       </c>
       <c r="P132" t="n">
         <v>6200</v>
@@ -6054,10 +6053,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>4890.9300454545</v>
+        <v>4890.930045977</v>
       </c>
       <c r="O134" t="n">
-        <v>313019.522909088</v>
+        <v>313019.522942528</v>
       </c>
       <c r="P134" t="n">
         <v>8200</v>
@@ -6152,10 +6151,10 @@
         <v>720</v>
       </c>
       <c r="N136" t="n">
-        <v>1203.38</v>
+        <v>1213.150338295</v>
       </c>
       <c r="O136" t="n">
-        <v>866433.6000000001</v>
+        <v>873468.2435724</v>
       </c>
       <c r="P136" t="n">
         <v>1900</v>
@@ -6377,10 +6376,10 @@
         <v>24</v>
       </c>
       <c r="N141" t="n">
-        <v>2267.0481788216</v>
+        <v>2286.8353823774</v>
       </c>
       <c r="O141" t="n">
-        <v>54409.15629171839</v>
+        <v>54884.0491770576</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
@@ -6556,10 +6555,10 @@
         <v>546</v>
       </c>
       <c r="N145" t="n">
-        <v>8662</v>
+        <v>8687.96003996</v>
       </c>
       <c r="O145" t="n">
-        <v>4729452</v>
+        <v>4743626.18181816</v>
       </c>
       <c r="P145" t="n">
         <v>14200</v>
@@ -6733,10 +6732,10 @@
         <v>264</v>
       </c>
       <c r="N149" t="n">
-        <v>3594.2542583732</v>
+        <v>3594.2542480527</v>
       </c>
       <c r="O149" t="n">
-        <v>948883.1242105248</v>
+        <v>948883.1214859128</v>
       </c>
       <c r="P149" t="n">
         <v>6500</v>
@@ -6912,10 +6911,10 @@
         <v>96</v>
       </c>
       <c r="N153" t="n">
-        <v>8154</v>
+        <v>8209.849315068501</v>
       </c>
       <c r="O153" t="n">
-        <v>782784</v>
+        <v>788145.534246576</v>
       </c>
       <c r="P153" t="n">
         <v>13500</v>
@@ -6927,24 +6926,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C1468</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>8596162180435</v>
+          <t>C1463</t>
+        </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO SURTIDO M</t>
+          <t>MUÑECA CON ACCESORIOS LUZ Y SONIDO C1463</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>15671</v>
+        <v>432</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6953,33 +6954,33 @@
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>15671</v>
+        <v>432</v>
       </c>
       <c r="N154" t="n">
-        <v>616.01871952955</v>
+        <v>14822.378867925</v>
       </c>
       <c r="O154" t="n">
-        <v>9653629.353747578</v>
+        <v>6403267.670943599</v>
       </c>
       <c r="P154" t="n">
-        <v>800</v>
+        <v>24900</v>
       </c>
       <c r="Q154" t="n">
-        <v>12536800</v>
+        <v>10756800</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C1472</t>
+          <t>C1468</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2019892166532</v>
+        <v>8596162180435</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BURBUJERO TUBO TIJERA</t>
+          <t>GLOBO METALIZADO SURTIDO M</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6988,7 +6989,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>2243</v>
+        <v>15671</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6997,33 +6998,33 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>2243</v>
+        <v>15671</v>
       </c>
       <c r="N155" t="n">
-        <v>2090.85</v>
+        <v>616.28176305926</v>
       </c>
       <c r="O155" t="n">
-        <v>4689776.55</v>
+        <v>9657751.508901663</v>
       </c>
       <c r="P155" t="n">
-        <v>2900</v>
+        <v>800</v>
       </c>
       <c r="Q155" t="n">
-        <v>6504700</v>
+        <v>12536800</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C1472</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>7891276180168</v>
+        <v>2019892166532</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>INFLABLE UNICORNIO</t>
+          <t>BURBUJERO TUBO TIJERA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7032,7 +7033,7 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>50</v>
+        <v>2243</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -7041,33 +7042,33 @@
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>50</v>
+        <v>2243</v>
       </c>
       <c r="N156" t="n">
-        <v>2769.98</v>
+        <v>2090.85</v>
       </c>
       <c r="O156" t="n">
-        <v>138499</v>
+        <v>4689776.55</v>
       </c>
       <c r="P156" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="Q156" t="n">
-        <v>175000</v>
+        <v>6504700</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C1500</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6902018818186</v>
+        <v>7891276180168</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GLOBO METALIZDO SUTIDO S</t>
+          <t>INFLABLE UNICORNIO</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7076,7 +7077,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>8282</v>
+        <v>50</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -7085,33 +7086,33 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>8282</v>
+        <v>50</v>
       </c>
       <c r="N157" t="n">
-        <v>381.16028283297</v>
+        <v>2769.98</v>
       </c>
       <c r="O157" t="n">
-        <v>3156769.462422657</v>
+        <v>138499</v>
       </c>
       <c r="P157" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="Q157" t="n">
-        <v>4141000</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C1527</t>
+          <t>C1500</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>6914919099717</v>
+        <v>6902018818186</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MU?ECA FLACA FASHION MEDIANA</t>
+          <t>GLOBO METALIZDO SUTIDO S</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7120,7 +7121,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>192</v>
+        <v>8282</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -7129,38 +7130,33 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>192</v>
+        <v>8282</v>
       </c>
       <c r="N158" t="n">
-        <v>2665.4</v>
+        <v>381.16028283297</v>
       </c>
       <c r="O158" t="n">
-        <v>511756.8</v>
+        <v>3156769.462422657</v>
       </c>
       <c r="P158" t="n">
-        <v>20900</v>
+        <v>500</v>
       </c>
       <c r="Q158" t="n">
-        <v>4012800</v>
+        <v>4141000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C1564</t>
+          <t>C1527</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6962329874837</v>
+        <v>6914919099717</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BOLITRON PATO</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MU?ECA FLACA FASHION MEDIANA</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7169,7 +7165,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>681</v>
+        <v>192</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -7178,30 +7174,38 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>681</v>
+        <v>192</v>
       </c>
       <c r="N159" t="n">
-        <v>1381.75</v>
+        <v>2665.4</v>
       </c>
       <c r="O159" t="n">
-        <v>940971.75</v>
+        <v>511756.8</v>
       </c>
       <c r="P159" t="n">
-        <v>2500</v>
+        <v>20900</v>
       </c>
       <c r="Q159" t="n">
-        <v>1702500</v>
+        <v>4012800</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C157</t>
-        </is>
+          <t>C1564</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6962329874837</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BLISTER BELLEZA</t>
+          <t>BOLITRON PATO</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7210,7 +7214,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>75</v>
+        <v>681</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7219,33 +7223,30 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>75</v>
+        <v>681</v>
       </c>
       <c r="N160" t="n">
-        <v>2696.09</v>
+        <v>1381.75</v>
       </c>
       <c r="O160" t="n">
-        <v>202206.75</v>
+        <v>940971.75</v>
       </c>
       <c r="P160" t="n">
-        <v>8200</v>
+        <v>2500</v>
       </c>
       <c r="Q160" t="n">
-        <v>615000</v>
+        <v>1702500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>7891276139739</v>
+          <t>C157</t>
+        </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>INFLABLE PERRO AZUL</t>
+          <t>BLISTER BELLEZA</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7254,7 +7255,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>5529</v>
+        <v>75</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7263,38 +7264,33 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>5529</v>
+        <v>75</v>
       </c>
       <c r="N161" t="n">
-        <v>1441.01</v>
+        <v>2696.09</v>
       </c>
       <c r="O161" t="n">
-        <v>7967344.29</v>
+        <v>202206.75</v>
       </c>
       <c r="P161" t="n">
-        <v>2100</v>
+        <v>8200</v>
       </c>
       <c r="Q161" t="n">
-        <v>11610900</v>
+        <v>615000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C1646</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>6999899236130</v>
+        <v>7891276139739</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CHALECO INFLABLE TALLA C 40 CM</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLE PERRO AZUL</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7303,7 +7299,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>78</v>
+        <v>5529</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7312,30 +7308,38 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>78</v>
+        <v>5529</v>
       </c>
       <c r="N162" t="n">
-        <v>3041.6600123153</v>
+        <v>1441.01</v>
       </c>
       <c r="O162" t="n">
-        <v>237249.4809605934</v>
+        <v>7967344.29</v>
       </c>
       <c r="P162" t="n">
-        <v>5500</v>
+        <v>2100</v>
       </c>
       <c r="Q162" t="n">
-        <v>429000</v>
+        <v>11610900</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C1648</t>
-        </is>
+          <t>C1646</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>6999899236130</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FLOTADOR PATO PIERNITAS</t>
+          <t>CHALECO INFLABLE TALLA C 40 CM</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7344,7 +7348,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7353,35 +7357,30 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="N163" t="n">
-        <v>3981.47</v>
+        <v>3041.6600123457</v>
       </c>
       <c r="O163" t="n">
-        <v>955552.7999999999</v>
+        <v>237249.4809629646</v>
       </c>
       <c r="P163" t="n">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="Q163" t="n">
-        <v>1680000</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C1654</t>
+          <t>C1648</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MUECA HIELO ZAPATOS</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FLOTADOR PATO PIERNITAS</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7390,7 +7389,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>912</v>
+        <v>240</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -7399,33 +7398,35 @@
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>912</v>
+        <v>240</v>
       </c>
       <c r="N164" t="n">
-        <v>4086.2</v>
+        <v>3981.47</v>
       </c>
       <c r="O164" t="n">
-        <v>3726614.4</v>
+        <v>955552.7999999999</v>
       </c>
       <c r="P164" t="n">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="Q164" t="n">
-        <v>6292800</v>
+        <v>1680000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C1673</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>6902748213923</v>
+          <t>C1654</t>
+        </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL #5</t>
+          <t>MUECA HIELO ZAPATOS</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7434,7 +7435,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>73</v>
+        <v>912</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -7443,30 +7444,33 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>73</v>
+        <v>912</v>
       </c>
       <c r="N165" t="n">
-        <v>6441.03</v>
+        <v>4372.2107862617</v>
       </c>
       <c r="O165" t="n">
-        <v>470195.19</v>
+        <v>3987456.237070671</v>
       </c>
       <c r="P165" t="n">
-        <v>10500</v>
+        <v>7500</v>
       </c>
       <c r="Q165" t="n">
-        <v>766500</v>
+        <v>6840000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
+          <t>C1673</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>6902748213923</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>INFLABLE AVION</t>
+          <t>BALON FOOTBALL #5</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7475,7 +7479,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7484,30 +7488,30 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="N166" t="n">
-        <v>1121.98</v>
+        <v>6493.1840890688</v>
       </c>
       <c r="O166" t="n">
-        <v>5609.9</v>
+        <v>474002.4385020224</v>
       </c>
       <c r="P166" t="n">
-        <v>2400</v>
+        <v>10500</v>
       </c>
       <c r="Q166" t="n">
-        <v>12000</v>
+        <v>766500</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C1720</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CUBO MAGICO GDE</t>
+          <t>INFLABLE AVION</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7516,7 +7520,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7525,30 +7529,30 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="N167" t="n">
-        <v>4513.76</v>
+        <v>1121.98</v>
       </c>
       <c r="O167" t="n">
-        <v>167009.12</v>
+        <v>5609.9</v>
       </c>
       <c r="P167" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="Q167" t="n">
-        <v>329300</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C1721</t>
+          <t>C1720</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CUBO MAGICO</t>
+          <t>CUBO MAGICO GDE</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7557,7 +7561,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7566,35 +7570,30 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="N168" t="n">
-        <v>2224.56</v>
+        <v>4513.76</v>
       </c>
       <c r="O168" t="n">
-        <v>33368.4</v>
+        <v>167009.12</v>
       </c>
       <c r="P168" t="n">
-        <v>3900</v>
+        <v>8900</v>
       </c>
       <c r="Q168" t="n">
-        <v>58500</v>
+        <v>329300</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C1722</t>
+          <t>C1721</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ESPADA DE LUZ Y SONIDO TIBURON GDE</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>CUBO MAGICO</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7603,7 +7602,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>2655</v>
+        <v>15</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7612,30 +7611,30 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>2655</v>
+        <v>15</v>
       </c>
       <c r="N169" t="n">
-        <v>3655.96</v>
+        <v>2224.56</v>
       </c>
       <c r="O169" t="n">
-        <v>9706573.800000001</v>
+        <v>33368.4</v>
       </c>
       <c r="P169" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q169" t="n">
-        <v>14602500</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C1757</t>
+          <t>C1722</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ESPADA MINECRAFT PIRATA 68CM C1757</t>
+          <t>ESPADA DE LUZ Y SONIDO TIBURON GDE</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7649,7 +7648,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>144</v>
+        <v>2655</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7658,33 +7657,30 @@
         <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>144</v>
+        <v>2655</v>
       </c>
       <c r="N170" t="n">
-        <v>6242.93</v>
+        <v>3660.708</v>
       </c>
       <c r="O170" t="n">
-        <v>898981.92</v>
+        <v>9719179.74</v>
       </c>
       <c r="P170" t="n">
-        <v>10400</v>
+        <v>5500</v>
       </c>
       <c r="Q170" t="n">
-        <v>1497600</v>
+        <v>14602500</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C1758</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>6914919067549</v>
+          <t>C1757</t>
+        </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>ESPADA MINECRAFT PIRATA 68CM C1757</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7698,7 +7694,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>5706</v>
+        <v>144</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7707,33 +7703,38 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>5706</v>
+        <v>144</v>
       </c>
       <c r="N171" t="n">
-        <v>4648.6</v>
+        <v>6242.93</v>
       </c>
       <c r="O171" t="n">
-        <v>26524911.6</v>
+        <v>898981.92</v>
       </c>
       <c r="P171" t="n">
-        <v>8900</v>
+        <v>10400</v>
       </c>
       <c r="Q171" t="n">
-        <v>50783400</v>
+        <v>1497600</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C1758</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7891276122007</v>
+        <v>6914919067549</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>INFLABLE DELFIN</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7742,7 +7743,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>386</v>
+        <v>5706</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7751,30 +7752,33 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>386</v>
+        <v>5706</v>
       </c>
       <c r="N172" t="n">
-        <v>1312.43</v>
+        <v>4648.6</v>
       </c>
       <c r="O172" t="n">
-        <v>506597.98</v>
+        <v>26524911.6</v>
       </c>
       <c r="P172" t="n">
-        <v>2300</v>
+        <v>8900</v>
       </c>
       <c r="Q172" t="n">
-        <v>887800</v>
+        <v>50783400</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C1812</t>
-        </is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>7891276122007</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CORTINA METALIZADA</t>
+          <t>INFLABLE DELFIN</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -7783,7 +7787,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>10357</v>
+        <v>386</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7792,30 +7796,30 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>10357</v>
+        <v>386</v>
       </c>
       <c r="N173" t="n">
-        <v>1532.6290334949</v>
+        <v>1312.43</v>
       </c>
       <c r="O173" t="n">
-        <v>15873438.89990668</v>
+        <v>506597.98</v>
       </c>
       <c r="P173" t="n">
-        <v>1200</v>
+        <v>2300</v>
       </c>
       <c r="Q173" t="n">
-        <v>12428400</v>
+        <v>887800</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C1814</t>
+          <t>C1812</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CARTA UNO FLIP</t>
+          <t>CORTINA METALIZADA</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -7824,7 +7828,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>4601</v>
+        <v>10357</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -7833,33 +7837,30 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>4601</v>
+        <v>10357</v>
       </c>
       <c r="N174" t="n">
-        <v>17472.91</v>
+        <v>1535.9702761427</v>
       </c>
       <c r="O174" t="n">
-        <v>80392858.91</v>
+        <v>15908044.15000994</v>
       </c>
       <c r="P174" t="n">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="Q174" t="n">
-        <v>13342900</v>
+        <v>12428400</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C1815</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>657813018159</v>
+          <t>C1814</t>
+        </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CARTA FLIP1 ROJA</t>
+          <t>CARTA UNO FLIP</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7868,7 +7869,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>3600</v>
+        <v>4601</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -7877,33 +7878,33 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3600</v>
+        <v>4601</v>
       </c>
       <c r="N175" t="n">
-        <v>1343.77</v>
+        <v>17472.91</v>
       </c>
       <c r="O175" t="n">
-        <v>4837572</v>
+        <v>80392858.91</v>
       </c>
       <c r="P175" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q175" t="n">
-        <v>9000000</v>
+        <v>13342900</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C1816</t>
+          <t>C1815</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6578213018166</v>
+        <v>657813018159</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CARTA FASE2</t>
+          <t>CARTA FLIP1 ROJA</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -7912,7 +7913,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -7921,33 +7922,33 @@
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="N176" t="n">
-        <v>1530.63</v>
+        <v>1343.77</v>
       </c>
       <c r="O176" t="n">
-        <v>8265402.000000001</v>
+        <v>4837572</v>
       </c>
       <c r="P176" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q176" t="n">
-        <v>15660000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C1817</t>
+          <t>C1816</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>5055581618170</v>
+        <v>6578213018166</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CUBO 3X3 FORRADO</t>
+          <t>CARTA FASE2</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7956,7 +7957,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>720</v>
+        <v>5400</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -7965,33 +7966,33 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>720</v>
+        <v>5400</v>
       </c>
       <c r="N177" t="n">
-        <v>1647.46</v>
+        <v>1530.63</v>
       </c>
       <c r="O177" t="n">
-        <v>1186171.2</v>
+        <v>8265402.000000001</v>
       </c>
       <c r="P177" t="n">
         <v>2900</v>
       </c>
       <c r="Q177" t="n">
-        <v>2088000</v>
+        <v>15660000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C1818</t>
+          <t>C1817</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6912017139731</v>
+        <v>5055581618170</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MUNECA SIRENA COLORES</t>
+          <t>CUBO 3X3 FORRADO</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8000,7 +8001,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>412</v>
+        <v>720</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8009,33 +8010,33 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>412</v>
+        <v>720</v>
       </c>
       <c r="N178" t="n">
-        <v>9414.309999999999</v>
+        <v>1647.46</v>
       </c>
       <c r="O178" t="n">
-        <v>3878695.72</v>
+        <v>1186171.2</v>
       </c>
       <c r="P178" t="n">
-        <v>16900</v>
+        <v>2900</v>
       </c>
       <c r="Q178" t="n">
-        <v>6962800</v>
+        <v>2088000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C1820</t>
+          <t>C1818</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>10802610150303</v>
+        <v>6912017139731</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BOLITRON OSO LUZ</t>
+          <t>MUNECA SIRENA COLORES</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8044,7 +8045,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>10164</v>
+        <v>412</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -8053,30 +8054,33 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>10164</v>
+        <v>412</v>
       </c>
       <c r="N179" t="n">
-        <v>1387.55</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O179" t="n">
-        <v>14103058.2</v>
+        <v>3878695.72</v>
       </c>
       <c r="P179" t="n">
-        <v>2300</v>
+        <v>16900</v>
       </c>
       <c r="Q179" t="n">
-        <v>23377200</v>
+        <v>6962800</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C1843</t>
-        </is>
+          <t>C1820</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>10802610150303</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GLOBO HBD 16 DORADO Y PLATEADO</t>
+          <t>BOLITRON OSO LUZ</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8085,7 +8089,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>720</v>
+        <v>10164</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8094,33 +8098,30 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>720</v>
+        <v>10164</v>
       </c>
       <c r="N180" t="n">
-        <v>1461.54</v>
+        <v>1387.55</v>
       </c>
       <c r="O180" t="n">
-        <v>1052308.8</v>
+        <v>14103058.2</v>
       </c>
       <c r="P180" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="Q180" t="n">
-        <v>1368000</v>
+        <v>23377200</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C1877</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>6979860180020</v>
+          <t>C1843</t>
+        </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET MOTIVOS</t>
+          <t>GLOBO HBD 16 DORADO Y PLATEADO</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8129,7 +8130,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -8138,33 +8139,33 @@
         <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="N181" t="n">
-        <v>2021.7211191336</v>
+        <v>1466.9464364982</v>
       </c>
       <c r="O181" t="n">
-        <v>404344.22382672</v>
+        <v>1056201.434278704</v>
       </c>
       <c r="P181" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="Q181" t="n">
-        <v>480000</v>
+        <v>1368000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C1893</t>
+          <t>C1877</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>6914919003264</v>
+        <v>6979860180020</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SET MANICURE GIRLS</t>
+          <t>GLOBO BOUQUET MOTIVOS</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8173,7 +8174,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8182,33 +8183,33 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="N182" t="n">
-        <v>13304.13</v>
+        <v>2021.7211191336</v>
       </c>
       <c r="O182" t="n">
-        <v>3951326.61</v>
+        <v>404344.22382672</v>
       </c>
       <c r="P182" t="n">
-        <v>20900</v>
+        <v>2400</v>
       </c>
       <c r="Q182" t="n">
-        <v>6207300</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C1893</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7891276029719</v>
+        <v>6914919003264</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>INFLABLE VARA  DONA</t>
+          <t>SET MANICURE GIRLS</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8217,7 +8218,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>403</v>
+        <v>297</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8226,38 +8227,33 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>403</v>
+        <v>297</v>
       </c>
       <c r="N183" t="n">
-        <v>2204</v>
+        <v>13304.13</v>
       </c>
       <c r="O183" t="n">
-        <v>888212</v>
+        <v>3951326.61</v>
       </c>
       <c r="P183" t="n">
-        <v>1500</v>
+        <v>20900</v>
       </c>
       <c r="Q183" t="n">
-        <v>604500</v>
+        <v>6207300</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C1946</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>6914919131011</v>
+        <v>7891276029719</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BAIONICO BLISTER</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLE VARA  DONA</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8266,7 +8262,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>294</v>
+        <v>403</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8275,30 +8271,38 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>294</v>
+        <v>403</v>
       </c>
       <c r="N184" t="n">
-        <v>3761.6</v>
+        <v>2216.939334638</v>
       </c>
       <c r="O184" t="n">
-        <v>1105910.4</v>
+        <v>893426.5518591141</v>
       </c>
       <c r="P184" t="n">
-        <v>6900</v>
+        <v>1500</v>
       </c>
       <c r="Q184" t="n">
-        <v>2028600</v>
+        <v>604500</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C1975</t>
-        </is>
+          <t>C1946</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>6914919131011</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MALETA TOCADOR</t>
+          <t>BAIONICO BLISTER</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8307,7 +8311,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>128</v>
+        <v>294</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -8316,40 +8320,30 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>128</v>
+        <v>294</v>
       </c>
       <c r="N185" t="n">
-        <v>45945</v>
+        <v>3761.6</v>
       </c>
       <c r="O185" t="n">
-        <v>5880960</v>
+        <v>1105910.4</v>
       </c>
       <c r="P185" t="n">
-        <v>73900</v>
+        <v>6900</v>
       </c>
       <c r="Q185" t="n">
-        <v>9459200</v>
+        <v>2028600</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C1995</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>6914919 080111</t>
+          <t>C1975</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CARRO OJON CAJA</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MALETA TOCADOR</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8358,7 +8352,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>650</v>
+        <v>119</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8367,30 +8361,40 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>650</v>
+        <v>119</v>
       </c>
       <c r="N186" t="n">
-        <v>11921.4</v>
+        <v>45945</v>
       </c>
       <c r="O186" t="n">
-        <v>7748910</v>
+        <v>5467455</v>
       </c>
       <c r="P186" t="n">
-        <v>19900</v>
+        <v>73900</v>
       </c>
       <c r="Q186" t="n">
-        <v>12935000</v>
+        <v>8794100</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C2011NET</t>
+          <t>C1995</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>6914919 080111</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>JUEGO DE MEMORIA DIDÁCTICO</t>
+          <t>CARRO OJON CAJA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8399,7 +8403,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>8</v>
+        <v>650</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8408,33 +8412,30 @@
         <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>8</v>
+        <v>650</v>
       </c>
       <c r="N187" t="n">
-        <v>16846.15</v>
+        <v>11921.4</v>
       </c>
       <c r="O187" t="n">
-        <v>134769.2</v>
+        <v>7748910</v>
       </c>
       <c r="P187" t="n">
-        <v>21900</v>
+        <v>19900</v>
       </c>
       <c r="Q187" t="n">
-        <v>175200</v>
+        <v>12935000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C2096</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>6969458721216</v>
+          <t>C2011NET</t>
+        </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GLOBO METALIZADO PASTEL</t>
+          <t>JUEGO DE MEMORIA DIDÁCTICO</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8443,7 +8444,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>5338</v>
+        <v>8</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8452,30 +8453,33 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>5338</v>
+        <v>8</v>
       </c>
       <c r="N188" t="n">
-        <v>1151.3923550423</v>
+        <v>16846.15</v>
       </c>
       <c r="O188" t="n">
-        <v>6146132.391215798</v>
+        <v>134769.2</v>
       </c>
       <c r="P188" t="n">
-        <v>1500</v>
+        <v>21900</v>
       </c>
       <c r="Q188" t="n">
-        <v>8007000</v>
+        <v>175200</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C2096</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>6969458721216</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>GLOBO METALIZADO PASTEL</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8484,7 +8488,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>208</v>
+        <v>5338</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8493,38 +8497,30 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>208</v>
+        <v>5338</v>
       </c>
       <c r="N189" t="n">
-        <v>3751</v>
+        <v>1151.3923550423</v>
       </c>
       <c r="O189" t="n">
-        <v>780208</v>
+        <v>6146132.391215798</v>
       </c>
       <c r="P189" t="n">
-        <v>6400</v>
+        <v>1500</v>
       </c>
       <c r="Q189" t="n">
-        <v>1331200</v>
+        <v>8007000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C2161</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>6952216485222</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MUNECA NANCY MEDIANA</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8533,7 +8529,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>519</v>
+        <v>208</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -8542,30 +8538,33 @@
         <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>519</v>
+        <v>208</v>
       </c>
       <c r="N190" t="n">
-        <v>9903</v>
+        <v>3751</v>
       </c>
       <c r="O190" t="n">
-        <v>5139657</v>
+        <v>780208</v>
       </c>
       <c r="P190" t="n">
-        <v>15900</v>
+        <v>6400</v>
       </c>
       <c r="Q190" t="n">
-        <v>8252100</v>
+        <v>1331200</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C2228</t>
-        </is>
+          <t>C2161</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>6952216485222</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LANZADORA AGUA CHORROS EN MALLA C2228</t>
+          <t>MUNECA NANCY MEDIANA</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8575,11 +8574,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>64</v>
+        <v>519</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -8588,30 +8587,30 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>64</v>
+        <v>519</v>
       </c>
       <c r="N191" t="n">
-        <v>12754</v>
+        <v>9903</v>
       </c>
       <c r="O191" t="n">
-        <v>816256</v>
+        <v>5139657</v>
       </c>
       <c r="P191" t="n">
-        <v>21500</v>
+        <v>15900</v>
       </c>
       <c r="Q191" t="n">
-        <v>1376000</v>
+        <v>8252100</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C2234</t>
+          <t>C2228</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>C2234 SQUISHY MODELOS STDS</t>
+          <t>LANZADORA AGUA CHORROS EN MALLA C2228</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8625,7 +8624,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>1152</v>
+        <v>64</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8634,30 +8633,30 @@
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>1152</v>
+        <v>64</v>
       </c>
       <c r="N192" t="n">
-        <v>1630.9229356747</v>
+        <v>12754</v>
       </c>
       <c r="O192" t="n">
-        <v>1878823.221897254</v>
+        <v>816256</v>
       </c>
       <c r="P192" t="n">
-        <v>2500</v>
+        <v>21500</v>
       </c>
       <c r="Q192" t="n">
-        <v>2880000</v>
+        <v>1376000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C2240</t>
+          <t>C2234</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>C2240 SQUISHY UNICORNIO OSITO COMIDA</t>
+          <t>C2234 SQUISHY MODELOS STDS</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8683,27 +8682,27 @@
         <v>1152</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.6038424947</v>
+        <v>1630.9229788882</v>
       </c>
       <c r="O193" t="n">
-        <v>1947575.626553894</v>
+        <v>1878823.271679207</v>
       </c>
       <c r="P193" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q193" t="n">
-        <v>3340800</v>
+        <v>2880000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C2241</t>
+          <t>C2240</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>C2241 SQUISHY TRANSPARENTE MODELOS STD</t>
+          <t>C2240 SQUISHY UNICORNIO OSITO COMIDA</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8717,7 +8716,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>5472</v>
+        <v>1152</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -8726,30 +8725,30 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>5472</v>
+        <v>1152</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.192872291</v>
+        <v>1690.6043069815</v>
       </c>
       <c r="O194" t="n">
-        <v>8482655.397176351</v>
+        <v>1947576.161642688</v>
       </c>
       <c r="P194" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q194" t="n">
-        <v>13680000</v>
+        <v>3340800</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C2249</t>
+          <t>C2241</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SQUISHY CAMARA Y HELADOS STD C2249</t>
+          <t>C2241 SQUISHY TRANSPARENTE MODELOS STD</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8763,7 +8762,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>2016</v>
+        <v>5472</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8772,42 +8771,44 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>2016</v>
+        <v>5472</v>
       </c>
       <c r="N195" t="n">
-        <v>2403.5098964308</v>
+        <v>1550.1929105882</v>
       </c>
       <c r="O195" t="n">
-        <v>4845475.951204493</v>
+        <v>8482655.606738631</v>
       </c>
       <c r="P195" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="Q195" t="n">
-        <v>7056000</v>
+        <v>13680000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C226</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>6055338878016</v>
+          <t>C2249</t>
+        </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MUNECA HIELO CAJA GRANDE OJO DE VIDRIO</t>
+          <t>SQUISHY CAMARA Y HELADOS STD C2249</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>76</v>
+        <v>2016</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -8816,30 +8817,33 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>76</v>
+        <v>2016</v>
       </c>
       <c r="N196" t="n">
-        <v>24267.77</v>
+        <v>2403.5099727039</v>
       </c>
       <c r="O196" t="n">
-        <v>1844350.52</v>
+        <v>4845476.104971062</v>
       </c>
       <c r="P196" t="n">
-        <v>33400</v>
+        <v>3500</v>
       </c>
       <c r="Q196" t="n">
-        <v>2538400</v>
+        <v>7056000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C2288</t>
-        </is>
+          <t>C226</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6055338878016</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>GLOBOS BALL Z</t>
+          <t>MUNECA HIELO CAJA GRANDE OJO DE VIDRIO</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8848,7 +8852,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>9361</v>
+        <v>76</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -8857,30 +8861,30 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>9361</v>
+        <v>76</v>
       </c>
       <c r="N197" t="n">
-        <v>1000</v>
+        <v>24267.77</v>
       </c>
       <c r="O197" t="n">
-        <v>9361000</v>
+        <v>1844350.52</v>
       </c>
       <c r="P197" t="n">
-        <v>1300</v>
+        <v>33400</v>
       </c>
       <c r="Q197" t="n">
-        <v>12169300</v>
+        <v>2538400</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C236</t>
+          <t>C2288</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SCOOTER JUNIOR</t>
+          <t>GLOBOS BALL Z</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8889,7 +8893,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>18</v>
+        <v>9361</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -8898,33 +8902,30 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>18</v>
+        <v>9361</v>
       </c>
       <c r="N198" t="n">
-        <v>101770.01727273</v>
+        <v>1000</v>
       </c>
       <c r="O198" t="n">
-        <v>1831860.31090914</v>
+        <v>9361000</v>
       </c>
       <c r="P198" t="n">
-        <v>136900</v>
+        <v>1300</v>
       </c>
       <c r="Q198" t="n">
-        <v>2464200</v>
+        <v>12169300</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C243</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>6901234528824</v>
+          <t>C236</t>
+        </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AVION LUZ ICOPOR</t>
+          <t>SCOOTER JUNIOR</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -8933,7 +8934,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -8942,33 +8943,33 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N199" t="n">
-        <v>3560.97</v>
+        <v>101770.01727273</v>
       </c>
       <c r="O199" t="n">
-        <v>89024.25</v>
+        <v>1831860.31090914</v>
       </c>
       <c r="P199" t="n">
-        <v>6900</v>
+        <v>136900</v>
       </c>
       <c r="Q199" t="n">
-        <v>172500</v>
+        <v>2464200</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C254</t>
+          <t>C243</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>6920202102545</v>
+        <v>6901234528824</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 32</t>
+          <t>AVION LUZ ICOPOR</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -8977,7 +8978,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -8986,33 +8987,33 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N200" t="n">
-        <v>1020.1698591549</v>
+        <v>3560.97</v>
       </c>
       <c r="O200" t="n">
-        <v>40806.794366196</v>
+        <v>89024.25</v>
       </c>
       <c r="P200" t="n">
-        <v>1350</v>
+        <v>6900</v>
       </c>
       <c r="Q200" t="n">
-        <v>54000</v>
+        <v>172500</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C256</t>
+          <t>C254</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>6901700156414</v>
+        <v>6920202102545</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PATINES 4 RUEDAS CON LUZ</t>
+          <t>GLOBO NUMERO 32</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9021,7 +9022,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9030,40 +9031,33 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="N201" t="n">
-        <v>59081.6</v>
+        <v>1020.1698591549</v>
       </c>
       <c r="O201" t="n">
-        <v>3899385.6</v>
+        <v>40806.794366196</v>
       </c>
       <c r="P201" t="n">
-        <v>40000</v>
+        <v>1350</v>
       </c>
       <c r="Q201" t="n">
-        <v>2640000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C2560</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>6914921 802046</t>
-        </is>
+          <t>C256</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>6901700156414</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BOLSO PRINCESA PINATERO</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PATINES 4 RUEDAS CON LUZ</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9072,7 +9066,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>913</v>
+        <v>66</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -9081,35 +9075,40 @@
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>913</v>
+        <v>66</v>
       </c>
       <c r="N202" t="n">
-        <v>2973.29</v>
+        <v>59081.6</v>
       </c>
       <c r="O202" t="n">
-        <v>2714613.77</v>
+        <v>3899385.6</v>
       </c>
       <c r="P202" t="n">
-        <v>4900</v>
+        <v>40000</v>
       </c>
       <c r="Q202" t="n">
-        <v>4473700</v>
+        <v>2640000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C2565</t>
+          <t>C2560</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>6914921 100050</t>
+          <t>6914921 802046</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BOLA LABERINTO</t>
+          <t>BOLSO PRINCESA PINATERO</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9118,7 +9117,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>9</v>
+        <v>913</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -9127,33 +9126,35 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>9</v>
+        <v>913</v>
       </c>
       <c r="N203" t="n">
-        <v>2638</v>
+        <v>2973.29</v>
       </c>
       <c r="O203" t="n">
-        <v>23742</v>
+        <v>2714613.77</v>
       </c>
       <c r="P203" t="n">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="Q203" t="n">
-        <v>40500</v>
+        <v>4473700</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C258</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>6901700156438</v>
+          <t>C2565</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>6914921 100050</t>
+        </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PATINES 4 RUEDAS CORAZON Y RAYAS</t>
+          <t>BOLA LABERINTO</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9162,7 +9163,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9171,35 +9172,33 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N204" t="n">
-        <v>59880</v>
+        <v>2638</v>
       </c>
       <c r="O204" t="n">
-        <v>119760</v>
+        <v>23742</v>
       </c>
       <c r="P204" t="n">
-        <v>40000</v>
+        <v>4500</v>
       </c>
       <c r="Q204" t="n">
-        <v>80000</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C2654</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>6914921 000077</t>
-        </is>
+          <t>C258</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>6901700156438</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BURBUJERO</t>
+          <t>PATINES 4 RUEDAS CORAZON Y RAYAS</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -9208,7 +9207,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>1729</v>
+        <v>2</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9217,35 +9216,35 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>1729</v>
+        <v>2</v>
       </c>
       <c r="N205" t="n">
-        <v>5067.21</v>
+        <v>59880</v>
       </c>
       <c r="O205" t="n">
-        <v>8761206.09</v>
+        <v>119760</v>
       </c>
       <c r="P205" t="n">
-        <v>4200</v>
+        <v>40000</v>
       </c>
       <c r="Q205" t="n">
-        <v>7261800</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C2741</t>
+          <t>C2654</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>6914921 798387</t>
+          <t>6914921 000077</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DISCO BOLADOR</t>
+          <t>BURBUJERO</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9254,7 +9253,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>83</v>
+        <v>1729</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9263,30 +9262,35 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>83</v>
+        <v>1729</v>
       </c>
       <c r="N206" t="n">
-        <v>10034.5</v>
+        <v>5081.9760320544</v>
       </c>
       <c r="O206" t="n">
-        <v>832863.5</v>
+        <v>8786736.559422057</v>
       </c>
       <c r="P206" t="n">
-        <v>12900</v>
+        <v>4200</v>
       </c>
       <c r="Q206" t="n">
-        <v>1070700</v>
+        <v>7261800</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C2759</t>
+          <t>C2741</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>6914921 798387</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR LATA</t>
+          <t>DISCO BOLADOR</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -9295,7 +9299,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>1007</v>
+        <v>83</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -9304,35 +9308,30 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>1007</v>
+        <v>83</v>
       </c>
       <c r="N207" t="n">
-        <v>3253</v>
+        <v>10034.5</v>
       </c>
       <c r="O207" t="n">
-        <v>3275771</v>
+        <v>832863.5</v>
       </c>
       <c r="P207" t="n">
-        <v>3900</v>
+        <v>12900</v>
       </c>
       <c r="Q207" t="n">
-        <v>3927300</v>
+        <v>1070700</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C2760</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>6914921 011301</t>
+          <t>C2759</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CARPA</t>
+          <t>FICHAS DE ARMAR LATA</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -9341,7 +9340,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>180</v>
+        <v>1007</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9350,30 +9349,35 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>180</v>
+        <v>1007</v>
       </c>
       <c r="N208" t="n">
-        <v>17328</v>
+        <v>3319.8424657534</v>
       </c>
       <c r="O208" t="n">
-        <v>3119040</v>
+        <v>3343081.363013674</v>
       </c>
       <c r="P208" t="n">
-        <v>32900</v>
+        <v>3900</v>
       </c>
       <c r="Q208" t="n">
-        <v>5922000</v>
+        <v>3927300</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C2781</t>
+          <t>C2760</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>6914921 011301</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CITOFONO MUSICAL PARA CUNAS</t>
+          <t>CARPA</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9382,7 +9386,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9391,35 +9395,30 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="N209" t="n">
-        <v>10836.973589744</v>
+        <v>17328</v>
       </c>
       <c r="O209" t="n">
-        <v>682729.3361538721</v>
+        <v>3119040</v>
       </c>
       <c r="P209" t="n">
-        <v>19900</v>
+        <v>32900</v>
       </c>
       <c r="Q209" t="n">
-        <v>1253700</v>
+        <v>5922000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C2790</t>
+          <t>C2781</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BATALLA NAVAL</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>CITOFONO MUSICAL PARA CUNAS</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9428,7 +9427,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>371</v>
+        <v>63</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9437,30 +9436,35 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>371</v>
+        <v>63</v>
       </c>
       <c r="N210" t="n">
-        <v>7028</v>
+        <v>10836.973589744</v>
       </c>
       <c r="O210" t="n">
-        <v>2607388</v>
+        <v>682729.3361538721</v>
       </c>
       <c r="P210" t="n">
-        <v>15900</v>
+        <v>19900</v>
       </c>
       <c r="Q210" t="n">
-        <v>5898900</v>
+        <v>1253700</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C2801</t>
+          <t>C2790</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR LATAS</t>
+          <t>BATALLA NAVAL</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9469,7 +9473,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>700</v>
+        <v>371</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9478,33 +9482,30 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>700</v>
+        <v>371</v>
       </c>
       <c r="N211" t="n">
-        <v>3253</v>
+        <v>7028</v>
       </c>
       <c r="O211" t="n">
-        <v>2277100</v>
+        <v>2607388</v>
       </c>
       <c r="P211" t="n">
-        <v>3900</v>
+        <v>15900</v>
       </c>
       <c r="Q211" t="n">
-        <v>2730000</v>
+        <v>5898900</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C297</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>6912536200202</v>
+          <t>C2801</t>
+        </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>GLOBO PONQUE</t>
+          <t>FICHAS DE ARMAR LATAS</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -9513,7 +9514,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9522,30 +9523,33 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="N212" t="n">
-        <v>1692.31</v>
+        <v>3253</v>
       </c>
       <c r="O212" t="n">
-        <v>1692.31</v>
+        <v>2277100</v>
       </c>
       <c r="P212" t="n">
-        <v>2200</v>
+        <v>3900</v>
       </c>
       <c r="Q212" t="n">
-        <v>2200</v>
+        <v>2730000</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C3133</t>
-        </is>
+          <t>C297</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>6912536200202</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BALAS LANZADOR</t>
+          <t>GLOBO PONQUE</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9554,7 +9558,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>1026</v>
+        <v>1</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9563,35 +9567,30 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>1026</v>
+        <v>1</v>
       </c>
       <c r="N213" t="n">
-        <v>4231</v>
+        <v>1692.31</v>
       </c>
       <c r="O213" t="n">
-        <v>4341006</v>
+        <v>1692.31</v>
       </c>
       <c r="P213" t="n">
-        <v>6900</v>
+        <v>2200</v>
       </c>
       <c r="Q213" t="n">
-        <v>7079400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C3170</t>
+          <t>C3133</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>MALETIN DOCTOR AZUL Y ROSA</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>BALAS LANZADOR</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9600,7 +9599,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>111</v>
+        <v>1026</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9609,33 +9608,35 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>111</v>
+        <v>1026</v>
       </c>
       <c r="N214" t="n">
-        <v>9338</v>
+        <v>4231</v>
       </c>
       <c r="O214" t="n">
-        <v>1036518</v>
+        <v>4341006</v>
       </c>
       <c r="P214" t="n">
-        <v>15500</v>
+        <v>6900</v>
       </c>
       <c r="Q214" t="n">
-        <v>1720500</v>
+        <v>7079400</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C320</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>6914919006944</v>
+          <t>C3170</t>
+        </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BLISTER DARDOS</t>
+          <t>MALETIN DOCTOR AZUL Y ROSA</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -9644,7 +9645,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>1415</v>
+        <v>111</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9653,30 +9654,33 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>1415</v>
+        <v>111</v>
       </c>
       <c r="N215" t="n">
-        <v>4196.8725263158</v>
+        <v>9338</v>
       </c>
       <c r="O215" t="n">
-        <v>5938574.624736858</v>
+        <v>1036518</v>
       </c>
       <c r="P215" t="n">
-        <v>5900</v>
+        <v>15500</v>
       </c>
       <c r="Q215" t="n">
-        <v>8348500</v>
+        <v>1720500</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C3276</t>
-        </is>
+          <t>C320</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>6914919006944</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BLISTER BELLEZA</t>
+          <t>BLISTER DARDOS</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9685,7 +9689,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>384</v>
+        <v>1415</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9694,30 +9698,30 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>384</v>
+        <v>1415</v>
       </c>
       <c r="N216" t="n">
-        <v>2661.82</v>
+        <v>4196.8725263158</v>
       </c>
       <c r="O216" t="n">
-        <v>1022138.88</v>
+        <v>5938574.624736858</v>
       </c>
       <c r="P216" t="n">
-        <v>3200</v>
+        <v>5900</v>
       </c>
       <c r="Q216" t="n">
-        <v>1228800</v>
+        <v>8348500</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C3282</t>
+          <t>C3276</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BLISTER COCINA</t>
+          <t>BLISTER BELLEZA</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -9726,7 +9730,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -9735,25 +9739,25 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="N217" t="n">
-        <v>4488</v>
+        <v>2696.7673085339</v>
       </c>
       <c r="O217" t="n">
-        <v>4488</v>
+        <v>1035558.646477018</v>
       </c>
       <c r="P217" t="n">
-        <v>6200</v>
+        <v>3200</v>
       </c>
       <c r="Q217" t="n">
-        <v>6200</v>
+        <v>1228800</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C3284</t>
+          <t>C3282</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9767,7 +9771,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>481</v>
+        <v>1</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9776,25 +9780,25 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>481</v>
+        <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>2610</v>
+        <v>4550.9158878505</v>
       </c>
       <c r="O218" t="n">
-        <v>1255410</v>
+        <v>4550.9158878505</v>
       </c>
       <c r="P218" t="n">
-        <v>3200</v>
+        <v>6200</v>
       </c>
       <c r="Q218" t="n">
-        <v>1539200</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C3285</t>
+          <t>C3284</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9808,7 +9812,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>191</v>
+        <v>481</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -9817,25 +9821,25 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>191</v>
+        <v>481</v>
       </c>
       <c r="N219" t="n">
-        <v>2081</v>
+        <v>2621.3808139535</v>
       </c>
       <c r="O219" t="n">
-        <v>397471</v>
+        <v>1260884.171511634</v>
       </c>
       <c r="P219" t="n">
         <v>3200</v>
       </c>
       <c r="Q219" t="n">
-        <v>611200</v>
+        <v>1539200</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C3286</t>
+          <t>C3285</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9849,7 +9853,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>375</v>
+        <v>191</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -9858,30 +9862,30 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>375</v>
+        <v>191</v>
       </c>
       <c r="N220" t="n">
-        <v>2916</v>
+        <v>2081</v>
       </c>
       <c r="O220" t="n">
-        <v>1093500</v>
+        <v>397471</v>
       </c>
       <c r="P220" t="n">
         <v>3200</v>
       </c>
       <c r="Q220" t="n">
-        <v>1200000</v>
+        <v>611200</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C3287</t>
+          <t>C3286</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BLISTER TETERA</t>
+          <t>BLISTER COCINA</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -9890,7 +9894,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>158</v>
+        <v>375</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -9899,30 +9903,30 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>158</v>
+        <v>375</v>
       </c>
       <c r="N221" t="n">
-        <v>2286.55</v>
+        <v>2916</v>
       </c>
       <c r="O221" t="n">
-        <v>361274.9</v>
+        <v>1093500</v>
       </c>
       <c r="P221" t="n">
         <v>3200</v>
       </c>
       <c r="Q221" t="n">
-        <v>505600</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C3295</t>
+          <t>C3287</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BLISTER MILITAR</t>
+          <t>BLISTER TETERA</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -9931,7 +9935,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>491</v>
+        <v>158</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -9940,30 +9944,30 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>491</v>
+        <v>158</v>
       </c>
       <c r="N222" t="n">
-        <v>1969</v>
+        <v>2286.55</v>
       </c>
       <c r="O222" t="n">
-        <v>966779</v>
+        <v>361274.9</v>
       </c>
       <c r="P222" t="n">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="Q222" t="n">
-        <v>736500</v>
+        <v>505600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C3303</t>
+          <t>C3295</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BLISTER COSMÉTICO</t>
+          <t>BLISTER MILITAR</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9972,7 +9976,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>2</v>
+        <v>491</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -9981,30 +9985,30 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>2</v>
+        <v>491</v>
       </c>
       <c r="N223" t="n">
-        <v>1958.73</v>
+        <v>1979.2819843342</v>
       </c>
       <c r="O223" t="n">
-        <v>3917.46</v>
+        <v>971827.4543080921</v>
       </c>
       <c r="P223" t="n">
-        <v>3400</v>
+        <v>1500</v>
       </c>
       <c r="Q223" t="n">
-        <v>6800</v>
+        <v>736500</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C3308</t>
+          <t>C3303</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>KIT HERRAMIENTAS CASCO</t>
+          <t>BLISTER COSMÉTICO</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10013,7 +10017,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>576</v>
+        <v>2</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -10022,35 +10026,30 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>576</v>
+        <v>2</v>
       </c>
       <c r="N224" t="n">
-        <v>8794.48</v>
+        <v>2040.34375</v>
       </c>
       <c r="O224" t="n">
-        <v>5065620.48</v>
+        <v>4080.6875</v>
       </c>
       <c r="P224" t="n">
-        <v>14500</v>
+        <v>3400</v>
       </c>
       <c r="Q224" t="n">
-        <v>8352000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C3311</t>
+          <t>C3308</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HUEVO DINOSAURIO LLAVERO</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>KIT HERRAMIENTAS CASCO</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10059,7 +10058,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>1164</v>
+        <v>576</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10068,30 +10067,35 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>1164</v>
+        <v>576</v>
       </c>
       <c r="N225" t="n">
-        <v>2567</v>
+        <v>8818.9498942682</v>
       </c>
       <c r="O225" t="n">
-        <v>2987988</v>
+        <v>5079715.139098483</v>
       </c>
       <c r="P225" t="n">
-        <v>4500</v>
+        <v>14500</v>
       </c>
       <c r="Q225" t="n">
-        <v>5238000</v>
+        <v>8352000</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C3321</t>
+          <t>C3311</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BB CON ACCESORIOS Y FUNCIONES EN P.V.C.</t>
+          <t>HUEVO DINOSAURIO LLAVERO</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10100,7 +10104,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1</v>
+        <v>1164</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -10109,30 +10113,30 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>1</v>
+        <v>1164</v>
       </c>
       <c r="N226" t="n">
-        <v>11291.33</v>
+        <v>2567</v>
       </c>
       <c r="O226" t="n">
-        <v>11291.33</v>
+        <v>2987988</v>
       </c>
       <c r="P226" t="n">
-        <v>15900</v>
+        <v>4500</v>
       </c>
       <c r="Q226" t="n">
-        <v>15900</v>
+        <v>5238000</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C3324</t>
+          <t>C3321</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MUÑECAS BOLSA P.V.C.</t>
+          <t>BB CON ACCESORIOS Y FUNCIONES EN P.V.C.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -10141,7 +10145,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>515</v>
+        <v>1</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -10150,30 +10154,30 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>515</v>
+        <v>1</v>
       </c>
       <c r="N227" t="n">
-        <v>6652</v>
+        <v>11291.33</v>
       </c>
       <c r="O227" t="n">
-        <v>3425780</v>
+        <v>11291.33</v>
       </c>
       <c r="P227" t="n">
-        <v>5900</v>
+        <v>15900</v>
       </c>
       <c r="Q227" t="n">
-        <v>3038500</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C3331</t>
+          <t>C3324</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ANIMALES POR 12 DOMÉSTICOS Y SALVAJES EN TUBO PVC</t>
+          <t>MUÑECAS BOLSA P.V.C.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -10182,7 +10186,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>216</v>
+        <v>515</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10191,30 +10195,30 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>216</v>
+        <v>515</v>
       </c>
       <c r="N228" t="n">
-        <v>2517.22</v>
+        <v>6652</v>
       </c>
       <c r="O228" t="n">
-        <v>543719.5199999999</v>
+        <v>3425780</v>
       </c>
       <c r="P228" t="n">
-        <v>4200</v>
+        <v>5900</v>
       </c>
       <c r="Q228" t="n">
-        <v>907200</v>
+        <v>3038500</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C336</t>
+          <t>C3331</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>REGISTRADORA MOÑOS DULCES</t>
+          <t>ANIMALES POR 12 DOMÉSTICOS Y SALVAJES EN TUBO PVC</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -10223,7 +10227,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10232,30 +10236,30 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="N229" t="n">
-        <v>22485.695945946</v>
+        <v>2558.6841592313</v>
       </c>
       <c r="O229" t="n">
-        <v>2023712.63513514</v>
+        <v>552675.7783939608</v>
       </c>
       <c r="P229" t="n">
-        <v>36500</v>
+        <v>4200</v>
       </c>
       <c r="Q229" t="n">
-        <v>3285000</v>
+        <v>907200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C3393</t>
+          <t>C336</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CANCHA BASQUET PEQUENA</t>
+          <t>REGISTRADORA MOÑOS DULCES</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -10264,7 +10268,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10273,38 +10277,30 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="N230" t="n">
-        <v>2673</v>
+        <v>22561.918644068</v>
       </c>
       <c r="O230" t="n">
-        <v>58806</v>
+        <v>2030572.67796612</v>
       </c>
       <c r="P230" t="n">
-        <v>2500</v>
+        <v>36500</v>
       </c>
       <c r="Q230" t="n">
-        <v>55000</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>6914919018374</v>
+          <t>C3393</t>
+        </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>CANCHA BASQUET PEQUENA</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -10313,7 +10309,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10322,30 +10318,38 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="N231" t="n">
-        <v>24538.02</v>
+        <v>2673</v>
       </c>
       <c r="O231" t="n">
-        <v>6698879.46</v>
+        <v>58806</v>
       </c>
       <c r="P231" t="n">
-        <v>52900</v>
+        <v>2500</v>
       </c>
       <c r="Q231" t="n">
-        <v>14441700</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C3431</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CUBO MÁGICO</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -10354,7 +10358,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>381</v>
+        <v>273</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10363,30 +10367,30 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>381</v>
+        <v>273</v>
       </c>
       <c r="N232" t="n">
-        <v>2680.739700489</v>
+        <v>24538.02</v>
       </c>
       <c r="O232" t="n">
-        <v>1021361.825886309</v>
+        <v>6698879.46</v>
       </c>
       <c r="P232" t="n">
-        <v>4900</v>
+        <v>52900</v>
       </c>
       <c r="Q232" t="n">
-        <v>1866900</v>
+        <v>14441700</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C3433</t>
+          <t>C3431</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CULEBRA</t>
+          <t>CUBO MÁGICO</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -10395,7 +10399,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>1254</v>
+        <v>381</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10404,30 +10408,30 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>1254</v>
+        <v>381</v>
       </c>
       <c r="N233" t="n">
-        <v>880.32919651056</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O233" t="n">
-        <v>1103932.812424242</v>
+        <v>1021361.825886309</v>
       </c>
       <c r="P233" t="n">
-        <v>1200</v>
+        <v>4900</v>
       </c>
       <c r="Q233" t="n">
-        <v>1504800</v>
+        <v>1866900</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C3434</t>
+          <t>C3433</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DINOSAURIOS MÁGICOS</t>
+          <t>CULEBRA</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -10436,7 +10440,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>244</v>
+        <v>1254</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10445,35 +10449,30 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>244</v>
+        <v>1254</v>
       </c>
       <c r="N234" t="n">
-        <v>6773.76</v>
+        <v>880.32923254206</v>
       </c>
       <c r="O234" t="n">
-        <v>1652797.44</v>
+        <v>1103932.857607743</v>
       </c>
       <c r="P234" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="Q234" t="n">
-        <v>1220000</v>
+        <v>1504800</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C3444</t>
+          <t>C3434</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>COCHE MUNECA GDE C3444</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIOS MÁGICOS</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10482,7 +10481,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>50</v>
+        <v>244</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10491,30 +10490,35 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>50</v>
+        <v>244</v>
       </c>
       <c r="N235" t="n">
-        <v>11431.604880952</v>
+        <v>6773.76</v>
       </c>
       <c r="O235" t="n">
-        <v>571580.2440476</v>
+        <v>1652797.44</v>
       </c>
       <c r="P235" t="n">
-        <v>48900</v>
+        <v>5000</v>
       </c>
       <c r="Q235" t="n">
-        <v>2445000</v>
+        <v>1220000</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C347</t>
+          <t>C3444</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ROMBECABEZAS 3D</t>
+          <t>COCHE MUNECA GDE C3444</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10523,7 +10527,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>2738</v>
+        <v>50</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10532,35 +10536,30 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>2738</v>
+        <v>50</v>
       </c>
       <c r="N236" t="n">
-        <v>1732.9153957286</v>
+        <v>11431.604880952</v>
       </c>
       <c r="O236" t="n">
-        <v>4744722.353504907</v>
+        <v>571580.2440476</v>
       </c>
       <c r="P236" t="n">
-        <v>1900</v>
+        <v>48900</v>
       </c>
       <c r="Q236" t="n">
-        <v>5202200</v>
+        <v>2445000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C3484</t>
+          <t>C347</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>MÁQUINA DE COSER INFANTIL</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ROMBECABEZAS 3D</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10569,7 +10568,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>144</v>
+        <v>2738</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10578,30 +10577,30 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>144</v>
+        <v>2738</v>
       </c>
       <c r="N237" t="n">
-        <v>30611</v>
+        <v>1732.9153957286</v>
       </c>
       <c r="O237" t="n">
-        <v>4407984</v>
+        <v>4744722.353504907</v>
       </c>
       <c r="P237" t="n">
-        <v>38900</v>
+        <v>1900</v>
       </c>
       <c r="Q237" t="n">
-        <v>5601600</v>
+        <v>5202200</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C3485</t>
+          <t>C3484</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>COMPU INF</t>
+          <t>MÁQUINA DE COSER INFANTIL</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10615,7 +10614,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10624,30 +10623,35 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="N238" t="n">
-        <v>56503</v>
+        <v>30611</v>
       </c>
       <c r="O238" t="n">
-        <v>1017054</v>
+        <v>4407984</v>
       </c>
       <c r="P238" t="n">
-        <v>90500</v>
+        <v>38900</v>
       </c>
       <c r="Q238" t="n">
-        <v>1629000</v>
+        <v>5601600</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C3491</t>
+          <t>C3485</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ATARI AGUA DINO</t>
+          <t>COMPU INF</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -10656,7 +10660,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10665,35 +10669,30 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="N239" t="n">
-        <v>1651</v>
+        <v>56503</v>
       </c>
       <c r="O239" t="n">
-        <v>668655</v>
+        <v>1017054</v>
       </c>
       <c r="P239" t="n">
-        <v>2500</v>
+        <v>90500</v>
       </c>
       <c r="Q239" t="n">
-        <v>1012500</v>
+        <v>1629000</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C352</t>
+          <t>C3491</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ROMPECABEZAS 3D</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ATARI AGUA DINO</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -10702,7 +10701,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>523</v>
+        <v>405</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -10711,30 +10710,35 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>523</v>
+        <v>405</v>
       </c>
       <c r="N240" t="n">
-        <v>998.76125816993</v>
+        <v>1651</v>
       </c>
       <c r="O240" t="n">
-        <v>522352.1380228734</v>
+        <v>668655</v>
       </c>
       <c r="P240" t="n">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="Q240" t="n">
-        <v>836800</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C3637</t>
+          <t>C352</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>ROMPECABEZAS 3D</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -10743,7 +10747,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>1</v>
+        <v>523</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -10752,25 +10756,25 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>1</v>
+        <v>523</v>
       </c>
       <c r="N241" t="n">
-        <v>2081.1521621622</v>
+        <v>998.76125816993</v>
       </c>
       <c r="O241" t="n">
-        <v>2081.1521621622</v>
+        <v>522352.1380228734</v>
       </c>
       <c r="P241" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="Q241" t="n">
-        <v>3000</v>
+        <v>836800</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3637</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10778,18 +10782,13 @@
           <t>INFLABLE DONA</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
       <c r="I242" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -10798,25 +10797,25 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="N242" t="n">
-        <v>3877.89</v>
+        <v>2081.1521621622</v>
       </c>
       <c r="O242" t="n">
-        <v>4653468</v>
+        <v>2081.1521621622</v>
       </c>
       <c r="P242" t="n">
-        <v>6500</v>
+        <v>3000</v>
       </c>
       <c r="Q242" t="n">
-        <v>7800000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C3639</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10824,13 +10823,18 @@
           <t>INFLABLE DONA</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
       <c r="J243" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -10839,38 +10843,30 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="N243" t="n">
-        <v>2251.28</v>
+        <v>3877.89</v>
       </c>
       <c r="O243" t="n">
-        <v>2251.28</v>
+        <v>4653468</v>
       </c>
       <c r="P243" t="n">
-        <v>3600</v>
+        <v>6500</v>
       </c>
       <c r="Q243" t="n">
-        <v>3600</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C3642</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>6999899236130</v>
+          <t>C3639</t>
+        </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>INFLABLE DINOSAURIO DONA</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLE DONA</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -10879,7 +10875,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -10888,25 +10884,25 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>390</v>
+        <v>1</v>
       </c>
       <c r="N244" t="n">
-        <v>4285.1952156057</v>
+        <v>2251.28</v>
       </c>
       <c r="O244" t="n">
-        <v>1671226.134086223</v>
+        <v>2251.28</v>
       </c>
       <c r="P244" t="n">
-        <v>6900</v>
+        <v>3600</v>
       </c>
       <c r="Q244" t="n">
-        <v>2691000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C3645</t>
+          <t>C3642</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -10914,7 +10910,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>INFLABLE TECHO PIECITOS</t>
+          <t>INFLABLE DINOSAURIO DONA</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -10928,7 +10924,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -10937,30 +10933,38 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="N245" t="n">
-        <v>9776.99</v>
+        <v>4285.1952263374</v>
       </c>
       <c r="O245" t="n">
-        <v>3167744.76</v>
+        <v>1671226.138271586</v>
       </c>
       <c r="P245" t="n">
-        <v>15900</v>
+        <v>6900</v>
       </c>
       <c r="Q245" t="n">
-        <v>5151600</v>
+        <v>2691000</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C3662</t>
-        </is>
+          <t>C3645</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>6999899236130</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>TERMO INFANTIL</t>
+          <t>INFLABLE TECHO PIECITOS</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10969,7 +10973,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>5</v>
+        <v>324</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -10978,25 +10982,25 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>5</v>
+        <v>324</v>
       </c>
       <c r="N246" t="n">
-        <v>11461.54</v>
+        <v>9776.99</v>
       </c>
       <c r="O246" t="n">
-        <v>57307.7</v>
+        <v>3167744.76</v>
       </c>
       <c r="P246" t="n">
-        <v>14900</v>
+        <v>15900</v>
       </c>
       <c r="Q246" t="n">
-        <v>74500</v>
+        <v>5151600</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C3665</t>
+          <t>C3662</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11010,7 +11014,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>248</v>
+        <v>5</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -11019,25 +11023,25 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>248</v>
+        <v>5</v>
       </c>
       <c r="N247" t="n">
-        <v>12132.858175439</v>
+        <v>11461.54</v>
       </c>
       <c r="O247" t="n">
-        <v>3008948.827508872</v>
+        <v>57307.7</v>
       </c>
       <c r="P247" t="n">
-        <v>15900</v>
+        <v>14900</v>
       </c>
       <c r="Q247" t="n">
-        <v>3943200</v>
+        <v>74500</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C3666</t>
+          <t>C3665</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11051,7 +11055,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>67</v>
+        <v>248</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -11060,30 +11064,30 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>67</v>
+        <v>248</v>
       </c>
       <c r="N248" t="n">
-        <v>11230.77</v>
+        <v>12132.858175439</v>
       </c>
       <c r="O248" t="n">
-        <v>752461.5900000001</v>
+        <v>3008948.827508872</v>
       </c>
       <c r="P248" t="n">
-        <v>14600</v>
+        <v>15900</v>
       </c>
       <c r="Q248" t="n">
-        <v>978200</v>
+        <v>3943200</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C3668</t>
+          <t>C3666</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>PATINETA MEDIANA</t>
+          <t>TERMO INFANTIL</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -11092,7 +11096,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11101,30 +11105,30 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="N249" t="n">
-        <v>8963</v>
+        <v>11230.77</v>
       </c>
       <c r="O249" t="n">
-        <v>2016675</v>
+        <v>752461.5900000001</v>
       </c>
       <c r="P249" t="n">
-        <v>15200</v>
+        <v>14600</v>
       </c>
       <c r="Q249" t="n">
-        <v>3420000</v>
+        <v>978200</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C3670</t>
+          <t>C3668</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>PATINETA DE COLORES PLÁSTICA</t>
+          <t>PATINETA MEDIANA</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -11133,7 +11137,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -11142,30 +11146,30 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="N250" t="n">
-        <v>16275</v>
+        <v>8963</v>
       </c>
       <c r="O250" t="n">
-        <v>1790250</v>
+        <v>2016675</v>
       </c>
       <c r="P250" t="n">
-        <v>27600</v>
+        <v>15200</v>
       </c>
       <c r="Q250" t="n">
-        <v>3036000</v>
+        <v>3420000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C3684</t>
+          <t>C3670</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>AGENDA DINOSAURIO SURTIDA</t>
+          <t>PATINETA DE COLORES PLÁSTICA</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -11174,7 +11178,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11183,30 +11187,30 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="N251" t="n">
-        <v>1430.38</v>
+        <v>16275</v>
       </c>
       <c r="O251" t="n">
-        <v>201683.58</v>
+        <v>1790250</v>
       </c>
       <c r="P251" t="n">
-        <v>4000</v>
+        <v>27600</v>
       </c>
       <c r="Q251" t="n">
-        <v>564000</v>
+        <v>3036000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C3686</t>
+          <t>C3684</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>JUEGO ORGANIZADOR DE BAÑO</t>
+          <t>AGENDA DINOSAURIO SURTIDA</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -11215,7 +11219,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11224,30 +11228,30 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="N252" t="n">
-        <v>96089.827419355</v>
+        <v>1430.38</v>
       </c>
       <c r="O252" t="n">
-        <v>1441347.411290325</v>
+        <v>201683.58</v>
       </c>
       <c r="P252" t="n">
-        <v>133500</v>
+        <v>4000</v>
       </c>
       <c r="Q252" t="n">
-        <v>2002500</v>
+        <v>564000</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C3687</t>
+          <t>C3686</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ORGANIZADORES DE BANO</t>
+          <t>JUEGO ORGANIZADOR DE BAÑO</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -11256,7 +11260,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11265,30 +11269,30 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N253" t="n">
-        <v>78951.191923077</v>
+        <v>96089.827419355</v>
       </c>
       <c r="O253" t="n">
-        <v>1263219.070769232</v>
+        <v>1441347.411290325</v>
       </c>
       <c r="P253" t="n">
-        <v>108000</v>
+        <v>133500</v>
       </c>
       <c r="Q253" t="n">
-        <v>1728000</v>
+        <v>2002500</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>C3688</t>
+          <t>C3687</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Organizador de baños</t>
+          <t>ORGANIZADORES DE BANO</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -11297,7 +11301,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -11306,35 +11310,30 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N254" t="n">
-        <v>77580.701694915</v>
+        <v>78951.191923077</v>
       </c>
       <c r="O254" t="n">
-        <v>2327421.05084745</v>
+        <v>1263219.070769232</v>
       </c>
       <c r="P254" t="n">
-        <v>113900</v>
+        <v>108000</v>
       </c>
       <c r="Q254" t="n">
-        <v>3417000</v>
+        <v>1728000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>C3690</t>
+          <t>C3688</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>BEBÉ LLORÓN QUE CAMINA</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>Organizador de baños</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -11343,7 +11342,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11352,30 +11351,35 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N255" t="n">
-        <v>30244.600034662</v>
+        <v>77580.701694915</v>
       </c>
       <c r="O255" t="n">
-        <v>30244.600034662</v>
+        <v>2327421.05084745</v>
       </c>
       <c r="P255" t="n">
-        <v>48900</v>
+        <v>113900</v>
       </c>
       <c r="Q255" t="n">
-        <v>48900</v>
+        <v>3417000</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>C3694</t>
+          <t>C3690</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MUÑECAS CON VESTIDOS SENCILLA</t>
+          <t>BEBÉ LLORÓN QUE CAMINA</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -11384,7 +11388,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>2394</v>
+        <v>1</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11393,35 +11397,30 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>2394</v>
+        <v>1</v>
       </c>
       <c r="N256" t="n">
-        <v>3591.13</v>
+        <v>30244.600034662</v>
       </c>
       <c r="O256" t="n">
-        <v>8597165.220000001</v>
+        <v>30244.600034662</v>
       </c>
       <c r="P256" t="n">
-        <v>6300</v>
+        <v>48900</v>
       </c>
       <c r="Q256" t="n">
-        <v>15082200</v>
+        <v>48900</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>C3697</t>
+          <t>C3694</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>MUÑECAS CON ACCESORIOS</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECAS CON VESTIDOS SENCILLA</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11430,7 +11429,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>150</v>
+        <v>2394</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11439,30 +11438,30 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>150</v>
+        <v>2394</v>
       </c>
       <c r="N257" t="n">
-        <v>11562.038545455</v>
+        <v>3591.13</v>
       </c>
       <c r="O257" t="n">
-        <v>1734305.78181825</v>
+        <v>8597165.220000001</v>
       </c>
       <c r="P257" t="n">
-        <v>18500</v>
+        <v>6300</v>
       </c>
       <c r="Q257" t="n">
-        <v>2775000</v>
+        <v>15082200</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>C3699</t>
+          <t>C3697</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA</t>
+          <t>MUÑECAS CON ACCESORIOS</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -11476,7 +11475,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -11485,30 +11484,30 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="N258" t="n">
-        <v>12005.159834711</v>
+        <v>11652.839895288</v>
       </c>
       <c r="O258" t="n">
-        <v>1140490.184297545</v>
+        <v>1747925.9842932</v>
       </c>
       <c r="P258" t="n">
-        <v>19500</v>
+        <v>18500</v>
       </c>
       <c r="Q258" t="n">
-        <v>1852500</v>
+        <v>2775000</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3699</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>MUÑECA CON MASCOTA</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11522,7 +11521,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11531,19 +11530,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="N259" t="n">
-        <v>60174</v>
+        <v>12155.852217573</v>
       </c>
       <c r="O259" t="n">
-        <v>180522</v>
+        <v>1154805.960669435</v>
       </c>
       <c r="P259" t="n">
-        <v>96900</v>
+        <v>19500</v>
       </c>
       <c r="Q259" t="n">
-        <v>290700</v>
+        <v>1852500</v>
       </c>
     </row>
     <row r="260">
@@ -12174,10 +12173,10 @@
         <v>360</v>
       </c>
       <c r="N274" t="n">
-        <v>22730.48</v>
+        <v>22817.681329923</v>
       </c>
       <c r="O274" t="n">
-        <v>8182972.8</v>
+        <v>8214365.278772281</v>
       </c>
       <c r="P274" t="n">
         <v>36900</v>
@@ -12829,10 +12828,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3113.8900238095</v>
+        <v>3113.8900239521</v>
       </c>
       <c r="O289" t="n">
-        <v>1348314.380309513</v>
+        <v>1348314.380371259</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13013,10 +13012,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4163.16016</v>
+        <v>4265.5329508197</v>
       </c>
       <c r="O293" t="n">
-        <v>287258.05104</v>
+        <v>294321.7736065593</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13197,10 +13196,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5218.1704646251</v>
+        <v>5218.1704756757</v>
       </c>
       <c r="O297" t="n">
-        <v>2082050.015385415</v>
+        <v>2082050.019794604</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13243,10 +13242,10 @@
         <v>206</v>
       </c>
       <c r="N298" t="n">
-        <v>1595.0095153061</v>
+        <v>1595.0095090439</v>
       </c>
       <c r="O298" t="n">
-        <v>328571.9601530566</v>
+        <v>328571.9588630434</v>
       </c>
       <c r="P298" t="n">
         <v>2600</v>
@@ -13289,10 +13288,10 @@
         <v>601</v>
       </c>
       <c r="N299" t="n">
-        <v>3610.650023015</v>
+        <v>3610.6500232019</v>
       </c>
       <c r="O299" t="n">
-        <v>2170000.663832015</v>
+        <v>2170000.663944342</v>
       </c>
       <c r="P299" t="n">
         <v>5800</v>
@@ -13335,10 +13334,10 @@
         <v>216</v>
       </c>
       <c r="N300" t="n">
-        <v>5194</v>
+        <v>5220.5451448041</v>
       </c>
       <c r="O300" t="n">
-        <v>1121904</v>
+        <v>1127637.751277686</v>
       </c>
       <c r="P300" t="n">
         <v>9000</v>
@@ -13703,10 +13702,10 @@
         <v>384</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.3615095729</v>
+        <v>1664.3613046757</v>
       </c>
       <c r="O308" t="n">
-        <v>639114.8196759936</v>
+        <v>639114.7409954688</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -14393,10 +14392,10 @@
         <v>1145</v>
       </c>
       <c r="N323" t="n">
-        <v>1778.4725043029</v>
+        <v>1778.4725093418</v>
       </c>
       <c r="O323" t="n">
-        <v>2036351.01742682</v>
+        <v>2036351.023196361</v>
       </c>
       <c r="P323" t="n">
         <v>4900</v>
@@ -14703,7 +14702,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -14712,19 +14711,19 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N330" t="n">
         <v>44055</v>
       </c>
       <c r="O330" t="n">
-        <v>5418765</v>
+        <v>5022270</v>
       </c>
       <c r="P330" t="n">
         <v>70900</v>
       </c>
       <c r="Q330" t="n">
-        <v>8720700</v>
+        <v>8082600</v>
       </c>
     </row>
     <row r="331">
@@ -14853,10 +14852,10 @@
         <v>60</v>
       </c>
       <c r="N333" t="n">
-        <v>13687</v>
+        <v>13863.987068966</v>
       </c>
       <c r="O333" t="n">
-        <v>821220</v>
+        <v>831839.22413796</v>
       </c>
       <c r="P333" t="n">
         <v>21900</v>
@@ -15221,10 +15220,10 @@
         <v>28</v>
       </c>
       <c r="N341" t="n">
-        <v>2252.2962193699</v>
+        <v>2252.2963076923</v>
       </c>
       <c r="O341" t="n">
-        <v>63064.2941423572</v>
+        <v>63064.2966153844</v>
       </c>
       <c r="P341" t="n">
         <v>3900</v>
@@ -15403,10 +15402,10 @@
         <v>864</v>
       </c>
       <c r="N345" t="n">
-        <v>2328.1187566293</v>
+        <v>2328.1187536917</v>
       </c>
       <c r="O345" t="n">
-        <v>2011494.605727715</v>
+        <v>2011494.603189629</v>
       </c>
       <c r="P345" t="n">
         <v>4500</v>
@@ -15587,10 +15586,10 @@
         <v>108</v>
       </c>
       <c r="N349" t="n">
-        <v>9003</v>
+        <v>9045.4669811321</v>
       </c>
       <c r="O349" t="n">
-        <v>972324</v>
+        <v>976910.4339622668</v>
       </c>
       <c r="P349" t="n">
         <v>14900</v>
@@ -15996,10 +15995,10 @@
         <v>70</v>
       </c>
       <c r="N358" t="n">
-        <v>4202</v>
+        <v>4223.6597938144</v>
       </c>
       <c r="O358" t="n">
-        <v>294140</v>
+        <v>295656.185567008</v>
       </c>
       <c r="P358" t="n">
         <v>7900</v>
@@ -16134,10 +16133,10 @@
         <v>216</v>
       </c>
       <c r="N361" t="n">
-        <v>5869.1727755511</v>
+        <v>5869.1727610442</v>
       </c>
       <c r="O361" t="n">
-        <v>1267741.319519038</v>
+        <v>1267741.316385547</v>
       </c>
       <c r="P361" t="n">
         <v>9500</v>
@@ -18064,10 +18063,10 @@
         <v>4224</v>
       </c>
       <c r="N403" t="n">
-        <v>1516.0388180509</v>
+        <v>1516.0388166875</v>
       </c>
       <c r="O403" t="n">
-        <v>6403747.967447002</v>
+        <v>6403747.961688</v>
       </c>
       <c r="P403" t="n">
         <v>2300</v>
@@ -18110,10 +18109,10 @@
         <v>1152</v>
       </c>
       <c r="N404" t="n">
-        <v>2458.5135821813</v>
+        <v>2458.5134637046</v>
       </c>
       <c r="O404" t="n">
-        <v>2832207.646672858</v>
+        <v>2832207.510187699</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -18156,10 +18155,10 @@
         <v>480</v>
       </c>
       <c r="N405" t="n">
-        <v>1907.3945816073</v>
+        <v>1946.0906677937</v>
       </c>
       <c r="O405" t="n">
-        <v>915549.3991715041</v>
+        <v>934123.520540976</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18202,10 +18201,10 @@
         <v>576</v>
       </c>
       <c r="N406" t="n">
-        <v>1771.0914183976</v>
+        <v>1796.7129837251</v>
       </c>
       <c r="O406" t="n">
-        <v>1020148.656997018</v>
+        <v>1034906.678625658</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18248,10 +18247,10 @@
         <v>960</v>
       </c>
       <c r="N407" t="n">
-        <v>2079.384280218</v>
+        <v>2095.5452849741</v>
       </c>
       <c r="O407" t="n">
-        <v>1996208.90900928</v>
+        <v>2011723.473575136</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -18294,10 +18293,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1803.0149016773</v>
+        <v>1828.4692441176</v>
       </c>
       <c r="O408" t="n">
-        <v>2423252.027854291</v>
+        <v>2457462.664094055</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18340,10 +18339,10 @@
         <v>144</v>
       </c>
       <c r="N409" t="n">
-        <v>3306.5954716981</v>
+        <v>3306.5954602774</v>
       </c>
       <c r="O409" t="n">
-        <v>476149.7479245264</v>
+        <v>476149.7462799456</v>
       </c>
       <c r="P409" t="n">
         <v>4900</v>
@@ -18386,10 +18385,10 @@
         <v>1440</v>
       </c>
       <c r="N410" t="n">
-        <v>2122.1641716329</v>
+        <v>2137.4820360902</v>
       </c>
       <c r="O410" t="n">
-        <v>3055916.407151376</v>
+        <v>3077974.131969888</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18432,10 +18431,10 @@
         <v>612</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7895881384</v>
+        <v>2108.7897270195</v>
       </c>
       <c r="O411" t="n">
-        <v>1290579.227940701</v>
+        <v>1290579.312935934</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18478,10 +18477,10 @@
         <v>864</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.0839842611</v>
+        <v>2056.0839525344</v>
       </c>
       <c r="O412" t="n">
-        <v>1776456.56240159</v>
+        <v>1776456.534989722</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18524,10 +18523,10 @@
         <v>714</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.5678063672</v>
+        <v>3276.0008772707</v>
       </c>
       <c r="O413" t="n">
-        <v>2302341.41374618</v>
+        <v>2339064.62637128</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18570,10 +18569,10 @@
         <v>1152</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.9314682295</v>
+        <v>1655.9314259144</v>
       </c>
       <c r="O414" t="n">
-        <v>1907633.051400384</v>
+        <v>1907633.002653389</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -18893,10 +18892,10 @@
         <v>50</v>
       </c>
       <c r="N421" t="n">
-        <v>5347.73</v>
+        <v>5414.576625</v>
       </c>
       <c r="O421" t="n">
-        <v>267386.5</v>
+        <v>270728.83125</v>
       </c>
       <c r="P421" t="n">
         <v>9500</v>
@@ -19320,10 +19319,10 @@
         <v>72</v>
       </c>
       <c r="N430" t="n">
-        <v>2682.71</v>
+        <v>2769.7168108108</v>
       </c>
       <c r="O430" t="n">
-        <v>193155.12</v>
+        <v>199419.6103783776</v>
       </c>
       <c r="P430" t="n">
         <v>10900</v>
@@ -19459,10 +19458,10 @@
         <v>1909</v>
       </c>
       <c r="N433" t="n">
-        <v>574.67193864057</v>
+        <v>577.72789151821</v>
       </c>
       <c r="O433" t="n">
-        <v>1097048.730864848</v>
+        <v>1102882.544908263</v>
       </c>
       <c r="P433" t="n">
         <v>800</v>
@@ -19724,10 +19723,10 @@
         <v>1</v>
       </c>
       <c r="N439" t="n">
-        <v>2590.4173043478</v>
+        <v>2733.0090825688</v>
       </c>
       <c r="O439" t="n">
-        <v>2590.4173043478</v>
+        <v>2733.0090825688</v>
       </c>
       <c r="P439" t="n">
         <v>2800</v>
@@ -19814,10 +19813,10 @@
         <v>60</v>
       </c>
       <c r="N441" t="n">
-        <v>6213.51</v>
+        <v>6349.5722627737</v>
       </c>
       <c r="O441" t="n">
-        <v>372810.6</v>
+        <v>380974.335766422</v>
       </c>
       <c r="P441" t="n">
         <v>10300</v>
@@ -19858,10 +19857,10 @@
         <v>1</v>
       </c>
       <c r="N442" t="n">
-        <v>1283.65434375</v>
+        <v>1283.6542902208</v>
       </c>
       <c r="O442" t="n">
-        <v>1283.65434375</v>
+        <v>1283.6542902208</v>
       </c>
       <c r="P442" t="n">
         <v>1900</v>
@@ -20039,10 +20038,10 @@
         <v>7572</v>
       </c>
       <c r="N446" t="n">
-        <v>517.28742027978</v>
+        <v>517.28747614462</v>
       </c>
       <c r="O446" t="n">
-        <v>3916900.346358494</v>
+        <v>3916900.769367062</v>
       </c>
       <c r="P446" t="n">
         <v>900</v>
@@ -20088,10 +20087,10 @@
         <v>504</v>
       </c>
       <c r="N447" t="n">
-        <v>3110.8434146796</v>
+        <v>3110.8433414956</v>
       </c>
       <c r="O447" t="n">
-        <v>1567865.080998518</v>
+        <v>1567865.044113782</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
@@ -20132,10 +20131,10 @@
         <v>1386</v>
       </c>
       <c r="N448" t="n">
-        <v>2030.02</v>
+        <v>2047.4600343643</v>
       </c>
       <c r="O448" t="n">
-        <v>2813607.72</v>
+        <v>2837779.60762892</v>
       </c>
       <c r="P448" t="n">
         <v>3600</v>
@@ -20220,10 +20219,10 @@
         <v>18248</v>
       </c>
       <c r="N450" t="n">
-        <v>703.79546441605</v>
+        <v>704.1779547101401</v>
       </c>
       <c r="O450" t="n">
-        <v>12842859.63466408</v>
+        <v>12849839.31755063</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
@@ -20269,10 +20268,10 @@
         <v>127</v>
       </c>
       <c r="N451" t="n">
-        <v>3182.2510791367</v>
+        <v>3216.9665454545</v>
       </c>
       <c r="O451" t="n">
-        <v>404145.8870503609</v>
+        <v>408554.7512727215</v>
       </c>
       <c r="P451" t="n">
         <v>6900</v>
@@ -20447,10 +20446,10 @@
         <v>501</v>
       </c>
       <c r="N455" t="n">
-        <v>3384.9036995828</v>
+        <v>3442.356096181</v>
       </c>
       <c r="O455" t="n">
-        <v>1695836.753490983</v>
+        <v>1724620.404186681</v>
       </c>
       <c r="P455" t="n">
         <v>4500</v>
@@ -20622,10 +20621,10 @@
         <v>381</v>
       </c>
       <c r="N459" t="n">
-        <v>3629.7161601643</v>
+        <v>3674.9932848233</v>
       </c>
       <c r="O459" t="n">
-        <v>1382921.857022598</v>
+        <v>1400172.441517677</v>
       </c>
       <c r="P459" t="n">
         <v>4900</v>
@@ -20797,10 +20796,10 @@
         <v>2569</v>
       </c>
       <c r="N463" t="n">
-        <v>1595.5193419662</v>
+        <v>1595.51921946</v>
       </c>
       <c r="O463" t="n">
-        <v>4098889.189511168</v>
+        <v>4098888.87479274</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -21214,10 +21213,10 @@
         <v>91</v>
       </c>
       <c r="N472" t="n">
-        <v>2505.7604968944</v>
+        <v>2602.7576774194</v>
       </c>
       <c r="O472" t="n">
-        <v>228024.2052173904</v>
+        <v>236850.9486451654</v>
       </c>
       <c r="P472" t="n">
         <v>3000</v>
@@ -21674,10 +21673,10 @@
         <v>1976</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.9398307595</v>
+        <v>7046.9398305803</v>
       </c>
       <c r="O482" t="n">
-        <v>13924753.10558077</v>
+        <v>13924753.10522667</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
@@ -22145,10 +22144,10 @@
         <v>10</v>
       </c>
       <c r="N492" t="n">
-        <v>2010.71</v>
+        <v>2251.9952</v>
       </c>
       <c r="O492" t="n">
-        <v>20107.1</v>
+        <v>22519.952</v>
       </c>
       <c r="P492" t="n">
         <v>7200</v>
@@ -22230,10 +22229,10 @@
         <v>100</v>
       </c>
       <c r="N494" t="n">
-        <v>704.89680318544</v>
+        <v>714.37850499616</v>
       </c>
       <c r="O494" t="n">
-        <v>70489.68031854401</v>
+        <v>71437.850499616</v>
       </c>
       <c r="P494" t="n">
         <v>900</v>
@@ -22394,10 +22393,10 @@
         <v>357</v>
       </c>
       <c r="N498" t="n">
-        <v>6172.7748154093</v>
+        <v>6172.7748309179</v>
       </c>
       <c r="O498" t="n">
-        <v>2203680.60910112</v>
+        <v>2203680.61463769</v>
       </c>
       <c r="P498" t="n">
         <v>8000</v>
@@ -22561,10 +22560,10 @@
         <v>2463</v>
       </c>
       <c r="N502" t="n">
-        <v>824.64110643805</v>
+        <v>827.85503734979</v>
       </c>
       <c r="O502" t="n">
-        <v>2031091.045156917</v>
+        <v>2039006.956992533</v>
       </c>
       <c r="P502" t="n">
         <v>1000</v>
@@ -22646,10 +22645,10 @@
         <v>1446</v>
       </c>
       <c r="N504" t="n">
-        <v>2489.1752825298</v>
+        <v>2496.9418200728</v>
       </c>
       <c r="O504" t="n">
-        <v>3599347.458538091</v>
+        <v>3610577.871825269</v>
       </c>
       <c r="P504" t="n">
         <v>3000</v>
@@ -22690,10 +22689,10 @@
         <v>499</v>
       </c>
       <c r="N505" t="n">
-        <v>2952.08775</v>
+        <v>2967.9876840215</v>
       </c>
       <c r="O505" t="n">
-        <v>1473091.78725</v>
+        <v>1481025.854326728</v>
       </c>
       <c r="P505" t="n">
         <v>3800</v>
@@ -22734,10 +22733,10 @@
         <v>650</v>
       </c>
       <c r="N506" t="n">
-        <v>3167.0258364312</v>
+        <v>3178.8430970149</v>
       </c>
       <c r="O506" t="n">
-        <v>2058566.79368028</v>
+        <v>2066248.013059685</v>
       </c>
       <c r="P506" t="n">
         <v>4000</v>
@@ -22907,10 +22906,10 @@
         <v>820</v>
       </c>
       <c r="N510" t="n">
-        <v>2988.7998657718</v>
+        <v>2998.8631649832</v>
       </c>
       <c r="O510" t="n">
-        <v>2450815.889932876</v>
+        <v>2459067.795286224</v>
       </c>
       <c r="P510" t="n">
         <v>3800</v>
@@ -23077,10 +23076,10 @@
         <v>478</v>
       </c>
       <c r="N514" t="n">
-        <v>3181.9</v>
+        <v>3192.6751439214</v>
       </c>
       <c r="O514" t="n">
-        <v>1520948.2</v>
+        <v>1526098.718794429</v>
       </c>
       <c r="P514" t="n">
         <v>5100</v>
@@ -23121,10 +23120,10 @@
         <v>5129</v>
       </c>
       <c r="N515" t="n">
-        <v>1794.2879877441</v>
+        <v>1803.5408695029</v>
       </c>
       <c r="O515" t="n">
-        <v>9202903.089139489</v>
+        <v>9250361.119680375</v>
       </c>
       <c r="P515" t="n">
         <v>1600</v>
@@ -23253,10 +23252,10 @@
         <v>68</v>
       </c>
       <c r="N518" t="n">
-        <v>2830.224701087</v>
+        <v>3081.4280769231</v>
       </c>
       <c r="O518" t="n">
-        <v>192455.279673916</v>
+        <v>209537.1092307708</v>
       </c>
       <c r="P518" t="n">
         <v>2400</v>
@@ -23382,10 +23381,10 @@
         <v>1329</v>
       </c>
       <c r="N521" t="n">
-        <v>2523.3377665827</v>
+        <v>2540.4017582418</v>
       </c>
       <c r="O521" t="n">
-        <v>3353515.891788409</v>
+        <v>3376193.936703352</v>
       </c>
       <c r="P521" t="n">
         <v>2800</v>
@@ -23804,10 +23803,10 @@
         <v>69</v>
       </c>
       <c r="N531" t="n">
-        <v>4985.404494382</v>
+        <v>4985.4045627376</v>
       </c>
       <c r="O531" t="n">
-        <v>343992.910112358</v>
+        <v>343992.9148288944</v>
       </c>
       <c r="P531" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O14" t="n">
-        <v>1561756.806563032</v>
+        <v>1557721.267702956</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1046,10 +1046,10 @@
         <v>112</v>
       </c>
       <c r="N16" t="n">
-        <v>2001.2446341463</v>
+        <v>1990.0436022514</v>
       </c>
       <c r="O16" t="n">
-        <v>224139.3990243856</v>
+        <v>222884.8834521568</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6300.2067296512</v>
+        <v>6272.8541860465</v>
       </c>
       <c r="O37" t="n">
-        <v>1360844.653604659</v>
+        <v>1354936.504186044</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -3767,10 +3767,10 @@
         <v>301</v>
       </c>
       <c r="N82" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O82" t="n">
-        <v>1165569.366506024</v>
+        <v>1163566.67</v>
       </c>
       <c r="P82" t="n">
         <v>5500</v>
@@ -3813,10 +3813,10 @@
         <v>131</v>
       </c>
       <c r="N83" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O83" t="n">
-        <v>339284.6878091357</v>
+        <v>337019.77</v>
       </c>
       <c r="P83" t="n">
         <v>4700</v>
@@ -3905,10 +3905,10 @@
         <v>67</v>
       </c>
       <c r="N85" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O85" t="n">
-        <v>174028.7531210177</v>
+        <v>172200.72</v>
       </c>
       <c r="P85" t="n">
         <v>4700</v>
@@ -3944,10 +3944,10 @@
         <v>33</v>
       </c>
       <c r="N86" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O86" t="n">
-        <v>103161.1942360263</v>
+        <v>102778.17</v>
       </c>
       <c r="P86" t="n">
         <v>5500</v>
@@ -3988,10 +3988,10 @@
         <v>72</v>
       </c>
       <c r="N87" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O87" t="n">
-        <v>187034.4810723888</v>
+        <v>184560.48</v>
       </c>
       <c r="P87" t="n">
         <v>4700</v>
@@ -4111,10 +4111,10 @@
         <v>2130</v>
       </c>
       <c r="N90" t="n">
-        <v>2837.5718128026</v>
+        <v>2833</v>
       </c>
       <c r="O90" t="n">
-        <v>6044027.961269538</v>
+        <v>6034290</v>
       </c>
       <c r="P90" t="n">
         <v>3500</v>
@@ -5140,10 +5140,10 @@
         <v>1080</v>
       </c>
       <c r="N114" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O114" t="n">
-        <v>2795424.377952744</v>
+        <v>2788836.565039416</v>
       </c>
       <c r="P114" t="n">
         <v>4500</v>
@@ -5319,10 +5319,10 @@
         <v>75</v>
       </c>
       <c r="N118" t="n">
-        <v>6816.3581538462</v>
+        <v>6713.08</v>
       </c>
       <c r="O118" t="n">
-        <v>511226.861538465</v>
+        <v>503481</v>
       </c>
       <c r="P118" t="n">
         <v>9900</v>
@@ -5733,10 +5733,10 @@
         <v>360</v>
       </c>
       <c r="N127" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O127" t="n">
-        <v>2713905.8662968</v>
+        <v>2702660.4</v>
       </c>
       <c r="P127" t="n">
         <v>13500</v>
@@ -5782,10 +5782,10 @@
         <v>220</v>
       </c>
       <c r="N128" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O128" t="n">
-        <v>1959739.847328252</v>
+        <v>1935120</v>
       </c>
       <c r="P128" t="n">
         <v>14900</v>
@@ -5915,10 +5915,10 @@
         <v>3024</v>
       </c>
       <c r="N131" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O131" t="n">
-        <v>11496436.83452154</v>
+        <v>11478227.06132192</v>
       </c>
       <c r="P131" t="n">
         <v>6200</v>
@@ -5961,10 +5961,10 @@
         <v>1303</v>
       </c>
       <c r="N132" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O132" t="n">
-        <v>4814971.682453118</v>
+        <v>4800252</v>
       </c>
       <c r="P132" t="n">
         <v>6200</v>
@@ -6151,10 +6151,10 @@
         <v>720</v>
       </c>
       <c r="N136" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O136" t="n">
-        <v>873468.2435724</v>
+        <v>866433.6000000001</v>
       </c>
       <c r="P136" t="n">
         <v>1900</v>
@@ -6376,10 +6376,10 @@
         <v>24</v>
       </c>
       <c r="N141" t="n">
-        <v>2286.8353823774</v>
+        <v>2267.048162926</v>
       </c>
       <c r="O141" t="n">
-        <v>54884.0491770576</v>
+        <v>54409.155910224</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
@@ -6555,10 +6555,10 @@
         <v>546</v>
       </c>
       <c r="N145" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O145" t="n">
-        <v>4743626.18181816</v>
+        <v>4729452</v>
       </c>
       <c r="P145" t="n">
         <v>14200</v>
@@ -6911,10 +6911,10 @@
         <v>96</v>
       </c>
       <c r="N153" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O153" t="n">
-        <v>788145.534246576</v>
+        <v>782784</v>
       </c>
       <c r="P153" t="n">
         <v>13500</v>
@@ -7001,10 +7001,10 @@
         <v>15671</v>
       </c>
       <c r="N155" t="n">
-        <v>616.28176305926</v>
+        <v>616.01871898278</v>
       </c>
       <c r="O155" t="n">
-        <v>9657751.508901663</v>
+        <v>9653629.345179146</v>
       </c>
       <c r="P155" t="n">
         <v>800</v>
@@ -7491,10 +7491,10 @@
         <v>73</v>
       </c>
       <c r="N166" t="n">
-        <v>6493.1840890688</v>
+        <v>6441.03</v>
       </c>
       <c r="O166" t="n">
-        <v>474002.4385020224</v>
+        <v>470195.19</v>
       </c>
       <c r="P166" t="n">
         <v>10500</v>
@@ -7660,10 +7660,10 @@
         <v>2655</v>
       </c>
       <c r="N170" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O170" t="n">
-        <v>9719179.74</v>
+        <v>9706573.800000001</v>
       </c>
       <c r="P170" t="n">
         <v>5500</v>
@@ -7840,10 +7840,10 @@
         <v>10357</v>
       </c>
       <c r="N174" t="n">
-        <v>1535.9702761427</v>
+        <v>1532.6290291403</v>
       </c>
       <c r="O174" t="n">
-        <v>15908044.15000994</v>
+        <v>15873438.85480609</v>
       </c>
       <c r="P174" t="n">
         <v>1200</v>
@@ -8142,10 +8142,10 @@
         <v>720</v>
       </c>
       <c r="N181" t="n">
-        <v>1466.9464364982</v>
+        <v>1461.54</v>
       </c>
       <c r="O181" t="n">
-        <v>1056201.434278704</v>
+        <v>1052308.8</v>
       </c>
       <c r="P181" t="n">
         <v>1900</v>
@@ -8274,10 +8274,10 @@
         <v>403</v>
       </c>
       <c r="N184" t="n">
-        <v>2216.939334638</v>
+        <v>2204</v>
       </c>
       <c r="O184" t="n">
-        <v>893426.5518591141</v>
+        <v>888212</v>
       </c>
       <c r="P184" t="n">
         <v>1500</v>
@@ -9265,10 +9265,10 @@
         <v>1729</v>
       </c>
       <c r="N206" t="n">
-        <v>5081.9760320544</v>
+        <v>5067.21</v>
       </c>
       <c r="O206" t="n">
-        <v>8786736.559422057</v>
+        <v>8761206.09</v>
       </c>
       <c r="P206" t="n">
         <v>4200</v>
@@ -9352,10 +9352,10 @@
         <v>1007</v>
       </c>
       <c r="N208" t="n">
-        <v>3319.8424657534</v>
+        <v>3253</v>
       </c>
       <c r="O208" t="n">
-        <v>3343081.363013674</v>
+        <v>3275771</v>
       </c>
       <c r="P208" t="n">
         <v>3900</v>
@@ -9742,10 +9742,10 @@
         <v>384</v>
       </c>
       <c r="N217" t="n">
-        <v>2696.7673085339</v>
+        <v>2661.82</v>
       </c>
       <c r="O217" t="n">
-        <v>1035558.646477018</v>
+        <v>1022138.88</v>
       </c>
       <c r="P217" t="n">
         <v>3200</v>
@@ -9783,10 +9783,10 @@
         <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O218" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="P218" t="n">
         <v>6200</v>
@@ -9824,10 +9824,10 @@
         <v>481</v>
       </c>
       <c r="N219" t="n">
-        <v>2621.3808139535</v>
+        <v>2610</v>
       </c>
       <c r="O219" t="n">
-        <v>1260884.171511634</v>
+        <v>1255410</v>
       </c>
       <c r="P219" t="n">
         <v>3200</v>
@@ -9988,10 +9988,10 @@
         <v>491</v>
       </c>
       <c r="N223" t="n">
-        <v>1979.2819843342</v>
+        <v>1969</v>
       </c>
       <c r="O223" t="n">
-        <v>971827.4543080921</v>
+        <v>966779</v>
       </c>
       <c r="P223" t="n">
         <v>1500</v>
@@ -10029,10 +10029,10 @@
         <v>2</v>
       </c>
       <c r="N224" t="n">
-        <v>2040.34375</v>
+        <v>1958.73</v>
       </c>
       <c r="O224" t="n">
-        <v>4080.6875</v>
+        <v>3917.46</v>
       </c>
       <c r="P224" t="n">
         <v>3400</v>
@@ -10070,10 +10070,10 @@
         <v>576</v>
       </c>
       <c r="N225" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O225" t="n">
-        <v>5079715.139098483</v>
+        <v>5065620.48</v>
       </c>
       <c r="P225" t="n">
         <v>14500</v>
@@ -10239,10 +10239,10 @@
         <v>216</v>
       </c>
       <c r="N229" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O229" t="n">
-        <v>552675.7783939608</v>
+        <v>543719.5199999999</v>
       </c>
       <c r="P229" t="n">
         <v>4200</v>
@@ -10280,10 +10280,10 @@
         <v>90</v>
       </c>
       <c r="N230" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O230" t="n">
-        <v>2030572.67796612</v>
+        <v>2023712.63389827</v>
       </c>
       <c r="P230" t="n">
         <v>36500</v>
@@ -11487,10 +11487,10 @@
         <v>150</v>
       </c>
       <c r="N258" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O258" t="n">
-        <v>1747925.9842932</v>
+        <v>1734305.78010465</v>
       </c>
       <c r="P258" t="n">
         <v>18500</v>
@@ -11533,10 +11533,10 @@
         <v>95</v>
       </c>
       <c r="N259" t="n">
-        <v>12155.852217573</v>
+        <v>12005.159832636</v>
       </c>
       <c r="O259" t="n">
-        <v>1154805.960669435</v>
+        <v>1140490.18410042</v>
       </c>
       <c r="P259" t="n">
         <v>19500</v>
@@ -12173,10 +12173,10 @@
         <v>360</v>
       </c>
       <c r="N274" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O274" t="n">
-        <v>8214365.278772281</v>
+        <v>8182972.8</v>
       </c>
       <c r="P274" t="n">
         <v>36900</v>
@@ -13012,10 +13012,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4265.5329508197</v>
+        <v>4163.1601639344</v>
       </c>
       <c r="O293" t="n">
-        <v>294321.7736065593</v>
+        <v>287258.0513114736</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13334,10 +13334,10 @@
         <v>216</v>
       </c>
       <c r="N300" t="n">
-        <v>5220.5451448041</v>
+        <v>5194</v>
       </c>
       <c r="O300" t="n">
-        <v>1127637.751277686</v>
+        <v>1121904</v>
       </c>
       <c r="P300" t="n">
         <v>9000</v>
@@ -14852,10 +14852,10 @@
         <v>60</v>
       </c>
       <c r="N333" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O333" t="n">
-        <v>831839.22413796</v>
+        <v>821220</v>
       </c>
       <c r="P333" t="n">
         <v>21900</v>
@@ -15586,10 +15586,10 @@
         <v>108</v>
       </c>
       <c r="N349" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O349" t="n">
-        <v>976910.4339622668</v>
+        <v>972324</v>
       </c>
       <c r="P349" t="n">
         <v>14900</v>
@@ -15995,10 +15995,10 @@
         <v>70</v>
       </c>
       <c r="N358" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O358" t="n">
-        <v>295656.185567008</v>
+        <v>294140</v>
       </c>
       <c r="P358" t="n">
         <v>7900</v>
@@ -18155,10 +18155,10 @@
         <v>480</v>
       </c>
       <c r="N405" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O405" t="n">
-        <v>934123.520540976</v>
+        <v>915549.346407456</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18201,10 +18201,10 @@
         <v>576</v>
       </c>
       <c r="N406" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O406" t="n">
-        <v>1034906.678625658</v>
+        <v>1020148.579529856</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18247,10 +18247,10 @@
         <v>960</v>
       </c>
       <c r="N407" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O407" t="n">
-        <v>2011723.473575136</v>
+        <v>1996208.853885984</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -18293,10 +18293,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O408" t="n">
-        <v>2457462.664094055</v>
+        <v>2423252.14023527</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18385,10 +18385,10 @@
         <v>1440</v>
       </c>
       <c r="N410" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O410" t="n">
-        <v>3077974.131969888</v>
+        <v>3055916.328902208</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18523,10 +18523,10 @@
         <v>714</v>
       </c>
       <c r="N413" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O413" t="n">
-        <v>2339064.62637128</v>
+        <v>2302341.502649534</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18892,10 +18892,10 @@
         <v>50</v>
       </c>
       <c r="N421" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O421" t="n">
-        <v>270728.83125</v>
+        <v>267386.5</v>
       </c>
       <c r="P421" t="n">
         <v>9500</v>
@@ -19319,10 +19319,10 @@
         <v>72</v>
       </c>
       <c r="N430" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O430" t="n">
-        <v>199419.6103783776</v>
+        <v>193155.12</v>
       </c>
       <c r="P430" t="n">
         <v>10900</v>
@@ -19458,10 +19458,10 @@
         <v>1909</v>
       </c>
       <c r="N433" t="n">
-        <v>577.72789151821</v>
+        <v>574.67194894975</v>
       </c>
       <c r="O433" t="n">
-        <v>1102882.544908263</v>
+        <v>1097048.750545073</v>
       </c>
       <c r="P433" t="n">
         <v>800</v>
@@ -19723,10 +19723,10 @@
         <v>1</v>
       </c>
       <c r="N439" t="n">
-        <v>2733.0090825688</v>
+        <v>2590.4171559633</v>
       </c>
       <c r="O439" t="n">
-        <v>2733.0090825688</v>
+        <v>2590.4171559633</v>
       </c>
       <c r="P439" t="n">
         <v>2800</v>
@@ -19813,10 +19813,10 @@
         <v>60</v>
       </c>
       <c r="N441" t="n">
-        <v>6349.5722627737</v>
+        <v>6213.51</v>
       </c>
       <c r="O441" t="n">
-        <v>380974.335766422</v>
+        <v>372810.6</v>
       </c>
       <c r="P441" t="n">
         <v>10300</v>
@@ -20131,10 +20131,10 @@
         <v>1386</v>
       </c>
       <c r="N448" t="n">
-        <v>2047.4600343643</v>
+        <v>2030.02</v>
       </c>
       <c r="O448" t="n">
-        <v>2837779.60762892</v>
+        <v>2813607.72</v>
       </c>
       <c r="P448" t="n">
         <v>3600</v>
@@ -20219,10 +20219,10 @@
         <v>18248</v>
       </c>
       <c r="N450" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O450" t="n">
-        <v>12849839.31755063</v>
+        <v>12842859.45755082</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
@@ -20268,10 +20268,10 @@
         <v>127</v>
       </c>
       <c r="N451" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O451" t="n">
-        <v>408554.7512727215</v>
+        <v>404145.8885454557</v>
       </c>
       <c r="P451" t="n">
         <v>6900</v>
@@ -20446,10 +20446,10 @@
         <v>501</v>
       </c>
       <c r="N455" t="n">
-        <v>3442.356096181</v>
+        <v>3384.9037623762</v>
       </c>
       <c r="O455" t="n">
-        <v>1724620.404186681</v>
+        <v>1695836.784950476</v>
       </c>
       <c r="P455" t="n">
         <v>4500</v>
@@ -20621,10 +20621,10 @@
         <v>381</v>
       </c>
       <c r="N459" t="n">
-        <v>3674.9932848233</v>
+        <v>3629.7161122661</v>
       </c>
       <c r="O459" t="n">
-        <v>1400172.441517677</v>
+        <v>1382921.838773384</v>
       </c>
       <c r="P459" t="n">
         <v>4900</v>
@@ -21213,10 +21213,10 @@
         <v>91</v>
       </c>
       <c r="N472" t="n">
-        <v>2602.7576774194</v>
+        <v>2505.760516129</v>
       </c>
       <c r="O472" t="n">
-        <v>236850.9486451654</v>
+        <v>228024.206967739</v>
       </c>
       <c r="P472" t="n">
         <v>3000</v>
@@ -22144,10 +22144,10 @@
         <v>10</v>
       </c>
       <c r="N492" t="n">
-        <v>2251.9952</v>
+        <v>2010.71</v>
       </c>
       <c r="O492" t="n">
-        <v>22519.952</v>
+        <v>20107.1</v>
       </c>
       <c r="P492" t="n">
         <v>7200</v>
@@ -22229,10 +22229,10 @@
         <v>100</v>
       </c>
       <c r="N494" t="n">
-        <v>714.37850499616</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O494" t="n">
-        <v>71437.850499616</v>
+        <v>70489.68946963899</v>
       </c>
       <c r="P494" t="n">
         <v>900</v>
@@ -22560,10 +22560,10 @@
         <v>2463</v>
       </c>
       <c r="N502" t="n">
-        <v>827.85503734979</v>
+        <v>824.64111075024</v>
       </c>
       <c r="O502" t="n">
-        <v>2039006.956992533</v>
+        <v>2031091.055777841</v>
       </c>
       <c r="P502" t="n">
         <v>1000</v>
@@ -22645,10 +22645,10 @@
         <v>1446</v>
       </c>
       <c r="N504" t="n">
-        <v>2496.9418200728</v>
+        <v>2489.1752678107</v>
       </c>
       <c r="O504" t="n">
-        <v>3610577.871825269</v>
+        <v>3599347.437254272</v>
       </c>
       <c r="P504" t="n">
         <v>3000</v>
@@ -22689,10 +22689,10 @@
         <v>499</v>
       </c>
       <c r="N505" t="n">
-        <v>2967.9876840215</v>
+        <v>2952.0877378815</v>
       </c>
       <c r="O505" t="n">
-        <v>1481025.854326728</v>
+        <v>1473091.781202868</v>
       </c>
       <c r="P505" t="n">
         <v>3800</v>
@@ -22733,10 +22733,10 @@
         <v>650</v>
       </c>
       <c r="N506" t="n">
-        <v>3178.8430970149</v>
+        <v>3167.0258208955</v>
       </c>
       <c r="O506" t="n">
-        <v>2066248.013059685</v>
+        <v>2058566.783582075</v>
       </c>
       <c r="P506" t="n">
         <v>4000</v>
@@ -22906,10 +22906,10 @@
         <v>820</v>
       </c>
       <c r="N510" t="n">
-        <v>2998.8631649832</v>
+        <v>2988.7998653199</v>
       </c>
       <c r="O510" t="n">
-        <v>2459067.795286224</v>
+        <v>2450815.889562318</v>
       </c>
       <c r="P510" t="n">
         <v>3800</v>
@@ -23076,10 +23076,10 @@
         <v>478</v>
       </c>
       <c r="N514" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O514" t="n">
-        <v>1526098.718794429</v>
+        <v>1520948.2</v>
       </c>
       <c r="P514" t="n">
         <v>5100</v>
@@ -23120,10 +23120,10 @@
         <v>5129</v>
       </c>
       <c r="N515" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O515" t="n">
-        <v>9250361.119680375</v>
+        <v>9202903.035915855</v>
       </c>
       <c r="P515" t="n">
         <v>1600</v>
@@ -23252,10 +23252,10 @@
         <v>68</v>
       </c>
       <c r="N518" t="n">
-        <v>3081.4280769231</v>
+        <v>2830.2251183432</v>
       </c>
       <c r="O518" t="n">
-        <v>209537.1092307708</v>
+        <v>192455.3080473376</v>
       </c>
       <c r="P518" t="n">
         <v>2400</v>
@@ -23381,10 +23381,10 @@
         <v>1329</v>
       </c>
       <c r="N521" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O521" t="n">
-        <v>3376193.936703352</v>
+        <v>3353515.87171599</v>
       </c>
       <c r="P521" t="n">
         <v>2800</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -603,10 +603,10 @@
         <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.407037037</v>
+        <v>96741.407125</v>
       </c>
       <c r="O5" t="n">
-        <v>5611001.608148146</v>
+        <v>5611001.613249999</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3037996546</v>
+        <v>1811.3039621792</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.267702956</v>
+        <v>1557721.407474112</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1046,10 +1046,10 @@
         <v>112</v>
       </c>
       <c r="N16" t="n">
-        <v>1990.0436022514</v>
+        <v>1990.0435660377</v>
       </c>
       <c r="O16" t="n">
-        <v>222884.8834521568</v>
+        <v>222884.8793962224</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8541860465</v>
+        <v>6272.8542228739</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.504186044</v>
+        <v>1354936.512140762</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -1920,10 +1920,10 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O38" t="n">
-        <v>2548517.299068109</v>
+        <v>2548517.297160438</v>
       </c>
       <c r="P38" t="n">
         <v>4800</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.620000006</v>
+        <v>1271651.544421513</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2123,10 +2123,10 @@
         <v>144</v>
       </c>
       <c r="N43" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O43" t="n">
-        <v>535151.547127152</v>
+        <v>535151.5472126016</v>
       </c>
       <c r="P43" t="n">
         <v>9500</v>
@@ -2594,10 +2594,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>10994.352244898</v>
+        <v>10994.353043478</v>
       </c>
       <c r="O55" t="n">
-        <v>527728.907755104</v>
+        <v>527728.9460869441</v>
       </c>
       <c r="P55" t="n">
         <v>16900</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.966215139</v>
+        <v>15711.9662</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.567490008</v>
+        <v>1131261.5664</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -2764,10 +2764,10 @@
         <v>60</v>
       </c>
       <c r="N59" t="n">
-        <v>30238.812278481</v>
+        <v>30238.812307692</v>
       </c>
       <c r="O59" t="n">
-        <v>1814328.73670886</v>
+        <v>1814328.73846152</v>
       </c>
       <c r="P59" t="n">
         <v>51100</v>
@@ -3009,10 +3009,10 @@
         <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>36306.276</v>
+        <v>36306.278421053</v>
       </c>
       <c r="O65" t="n">
-        <v>435675.312</v>
+        <v>435675.341052636</v>
       </c>
       <c r="P65" t="n">
         <v>64900</v>
@@ -3056,10 +3056,10 @@
         <v>40</v>
       </c>
       <c r="N66" t="n">
-        <v>56906.800422535</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O66" t="n">
-        <v>2276272.0169014</v>
+        <v>2276272.02285716</v>
       </c>
       <c r="P66" t="n">
         <v>95900</v>
@@ -3150,10 +3150,10 @@
         <v>102</v>
       </c>
       <c r="N68" t="n">
-        <v>77455.73771929801</v>
+        <v>77455.737927928</v>
       </c>
       <c r="O68" t="n">
-        <v>7900485.247368396</v>
+        <v>7900485.268648656</v>
       </c>
       <c r="P68" t="n">
         <v>122900</v>
@@ -3197,10 +3197,10 @@
         <v>112</v>
       </c>
       <c r="N69" t="n">
-        <v>141416.88447284</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O69" t="n">
-        <v>15838691.06095808</v>
+        <v>15838691.06744288</v>
       </c>
       <c r="P69" t="n">
         <v>251900</v>
@@ -3375,10 +3375,10 @@
         <v>22</v>
       </c>
       <c r="N73" t="n">
-        <v>344599.17881356</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O73" t="n">
-        <v>7581181.933898319</v>
+        <v>7581181.9334482</v>
       </c>
       <c r="P73" t="n">
         <v>532900</v>
@@ -3684,10 +3684,10 @@
         <v>97</v>
       </c>
       <c r="N80" t="n">
-        <v>61666.873842239</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O80" t="n">
-        <v>5981686.762697184</v>
+        <v>5981686.763647976</v>
       </c>
       <c r="P80" t="n">
         <v>98900</v>
@@ -4198,10 +4198,10 @@
         <v>200</v>
       </c>
       <c r="N92" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O92" t="n">
-        <v>987462.0319071801</v>
+        <v>987462.0320232799</v>
       </c>
       <c r="P92" t="n">
         <v>7500</v>
@@ -4541,10 +4541,10 @@
         <v>157</v>
       </c>
       <c r="N100" t="n">
-        <v>31233.611787072</v>
+        <v>31233.611793893</v>
       </c>
       <c r="O100" t="n">
-        <v>4903677.050570305</v>
+        <v>4903677.051641201</v>
       </c>
       <c r="P100" t="n">
         <v>45500</v>
@@ -5140,10 +5140,10 @@
         <v>1080</v>
       </c>
       <c r="N114" t="n">
-        <v>2582.2560787402</v>
+        <v>2582.2560663507</v>
       </c>
       <c r="O114" t="n">
-        <v>2788836.565039416</v>
+        <v>2788836.551658756</v>
       </c>
       <c r="P114" t="n">
         <v>4500</v>
@@ -6053,10 +6053,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O134" t="n">
-        <v>313019.522942528</v>
+        <v>313019.5229459136</v>
       </c>
       <c r="P134" t="n">
         <v>8200</v>
@@ -6376,10 +6376,10 @@
         <v>24</v>
       </c>
       <c r="N141" t="n">
-        <v>2267.048162926</v>
+        <v>2267.0481598668</v>
       </c>
       <c r="O141" t="n">
-        <v>54409.155910224</v>
+        <v>54409.1558368032</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
@@ -6732,10 +6732,10 @@
         <v>264</v>
       </c>
       <c r="N149" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O149" t="n">
-        <v>948883.1214859128</v>
+        <v>948883.1169230689</v>
       </c>
       <c r="P149" t="n">
         <v>6500</v>
@@ -7039,22 +7039,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="M156" t="n">
-        <v>2243</v>
+        <v>1859</v>
       </c>
       <c r="N156" t="n">
         <v>2090.85</v>
       </c>
       <c r="O156" t="n">
-        <v>4689776.55</v>
+        <v>3886890.15</v>
       </c>
       <c r="P156" t="n">
         <v>2900</v>
       </c>
       <c r="Q156" t="n">
-        <v>6504700</v>
+        <v>5391100</v>
       </c>
     </row>
     <row r="157">
@@ -7360,10 +7360,10 @@
         <v>78</v>
       </c>
       <c r="N163" t="n">
-        <v>3041.6600123457</v>
+        <v>3041.6600124378</v>
       </c>
       <c r="O163" t="n">
-        <v>237249.4809629646</v>
+        <v>237249.4809701484</v>
       </c>
       <c r="P163" t="n">
         <v>5500</v>
@@ -7447,10 +7447,10 @@
         <v>912</v>
       </c>
       <c r="N165" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O165" t="n">
-        <v>3987456.237070671</v>
+        <v>3987456.23712156</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -7840,10 +7840,10 @@
         <v>10357</v>
       </c>
       <c r="N174" t="n">
-        <v>1532.6290291403</v>
+        <v>1532.629028858</v>
       </c>
       <c r="O174" t="n">
-        <v>15873438.85480609</v>
+        <v>15873438.85188231</v>
       </c>
       <c r="P174" t="n">
         <v>1200</v>
@@ -8186,10 +8186,10 @@
         <v>200</v>
       </c>
       <c r="N182" t="n">
-        <v>2021.7211191336</v>
+        <v>2021.7211218335</v>
       </c>
       <c r="O182" t="n">
-        <v>404344.22382672</v>
+        <v>404344.2243667</v>
       </c>
       <c r="P182" t="n">
         <v>2400</v>
@@ -8682,10 +8682,10 @@
         <v>1152</v>
       </c>
       <c r="N193" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O193" t="n">
-        <v>1878823.271679207</v>
+        <v>1878823.318162522</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8728,10 +8728,10 @@
         <v>1152</v>
       </c>
       <c r="N194" t="n">
-        <v>1690.6043069815</v>
+        <v>1690.603799682</v>
       </c>
       <c r="O194" t="n">
-        <v>1947576.161642688</v>
+        <v>1947575.577233664</v>
       </c>
       <c r="P194" t="n">
         <v>2900</v>
@@ -8774,10 +8774,10 @@
         <v>5472</v>
       </c>
       <c r="N195" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O195" t="n">
-        <v>8482655.606738631</v>
+        <v>8482655.7466128</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -8820,10 +8820,10 @@
         <v>2016</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5099727039</v>
+        <v>2403.5100306848</v>
       </c>
       <c r="O196" t="n">
-        <v>4845476.104971062</v>
+        <v>4845476.221860557</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10280,10 +10280,10 @@
         <v>90</v>
       </c>
       <c r="N230" t="n">
-        <v>22485.695932203</v>
+        <v>22485.695927602</v>
       </c>
       <c r="O230" t="n">
-        <v>2023712.63389827</v>
+        <v>2023712.63348418</v>
       </c>
       <c r="P230" t="n">
         <v>36500</v>
@@ -10411,10 +10411,10 @@
         <v>381</v>
       </c>
       <c r="N233" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O233" t="n">
-        <v>1021361.825886309</v>
+        <v>1021361.825676683</v>
       </c>
       <c r="P233" t="n">
         <v>4900</v>
@@ -10452,10 +10452,10 @@
         <v>1254</v>
       </c>
       <c r="N234" t="n">
-        <v>880.32923254206</v>
+        <v>880.32929682061</v>
       </c>
       <c r="O234" t="n">
-        <v>1103932.857607743</v>
+        <v>1103932.938213045</v>
       </c>
       <c r="P234" t="n">
         <v>1200</v>
@@ -10539,10 +10539,10 @@
         <v>50</v>
       </c>
       <c r="N236" t="n">
-        <v>11431.604880952</v>
+        <v>11431.604819277</v>
       </c>
       <c r="O236" t="n">
-        <v>571580.2440476</v>
+        <v>571580.2409638499</v>
       </c>
       <c r="P236" t="n">
         <v>48900</v>
@@ -10580,10 +10580,10 @@
         <v>2738</v>
       </c>
       <c r="N237" t="n">
-        <v>1732.9153957286</v>
+        <v>1732.9153666245</v>
       </c>
       <c r="O237" t="n">
-        <v>4744722.353504907</v>
+        <v>4744722.273817881</v>
       </c>
       <c r="P237" t="n">
         <v>1900</v>
@@ -10936,10 +10936,10 @@
         <v>390</v>
       </c>
       <c r="N245" t="n">
-        <v>4285.1952263374</v>
+        <v>4285.1952479339</v>
       </c>
       <c r="O245" t="n">
-        <v>1671226.138271586</v>
+        <v>1671226.146694221</v>
       </c>
       <c r="P245" t="n">
         <v>6900</v>
@@ -11400,10 +11400,10 @@
         <v>1</v>
       </c>
       <c r="N256" t="n">
-        <v>30244.600034662</v>
+        <v>30244.600034682</v>
       </c>
       <c r="O256" t="n">
-        <v>30244.600034662</v>
+        <v>30244.600034682</v>
       </c>
       <c r="P256" t="n">
         <v>48900</v>
@@ -12219,10 +12219,10 @@
         <v>34</v>
       </c>
       <c r="N275" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O275" t="n">
-        <v>922208.0188148059</v>
+        <v>922208.0185157759</v>
       </c>
       <c r="P275" t="n">
         <v>44500</v>
@@ -12480,10 +12480,10 @@
         <v>480</v>
       </c>
       <c r="N281" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O281" t="n">
-        <v>3825576.078864816</v>
+        <v>3825576.07910112</v>
       </c>
       <c r="P281" t="n">
         <v>12900</v>
@@ -12828,10 +12828,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3113.8900239521</v>
+        <v>3113.8900249066</v>
       </c>
       <c r="O289" t="n">
-        <v>1348314.380371259</v>
+        <v>1348314.380784558</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13012,10 +13012,10 @@
         <v>69</v>
       </c>
       <c r="N293" t="n">
-        <v>4163.1601639344</v>
+        <v>4163.1601724138</v>
       </c>
       <c r="O293" t="n">
-        <v>287258.0513114736</v>
+        <v>287258.0518965522</v>
       </c>
       <c r="P293" t="n">
         <v>6700</v>
@@ -13196,10 +13196,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5218.1704756757</v>
+        <v>5218.1704867257</v>
       </c>
       <c r="O297" t="n">
-        <v>2082050.019794604</v>
+        <v>2082050.024203554</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13242,10 +13242,10 @@
         <v>206</v>
       </c>
       <c r="N298" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="O298" t="n">
-        <v>328571.9588630434</v>
+        <v>328571.956455027</v>
       </c>
       <c r="P298" t="n">
         <v>2600</v>
@@ -13282,22 +13282,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M299" t="n">
-        <v>601</v>
+        <v>541</v>
       </c>
       <c r="N299" t="n">
-        <v>3610.6500232019</v>
+        <v>3610.6500236967</v>
       </c>
       <c r="O299" t="n">
-        <v>2170000.663944342</v>
+        <v>1953361.662819915</v>
       </c>
       <c r="P299" t="n">
         <v>5800</v>
       </c>
       <c r="Q299" t="n">
-        <v>3485800</v>
+        <v>3137800</v>
       </c>
     </row>
     <row r="300">
@@ -13702,10 +13702,10 @@
         <v>384</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.3613046757</v>
+        <v>1664.3609992194</v>
       </c>
       <c r="O308" t="n">
-        <v>639114.7409954688</v>
+        <v>639114.6237002496</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -14392,10 +14392,10 @@
         <v>1145</v>
       </c>
       <c r="N323" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O323" t="n">
-        <v>2036351.023196361</v>
+        <v>2036351.035221495</v>
       </c>
       <c r="P323" t="n">
         <v>4900</v>
@@ -15402,10 +15402,10 @@
         <v>864</v>
       </c>
       <c r="N345" t="n">
-        <v>2328.1187536917</v>
+        <v>2328.1187525865</v>
       </c>
       <c r="O345" t="n">
-        <v>2011494.603189629</v>
+        <v>2011494.602234736</v>
       </c>
       <c r="P345" t="n">
         <v>4500</v>
@@ -16133,10 +16133,10 @@
         <v>216</v>
       </c>
       <c r="N361" t="n">
-        <v>5869.1727610442</v>
+        <v>5869.1727464789</v>
       </c>
       <c r="O361" t="n">
-        <v>1267741.316385547</v>
+        <v>1267741.313239442</v>
       </c>
       <c r="P361" t="n">
         <v>9500</v>
@@ -18063,10 +18063,10 @@
         <v>4224</v>
       </c>
       <c r="N403" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O403" t="n">
-        <v>6403747.961688</v>
+        <v>6403747.949164685</v>
       </c>
       <c r="P403" t="n">
         <v>2300</v>
@@ -18109,10 +18109,10 @@
         <v>1152</v>
       </c>
       <c r="N404" t="n">
-        <v>2458.5134637046</v>
+        <v>2458.5134514107</v>
       </c>
       <c r="O404" t="n">
-        <v>2832207.510187699</v>
+        <v>2832207.496025126</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -18293,10 +18293,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1803.0149852941</v>
+        <v>1803.0149867608</v>
       </c>
       <c r="O408" t="n">
-        <v>2423252.14023527</v>
+        <v>2423252.142206515</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18431,10 +18431,10 @@
         <v>612</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7897270195</v>
+        <v>2108.7897651007</v>
       </c>
       <c r="O411" t="n">
-        <v>1290579.312935934</v>
+        <v>1290579.336241629</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18477,10 +18477,10 @@
         <v>864</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.0839525344</v>
+        <v>2056.0838952972</v>
       </c>
       <c r="O412" t="n">
-        <v>1776456.534989722</v>
+        <v>1776456.485536781</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
@@ -18523,10 +18523,10 @@
         <v>714</v>
       </c>
       <c r="N413" t="n">
-        <v>3224.5679308817</v>
+        <v>3224.5679626335</v>
       </c>
       <c r="O413" t="n">
-        <v>2302341.502649534</v>
+        <v>2302341.525320319</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18569,10 +18569,10 @@
         <v>1152</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.9314259144</v>
+        <v>1655.93135625</v>
       </c>
       <c r="O414" t="n">
-        <v>1907633.002653389</v>
+        <v>1907632.9224</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -19682,10 +19682,10 @@
         <v>912</v>
       </c>
       <c r="N438" t="n">
-        <v>2286.1661853593</v>
+        <v>2286.1661647535</v>
       </c>
       <c r="O438" t="n">
-        <v>2084983.561047682</v>
+        <v>2084983.542255192</v>
       </c>
       <c r="P438" t="n">
         <v>3000</v>
@@ -19857,10 +19857,10 @@
         <v>1</v>
       </c>
       <c r="N442" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="O442" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="P442" t="n">
         <v>1900</v>
@@ -20038,10 +20038,10 @@
         <v>7572</v>
       </c>
       <c r="N446" t="n">
-        <v>517.28747614462</v>
+        <v>517.28760395334</v>
       </c>
       <c r="O446" t="n">
-        <v>3916900.769367062</v>
+        <v>3916901.73713469</v>
       </c>
       <c r="P446" t="n">
         <v>900</v>
@@ -20087,10 +20087,10 @@
         <v>504</v>
       </c>
       <c r="N447" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O447" t="n">
-        <v>1567865.044113782</v>
+        <v>1567865.014139088</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
@@ -20219,10 +20219,10 @@
         <v>18248</v>
       </c>
       <c r="N450" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O450" t="n">
-        <v>12842859.45755082</v>
+        <v>12842859.13039319</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
@@ -20312,10 +20312,10 @@
         <v>50</v>
       </c>
       <c r="N452" t="n">
-        <v>3920.10552</v>
+        <v>3920.1054098361</v>
       </c>
       <c r="O452" t="n">
-        <v>196005.276</v>
+        <v>196005.270491805</v>
       </c>
       <c r="P452" t="n">
         <v>5500</v>
@@ -20621,10 +20621,10 @@
         <v>381</v>
       </c>
       <c r="N459" t="n">
-        <v>3629.7161122661</v>
+        <v>3629.7161041667</v>
       </c>
       <c r="O459" t="n">
-        <v>1382921.838773384</v>
+        <v>1382921.835687513</v>
       </c>
       <c r="P459" t="n">
         <v>4900</v>
@@ -20796,10 +20796,10 @@
         <v>2569</v>
       </c>
       <c r="N463" t="n">
-        <v>1595.51921946</v>
+        <v>1595.5191410878</v>
       </c>
       <c r="O463" t="n">
-        <v>4098888.87479274</v>
+        <v>4098888.673454558</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -21301,10 +21301,10 @@
         <v>4</v>
       </c>
       <c r="N474" t="n">
-        <v>1783.7988878843</v>
+        <v>1783.7988868778</v>
       </c>
       <c r="O474" t="n">
-        <v>7135.1955515372</v>
+        <v>7135.1955475112</v>
       </c>
       <c r="P474" t="n">
         <v>1500</v>
@@ -21673,10 +21673,10 @@
         <v>1976</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O482" t="n">
-        <v>13924753.10522667</v>
+        <v>13924753.10458724</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
@@ -23381,10 +23381,10 @@
         <v>1329</v>
       </c>
       <c r="N521" t="n">
-        <v>2523.3377514793</v>
+        <v>2523.3377476715</v>
       </c>
       <c r="O521" t="n">
-        <v>3353515.87171599</v>
+        <v>3353515.866655423</v>
       </c>
       <c r="P521" t="n">
         <v>2800</v>
@@ -23803,10 +23803,10 @@
         <v>69</v>
       </c>
       <c r="N531" t="n">
-        <v>4985.4045627376</v>
+        <v>4985.4046332046</v>
       </c>
       <c r="O531" t="n">
-        <v>343992.9148288944</v>
+        <v>343992.9196911174</v>
       </c>
       <c r="P531" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -7033,13 +7033,13 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>2243</v>
+        <v>1859</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>1859</v>
@@ -13276,13 +13276,13 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>601</v>
+        <v>541</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
         <v>541</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -597,22 +597,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.407125</v>
+        <v>96741.407307692</v>
       </c>
       <c r="O5" t="n">
-        <v>5611001.613249999</v>
+        <v>5224035.994615369</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
       </c>
       <c r="Q5" t="n">
-        <v>10956200</v>
+        <v>10200600</v>
       </c>
     </row>
     <row r="6">
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3039621792</v>
+        <v>1811.3040256176</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.407474112</v>
+        <v>1557721.462031136</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1085,10 +1085,10 @@
         <v>343</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O17" t="n">
-        <v>1158224.055509429</v>
+        <v>1158224.053574497</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -1836,22 +1836,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M36" t="n">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="N36" t="n">
         <v>3585</v>
       </c>
       <c r="O36" t="n">
-        <v>1032480</v>
+        <v>774360</v>
       </c>
       <c r="P36" t="n">
         <v>4500</v>
       </c>
       <c r="Q36" t="n">
-        <v>1296000</v>
+        <v>972000</v>
       </c>
     </row>
     <row r="37">
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8542228739</v>
+        <v>6272.8542666667</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.512140762</v>
+        <v>1354936.521600007</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -2636,10 +2636,10 @@
         <v>60</v>
       </c>
       <c r="N56" t="n">
-        <v>16486.410204082</v>
+        <v>16486.41</v>
       </c>
       <c r="O56" t="n">
-        <v>989184.61224492</v>
+        <v>989184.6</v>
       </c>
       <c r="P56" t="n">
         <v>30500</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.5664</v>
+        <v>1131261.565301208</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -2758,22 +2758,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M59" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N59" t="n">
-        <v>30238.812307692</v>
+        <v>30238.812337662</v>
       </c>
       <c r="O59" t="n">
-        <v>1814328.73846152</v>
+        <v>1451462.992207776</v>
       </c>
       <c r="P59" t="n">
         <v>51100</v>
       </c>
       <c r="Q59" t="n">
-        <v>3066000</v>
+        <v>2452800</v>
       </c>
     </row>
     <row r="60">
@@ -2811,10 +2811,10 @@
         <v>26</v>
       </c>
       <c r="N60" t="n">
-        <v>13712.849787234</v>
+        <v>13712.847027027</v>
       </c>
       <c r="O60" t="n">
-        <v>356534.094468084</v>
+        <v>356534.022702702</v>
       </c>
       <c r="P60" t="n">
         <v>22600</v>
@@ -3009,10 +3009,10 @@
         <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>36306.278421053</v>
+        <v>36306.281111111</v>
       </c>
       <c r="O65" t="n">
-        <v>435675.341052636</v>
+        <v>435675.373333332</v>
       </c>
       <c r="P65" t="n">
         <v>64900</v>
@@ -3233,22 +3233,22 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M70" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="N70" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O70" t="n">
-        <v>7802815.766808661</v>
+        <v>5401949.39386371</v>
       </c>
       <c r="P70" t="n">
         <v>312000</v>
       </c>
       <c r="Q70" t="n">
-        <v>12168000</v>
+        <v>8424000</v>
       </c>
     </row>
     <row r="71">
@@ -3275,22 +3275,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M71" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>174389.78756757</v>
+        <v>174389.79096774</v>
       </c>
       <c r="O71" t="n">
-        <v>2441457.02594598</v>
+        <v>1046338.74580644</v>
       </c>
       <c r="P71" t="n">
         <v>368200</v>
       </c>
       <c r="Q71" t="n">
-        <v>5154800</v>
+        <v>2209200</v>
       </c>
     </row>
     <row r="72">
@@ -3322,22 +3322,22 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N72" t="n">
         <v>251809.29393939</v>
       </c>
       <c r="O72" t="n">
-        <v>4532567.29090902</v>
+        <v>4028948.70303024</v>
       </c>
       <c r="P72" t="n">
         <v>584000</v>
       </c>
       <c r="Q72" t="n">
-        <v>10512000</v>
+        <v>9344000</v>
       </c>
     </row>
     <row r="73">
@@ -4029,10 +4029,10 @@
         <v>31</v>
       </c>
       <c r="N88" t="n">
-        <v>27450.51804878</v>
+        <v>27450.518024691</v>
       </c>
       <c r="O88" t="n">
-        <v>850966.0595121799</v>
+        <v>850966.0587654209</v>
       </c>
       <c r="P88" t="n">
         <v>40900</v>
@@ -4146,22 +4146,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M91" t="n">
-        <v>12735</v>
+        <v>12585</v>
       </c>
       <c r="N91" t="n">
         <v>1726.32</v>
       </c>
       <c r="O91" t="n">
-        <v>21984685.2</v>
+        <v>21725737.2</v>
       </c>
       <c r="P91" t="n">
         <v>1500</v>
       </c>
       <c r="Q91" t="n">
-        <v>19102500</v>
+        <v>18877500</v>
       </c>
     </row>
     <row r="92">
@@ -5140,10 +5140,10 @@
         <v>1080</v>
       </c>
       <c r="N114" t="n">
-        <v>2582.2560663507</v>
+        <v>2582.256064019</v>
       </c>
       <c r="O114" t="n">
-        <v>2788836.551658756</v>
+        <v>2788836.54914052</v>
       </c>
       <c r="P114" t="n">
         <v>4500</v>
@@ -5595,10 +5595,10 @@
         <v>224</v>
       </c>
       <c r="N124" t="n">
-        <v>2694.8235120643</v>
+        <v>2694.8234975369</v>
       </c>
       <c r="O124" t="n">
-        <v>603640.4667024032</v>
+        <v>603640.4634482656</v>
       </c>
       <c r="P124" t="n">
         <v>4900</v>
@@ -6636,22 +6636,22 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M147" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="N147" t="n">
         <v>10716.34</v>
       </c>
       <c r="O147" t="n">
-        <v>1543152.96</v>
+        <v>1425273.22</v>
       </c>
       <c r="P147" t="n">
         <v>39000</v>
       </c>
       <c r="Q147" t="n">
-        <v>5616000</v>
+        <v>5187000</v>
       </c>
     </row>
     <row r="148">
@@ -6957,10 +6957,10 @@
         <v>432</v>
       </c>
       <c r="N154" t="n">
-        <v>14822.378867925</v>
+        <v>14822.378867257</v>
       </c>
       <c r="O154" t="n">
-        <v>6403267.670943599</v>
+        <v>6403267.670655024</v>
       </c>
       <c r="P154" t="n">
         <v>24900</v>
@@ -7305,22 +7305,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M162" t="n">
-        <v>5529</v>
+        <v>5373</v>
       </c>
       <c r="N162" t="n">
         <v>1441.01</v>
       </c>
       <c r="O162" t="n">
-        <v>7967344.29</v>
+        <v>7742546.73</v>
       </c>
       <c r="P162" t="n">
         <v>2100</v>
       </c>
       <c r="Q162" t="n">
-        <v>11610900</v>
+        <v>11283300</v>
       </c>
     </row>
     <row r="163">
@@ -7360,10 +7360,10 @@
         <v>78</v>
       </c>
       <c r="N163" t="n">
-        <v>3041.6600124378</v>
+        <v>3041.6600124456</v>
       </c>
       <c r="O163" t="n">
-        <v>237249.4809701484</v>
+        <v>237249.4809707568</v>
       </c>
       <c r="P163" t="n">
         <v>5500</v>
@@ -7485,22 +7485,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M166" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
         <v>6441.03</v>
       </c>
       <c r="O166" t="n">
-        <v>470195.19</v>
+        <v>0</v>
       </c>
       <c r="P166" t="n">
         <v>10500</v>
       </c>
       <c r="Q166" t="n">
-        <v>766500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -8317,22 +8317,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M185" t="n">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="N185" t="n">
         <v>3761.6</v>
       </c>
       <c r="O185" t="n">
-        <v>1105910.4</v>
+        <v>895260.7999999999</v>
       </c>
       <c r="P185" t="n">
         <v>6900</v>
       </c>
       <c r="Q185" t="n">
-        <v>2028600</v>
+        <v>1642200</v>
       </c>
     </row>
     <row r="186">
@@ -8682,10 +8682,10 @@
         <v>1152</v>
       </c>
       <c r="N193" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O193" t="n">
-        <v>1878823.318162522</v>
+        <v>1878823.342918195</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8722,22 +8722,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="M194" t="n">
-        <v>1152</v>
+        <v>768</v>
       </c>
       <c r="N194" t="n">
-        <v>1690.603799682</v>
+        <v>1690.6035821697</v>
       </c>
       <c r="O194" t="n">
-        <v>1947575.577233664</v>
+        <v>1298383.55110633</v>
       </c>
       <c r="P194" t="n">
         <v>2900</v>
       </c>
       <c r="Q194" t="n">
-        <v>3340800</v>
+        <v>2227200</v>
       </c>
     </row>
     <row r="195">
@@ -8774,10 +8774,10 @@
         <v>5472</v>
       </c>
       <c r="N195" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O195" t="n">
-        <v>8482655.7466128</v>
+        <v>8482655.865710333</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -8820,10 +8820,10 @@
         <v>2016</v>
       </c>
       <c r="N196" t="n">
-        <v>2403.5100306848</v>
+        <v>2403.5100778841</v>
       </c>
       <c r="O196" t="n">
-        <v>4845476.221860557</v>
+        <v>4845476.317014346</v>
       </c>
       <c r="P196" t="n">
         <v>3500</v>
@@ -10110,22 +10110,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M226" t="n">
-        <v>1164</v>
+        <v>864</v>
       </c>
       <c r="N226" t="n">
         <v>2567</v>
       </c>
       <c r="O226" t="n">
-        <v>2987988</v>
+        <v>2217888</v>
       </c>
       <c r="P226" t="n">
         <v>4500</v>
       </c>
       <c r="Q226" t="n">
-        <v>5238000</v>
+        <v>3888000</v>
       </c>
     </row>
     <row r="227">
@@ -10452,10 +10452,10 @@
         <v>1254</v>
       </c>
       <c r="N234" t="n">
-        <v>880.32929682061</v>
+        <v>880.32931844615</v>
       </c>
       <c r="O234" t="n">
-        <v>1103932.938213045</v>
+        <v>1103932.965331472</v>
       </c>
       <c r="P234" t="n">
         <v>1200</v>
@@ -12828,10 +12828,10 @@
         <v>433</v>
       </c>
       <c r="N289" t="n">
-        <v>3113.8900249066</v>
+        <v>3113.8900261438</v>
       </c>
       <c r="O289" t="n">
-        <v>1348314.380784558</v>
+        <v>1348314.381320265</v>
       </c>
       <c r="P289" t="n">
         <v>5000</v>
@@ -13196,10 +13196,10 @@
         <v>399</v>
       </c>
       <c r="N297" t="n">
-        <v>5218.1704867257</v>
+        <v>5218.170490524</v>
       </c>
       <c r="O297" t="n">
-        <v>2082050.024203554</v>
+        <v>2082050.025719076</v>
       </c>
       <c r="P297" t="n">
         <v>8500</v>
@@ -13242,10 +13242,10 @@
         <v>206</v>
       </c>
       <c r="N298" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="O298" t="n">
-        <v>328571.956455027</v>
+        <v>328571.954216219</v>
       </c>
       <c r="P298" t="n">
         <v>2600</v>
@@ -13288,10 +13288,10 @@
         <v>541</v>
       </c>
       <c r="N299" t="n">
-        <v>3610.6500236967</v>
+        <v>3610.6500238379</v>
       </c>
       <c r="O299" t="n">
-        <v>1953361.662819915</v>
+        <v>1953361.662896304</v>
       </c>
       <c r="P299" t="n">
         <v>5800</v>
@@ -13702,10 +13702,10 @@
         <v>384</v>
       </c>
       <c r="N308" t="n">
-        <v>1664.3609992194</v>
+        <v>1664.360841938</v>
       </c>
       <c r="O308" t="n">
-        <v>639114.6237002496</v>
+        <v>639114.563304192</v>
       </c>
       <c r="P308" t="n">
         <v>2900</v>
@@ -13742,22 +13742,22 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M309" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N309" t="n">
         <v>15502</v>
       </c>
       <c r="O309" t="n">
-        <v>1395180</v>
+        <v>930120</v>
       </c>
       <c r="P309" t="n">
         <v>25900</v>
       </c>
       <c r="Q309" t="n">
-        <v>2331000</v>
+        <v>1554000</v>
       </c>
     </row>
     <row r="310">
@@ -14392,10 +14392,10 @@
         <v>1145</v>
       </c>
       <c r="N323" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O323" t="n">
-        <v>2036351.035221495</v>
+        <v>2036351.038974003</v>
       </c>
       <c r="P323" t="n">
         <v>4900</v>
@@ -15220,10 +15220,10 @@
         <v>28</v>
       </c>
       <c r="N341" t="n">
-        <v>2252.2963076923</v>
+        <v>2252.2963603819</v>
       </c>
       <c r="O341" t="n">
-        <v>63064.2966153844</v>
+        <v>63064.29809069319</v>
       </c>
       <c r="P341" t="n">
         <v>3900</v>
@@ -16869,10 +16869,10 @@
         <v>192</v>
       </c>
       <c r="N377" t="n">
-        <v>17075.98952512</v>
+        <v>17075.989524793</v>
       </c>
       <c r="O377" t="n">
-        <v>3278589.98882304</v>
+        <v>3278589.988760256</v>
       </c>
       <c r="P377" t="n">
         <v>27500</v>
@@ -17229,22 +17229,22 @@
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M385" t="n">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="N385" t="n">
         <v>10755</v>
       </c>
       <c r="O385" t="n">
-        <v>3215745</v>
+        <v>2893095</v>
       </c>
       <c r="P385" t="n">
         <v>17900</v>
       </c>
       <c r="Q385" t="n">
-        <v>5352100</v>
+        <v>4815100</v>
       </c>
     </row>
     <row r="386">
@@ -17459,22 +17459,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M390" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="N390" t="n">
         <v>16282</v>
       </c>
       <c r="O390" t="n">
-        <v>504742</v>
+        <v>16282</v>
       </c>
       <c r="P390" t="n">
         <v>27900</v>
       </c>
       <c r="Q390" t="n">
-        <v>864900</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="391">
@@ -17827,22 +17827,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M398" t="n">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="N398" t="n">
         <v>4118</v>
       </c>
       <c r="O398" t="n">
-        <v>827718</v>
+        <v>452980</v>
       </c>
       <c r="P398" t="n">
         <v>6900</v>
       </c>
       <c r="Q398" t="n">
-        <v>1386900</v>
+        <v>759000</v>
       </c>
     </row>
     <row r="399">
@@ -17965,22 +17965,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M401" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N401" t="n">
         <v>64612</v>
       </c>
       <c r="O401" t="n">
-        <v>1550688</v>
+        <v>0</v>
       </c>
       <c r="P401" t="n">
         <v>103900</v>
       </c>
       <c r="Q401" t="n">
-        <v>2493600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -18011,22 +18011,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M402" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="N402" t="n">
         <v>38252</v>
       </c>
       <c r="O402" t="n">
-        <v>1377072</v>
+        <v>918048</v>
       </c>
       <c r="P402" t="n">
         <v>61900</v>
       </c>
       <c r="Q402" t="n">
-        <v>2228400</v>
+        <v>1485600</v>
       </c>
     </row>
     <row r="403">
@@ -18063,10 +18063,10 @@
         <v>4224</v>
       </c>
       <c r="N403" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O403" t="n">
-        <v>6403747.949164685</v>
+        <v>6403747.946748979</v>
       </c>
       <c r="P403" t="n">
         <v>2300</v>
@@ -18201,10 +18201,10 @@
         <v>576</v>
       </c>
       <c r="N406" t="n">
-        <v>1771.091283906</v>
+        <v>1771.0912628399</v>
       </c>
       <c r="O406" t="n">
-        <v>1020148.579529856</v>
+        <v>1020148.567395782</v>
       </c>
       <c r="P406" t="n">
         <v>2500</v>
@@ -18247,10 +18247,10 @@
         <v>960</v>
       </c>
       <c r="N407" t="n">
-        <v>2079.3842227979</v>
+        <v>2079.3842209265</v>
       </c>
       <c r="O407" t="n">
-        <v>1996208.853885984</v>
+        <v>1996208.85208944</v>
       </c>
       <c r="P407" t="n">
         <v>2900</v>
@@ -18293,10 +18293,10 @@
         <v>1344</v>
       </c>
       <c r="N408" t="n">
-        <v>1803.0149867608</v>
+        <v>1803.0149882284</v>
       </c>
       <c r="O408" t="n">
-        <v>2423252.142206515</v>
+        <v>2423252.144178969</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18339,10 +18339,10 @@
         <v>144</v>
       </c>
       <c r="N409" t="n">
-        <v>3306.5954602774</v>
+        <v>3306.5954545455</v>
       </c>
       <c r="O409" t="n">
-        <v>476149.7462799456</v>
+        <v>476149.745454552</v>
       </c>
       <c r="P409" t="n">
         <v>4900</v>
@@ -18385,10 +18385,10 @@
         <v>1440</v>
       </c>
       <c r="N410" t="n">
-        <v>2122.1641172932</v>
+        <v>2122.1641155235</v>
       </c>
       <c r="O410" t="n">
-        <v>3055916.328902208</v>
+        <v>3055916.32635384</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18431,10 +18431,10 @@
         <v>612</v>
       </c>
       <c r="N411" t="n">
-        <v>2108.7897651007</v>
+        <v>2108.7897869955</v>
       </c>
       <c r="O411" t="n">
-        <v>1290579.336241629</v>
+        <v>1290579.349641246</v>
       </c>
       <c r="P411" t="n">
         <v>2900</v>
@@ -18471,22 +18471,22 @@
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M412" t="n">
-        <v>864</v>
+        <v>684</v>
       </c>
       <c r="N412" t="n">
-        <v>2056.0838952972</v>
+        <v>2056.0838880663</v>
       </c>
       <c r="O412" t="n">
-        <v>1776456.485536781</v>
+        <v>1406361.379437349</v>
       </c>
       <c r="P412" t="n">
         <v>2900</v>
       </c>
       <c r="Q412" t="n">
-        <v>2505600</v>
+        <v>1983600</v>
       </c>
     </row>
     <row r="413">
@@ -18569,10 +18569,10 @@
         <v>1152</v>
       </c>
       <c r="N414" t="n">
-        <v>1655.93135625</v>
+        <v>1655.931342723</v>
       </c>
       <c r="O414" t="n">
-        <v>1907632.9224</v>
+        <v>1907632.906816896</v>
       </c>
       <c r="P414" t="n">
         <v>2500</v>
@@ -19030,10 +19030,10 @@
         <v>1400</v>
       </c>
       <c r="N424" t="n">
-        <v>1185.3195720165</v>
+        <v>1185.3195716639</v>
       </c>
       <c r="O424" t="n">
-        <v>1659447.4008231</v>
+        <v>1659447.40032946</v>
       </c>
       <c r="P424" t="n">
         <v>1900</v>
@@ -19588,22 +19588,22 @@
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M436" t="n">
-        <v>676</v>
+        <v>554</v>
       </c>
       <c r="N436" t="n">
         <v>1828.64</v>
       </c>
       <c r="O436" t="n">
-        <v>1236160.64</v>
+        <v>1013066.56</v>
       </c>
       <c r="P436" t="n">
         <v>2000</v>
       </c>
       <c r="Q436" t="n">
-        <v>1352000</v>
+        <v>1108000</v>
       </c>
     </row>
     <row r="437">
@@ -19676,22 +19676,22 @@
         <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="M438" t="n">
-        <v>912</v>
+        <v>216</v>
       </c>
       <c r="N438" t="n">
-        <v>2286.1661647535</v>
+        <v>2286.1649330955</v>
       </c>
       <c r="O438" t="n">
-        <v>2084983.542255192</v>
+        <v>493811.625548628</v>
       </c>
       <c r="P438" t="n">
         <v>3000</v>
       </c>
       <c r="Q438" t="n">
-        <v>2736000</v>
+        <v>648000</v>
       </c>
     </row>
     <row r="439">
@@ -20038,10 +20038,10 @@
         <v>7572</v>
       </c>
       <c r="N446" t="n">
-        <v>517.28760395334</v>
+        <v>517.28764753291</v>
       </c>
       <c r="O446" t="n">
-        <v>3916901.73713469</v>
+        <v>3916902.067119195</v>
       </c>
       <c r="P446" t="n">
         <v>900</v>
@@ -20087,10 +20087,10 @@
         <v>504</v>
       </c>
       <c r="N447" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O447" t="n">
-        <v>1567865.014139088</v>
+        <v>1567864.956551998</v>
       </c>
       <c r="P447" t="n">
         <v>4500</v>
@@ -20219,10 +20219,10 @@
         <v>18248</v>
       </c>
       <c r="N450" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O450" t="n">
-        <v>12842859.13039319</v>
+        <v>12842858.92068188</v>
       </c>
       <c r="P450" t="n">
         <v>900</v>
@@ -20268,10 +20268,10 @@
         <v>127</v>
       </c>
       <c r="N451" t="n">
-        <v>3182.2510909091</v>
+        <v>3182.2510928962</v>
       </c>
       <c r="O451" t="n">
-        <v>404145.8885454557</v>
+        <v>404145.8887978174</v>
       </c>
       <c r="P451" t="n">
         <v>6900</v>
@@ -20796,10 +20796,10 @@
         <v>2569</v>
       </c>
       <c r="N463" t="n">
-        <v>1595.5191410878</v>
+        <v>1595.5191323094</v>
       </c>
       <c r="O463" t="n">
-        <v>4098888.673454558</v>
+        <v>4098888.650902849</v>
       </c>
       <c r="P463" t="n">
         <v>2500</v>
@@ -21022,22 +21022,22 @@
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M468" t="n">
-        <v>1490</v>
+        <v>1322</v>
       </c>
       <c r="N468" t="n">
         <v>1669.6</v>
       </c>
       <c r="O468" t="n">
-        <v>2487704</v>
+        <v>2207211.2</v>
       </c>
       <c r="P468" t="n">
         <v>2900</v>
       </c>
       <c r="Q468" t="n">
-        <v>4321000</v>
+        <v>3833800</v>
       </c>
     </row>
     <row r="469">
@@ -23797,22 +23797,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M531" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="N531" t="n">
         <v>4985.4046332046</v>
       </c>
       <c r="O531" t="n">
-        <v>343992.9196911174</v>
+        <v>4985.4046332046</v>
       </c>
       <c r="P531" t="n">
         <v>7900</v>
       </c>
       <c r="Q531" t="n">
-        <v>545100</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="532">

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -556,10 +556,10 @@
         <v>258</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>6966000</v>
+        <v>6977110.047846906</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -806,10 +806,10 @@
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>27000</v>
+        <v>31500</v>
       </c>
       <c r="O10" t="n">
-        <v>54000</v>
+        <v>63000</v>
       </c>
       <c r="P10" t="n">
         <v>48900</v>
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3040256176</v>
+        <v>1811.3041548631</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.462031136</v>
+        <v>1557721.573182266</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1085,10 +1085,10 @@
         <v>343</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.746511879</v>
+        <v>3376.7465109371</v>
       </c>
       <c r="O17" t="n">
-        <v>1158224.053574497</v>
+        <v>1158224.053251425</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -1920,10 +1920,10 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O38" t="n">
-        <v>2548517.297160438</v>
+        <v>2548517.295248874</v>
       </c>
       <c r="P38" t="n">
         <v>4800</v>
@@ -2123,10 +2123,10 @@
         <v>144</v>
       </c>
       <c r="N43" t="n">
-        <v>3716.3301889764</v>
+        <v>3716.3301892744</v>
       </c>
       <c r="O43" t="n">
-        <v>535151.5472126016</v>
+        <v>535151.5472555136</v>
       </c>
       <c r="P43" t="n">
         <v>9500</v>
@@ -2396,10 +2396,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="n">
-        <v>21333.69</v>
+        <v>21423.327352941</v>
       </c>
       <c r="O50" t="n">
-        <v>640010.7</v>
+        <v>642699.82058823</v>
       </c>
       <c r="P50" t="n">
         <v>30000</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M55" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>10994.353043478</v>
+        <v>10994.353483146</v>
       </c>
       <c r="O55" t="n">
-        <v>527728.9460869441</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>16900</v>
       </c>
       <c r="Q55" t="n">
-        <v>811200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2636,10 +2636,10 @@
         <v>60</v>
       </c>
       <c r="N56" t="n">
-        <v>16486.41</v>
+        <v>16486.409489051</v>
       </c>
       <c r="O56" t="n">
-        <v>989184.6</v>
+        <v>989184.5693430599</v>
       </c>
       <c r="P56" t="n">
         <v>30500</v>
@@ -2717,10 +2717,10 @@
         <v>72</v>
       </c>
       <c r="N58" t="n">
-        <v>15711.966184739</v>
+        <v>15711.966106557</v>
       </c>
       <c r="O58" t="n">
-        <v>1131261.565301208</v>
+        <v>1131261.559672104</v>
       </c>
       <c r="P58" t="n">
         <v>28500</v>
@@ -2764,10 +2764,10 @@
         <v>48</v>
       </c>
       <c r="N59" t="n">
-        <v>30238.812337662</v>
+        <v>30238.8124</v>
       </c>
       <c r="O59" t="n">
-        <v>1451462.992207776</v>
+        <v>1451462.9952</v>
       </c>
       <c r="P59" t="n">
         <v>51100</v>
@@ -2805,22 +2805,22 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M60" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="N60" t="n">
-        <v>13712.847027027</v>
+        <v>13712.845882353</v>
       </c>
       <c r="O60" t="n">
-        <v>356534.022702702</v>
+        <v>27425.691764706</v>
       </c>
       <c r="P60" t="n">
         <v>22600</v>
       </c>
       <c r="Q60" t="n">
-        <v>587600</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="61">
@@ -2850,10 +2850,10 @@
         <v>184</v>
       </c>
       <c r="N61" t="n">
-        <v>7407.730052356</v>
+        <v>7407.7300524934</v>
       </c>
       <c r="O61" t="n">
-        <v>1363022.329633504</v>
+        <v>1363022.329658786</v>
       </c>
       <c r="P61" t="n">
         <v>10900</v>
@@ -3281,10 +3281,10 @@
         <v>6</v>
       </c>
       <c r="N71" t="n">
-        <v>174389.79096774</v>
+        <v>174389.79241379</v>
       </c>
       <c r="O71" t="n">
-        <v>1046338.74580644</v>
+        <v>1046338.75448274</v>
       </c>
       <c r="P71" t="n">
         <v>368200</v>
@@ -3369,22 +3369,22 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M73" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N73" t="n">
-        <v>344599.1787931</v>
+        <v>344599.17865385</v>
       </c>
       <c r="O73" t="n">
-        <v>7581181.9334482</v>
+        <v>5513586.8584616</v>
       </c>
       <c r="P73" t="n">
         <v>532900</v>
       </c>
       <c r="Q73" t="n">
-        <v>11723800</v>
+        <v>8526400</v>
       </c>
     </row>
     <row r="74">
@@ -3684,10 +3684,10 @@
         <v>97</v>
       </c>
       <c r="N80" t="n">
-        <v>61666.873852041</v>
+        <v>61666.873861893</v>
       </c>
       <c r="O80" t="n">
-        <v>5981686.763647976</v>
+        <v>5981686.764603621</v>
       </c>
       <c r="P80" t="n">
         <v>98900</v>
@@ -4070,10 +4070,10 @@
         <v>1440</v>
       </c>
       <c r="N89" t="n">
-        <v>1950.2152574526</v>
+        <v>1950.2152424105</v>
       </c>
       <c r="O89" t="n">
-        <v>2808309.970731744</v>
+        <v>2808309.94907112</v>
       </c>
       <c r="P89" t="n">
         <v>2900</v>
@@ -4146,22 +4146,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M91" t="n">
-        <v>12585</v>
+        <v>12285</v>
       </c>
       <c r="N91" t="n">
         <v>1726.32</v>
       </c>
       <c r="O91" t="n">
-        <v>21725737.2</v>
+        <v>21207841.2</v>
       </c>
       <c r="P91" t="n">
         <v>1500</v>
       </c>
       <c r="Q91" t="n">
-        <v>18877500</v>
+        <v>18427500</v>
       </c>
     </row>
     <row r="92">
@@ -4198,10 +4198,10 @@
         <v>200</v>
       </c>
       <c r="N92" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="O92" t="n">
-        <v>987462.0320232799</v>
+        <v>987462.0320699799</v>
       </c>
       <c r="P92" t="n">
         <v>7500</v>
@@ -4920,10 +4920,10 @@
         <v>101</v>
       </c>
       <c r="N109" t="n">
-        <v>17207.41</v>
+        <v>17261.351724138</v>
       </c>
       <c r="O109" t="n">
-        <v>1737948.41</v>
+        <v>1743396.524137938</v>
       </c>
       <c r="P109" t="n">
         <v>20000</v>
@@ -5002,10 +5002,10 @@
         <v>5</v>
       </c>
       <c r="N111" t="n">
-        <v>2913</v>
+        <v>2933.514084507</v>
       </c>
       <c r="O111" t="n">
-        <v>14565</v>
+        <v>14667.570422535</v>
       </c>
       <c r="P111" t="n">
         <v>4950</v>
@@ -5048,10 +5048,10 @@
         <v>708</v>
       </c>
       <c r="N112" t="n">
-        <v>2804.33</v>
+        <v>2808.0329005282</v>
       </c>
       <c r="O112" t="n">
-        <v>1985465.64</v>
+        <v>1988087.293573966</v>
       </c>
       <c r="P112" t="n">
         <v>4900</v>
@@ -5088,22 +5088,22 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M113" t="n">
-        <v>468</v>
+        <v>382</v>
       </c>
       <c r="N113" t="n">
         <v>3247</v>
       </c>
       <c r="O113" t="n">
-        <v>1519596</v>
+        <v>1240354</v>
       </c>
       <c r="P113" t="n">
         <v>5200</v>
       </c>
       <c r="Q113" t="n">
-        <v>2433600</v>
+        <v>1986400</v>
       </c>
     </row>
     <row r="114">
@@ -5140,10 +5140,10 @@
         <v>1080</v>
       </c>
       <c r="N114" t="n">
-        <v>2582.256064019</v>
+        <v>2582.2560562265</v>
       </c>
       <c r="O114" t="n">
-        <v>2788836.54914052</v>
+        <v>2788836.54072462</v>
       </c>
       <c r="P114" t="n">
         <v>4500</v>
@@ -5226,22 +5226,22 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M116" t="n">
-        <v>2160</v>
+        <v>2073</v>
       </c>
       <c r="N116" t="n">
         <v>5216.8959875629</v>
       </c>
       <c r="O116" t="n">
-        <v>11268495.33313586</v>
+        <v>10814625.38221789</v>
       </c>
       <c r="P116" t="n">
         <v>8500</v>
       </c>
       <c r="Q116" t="n">
-        <v>18360000</v>
+        <v>17620500</v>
       </c>
     </row>
     <row r="117">
@@ -5365,10 +5365,10 @@
         <v>6298</v>
       </c>
       <c r="N119" t="n">
-        <v>3158.8608137572</v>
+        <v>3158.860813875</v>
       </c>
       <c r="O119" t="n">
-        <v>19894505.40504285</v>
+        <v>19894505.40578475</v>
       </c>
       <c r="P119" t="n">
         <v>5600</v>
@@ -5457,10 +5457,10 @@
         <v>144</v>
       </c>
       <c r="N121" t="n">
-        <v>3841.6246911197</v>
+        <v>3841.6247184466</v>
       </c>
       <c r="O121" t="n">
-        <v>553193.9555212368</v>
+        <v>553193.9594563104</v>
       </c>
       <c r="P121" t="n">
         <v>6900</v>
@@ -5595,10 +5595,10 @@
         <v>224</v>
       </c>
       <c r="N124" t="n">
-        <v>2694.8234975369</v>
+        <v>2694.8234682861</v>
       </c>
       <c r="O124" t="n">
-        <v>603640.4634482656</v>
+        <v>603640.4568960863</v>
       </c>
       <c r="P124" t="n">
         <v>4900</v>
@@ -5828,10 +5828,10 @@
         <v>1081</v>
       </c>
       <c r="N129" t="n">
-        <v>6507</v>
+        <v>6511.2612966601</v>
       </c>
       <c r="O129" t="n">
-        <v>7034067</v>
+        <v>7038673.461689568</v>
       </c>
       <c r="P129" t="n">
         <v>9900</v>
@@ -5915,10 +5915,10 @@
         <v>3024</v>
       </c>
       <c r="N131" t="n">
-        <v>3795.7100070509</v>
+        <v>3795.7100070547</v>
       </c>
       <c r="O131" t="n">
-        <v>11478227.06132192</v>
+        <v>11478227.06133341</v>
       </c>
       <c r="P131" t="n">
         <v>6200</v>
@@ -6053,10 +6053,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>4890.9300460299</v>
+        <v>4890.9300461095</v>
       </c>
       <c r="O134" t="n">
-        <v>313019.5229459136</v>
+        <v>313019.522951008</v>
       </c>
       <c r="P134" t="n">
         <v>8200</v>
@@ -6191,22 +6191,22 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M137" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
         <v>3472</v>
       </c>
       <c r="O137" t="n">
-        <v>2083200</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
         <v>4800</v>
       </c>
       <c r="Q137" t="n">
-        <v>2880000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6463,10 +6463,10 @@
         <v>2452</v>
       </c>
       <c r="N143" t="n">
-        <v>5667.94</v>
+        <v>5672.995244381</v>
       </c>
       <c r="O143" t="n">
-        <v>13897788.88</v>
+        <v>13910184.33922221</v>
       </c>
       <c r="P143" t="n">
         <v>9500</v>
@@ -6555,10 +6555,10 @@
         <v>546</v>
       </c>
       <c r="N145" t="n">
-        <v>8662</v>
+        <v>8688.0641925777</v>
       </c>
       <c r="O145" t="n">
-        <v>4729452</v>
+        <v>4743683.049147424</v>
       </c>
       <c r="P145" t="n">
         <v>14200</v>
@@ -6732,10 +6732,10 @@
         <v>264</v>
       </c>
       <c r="N149" t="n">
-        <v>3594.2542307692</v>
+        <v>3594.254188862</v>
       </c>
       <c r="O149" t="n">
-        <v>948883.1169230689</v>
+        <v>948883.105859568</v>
       </c>
       <c r="P149" t="n">
         <v>6500</v>
@@ -6951,22 +6951,22 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M154" t="n">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="N154" t="n">
         <v>14822.378867257</v>
       </c>
       <c r="O154" t="n">
-        <v>6403267.670655024</v>
+        <v>6047530.577840856</v>
       </c>
       <c r="P154" t="n">
         <v>24900</v>
       </c>
       <c r="Q154" t="n">
-        <v>10756800</v>
+        <v>10159200</v>
       </c>
     </row>
     <row r="155">
@@ -7177,10 +7177,10 @@
         <v>192</v>
       </c>
       <c r="N159" t="n">
-        <v>2665.4</v>
+        <v>2670.3450834879</v>
       </c>
       <c r="O159" t="n">
-        <v>511756.8</v>
+        <v>512706.2560296768</v>
       </c>
       <c r="P159" t="n">
         <v>20900</v>
@@ -7360,10 +7360,10 @@
         <v>78</v>
       </c>
       <c r="N163" t="n">
-        <v>3041.6600124456</v>
+        <v>3041.6600125549</v>
       </c>
       <c r="O163" t="n">
-        <v>237249.4809707568</v>
+        <v>237249.4809792822</v>
       </c>
       <c r="P163" t="n">
         <v>5500</v>
@@ -7447,10 +7447,10 @@
         <v>912</v>
       </c>
       <c r="N165" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O165" t="n">
-        <v>3987456.23712156</v>
+        <v>3987456.23742708</v>
       </c>
       <c r="P165" t="n">
         <v>7500</v>
@@ -7749,22 +7749,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M172" t="n">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="N172" t="n">
         <v>1312.43</v>
       </c>
       <c r="O172" t="n">
-        <v>506597.98</v>
+        <v>309733.48</v>
       </c>
       <c r="P172" t="n">
         <v>2300</v>
       </c>
       <c r="Q172" t="n">
-        <v>887800</v>
+        <v>542800</v>
       </c>
     </row>
     <row r="173">
@@ -8051,22 +8051,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M179" t="n">
-        <v>10164</v>
+        <v>9876</v>
       </c>
       <c r="N179" t="n">
         <v>1387.55</v>
       </c>
       <c r="O179" t="n">
-        <v>14103058.2</v>
+        <v>13703443.8</v>
       </c>
       <c r="P179" t="n">
         <v>2300</v>
       </c>
       <c r="Q179" t="n">
-        <v>23377200</v>
+        <v>22714800</v>
       </c>
     </row>
     <row r="180">
@@ -8638,10 +8638,10 @@
         <v>1152</v>
       </c>
       <c r="N192" t="n">
-        <v>1630.9230407276</v>
+        <v>1630.9230521929</v>
       </c>
       <c r="O192" t="n">
-        <v>1878823.342918195</v>
+        <v>1878823.356126221</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8684,10 +8684,10 @@
         <v>768</v>
       </c>
       <c r="N193" t="n">
-        <v>1690.6035821697</v>
+        <v>1690.6034846029</v>
       </c>
       <c r="O193" t="n">
-        <v>1298383.55110633</v>
+        <v>1298383.476175027</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8730,10 +8730,10 @@
         <v>5472</v>
       </c>
       <c r="N194" t="n">
-        <v>1550.1929579149</v>
+        <v>1550.1930031561</v>
       </c>
       <c r="O194" t="n">
-        <v>8482655.865710333</v>
+        <v>8482656.11327018</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -8776,10 +8776,10 @@
         <v>2016</v>
       </c>
       <c r="N195" t="n">
-        <v>2403.5100778841</v>
+        <v>2403.5101337902</v>
       </c>
       <c r="O195" t="n">
-        <v>4845476.317014346</v>
+        <v>4845476.429721043</v>
       </c>
       <c r="P195" t="n">
         <v>3500</v>
@@ -9267,10 +9267,10 @@
         <v>83</v>
       </c>
       <c r="N206" t="n">
-        <v>10034.5</v>
+        <v>10089.035326087</v>
       </c>
       <c r="O206" t="n">
-        <v>832863.5</v>
+        <v>837389.932065221</v>
       </c>
       <c r="P206" t="n">
         <v>12900</v>
@@ -9698,10 +9698,10 @@
         <v>384</v>
       </c>
       <c r="N216" t="n">
-        <v>2661.82</v>
+        <v>2673.5203076923</v>
       </c>
       <c r="O216" t="n">
-        <v>1022138.88</v>
+        <v>1026631.798153843</v>
       </c>
       <c r="P216" t="n">
         <v>3200</v>
@@ -9739,10 +9739,10 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>4488</v>
+        <v>4530.3396226415</v>
       </c>
       <c r="O217" t="n">
-        <v>4488</v>
+        <v>4530.3396226415</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -9862,10 +9862,10 @@
         <v>375</v>
       </c>
       <c r="N220" t="n">
-        <v>2916</v>
+        <v>2927.9508196721</v>
       </c>
       <c r="O220" t="n">
-        <v>1093500</v>
+        <v>1097981.557377037</v>
       </c>
       <c r="P220" t="n">
         <v>3200</v>
@@ -10236,10 +10236,10 @@
         <v>90</v>
       </c>
       <c r="N229" t="n">
-        <v>22485.695927602</v>
+        <v>22485.695904437</v>
       </c>
       <c r="O229" t="n">
-        <v>2023712.63348418</v>
+        <v>2023712.63139933</v>
       </c>
       <c r="P229" t="n">
         <v>36500</v>
@@ -10408,10 +10408,10 @@
         <v>1254</v>
       </c>
       <c r="N233" t="n">
-        <v>880.32931844615</v>
+        <v>880.32932278334</v>
       </c>
       <c r="O233" t="n">
-        <v>1103932.965331472</v>
+        <v>1103932.970770308</v>
       </c>
       <c r="P233" t="n">
         <v>1200</v>
@@ -10715,10 +10715,10 @@
         <v>523</v>
       </c>
       <c r="N240" t="n">
-        <v>998.76125816993</v>
+        <v>998.76125988546</v>
       </c>
       <c r="O240" t="n">
-        <v>522352.1380228734</v>
+        <v>522352.1389200956</v>
       </c>
       <c r="P240" t="n">
         <v>1600</v>
@@ -11356,10 +11356,10 @@
         <v>1</v>
       </c>
       <c r="N255" t="n">
-        <v>30244.600034682</v>
+        <v>30262.092573742</v>
       </c>
       <c r="O255" t="n">
-        <v>30244.600034682</v>
+        <v>30262.092573742</v>
       </c>
       <c r="P255" t="n">
         <v>48900</v>
@@ -11397,10 +11397,10 @@
         <v>2394</v>
       </c>
       <c r="N256" t="n">
-        <v>3591.13</v>
+        <v>3592.9712903777</v>
       </c>
       <c r="O256" t="n">
-        <v>8597165.220000001</v>
+        <v>8601573.269164214</v>
       </c>
       <c r="P256" t="n">
         <v>6300</v>
@@ -11443,10 +11443,10 @@
         <v>150</v>
       </c>
       <c r="N257" t="n">
-        <v>11562.038534031</v>
+        <v>11562.038530184</v>
       </c>
       <c r="O257" t="n">
-        <v>1734305.78010465</v>
+        <v>1734305.7795276</v>
       </c>
       <c r="P257" t="n">
         <v>18500</v>
@@ -11945,10 +11945,10 @@
         <v>30</v>
       </c>
       <c r="N269" t="n">
-        <v>21418.04</v>
+        <v>21897.548358209</v>
       </c>
       <c r="O269" t="n">
-        <v>642541.2000000001</v>
+        <v>656926.4507462699</v>
       </c>
       <c r="P269" t="n">
         <v>34900</v>
@@ -12262,10 +12262,10 @@
         <v>85</v>
       </c>
       <c r="N276" t="n">
-        <v>4100.45</v>
+        <v>4107.7418494369</v>
       </c>
       <c r="O276" t="n">
-        <v>348538.25</v>
+        <v>349158.0572021366</v>
       </c>
       <c r="P276" t="n">
         <v>26900</v>
@@ -12477,10 +12477,10 @@
         <v>12</v>
       </c>
       <c r="N281" t="n">
-        <v>9994.7101428571</v>
+        <v>9994.7101470588</v>
       </c>
       <c r="O281" t="n">
-        <v>119936.5217142852</v>
+        <v>119936.5217647056</v>
       </c>
       <c r="P281" t="n">
         <v>20800</v>
@@ -12564,10 +12564,10 @@
         <v>78</v>
       </c>
       <c r="N283" t="n">
-        <v>12981.59</v>
+        <v>13028.454945848</v>
       </c>
       <c r="O283" t="n">
-        <v>1012564.02</v>
+        <v>1016219.485776144</v>
       </c>
       <c r="P283" t="n">
         <v>21900</v>
@@ -12610,10 +12610,10 @@
         <v>84</v>
       </c>
       <c r="N284" t="n">
-        <v>13878.97</v>
+        <v>13925.387959866</v>
       </c>
       <c r="O284" t="n">
-        <v>1165833.48</v>
+        <v>1169732.588628744</v>
       </c>
       <c r="P284" t="n">
         <v>21900</v>
@@ -13152,10 +13152,10 @@
         <v>399</v>
       </c>
       <c r="N296" t="n">
-        <v>5218.170490524</v>
+        <v>5218.1704988662</v>
       </c>
       <c r="O296" t="n">
-        <v>2082050.025719076</v>
+        <v>2082050.029047614</v>
       </c>
       <c r="P296" t="n">
         <v>8500</v>
@@ -13198,10 +13198,10 @@
         <v>206</v>
       </c>
       <c r="N297" t="n">
-        <v>1595.0094864865</v>
+        <v>1595.0094843962</v>
       </c>
       <c r="O297" t="n">
-        <v>328571.954216219</v>
+        <v>328571.9537856172</v>
       </c>
       <c r="P297" t="n">
         <v>2600</v>
@@ -13244,10 +13244,10 @@
         <v>541</v>
       </c>
       <c r="N298" t="n">
-        <v>3610.6500238379</v>
+        <v>3610.6500238663</v>
       </c>
       <c r="O298" t="n">
-        <v>1953361.662896304</v>
+        <v>1953361.662911668</v>
       </c>
       <c r="P298" t="n">
         <v>5800</v>
@@ -13658,10 +13658,10 @@
         <v>384</v>
       </c>
       <c r="N307" t="n">
-        <v>1664.360841938</v>
+        <v>1664.3605954323</v>
       </c>
       <c r="O307" t="n">
-        <v>639114.563304192</v>
+        <v>639114.4686460032</v>
       </c>
       <c r="P307" t="n">
         <v>2900</v>
@@ -14348,10 +14348,10 @@
         <v>1145</v>
       </c>
       <c r="N322" t="n">
-        <v>1778.4725231214</v>
+        <v>1778.4725400058</v>
       </c>
       <c r="O322" t="n">
-        <v>2036351.038974003</v>
+        <v>2036351.058306641</v>
       </c>
       <c r="P322" t="n">
         <v>4900</v>
@@ -14532,10 +14532,10 @@
         <v>720</v>
       </c>
       <c r="N326" t="n">
-        <v>16058</v>
+        <v>16069.364472753</v>
       </c>
       <c r="O326" t="n">
-        <v>11561760</v>
+        <v>11569942.42038216</v>
       </c>
       <c r="P326" t="n">
         <v>25900</v>
@@ -15588,10 +15588,10 @@
         <v>162</v>
       </c>
       <c r="N349" t="n">
-        <v>9178</v>
+        <v>9197.9305103149</v>
       </c>
       <c r="O349" t="n">
-        <v>1486836</v>
+        <v>1490064.742671014</v>
       </c>
       <c r="P349" t="n">
         <v>14900</v>
@@ -15772,10 +15772,10 @@
         <v>16</v>
       </c>
       <c r="N353" t="n">
-        <v>100129</v>
+        <v>105398.94736842</v>
       </c>
       <c r="O353" t="n">
-        <v>1602064</v>
+        <v>1686383.15789472</v>
       </c>
       <c r="P353" t="n">
         <v>159900</v>
@@ -15818,10 +15818,10 @@
         <v>120</v>
       </c>
       <c r="N354" t="n">
-        <v>76839</v>
+        <v>77344.519736842</v>
       </c>
       <c r="O354" t="n">
-        <v>9220680</v>
+        <v>9281342.36842104</v>
       </c>
       <c r="P354" t="n">
         <v>122900</v>
@@ -16779,10 +16779,10 @@
         <v>120</v>
       </c>
       <c r="N375" t="n">
-        <v>17992</v>
+        <v>18015.037131882</v>
       </c>
       <c r="O375" t="n">
-        <v>2159040</v>
+        <v>2161804.45582584</v>
       </c>
       <c r="P375" t="n">
         <v>28900</v>
@@ -16825,10 +16825,10 @@
         <v>192</v>
       </c>
       <c r="N376" t="n">
-        <v>17075.989524793</v>
+        <v>17075.989524138</v>
       </c>
       <c r="O376" t="n">
-        <v>3278589.988760256</v>
+        <v>3278589.988634496</v>
       </c>
       <c r="P376" t="n">
         <v>27500</v>
@@ -17421,10 +17421,10 @@
         <v>1</v>
       </c>
       <c r="N389" t="n">
-        <v>16282</v>
+        <v>16694.202531646</v>
       </c>
       <c r="O389" t="n">
-        <v>16282</v>
+        <v>16694.202531646</v>
       </c>
       <c r="P389" t="n">
         <v>27900</v>
@@ -17513,10 +17513,10 @@
         <v>426</v>
       </c>
       <c r="N391" t="n">
-        <v>8700</v>
+        <v>8709.5604395604</v>
       </c>
       <c r="O391" t="n">
-        <v>3706200</v>
+        <v>3710272.747252731</v>
       </c>
       <c r="P391" t="n">
         <v>14900</v>
@@ -17973,10 +17973,10 @@
         <v>4224</v>
       </c>
       <c r="N401" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O401" t="n">
-        <v>6403747.946748979</v>
+        <v>6403747.945782105</v>
       </c>
       <c r="P401" t="n">
         <v>2300</v>
@@ -18019,10 +18019,10 @@
         <v>1152</v>
       </c>
       <c r="N402" t="n">
-        <v>2458.5134514107</v>
+        <v>2458.5134452463</v>
       </c>
       <c r="O402" t="n">
-        <v>2832207.496025126</v>
+        <v>2832207.488923737</v>
       </c>
       <c r="P402" t="n">
         <v>3500</v>
@@ -18065,10 +18065,10 @@
         <v>480</v>
       </c>
       <c r="N403" t="n">
-        <v>1907.3944716822</v>
+        <v>1909.016377551</v>
       </c>
       <c r="O403" t="n">
-        <v>915549.346407456</v>
+        <v>916327.86122448</v>
       </c>
       <c r="P403" t="n">
         <v>2500</v>
@@ -18157,10 +18157,10 @@
         <v>960</v>
       </c>
       <c r="N405" t="n">
-        <v>2079.3842209265</v>
+        <v>2079.3842077922</v>
       </c>
       <c r="O405" t="n">
-        <v>1996208.85208944</v>
+        <v>1996208.839480512</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
@@ -18249,10 +18249,10 @@
         <v>144</v>
       </c>
       <c r="N407" t="n">
-        <v>3306.5954545455</v>
+        <v>3306.595443038</v>
       </c>
       <c r="O407" t="n">
-        <v>476149.745454552</v>
+        <v>476149.743797472</v>
       </c>
       <c r="P407" t="n">
         <v>4900</v>
@@ -18295,10 +18295,10 @@
         <v>1440</v>
       </c>
       <c r="N408" t="n">
-        <v>2122.1641155235</v>
+        <v>2122.1641066586</v>
       </c>
       <c r="O408" t="n">
-        <v>3055916.32635384</v>
+        <v>3055916.313588384</v>
       </c>
       <c r="P408" t="n">
         <v>2900</v>
@@ -18341,10 +18341,10 @@
         <v>612</v>
       </c>
       <c r="N409" t="n">
-        <v>2108.7897869955</v>
+        <v>2108.7898867497</v>
       </c>
       <c r="O409" t="n">
-        <v>1290579.349641246</v>
+        <v>1290579.410690817</v>
       </c>
       <c r="P409" t="n">
         <v>2900</v>
@@ -18387,10 +18387,10 @@
         <v>684</v>
       </c>
       <c r="N410" t="n">
-        <v>2056.0838880663</v>
+        <v>2056.692917654</v>
       </c>
       <c r="O410" t="n">
-        <v>1406361.379437349</v>
+        <v>1406777.955675336</v>
       </c>
       <c r="P410" t="n">
         <v>2900</v>
@@ -18433,10 +18433,10 @@
         <v>714</v>
       </c>
       <c r="N411" t="n">
-        <v>3224.5679626335</v>
+        <v>3224.5679768271</v>
       </c>
       <c r="O411" t="n">
-        <v>2302341.525320319</v>
+        <v>2302341.535454549</v>
       </c>
       <c r="P411" t="n">
         <v>4500</v>
@@ -18479,10 +18479,10 @@
         <v>1152</v>
       </c>
       <c r="N412" t="n">
-        <v>1655.931342723</v>
+        <v>1655.9313291536</v>
       </c>
       <c r="O412" t="n">
-        <v>1907632.906816896</v>
+        <v>1907632.891184947</v>
       </c>
       <c r="P412" t="n">
         <v>2500</v>
@@ -19278,10 +19278,10 @@
         <v>2</v>
       </c>
       <c r="N429" t="n">
-        <v>1530.4499204455</v>
+        <v>1530.4499204138</v>
       </c>
       <c r="O429" t="n">
-        <v>3060.899840891</v>
+        <v>3060.8998408276</v>
       </c>
       <c r="P429" t="n">
         <v>2600</v>
@@ -19414,10 +19414,10 @@
         <v>1</v>
       </c>
       <c r="N432" t="n">
-        <v>2357.74</v>
+        <v>2458.0693617021</v>
       </c>
       <c r="O432" t="n">
-        <v>2357.74</v>
+        <v>2458.0693617021</v>
       </c>
       <c r="P432" t="n">
         <v>3000</v>
@@ -19592,10 +19592,10 @@
         <v>216</v>
       </c>
       <c r="N436" t="n">
-        <v>2286.1649330955</v>
+        <v>2286.1648782687</v>
       </c>
       <c r="O436" t="n">
-        <v>493811.625548628</v>
+        <v>493811.6137060391</v>
       </c>
       <c r="P436" t="n">
         <v>3000</v>
@@ -19948,10 +19948,10 @@
         <v>7572</v>
       </c>
       <c r="N444" t="n">
-        <v>517.28764753291</v>
+        <v>517.28774146762</v>
       </c>
       <c r="O444" t="n">
-        <v>3916902.067119195</v>
+        <v>3916902.778392818</v>
       </c>
       <c r="P444" t="n">
         <v>900</v>
@@ -19997,10 +19997,10 @@
         <v>504</v>
       </c>
       <c r="N445" t="n">
-        <v>3110.8431677619</v>
+        <v>3110.8430699863</v>
       </c>
       <c r="O445" t="n">
-        <v>1567864.956551998</v>
+        <v>1567864.907273095</v>
       </c>
       <c r="P445" t="n">
         <v>4500</v>
@@ -20129,10 +20129,10 @@
         <v>18248</v>
       </c>
       <c r="N448" t="n">
-        <v>703.79542528945</v>
+        <v>703.79541200942</v>
       </c>
       <c r="O448" t="n">
-        <v>12842858.92068188</v>
+        <v>12842858.6783479</v>
       </c>
       <c r="P448" t="n">
         <v>900</v>
@@ -20178,10 +20178,10 @@
         <v>127</v>
       </c>
       <c r="N449" t="n">
-        <v>3182.2510928962</v>
+        <v>3182.2511009174</v>
       </c>
       <c r="O449" t="n">
-        <v>404145.8887978174</v>
+        <v>404145.8898165098</v>
       </c>
       <c r="P449" t="n">
         <v>6900</v>
@@ -21353,10 +21353,10 @@
         <v>50</v>
       </c>
       <c r="N475" t="n">
-        <v>4159.0002867384</v>
+        <v>4173.9607194245</v>
       </c>
       <c r="O475" t="n">
-        <v>207950.01433692</v>
+        <v>208698.035971225</v>
       </c>
       <c r="P475" t="n">
         <v>8900</v>
@@ -21673,10 +21673,10 @@
         <v>79</v>
       </c>
       <c r="N482" t="n">
-        <v>10197</v>
+        <v>10385.833333333</v>
       </c>
       <c r="O482" t="n">
-        <v>805563</v>
+        <v>820480.8333333069</v>
       </c>
       <c r="P482" t="n">
         <v>14300</v>
@@ -23074,10 +23074,10 @@
         <v>481</v>
       </c>
       <c r="N514" t="n">
-        <v>2181.4249032992</v>
+        <v>2181.4248974943</v>
       </c>
       <c r="O514" t="n">
-        <v>1049265.378486915</v>
+        <v>1049265.375694758</v>
       </c>
       <c r="P514" t="n">
         <v>2900</v>
@@ -23713,10 +23713,10 @@
         <v>1</v>
       </c>
       <c r="N529" t="n">
-        <v>4985.4046332046</v>
+        <v>5004.7279069767</v>
       </c>
       <c r="O529" t="n">
-        <v>4985.4046332046</v>
+        <v>5004.7279069767</v>
       </c>
       <c r="P529" t="n">
         <v>7900</v>
@@ -23978,22 +23978,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M535" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N535" t="n">
-        <v>21664.37125</v>
+        <v>21664.371428571</v>
       </c>
       <c r="O535" t="n">
-        <v>194979.34125</v>
+        <v>108321.857142855</v>
       </c>
       <c r="P535" t="n">
         <v>30000</v>
       </c>
       <c r="Q535" t="n">
-        <v>270000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="536">

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3043052838</v>
+        <v>1811.3044243338</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.702544068</v>
+        <v>1557721.804927068</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8544651163</v>
+        <v>6272.8545</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.564465121</v>
+        <v>1354936.572</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -1920,10 +1920,10 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O38" t="n">
-        <v>2548517.295248874</v>
+        <v>2548517.29333335</v>
       </c>
       <c r="P38" t="n">
         <v>4800</v>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O54" t="n">
-        <v>594415.4917647032</v>
+        <v>597932.7431952696</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -2594,10 +2594,10 @@
         <v>60</v>
       </c>
       <c r="N55" t="n">
-        <v>16486.409489051</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O55" t="n">
-        <v>989184.5693430599</v>
+        <v>989184.5503759199</v>
       </c>
       <c r="P55" t="n">
         <v>30500</v>
@@ -2722,10 +2722,10 @@
         <v>48</v>
       </c>
       <c r="N58" t="n">
-        <v>30238.8124</v>
+        <v>30238.812535211</v>
       </c>
       <c r="O58" t="n">
-        <v>1451462.9952</v>
+        <v>1451463.001690128</v>
       </c>
       <c r="P58" t="n">
         <v>51100</v>
@@ -3155,10 +3155,10 @@
         <v>27</v>
       </c>
       <c r="N68" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O68" t="n">
-        <v>5401949.39386371</v>
+        <v>5401949.39792316</v>
       </c>
       <c r="P68" t="n">
         <v>312000</v>
@@ -3291,10 +3291,10 @@
         <v>16</v>
       </c>
       <c r="N71" t="n">
-        <v>344599.17865385</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O71" t="n">
-        <v>5513586.8584616</v>
+        <v>5513586.8580392</v>
       </c>
       <c r="P71" t="n">
         <v>532900</v>
@@ -3338,10 +3338,10 @@
         <v>14</v>
       </c>
       <c r="N72" t="n">
-        <v>263530.179</v>
+        <v>263530.17666667</v>
       </c>
       <c r="O72" t="n">
-        <v>3689422.506</v>
+        <v>3689422.47333338</v>
       </c>
       <c r="P72" t="n">
         <v>402900</v>
@@ -3600,10 +3600,10 @@
         <v>91</v>
       </c>
       <c r="N78" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O78" t="n">
-        <v>5611685.527838572</v>
+        <v>5611685.533518519</v>
       </c>
       <c r="P78" t="n">
         <v>98900</v>
@@ -3986,10 +3986,10 @@
         <v>1440</v>
       </c>
       <c r="N87" t="n">
-        <v>1950.2151724138</v>
+        <v>1950.2147262682</v>
       </c>
       <c r="O87" t="n">
-        <v>2808309.848275872</v>
+        <v>2808309.205826208</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4027,10 +4027,10 @@
         <v>2130</v>
       </c>
       <c r="N88" t="n">
-        <v>2833</v>
+        <v>2837.5792025862</v>
       </c>
       <c r="O88" t="n">
-        <v>6034290</v>
+        <v>6044043.701508607</v>
       </c>
       <c r="P88" t="n">
         <v>3500</v>
@@ -4375,10 +4375,10 @@
         <v>244</v>
       </c>
       <c r="N96" t="n">
-        <v>21084.771455026</v>
+        <v>21084.771458886</v>
       </c>
       <c r="O96" t="n">
-        <v>5144684.235026344</v>
+        <v>5144684.235968184</v>
       </c>
       <c r="P96" t="n">
         <v>30000</v>
@@ -5148,10 +5148,10 @@
         <v>1986</v>
       </c>
       <c r="N114" t="n">
-        <v>5216.8959762435</v>
+        <v>5216.8959678619</v>
       </c>
       <c r="O114" t="n">
-        <v>10360755.40881959</v>
+        <v>10360755.39217373</v>
       </c>
       <c r="P114" t="n">
         <v>8500</v>
@@ -5281,10 +5281,10 @@
         <v>6298</v>
       </c>
       <c r="N117" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O117" t="n">
-        <v>19894505.40900114</v>
+        <v>19894505.41098249</v>
       </c>
       <c r="P117" t="n">
         <v>5600</v>
@@ -5511,10 +5511,10 @@
         <v>224</v>
       </c>
       <c r="N122" t="n">
-        <v>2694.8234624043</v>
+        <v>2694.8234565119</v>
       </c>
       <c r="O122" t="n">
-        <v>603640.4555785632</v>
+        <v>603640.4542586657</v>
       </c>
       <c r="P122" t="n">
         <v>4900</v>
@@ -5831,10 +5831,10 @@
         <v>3024</v>
       </c>
       <c r="N129" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O129" t="n">
-        <v>11478227.06133341</v>
+        <v>11478227.06135579</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -5969,10 +5969,10 @@
         <v>64</v>
       </c>
       <c r="N132" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O132" t="n">
-        <v>313019.5229629632</v>
+        <v>313019.5229663936</v>
       </c>
       <c r="P132" t="n">
         <v>8200</v>
@@ -6602,10 +6602,10 @@
         <v>264</v>
       </c>
       <c r="N146" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O146" t="n">
-        <v>948883.1021359272</v>
+        <v>948883.09369128</v>
       </c>
       <c r="P146" t="n">
         <v>6500</v>
@@ -6827,10 +6827,10 @@
         <v>384</v>
       </c>
       <c r="N151" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O151" t="n">
-        <v>5691793.483997568</v>
+        <v>5691793.483739519</v>
       </c>
       <c r="P151" t="n">
         <v>24900</v>
@@ -6909,22 +6909,22 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M153" t="n">
-        <v>1287</v>
+        <v>1095</v>
       </c>
       <c r="N153" t="n">
         <v>2090.85</v>
       </c>
       <c r="O153" t="n">
-        <v>2690923.95</v>
+        <v>2289480.75</v>
       </c>
       <c r="P153" t="n">
         <v>2900</v>
       </c>
       <c r="Q153" t="n">
-        <v>3732300</v>
+        <v>3175500</v>
       </c>
     </row>
     <row r="154">
@@ -7317,10 +7317,10 @@
         <v>912</v>
       </c>
       <c r="N162" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O162" t="n">
-        <v>3987456.237681801</v>
+        <v>3987456.238294027</v>
       </c>
       <c r="P162" t="n">
         <v>7500</v>
@@ -7666,10 +7666,10 @@
         <v>10357</v>
       </c>
       <c r="N170" t="n">
-        <v>1532.629028858</v>
+        <v>1532.6290284343</v>
       </c>
       <c r="O170" t="n">
-        <v>15873438.85188231</v>
+        <v>15873438.84749404</v>
       </c>
       <c r="P170" t="n">
         <v>1200</v>
@@ -8508,10 +8508,10 @@
         <v>1152</v>
       </c>
       <c r="N189" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O189" t="n">
-        <v>1878823.418622451</v>
+        <v>1878823.465488</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8554,10 +8554,10 @@
         <v>768</v>
       </c>
       <c r="N190" t="n">
-        <v>1690.6033768352</v>
+        <v>1690.6028354857</v>
       </c>
       <c r="O190" t="n">
-        <v>1298383.393409434</v>
+        <v>1298382.977653018</v>
       </c>
       <c r="P190" t="n">
         <v>2900</v>
@@ -8600,10 +8600,10 @@
         <v>5472</v>
       </c>
       <c r="N191" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O191" t="n">
-        <v>8482656.498446448</v>
+        <v>8482656.835184572</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
@@ -8646,10 +8646,10 @@
         <v>2016</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5102087442</v>
+        <v>2403.5103430475</v>
       </c>
       <c r="O192" t="n">
-        <v>4845476.580828307</v>
+        <v>4845476.85158376</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -10106,10 +10106,10 @@
         <v>90</v>
       </c>
       <c r="N226" t="n">
-        <v>22485.695904437</v>
+        <v>22511.306036446</v>
       </c>
       <c r="O226" t="n">
-        <v>2023712.63139933</v>
+        <v>2026017.54328014</v>
       </c>
       <c r="P226" t="n">
         <v>36500</v>
@@ -10278,10 +10278,10 @@
         <v>1254</v>
       </c>
       <c r="N230" t="n">
-        <v>880.32933581916</v>
+        <v>880.32935107376</v>
       </c>
       <c r="O230" t="n">
-        <v>1103932.987117226</v>
+        <v>1103933.006246495</v>
       </c>
       <c r="P230" t="n">
         <v>1200</v>
@@ -11313,10 +11313,10 @@
         <v>150</v>
       </c>
       <c r="N254" t="n">
-        <v>11562.038530184</v>
+        <v>11562.038526316</v>
       </c>
       <c r="O254" t="n">
-        <v>1734305.7795276</v>
+        <v>1734305.7789474</v>
       </c>
       <c r="P254" t="n">
         <v>18500</v>
@@ -11359,10 +11359,10 @@
         <v>95</v>
       </c>
       <c r="N255" t="n">
-        <v>12005.159832636</v>
+        <v>12005.159831933</v>
       </c>
       <c r="O255" t="n">
-        <v>1140490.18410042</v>
+        <v>1140490.184033635</v>
       </c>
       <c r="P255" t="n">
         <v>19500</v>
@@ -12045,10 +12045,10 @@
         <v>34</v>
       </c>
       <c r="N271" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O271" t="n">
-        <v>922208.018215624</v>
+        <v>922208.01791435</v>
       </c>
       <c r="P271" t="n">
         <v>44500</v>
@@ -12306,10 +12306,10 @@
         <v>480</v>
       </c>
       <c r="N277" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O277" t="n">
-        <v>3825576.0791604</v>
+        <v>3834198.714951168</v>
       </c>
       <c r="P277" t="n">
         <v>12900</v>
@@ -12654,10 +12654,10 @@
         <v>433</v>
       </c>
       <c r="N285" t="n">
-        <v>3113.8900261438</v>
+        <v>3113.8900262812</v>
       </c>
       <c r="O285" t="n">
-        <v>1348314.381320265</v>
+        <v>1348314.38137976</v>
       </c>
       <c r="P285" t="n">
         <v>5000</v>
@@ -12838,10 +12838,10 @@
         <v>69</v>
       </c>
       <c r="N289" t="n">
-        <v>4163.1601724138</v>
+        <v>4163.1601818182</v>
       </c>
       <c r="O289" t="n">
-        <v>287258.0518965522</v>
+        <v>287258.0525454558</v>
       </c>
       <c r="P289" t="n">
         <v>6700</v>
@@ -13022,10 +13022,10 @@
         <v>399</v>
       </c>
       <c r="N293" t="n">
-        <v>5218.1705022831</v>
+        <v>5218.1705134189</v>
       </c>
       <c r="O293" t="n">
-        <v>2082050.030410957</v>
+        <v>2082050.034854141</v>
       </c>
       <c r="P293" t="n">
         <v>8500</v>
@@ -13068,10 +13068,10 @@
         <v>206</v>
       </c>
       <c r="N294" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="O294" t="n">
-        <v>328571.9530601058</v>
+        <v>328571.9481714374</v>
       </c>
       <c r="P294" t="n">
         <v>2600</v>
@@ -13114,10 +13114,10 @@
         <v>541</v>
       </c>
       <c r="N295" t="n">
-        <v>3610.6500238663</v>
+        <v>3610.6500248756</v>
       </c>
       <c r="O295" t="n">
-        <v>1953361.662911668</v>
+        <v>1953361.6634577</v>
       </c>
       <c r="P295" t="n">
         <v>5800</v>
@@ -13528,10 +13528,10 @@
         <v>384</v>
       </c>
       <c r="N304" t="n">
-        <v>1664.360187234</v>
+        <v>1664.359264432</v>
       </c>
       <c r="O304" t="n">
-        <v>639114.311897856</v>
+        <v>639113.957541888</v>
       </c>
       <c r="P304" t="n">
         <v>2900</v>
@@ -13620,10 +13620,10 @@
         <v>4</v>
       </c>
       <c r="N306" t="n">
-        <v>10174</v>
+        <v>10716.613333333</v>
       </c>
       <c r="O306" t="n">
-        <v>40696</v>
+        <v>42866.453333332</v>
       </c>
       <c r="P306" t="n">
         <v>16900</v>
@@ -13896,10 +13896,10 @@
         <v>123</v>
       </c>
       <c r="N312" t="n">
-        <v>15824</v>
+        <v>15908.394666667</v>
       </c>
       <c r="O312" t="n">
-        <v>1946352</v>
+        <v>1956732.544000041</v>
       </c>
       <c r="P312" t="n">
         <v>26900</v>
@@ -14172,10 +14172,10 @@
         <v>156</v>
       </c>
       <c r="N318" t="n">
-        <v>3486</v>
+        <v>3502.5901249256</v>
       </c>
       <c r="O318" t="n">
-        <v>543816</v>
+        <v>546404.0594883936</v>
       </c>
       <c r="P318" t="n">
         <v>6900</v>
@@ -14218,10 +14218,10 @@
         <v>1145</v>
       </c>
       <c r="N319" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O319" t="n">
-        <v>2036351.068496339</v>
+        <v>2045924.047238091</v>
       </c>
       <c r="P319" t="n">
         <v>4900</v>
@@ -14902,22 +14902,22 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M334" t="n">
-        <v>720</v>
+        <v>624</v>
       </c>
       <c r="N334" t="n">
         <v>8858.16</v>
       </c>
       <c r="O334" t="n">
-        <v>6377875.2</v>
+        <v>5527491.84</v>
       </c>
       <c r="P334" t="n">
         <v>15500</v>
       </c>
       <c r="Q334" t="n">
-        <v>11160000</v>
+        <v>9672000</v>
       </c>
     </row>
     <row r="335">
@@ -14954,10 +14954,10 @@
         <v>108</v>
       </c>
       <c r="N335" t="n">
-        <v>13019</v>
+        <v>13090.336986301</v>
       </c>
       <c r="O335" t="n">
-        <v>1406052</v>
+        <v>1413756.394520508</v>
       </c>
       <c r="P335" t="n">
         <v>20900</v>
@@ -15228,10 +15228,10 @@
         <v>864</v>
       </c>
       <c r="N341" t="n">
-        <v>2328.1187507401</v>
+        <v>2328.1187488882</v>
       </c>
       <c r="O341" t="n">
-        <v>2011494.600639446</v>
+        <v>2011494.599039405</v>
       </c>
       <c r="P341" t="n">
         <v>4500</v>
@@ -15821,10 +15821,10 @@
         <v>70</v>
       </c>
       <c r="N354" t="n">
-        <v>4202</v>
+        <v>4235.616</v>
       </c>
       <c r="O354" t="n">
-        <v>294140</v>
+        <v>296493.12</v>
       </c>
       <c r="P354" t="n">
         <v>7900</v>
@@ -15913,10 +15913,10 @@
         <v>240</v>
       </c>
       <c r="N356" t="n">
-        <v>2629</v>
+        <v>2655.7582697201</v>
       </c>
       <c r="O356" t="n">
-        <v>630960</v>
+        <v>637381.984732824</v>
       </c>
       <c r="P356" t="n">
         <v>4500</v>
@@ -16051,10 +16051,10 @@
         <v>1134</v>
       </c>
       <c r="N359" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O359" t="n">
-        <v>6545448</v>
+        <v>6565256.013449877</v>
       </c>
       <c r="P359" t="n">
         <v>9900</v>
@@ -16143,10 +16143,10 @@
         <v>10</v>
       </c>
       <c r="N361" t="n">
-        <v>8637</v>
+        <v>9222.5593220339</v>
       </c>
       <c r="O361" t="n">
-        <v>86370</v>
+        <v>92225.593220339</v>
       </c>
       <c r="P361" t="n">
         <v>14500</v>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>1872</v>
+        <v>2016</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -16232,19 +16232,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>1872</v>
+        <v>2016</v>
       </c>
       <c r="N363" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O363" t="n">
-        <v>12439440</v>
+        <v>13432782.49319543</v>
       </c>
       <c r="P363" t="n">
         <v>10900</v>
       </c>
       <c r="Q363" t="n">
-        <v>20404800</v>
+        <v>21974400</v>
       </c>
     </row>
     <row r="364">
@@ -16275,22 +16275,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M364" t="n">
-        <v>684</v>
+        <v>624</v>
       </c>
       <c r="N364" t="n">
-        <v>13098</v>
+        <v>13167.485411141</v>
       </c>
       <c r="O364" t="n">
-        <v>8959032</v>
+        <v>8216510.896551984</v>
       </c>
       <c r="P364" t="n">
         <v>21200</v>
       </c>
       <c r="Q364" t="n">
-        <v>14500800</v>
+        <v>13228800</v>
       </c>
     </row>
     <row r="365">
@@ -16373,10 +16373,10 @@
         <v>480</v>
       </c>
       <c r="N366" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O366" t="n">
-        <v>1871040</v>
+        <v>1878308.997668976</v>
       </c>
       <c r="P366" t="n">
         <v>6900</v>
@@ -16966,10 +16966,10 @@
         <v>96</v>
       </c>
       <c r="N379" t="n">
-        <v>10219</v>
+        <v>10293.773170732</v>
       </c>
       <c r="O379" t="n">
-        <v>981024</v>
+        <v>988202.2243902721</v>
       </c>
       <c r="P379" t="n">
         <v>16900</v>
@@ -17107,10 +17107,10 @@
         <v>301</v>
       </c>
       <c r="N382" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O382" t="n">
-        <v>8203454</v>
+        <v>8224434.700767208</v>
       </c>
       <c r="P382" t="n">
         <v>43900</v>
@@ -17475,10 +17475,10 @@
         <v>528</v>
       </c>
       <c r="N390" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O390" t="n">
-        <v>2017488</v>
+        <v>2021584.422335016</v>
       </c>
       <c r="P390" t="n">
         <v>5900</v>
@@ -17659,10 +17659,10 @@
         <v>576</v>
       </c>
       <c r="N394" t="n">
-        <v>5476</v>
+        <v>5504.4467532468</v>
       </c>
       <c r="O394" t="n">
-        <v>3154176</v>
+        <v>3170561.329870156</v>
       </c>
       <c r="P394" t="n">
         <v>8900</v>
@@ -17797,10 +17797,10 @@
         <v>4224</v>
       </c>
       <c r="N397" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O397" t="n">
-        <v>6403747.945782105</v>
+        <v>6411166.846665293</v>
       </c>
       <c r="P397" t="n">
         <v>2300</v>
@@ -17843,10 +17843,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>2458.5134204724</v>
+        <v>2458.5134059343</v>
       </c>
       <c r="O398" t="n">
-        <v>2832207.460384205</v>
+        <v>2832207.443636314</v>
       </c>
       <c r="P398" t="n">
         <v>3500</v>
@@ -17889,10 +17889,10 @@
         <v>480</v>
       </c>
       <c r="N399" t="n">
-        <v>1907.3944245524</v>
+        <v>1907.3942832168</v>
       </c>
       <c r="O399" t="n">
-        <v>915549.3237851521</v>
+        <v>915549.255944064</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -17935,10 +17935,10 @@
         <v>576</v>
       </c>
       <c r="N400" t="n">
-        <v>1771.0912628399</v>
+        <v>1771.0911342735</v>
       </c>
       <c r="O400" t="n">
-        <v>1020148.567395782</v>
+        <v>1020148.493341536</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>
@@ -17981,10 +17981,10 @@
         <v>960</v>
       </c>
       <c r="N401" t="n">
-        <v>2079.384205911</v>
+        <v>2079.3842021449</v>
       </c>
       <c r="O401" t="n">
-        <v>1996208.83767456</v>
+        <v>1996208.834059104</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -18027,10 +18027,10 @@
         <v>1344</v>
       </c>
       <c r="N402" t="n">
-        <v>1803.0150073855</v>
+        <v>1803.0151441578</v>
       </c>
       <c r="O402" t="n">
-        <v>2423252.169926112</v>
+        <v>2423252.353748083</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -18073,10 +18073,10 @@
         <v>144</v>
       </c>
       <c r="N403" t="n">
-        <v>3306.5954372624</v>
+        <v>3306.5953548387</v>
       </c>
       <c r="O403" t="n">
-        <v>476149.7429657856</v>
+        <v>476149.7310967728</v>
       </c>
       <c r="P403" t="n">
         <v>4900</v>
@@ -18119,10 +18119,10 @@
         <v>1440</v>
       </c>
       <c r="N404" t="n">
-        <v>2122.1640959855</v>
+        <v>2126.0638621746</v>
       </c>
       <c r="O404" t="n">
-        <v>3055916.29821912</v>
+        <v>3061531.961531424</v>
       </c>
       <c r="P404" t="n">
         <v>2900</v>
@@ -18165,10 +18165,10 @@
         <v>612</v>
       </c>
       <c r="N405" t="n">
-        <v>2108.7899091941</v>
+        <v>2108.7899828473</v>
       </c>
       <c r="O405" t="n">
-        <v>1290579.424426789</v>
+        <v>1290579.469502548</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
@@ -18211,10 +18211,10 @@
         <v>684</v>
       </c>
       <c r="N406" t="n">
-        <v>2056.083871734</v>
+        <v>2059.7554464286</v>
       </c>
       <c r="O406" t="n">
-        <v>1406361.368266056</v>
+        <v>1408872.725357162</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -18257,10 +18257,10 @@
         <v>714</v>
       </c>
       <c r="N407" t="n">
-        <v>3224.5680666967</v>
+        <v>3224.5682755432</v>
       </c>
       <c r="O407" t="n">
-        <v>2302341.599621444</v>
+        <v>2302341.748737845</v>
       </c>
       <c r="P407" t="n">
         <v>4500</v>
@@ -18303,10 +18303,10 @@
         <v>1152</v>
       </c>
       <c r="N408" t="n">
-        <v>1655.9312964128</v>
+        <v>1657.5320592975</v>
       </c>
       <c r="O408" t="n">
-        <v>1907632.853467546</v>
+        <v>1909476.93231072</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18626,10 +18626,10 @@
         <v>50</v>
       </c>
       <c r="N415" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O415" t="n">
-        <v>267386.5</v>
+        <v>269681.66309013</v>
       </c>
       <c r="P415" t="n">
         <v>9500</v>
@@ -18672,10 +18672,10 @@
         <v>13104</v>
       </c>
       <c r="N416" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O416" t="n">
-        <v>23600304</v>
+        <v>23629845.92332947</v>
       </c>
       <c r="P416" t="n">
         <v>2900</v>
@@ -18955,10 +18955,10 @@
         <v>266</v>
       </c>
       <c r="N422" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O422" t="n">
-        <v>760020.5199999999</v>
+        <v>762174.569655177</v>
       </c>
       <c r="P422" t="n">
         <v>4900</v>
@@ -19004,10 +19004,10 @@
         <v>2370</v>
       </c>
       <c r="N423" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O423" t="n">
-        <v>21200550.6</v>
+        <v>21206736.02687101</v>
       </c>
       <c r="P423" t="n">
         <v>14900</v>
@@ -19102,10 +19102,10 @@
         <v>2</v>
       </c>
       <c r="N425" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O425" t="n">
-        <v>3060.8998408276</v>
+        <v>3060.8998412068</v>
       </c>
       <c r="P425" t="n">
         <v>2600</v>
@@ -19416,10 +19416,10 @@
         <v>216</v>
       </c>
       <c r="N432" t="n">
-        <v>2286.1648782687</v>
+        <v>2286.1648643761</v>
       </c>
       <c r="O432" t="n">
-        <v>493811.6137060391</v>
+        <v>493811.6107052376</v>
       </c>
       <c r="P432" t="n">
         <v>3000</v>
@@ -19772,10 +19772,10 @@
         <v>7572</v>
       </c>
       <c r="N440" t="n">
-        <v>517.2878865955601</v>
+        <v>523.15541944326</v>
       </c>
       <c r="O440" t="n">
-        <v>3916903.877301581</v>
+        <v>3961332.836024365</v>
       </c>
       <c r="P440" t="n">
         <v>900</v>
@@ -19821,10 +19821,10 @@
         <v>504</v>
       </c>
       <c r="N441" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O441" t="n">
-        <v>1567864.862894585</v>
+        <v>1567864.848086107</v>
       </c>
       <c r="P441" t="n">
         <v>4500</v>
@@ -19953,10 +19953,10 @@
         <v>18248</v>
       </c>
       <c r="N444" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O444" t="n">
-        <v>12842858.19717788</v>
+        <v>12842857.44033588</v>
       </c>
       <c r="P444" t="n">
         <v>900</v>
@@ -20530,10 +20530,10 @@
         <v>2569</v>
       </c>
       <c r="N457" t="n">
-        <v>1595.5190941049</v>
+        <v>1595.5190882035</v>
       </c>
       <c r="O457" t="n">
-        <v>4098888.552755488</v>
+        <v>4098888.537594791</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
@@ -22810,10 +22810,10 @@
         <v>478</v>
       </c>
       <c r="N508" t="n">
-        <v>3181.9</v>
+        <v>3209.0377398721</v>
       </c>
       <c r="O508" t="n">
-        <v>1520948.2</v>
+        <v>1533920.039658864</v>
       </c>
       <c r="P508" t="n">
         <v>5100</v>
@@ -22854,10 +22854,10 @@
         <v>5129</v>
       </c>
       <c r="N509" t="n">
-        <v>1794.2879767875</v>
+        <v>1794.2879750466</v>
       </c>
       <c r="O509" t="n">
-        <v>9202903.032943087</v>
+        <v>9202903.024014011</v>
       </c>
       <c r="P509" t="n">
         <v>1600</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3933.7680473373</v>
+        <v>3910.6282248521</v>
       </c>
       <c r="O54" t="n">
-        <v>597932.7431952696</v>
+        <v>594415.4901775193</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -4027,10 +4027,10 @@
         <v>2130</v>
       </c>
       <c r="N88" t="n">
-        <v>2837.5792025862</v>
+        <v>2833</v>
       </c>
       <c r="O88" t="n">
-        <v>6044043.701508607</v>
+        <v>6034290</v>
       </c>
       <c r="P88" t="n">
         <v>3500</v>
@@ -6903,13 +6903,13 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>1287</v>
+        <v>1095</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>1095</v>
@@ -10106,10 +10106,10 @@
         <v>90</v>
       </c>
       <c r="N226" t="n">
-        <v>22511.306036446</v>
+        <v>22485.695899772</v>
       </c>
       <c r="O226" t="n">
-        <v>2026017.54328014</v>
+        <v>2023712.63097948</v>
       </c>
       <c r="P226" t="n">
         <v>36500</v>
@@ -12306,10 +12306,10 @@
         <v>480</v>
       </c>
       <c r="N277" t="n">
-        <v>7987.9139894816</v>
+        <v>7969.9501652893</v>
       </c>
       <c r="O277" t="n">
-        <v>3834198.714951168</v>
+        <v>3825576.079338864</v>
       </c>
       <c r="P277" t="n">
         <v>12900</v>
@@ -13620,10 +13620,10 @@
         <v>4</v>
       </c>
       <c r="N306" t="n">
-        <v>10716.613333333</v>
+        <v>10174</v>
       </c>
       <c r="O306" t="n">
-        <v>42866.453333332</v>
+        <v>40696</v>
       </c>
       <c r="P306" t="n">
         <v>16900</v>
@@ -13896,10 +13896,10 @@
         <v>123</v>
       </c>
       <c r="N312" t="n">
-        <v>15908.394666667</v>
+        <v>15824</v>
       </c>
       <c r="O312" t="n">
-        <v>1956732.544000041</v>
+        <v>1946352</v>
       </c>
       <c r="P312" t="n">
         <v>26900</v>
@@ -14172,10 +14172,10 @@
         <v>156</v>
       </c>
       <c r="N318" t="n">
-        <v>3502.5901249256</v>
+        <v>3486</v>
       </c>
       <c r="O318" t="n">
-        <v>546404.0594883936</v>
+        <v>543816</v>
       </c>
       <c r="P318" t="n">
         <v>6900</v>
@@ -14218,10 +14218,10 @@
         <v>1145</v>
       </c>
       <c r="N319" t="n">
-        <v>1786.8332290289</v>
+        <v>1778.4725650066</v>
       </c>
       <c r="O319" t="n">
-        <v>2045924.047238091</v>
+        <v>2036351.086932557</v>
       </c>
       <c r="P319" t="n">
         <v>4900</v>
@@ -14896,13 +14896,13 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>720</v>
+        <v>624</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M334" t="n">
         <v>624</v>
@@ -14954,10 +14954,10 @@
         <v>108</v>
       </c>
       <c r="N335" t="n">
-        <v>13090.336986301</v>
+        <v>13019</v>
       </c>
       <c r="O335" t="n">
-        <v>1413756.394520508</v>
+        <v>1406052</v>
       </c>
       <c r="P335" t="n">
         <v>20900</v>
@@ -15821,10 +15821,10 @@
         <v>70</v>
       </c>
       <c r="N354" t="n">
-        <v>4235.616</v>
+        <v>4202</v>
       </c>
       <c r="O354" t="n">
-        <v>296493.12</v>
+        <v>294140</v>
       </c>
       <c r="P354" t="n">
         <v>7900</v>
@@ -15913,10 +15913,10 @@
         <v>240</v>
       </c>
       <c r="N356" t="n">
-        <v>2655.7582697201</v>
+        <v>2629</v>
       </c>
       <c r="O356" t="n">
-        <v>637381.984732824</v>
+        <v>630960</v>
       </c>
       <c r="P356" t="n">
         <v>4500</v>
@@ -16051,10 +16051,10 @@
         <v>1134</v>
       </c>
       <c r="N359" t="n">
-        <v>5789.4673839946</v>
+        <v>5772</v>
       </c>
       <c r="O359" t="n">
-        <v>6565256.013449877</v>
+        <v>6545448</v>
       </c>
       <c r="P359" t="n">
         <v>9900</v>
@@ -16143,10 +16143,10 @@
         <v>10</v>
       </c>
       <c r="N361" t="n">
-        <v>9222.5593220339</v>
+        <v>8637</v>
       </c>
       <c r="O361" t="n">
-        <v>92225.593220339</v>
+        <v>86370</v>
       </c>
       <c r="P361" t="n">
         <v>14500</v>
@@ -16235,10 +16235,10 @@
         <v>2016</v>
       </c>
       <c r="N363" t="n">
-        <v>6663.0865541644</v>
+        <v>6645</v>
       </c>
       <c r="O363" t="n">
-        <v>13432782.49319543</v>
+        <v>13396320</v>
       </c>
       <c r="P363" t="n">
         <v>10900</v>
@@ -16269,22 +16269,22 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>684</v>
+        <v>624</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M364" t="n">
         <v>624</v>
       </c>
       <c r="N364" t="n">
-        <v>13167.485411141</v>
+        <v>13098</v>
       </c>
       <c r="O364" t="n">
-        <v>8216510.896551984</v>
+        <v>8173152</v>
       </c>
       <c r="P364" t="n">
         <v>21200</v>
@@ -16373,10 +16373,10 @@
         <v>480</v>
       </c>
       <c r="N366" t="n">
-        <v>3913.1437451437</v>
+        <v>3898</v>
       </c>
       <c r="O366" t="n">
-        <v>1878308.997668976</v>
+        <v>1871040</v>
       </c>
       <c r="P366" t="n">
         <v>6900</v>
@@ -16966,10 +16966,10 @@
         <v>96</v>
       </c>
       <c r="N379" t="n">
-        <v>10293.773170732</v>
+        <v>10219</v>
       </c>
       <c r="O379" t="n">
-        <v>988202.2243902721</v>
+        <v>981024</v>
       </c>
       <c r="P379" t="n">
         <v>16900</v>
@@ -17107,10 +17107,10 @@
         <v>301</v>
       </c>
       <c r="N382" t="n">
-        <v>27323.703324808</v>
+        <v>27254</v>
       </c>
       <c r="O382" t="n">
-        <v>8224434.700767208</v>
+        <v>8203454</v>
       </c>
       <c r="P382" t="n">
         <v>43900</v>
@@ -17475,10 +17475,10 @@
         <v>528</v>
       </c>
       <c r="N390" t="n">
-        <v>3828.7583756345</v>
+        <v>3821</v>
       </c>
       <c r="O390" t="n">
-        <v>2021584.422335016</v>
+        <v>2017488</v>
       </c>
       <c r="P390" t="n">
         <v>5900</v>
@@ -17659,10 +17659,10 @@
         <v>576</v>
       </c>
       <c r="N394" t="n">
-        <v>5504.4467532468</v>
+        <v>5476</v>
       </c>
       <c r="O394" t="n">
-        <v>3170561.329870156</v>
+        <v>3154176</v>
       </c>
       <c r="P394" t="n">
         <v>8900</v>
@@ -17797,10 +17797,10 @@
         <v>4224</v>
       </c>
       <c r="N397" t="n">
-        <v>1517.7951815022</v>
+        <v>1516.0388115466</v>
       </c>
       <c r="O397" t="n">
-        <v>6411166.846665293</v>
+        <v>6403747.939972838</v>
       </c>
       <c r="P397" t="n">
         <v>2300</v>
@@ -18119,10 +18119,10 @@
         <v>1440</v>
       </c>
       <c r="N404" t="n">
-        <v>2126.0638621746</v>
+        <v>2122.1640091884</v>
       </c>
       <c r="O404" t="n">
-        <v>3061531.961531424</v>
+        <v>3055916.173231296</v>
       </c>
       <c r="P404" t="n">
         <v>2900</v>
@@ -18211,10 +18211,10 @@
         <v>684</v>
       </c>
       <c r="N406" t="n">
-        <v>2059.7554464286</v>
+        <v>2056.0838571429</v>
       </c>
       <c r="O406" t="n">
-        <v>1408872.725357162</v>
+        <v>1406361.358285744</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -18303,10 +18303,10 @@
         <v>1152</v>
       </c>
       <c r="N408" t="n">
-        <v>1657.5320592975</v>
+        <v>1655.9310860458</v>
       </c>
       <c r="O408" t="n">
-        <v>1909476.93231072</v>
+        <v>1907632.611124761</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -18626,10 +18626,10 @@
         <v>50</v>
       </c>
       <c r="N415" t="n">
-        <v>5393.6332618026</v>
+        <v>5347.73</v>
       </c>
       <c r="O415" t="n">
-        <v>269681.66309013</v>
+        <v>267386.5</v>
       </c>
       <c r="P415" t="n">
         <v>9500</v>
@@ -18672,10 +18672,10 @@
         <v>13104</v>
       </c>
       <c r="N416" t="n">
-        <v>1803.2544202785</v>
+        <v>1801</v>
       </c>
       <c r="O416" t="n">
-        <v>23629845.92332947</v>
+        <v>23600304</v>
       </c>
       <c r="P416" t="n">
         <v>2900</v>
@@ -18955,10 +18955,10 @@
         <v>266</v>
       </c>
       <c r="N422" t="n">
-        <v>2865.3179310345</v>
+        <v>2857.22</v>
       </c>
       <c r="O422" t="n">
-        <v>762174.569655177</v>
+        <v>760020.5199999999</v>
       </c>
       <c r="P422" t="n">
         <v>4900</v>
@@ -19004,10 +19004,10 @@
         <v>2370</v>
       </c>
       <c r="N423" t="n">
-        <v>8947.9898847557</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O423" t="n">
-        <v>21206736.02687101</v>
+        <v>21200550.6</v>
       </c>
       <c r="P423" t="n">
         <v>14900</v>
@@ -19772,10 +19772,10 @@
         <v>7572</v>
       </c>
       <c r="N440" t="n">
-        <v>523.15541944326</v>
+        <v>517.28807221513</v>
       </c>
       <c r="O440" t="n">
-        <v>3961332.836024365</v>
+        <v>3916905.282812964</v>
       </c>
       <c r="P440" t="n">
         <v>900</v>
@@ -22810,10 +22810,10 @@
         <v>478</v>
       </c>
       <c r="N508" t="n">
-        <v>3209.0377398721</v>
+        <v>3181.9</v>
       </c>
       <c r="O508" t="n">
-        <v>1533920.039658864</v>
+        <v>1520948.2</v>
       </c>
       <c r="P508" t="n">
         <v>5100</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -650,10 +650,10 @@
         <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>66707.97725</v>
+        <v>66707.977837838</v>
       </c>
       <c r="O6" t="n">
-        <v>1400867.52225</v>
+        <v>1400867.534594598</v>
       </c>
       <c r="P6" t="n">
         <v>125900</v>
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3044243338</v>
+        <v>1811.3044829343</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.804927068</v>
+        <v>1557721.855323498</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1046,10 +1046,10 @@
         <v>112</v>
       </c>
       <c r="N16" t="n">
-        <v>1990.0435660377</v>
+        <v>1990.0435416667</v>
       </c>
       <c r="O16" t="n">
-        <v>222884.8793962224</v>
+        <v>222884.8766666704</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -1079,22 +1079,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M17" t="n">
-        <v>343</v>
+        <v>244</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.7465014893</v>
+        <v>3376.746498645</v>
       </c>
       <c r="O17" t="n">
-        <v>1158224.05001083</v>
+        <v>823926.14566938</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
       </c>
       <c r="Q17" t="n">
-        <v>1543500</v>
+        <v>1098000</v>
       </c>
     </row>
     <row r="18">
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8545</v>
+        <v>6272.8545786963</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.572</v>
+        <v>1354936.588998401</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.001059322</v>
+        <v>2413.0010615711</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.558262694</v>
+        <v>1271651.55944797</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3910.6282248521</v>
+        <v>3910.6281963928</v>
       </c>
       <c r="O54" t="n">
-        <v>594415.4901775193</v>
+        <v>594415.4858517055</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -3155,10 +3155,10 @@
         <v>27</v>
       </c>
       <c r="N68" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O68" t="n">
-        <v>5401949.39792316</v>
+        <v>5401949.4</v>
       </c>
       <c r="P68" t="n">
         <v>312000</v>
@@ -4114,10 +4114,10 @@
         <v>200</v>
       </c>
       <c r="N90" t="n">
-        <v>4937.3101608187</v>
+        <v>4937.3101611722</v>
       </c>
       <c r="O90" t="n">
-        <v>987462.03216374</v>
+        <v>987462.0322344401</v>
       </c>
       <c r="P90" t="n">
         <v>7500</v>
@@ -5056,10 +5056,10 @@
         <v>1080</v>
       </c>
       <c r="N112" t="n">
-        <v>2582.2560231583</v>
+        <v>2582.2560112135</v>
       </c>
       <c r="O112" t="n">
-        <v>2788836.505010964</v>
+        <v>2788836.49211058</v>
       </c>
       <c r="P112" t="n">
         <v>4500</v>
@@ -5148,10 +5148,10 @@
         <v>1986</v>
       </c>
       <c r="N114" t="n">
-        <v>5216.8959678619</v>
+        <v>5216.8959654608</v>
       </c>
       <c r="O114" t="n">
-        <v>10360755.39217373</v>
+        <v>10360755.38740515</v>
       </c>
       <c r="P114" t="n">
         <v>8500</v>
@@ -5281,10 +5281,10 @@
         <v>6298</v>
       </c>
       <c r="N117" t="n">
-        <v>3158.8608147003</v>
+        <v>3158.860814779</v>
       </c>
       <c r="O117" t="n">
-        <v>19894505.41098249</v>
+        <v>19894505.41147814</v>
       </c>
       <c r="P117" t="n">
         <v>5600</v>
@@ -5373,10 +5373,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>3841.6247184466</v>
+        <v>3841.6247414634</v>
       </c>
       <c r="O119" t="n">
-        <v>553193.9594563104</v>
+        <v>553193.9627707296</v>
       </c>
       <c r="P119" t="n">
         <v>6900</v>
@@ -5969,10 +5969,10 @@
         <v>64</v>
       </c>
       <c r="N132" t="n">
-        <v>4890.9300463499</v>
+        <v>4890.9300464306</v>
       </c>
       <c r="O132" t="n">
-        <v>313019.5229663936</v>
+        <v>313019.5229715584</v>
       </c>
       <c r="P132" t="n">
         <v>8200</v>
@@ -6506,22 +6506,22 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M144" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N144" t="n">
         <v>10716.34</v>
       </c>
       <c r="O144" t="n">
-        <v>1425273.22</v>
+        <v>1275244.46</v>
       </c>
       <c r="P144" t="n">
         <v>39000</v>
       </c>
       <c r="Q144" t="n">
-        <v>5187000</v>
+        <v>4641000</v>
       </c>
     </row>
     <row r="145">
@@ -6602,10 +6602,10 @@
         <v>264</v>
       </c>
       <c r="N146" t="n">
-        <v>3594.25414277</v>
+        <v>3594.2541391941</v>
       </c>
       <c r="O146" t="n">
-        <v>948883.09369128</v>
+        <v>948883.0927472424</v>
       </c>
       <c r="P146" t="n">
         <v>6500</v>
@@ -6827,10 +6827,10 @@
         <v>384</v>
       </c>
       <c r="N151" t="n">
-        <v>14822.378863905</v>
+        <v>14822.378862559</v>
       </c>
       <c r="O151" t="n">
-        <v>5691793.483739519</v>
+        <v>5691793.483222656</v>
       </c>
       <c r="P151" t="n">
         <v>24900</v>
@@ -7230,10 +7230,10 @@
         <v>78</v>
       </c>
       <c r="N160" t="n">
-        <v>3041.6600125945</v>
+        <v>3041.6600126502</v>
       </c>
       <c r="O160" t="n">
-        <v>237249.480982371</v>
+        <v>237249.4809867156</v>
       </c>
       <c r="P160" t="n">
         <v>5500</v>
@@ -7265,22 +7265,22 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M161" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="N161" t="n">
         <v>3981.47</v>
       </c>
       <c r="O161" t="n">
-        <v>955552.7999999999</v>
+        <v>597220.5</v>
       </c>
       <c r="P161" t="n">
         <v>7000</v>
       </c>
       <c r="Q161" t="n">
-        <v>1680000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="162">
@@ -7311,22 +7311,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M162" t="n">
-        <v>912</v>
+        <v>809</v>
       </c>
       <c r="N162" t="n">
-        <v>4372.2107876031</v>
+        <v>4372.2107877711</v>
       </c>
       <c r="O162" t="n">
-        <v>3987456.238294027</v>
+        <v>3537118.52730682</v>
       </c>
       <c r="P162" t="n">
         <v>7500</v>
       </c>
       <c r="Q162" t="n">
-        <v>6840000</v>
+        <v>6067500</v>
       </c>
     </row>
     <row r="163">
@@ -7877,22 +7877,22 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M175" t="n">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="N175" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O175" t="n">
-        <v>3878695.72</v>
+        <v>3558609.18</v>
       </c>
       <c r="P175" t="n">
         <v>16900</v>
       </c>
       <c r="Q175" t="n">
-        <v>6962800</v>
+        <v>6388200</v>
       </c>
     </row>
     <row r="176">
@@ -8012,10 +8012,10 @@
         <v>200</v>
       </c>
       <c r="N178" t="n">
-        <v>2021.7211218335</v>
+        <v>2021.7211225106</v>
       </c>
       <c r="O178" t="n">
-        <v>404344.2243667</v>
+        <v>404344.22450212</v>
       </c>
       <c r="P178" t="n">
         <v>2400</v>
@@ -8235,22 +8235,22 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M183" t="n">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="N183" t="n">
         <v>11921.4</v>
       </c>
       <c r="O183" t="n">
-        <v>7748910</v>
+        <v>7593931.8</v>
       </c>
       <c r="P183" t="n">
         <v>19900</v>
       </c>
       <c r="Q183" t="n">
-        <v>12935000</v>
+        <v>12676300</v>
       </c>
     </row>
     <row r="184">
@@ -8456,22 +8456,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M188" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
         <v>12754</v>
       </c>
       <c r="O188" t="n">
-        <v>816256</v>
+        <v>0</v>
       </c>
       <c r="P188" t="n">
         <v>21500</v>
       </c>
       <c r="Q188" t="n">
-        <v>1376000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -8508,10 +8508,10 @@
         <v>1152</v>
       </c>
       <c r="N189" t="n">
-        <v>1630.923147125</v>
+        <v>1630.9231587595</v>
       </c>
       <c r="O189" t="n">
-        <v>1878823.465488</v>
+        <v>1878823.478890944</v>
       </c>
       <c r="P189" t="n">
         <v>2500</v>
@@ -8554,10 +8554,10 @@
         <v>768</v>
       </c>
       <c r="N190" t="n">
-        <v>1690.6028354857</v>
+        <v>1690.6026503973</v>
       </c>
       <c r="O190" t="n">
-        <v>1298382.977653018</v>
+        <v>1298382.835505127</v>
       </c>
       <c r="P190" t="n">
         <v>2900</v>
@@ -8600,10 +8600,10 @@
         <v>5472</v>
       </c>
       <c r="N191" t="n">
-        <v>1550.1931350849</v>
+        <v>1550.1931558806</v>
       </c>
       <c r="O191" t="n">
-        <v>8482656.835184572</v>
+        <v>8482656.948978644</v>
       </c>
       <c r="P191" t="n">
         <v>2500</v>
@@ -8646,10 +8646,10 @@
         <v>2016</v>
       </c>
       <c r="N192" t="n">
-        <v>2403.5103430475</v>
+        <v>2403.5103724115</v>
       </c>
       <c r="O192" t="n">
-        <v>4845476.85158376</v>
+        <v>4845476.910781585</v>
       </c>
       <c r="P192" t="n">
         <v>3500</v>
@@ -10278,10 +10278,10 @@
         <v>1254</v>
       </c>
       <c r="N230" t="n">
-        <v>880.32935107376</v>
+        <v>880.3293685687599</v>
       </c>
       <c r="O230" t="n">
-        <v>1103933.006246495</v>
+        <v>1103933.028185225</v>
       </c>
       <c r="P230" t="n">
         <v>1200</v>
@@ -10533,22 +10533,22 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M236" t="n">
-        <v>405</v>
+        <v>345</v>
       </c>
       <c r="N236" t="n">
         <v>1651</v>
       </c>
       <c r="O236" t="n">
-        <v>668655</v>
+        <v>569595</v>
       </c>
       <c r="P236" t="n">
         <v>2500</v>
       </c>
       <c r="Q236" t="n">
-        <v>1012500</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="237">
@@ -11261,22 +11261,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M253" t="n">
-        <v>2394</v>
+        <v>2330</v>
       </c>
       <c r="N253" t="n">
         <v>3591.13</v>
       </c>
       <c r="O253" t="n">
-        <v>8597165.220000001</v>
+        <v>8367332.9</v>
       </c>
       <c r="P253" t="n">
         <v>6300</v>
       </c>
       <c r="Q253" t="n">
-        <v>15082200</v>
+        <v>14679000</v>
       </c>
     </row>
     <row r="254">
@@ -11809,22 +11809,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M266" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
         <v>21418.04</v>
       </c>
       <c r="O266" t="n">
-        <v>642541.2000000001</v>
+        <v>0</v>
       </c>
       <c r="P266" t="n">
         <v>34900</v>
       </c>
       <c r="Q266" t="n">
-        <v>1047000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -12126,22 +12126,22 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M273" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="N273" t="n">
         <v>4100.45</v>
       </c>
       <c r="O273" t="n">
-        <v>348538.25</v>
+        <v>250127.45</v>
       </c>
       <c r="P273" t="n">
         <v>26900</v>
       </c>
       <c r="Q273" t="n">
-        <v>2286500</v>
+        <v>1640900</v>
       </c>
     </row>
     <row r="274">
@@ -13022,10 +13022,10 @@
         <v>399</v>
       </c>
       <c r="N293" t="n">
-        <v>5218.1705134189</v>
+        <v>5218.1705164319</v>
       </c>
       <c r="O293" t="n">
-        <v>2082050.034854141</v>
+        <v>2082050.036056328</v>
       </c>
       <c r="P293" t="n">
         <v>8500</v>
@@ -13068,10 +13068,10 @@
         <v>206</v>
       </c>
       <c r="N294" t="n">
-        <v>1595.0094571429</v>
+        <v>1595.0094492754</v>
       </c>
       <c r="O294" t="n">
-        <v>328571.9481714374</v>
+        <v>328571.9465507324</v>
       </c>
       <c r="P294" t="n">
         <v>2600</v>
@@ -13528,10 +13528,10 @@
         <v>384</v>
       </c>
       <c r="N304" t="n">
-        <v>1664.359264432</v>
+        <v>1664.3592041199</v>
       </c>
       <c r="O304" t="n">
-        <v>639113.957541888</v>
+        <v>639113.9343820416</v>
       </c>
       <c r="P304" t="n">
         <v>2900</v>
@@ -14218,10 +14218,10 @@
         <v>1145</v>
       </c>
       <c r="N319" t="n">
-        <v>1778.4725650066</v>
+        <v>1778.4725680247</v>
       </c>
       <c r="O319" t="n">
-        <v>2036351.086932557</v>
+        <v>2036351.090388282</v>
       </c>
       <c r="P319" t="n">
         <v>4900</v>
@@ -14304,22 +14304,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M321" t="n">
-        <v>672</v>
+        <v>648</v>
       </c>
       <c r="N321" t="n">
         <v>22739</v>
       </c>
       <c r="O321" t="n">
-        <v>15280608</v>
+        <v>14734872</v>
       </c>
       <c r="P321" t="n">
         <v>36900</v>
       </c>
       <c r="Q321" t="n">
-        <v>24796800</v>
+        <v>23911200</v>
       </c>
     </row>
     <row r="322">
@@ -15046,10 +15046,10 @@
         <v>28</v>
       </c>
       <c r="N337" t="n">
-        <v>2252.2964527845</v>
+        <v>2252.2965479115</v>
       </c>
       <c r="O337" t="n">
-        <v>63064.30067796601</v>
+        <v>63064.303341522</v>
       </c>
       <c r="P337" t="n">
         <v>3900</v>
@@ -16868,22 +16868,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M377" t="n">
-        <v>355</v>
+        <v>254</v>
       </c>
       <c r="N377" t="n">
         <v>59834</v>
       </c>
       <c r="O377" t="n">
-        <v>21241070</v>
+        <v>15197836</v>
       </c>
       <c r="P377" t="n">
         <v>7900</v>
       </c>
       <c r="Q377" t="n">
-        <v>2804500</v>
+        <v>2006600</v>
       </c>
     </row>
     <row r="378">
@@ -16914,22 +16914,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M378" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N378" t="n">
         <v>18001</v>
       </c>
       <c r="O378" t="n">
-        <v>1296072</v>
+        <v>864048</v>
       </c>
       <c r="P378" t="n">
         <v>28900</v>
       </c>
       <c r="Q378" t="n">
-        <v>2080800</v>
+        <v>1387200</v>
       </c>
     </row>
     <row r="379">
@@ -16960,22 +16960,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M379" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N379" t="n">
         <v>10219</v>
       </c>
       <c r="O379" t="n">
-        <v>981024</v>
+        <v>0</v>
       </c>
       <c r="P379" t="n">
         <v>16900</v>
       </c>
       <c r="Q379" t="n">
-        <v>1622400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -17797,10 +17797,10 @@
         <v>4224</v>
       </c>
       <c r="N397" t="n">
-        <v>1516.0388115466</v>
+        <v>1516.0388110875</v>
       </c>
       <c r="O397" t="n">
-        <v>6403747.939972838</v>
+        <v>6403747.9380336</v>
       </c>
       <c r="P397" t="n">
         <v>2300</v>
@@ -17843,10 +17843,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>2458.5134059343</v>
+        <v>2458.5133829585</v>
       </c>
       <c r="O398" t="n">
-        <v>2832207.443636314</v>
+        <v>2832207.417168192</v>
       </c>
       <c r="P398" t="n">
         <v>3500</v>
@@ -17889,10 +17889,10 @@
         <v>480</v>
       </c>
       <c r="N399" t="n">
-        <v>1907.3942832168</v>
+        <v>1907.3941918295</v>
       </c>
       <c r="O399" t="n">
-        <v>915549.255944064</v>
+        <v>915549.21207816</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -17981,10 +17981,10 @@
         <v>960</v>
       </c>
       <c r="N401" t="n">
-        <v>2079.3842021449</v>
+        <v>2079.3841889251</v>
       </c>
       <c r="O401" t="n">
-        <v>1996208.834059104</v>
+        <v>1996208.821368096</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -18027,10 +18027,10 @@
         <v>1344</v>
       </c>
       <c r="N402" t="n">
-        <v>1803.0151441578</v>
+        <v>1803.0151566778</v>
       </c>
       <c r="O402" t="n">
-        <v>2423252.353748083</v>
+        <v>2423252.370574963</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -18073,10 +18073,10 @@
         <v>144</v>
       </c>
       <c r="N403" t="n">
-        <v>3306.5953548387</v>
+        <v>3306.5953488372</v>
       </c>
       <c r="O403" t="n">
-        <v>476149.7310967728</v>
+        <v>476149.7302325568</v>
       </c>
       <c r="P403" t="n">
         <v>4900</v>
@@ -18119,10 +18119,10 @@
         <v>1440</v>
       </c>
       <c r="N404" t="n">
-        <v>2122.1640091884</v>
+        <v>2122.1640073529</v>
       </c>
       <c r="O404" t="n">
-        <v>3055916.173231296</v>
+        <v>3055916.170588176</v>
       </c>
       <c r="P404" t="n">
         <v>2900</v>
@@ -18165,10 +18165,10 @@
         <v>612</v>
       </c>
       <c r="N405" t="n">
-        <v>2108.7899828473</v>
+        <v>2108.7899885584</v>
       </c>
       <c r="O405" t="n">
-        <v>1290579.469502548</v>
+        <v>1290579.472997741</v>
       </c>
       <c r="P405" t="n">
         <v>2900</v>
@@ -18211,10 +18211,10 @@
         <v>684</v>
       </c>
       <c r="N406" t="n">
-        <v>2056.0838571429</v>
+        <v>2056.0838222089</v>
       </c>
       <c r="O406" t="n">
-        <v>1406361.358285744</v>
+        <v>1406361.334390888</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
@@ -18257,10 +18257,10 @@
         <v>714</v>
       </c>
       <c r="N407" t="n">
-        <v>3224.5682755432</v>
+        <v>3224.568287037</v>
       </c>
       <c r="O407" t="n">
-        <v>2302341.748737845</v>
+        <v>2302341.756944418</v>
       </c>
       <c r="P407" t="n">
         <v>4500</v>
@@ -18303,10 +18303,10 @@
         <v>1152</v>
       </c>
       <c r="N408" t="n">
-        <v>1655.9310860458</v>
+        <v>1655.931057226</v>
       </c>
       <c r="O408" t="n">
-        <v>1907632.611124761</v>
+        <v>1907632.577924352</v>
       </c>
       <c r="P408" t="n">
         <v>2500</v>
@@ -19372,10 +19372,10 @@
         <v>75</v>
       </c>
       <c r="N431" t="n">
-        <v>345.55838640256</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O431" t="n">
-        <v>25916.878980192</v>
+        <v>25916.87897487675</v>
       </c>
       <c r="P431" t="n">
         <v>600</v>
@@ -19416,10 +19416,10 @@
         <v>216</v>
       </c>
       <c r="N432" t="n">
-        <v>2286.1648643761</v>
+        <v>2286.164845735</v>
       </c>
       <c r="O432" t="n">
-        <v>493811.6107052376</v>
+        <v>493811.60667876</v>
       </c>
       <c r="P432" t="n">
         <v>3000</v>
@@ -19591,10 +19591,10 @@
         <v>1</v>
       </c>
       <c r="N436" t="n">
-        <v>1283.6540655738</v>
+        <v>1283.653986711</v>
       </c>
       <c r="O436" t="n">
-        <v>1283.6540655738</v>
+        <v>1283.653986711</v>
       </c>
       <c r="P436" t="n">
         <v>1900</v>
@@ -19772,10 +19772,10 @@
         <v>7572</v>
       </c>
       <c r="N440" t="n">
-        <v>517.28807221513</v>
+        <v>517.28815469086</v>
       </c>
       <c r="O440" t="n">
-        <v>3916905.282812964</v>
+        <v>3916905.907319192</v>
       </c>
       <c r="P440" t="n">
         <v>900</v>
@@ -19821,10 +19821,10 @@
         <v>504</v>
       </c>
       <c r="N441" t="n">
-        <v>3110.8429525518</v>
+        <v>3110.8427709611</v>
       </c>
       <c r="O441" t="n">
-        <v>1567864.848086107</v>
+        <v>1567864.756564394</v>
       </c>
       <c r="P441" t="n">
         <v>4500</v>
@@ -19953,10 +19953,10 @@
         <v>18248</v>
       </c>
       <c r="N444" t="n">
-        <v>703.79534416571</v>
+        <v>703.79533220158</v>
       </c>
       <c r="O444" t="n">
-        <v>12842857.44033588</v>
+        <v>12842857.22201443</v>
       </c>
       <c r="P444" t="n">
         <v>900</v>
@@ -20524,22 +20524,22 @@
         <v>0</v>
       </c>
       <c r="L457" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="M457" t="n">
-        <v>2569</v>
+        <v>1669</v>
       </c>
       <c r="N457" t="n">
-        <v>1595.5190882035</v>
+        <v>1595.5155551576</v>
       </c>
       <c r="O457" t="n">
-        <v>4098888.537594791</v>
+        <v>2662915.461558034</v>
       </c>
       <c r="P457" t="n">
         <v>2500</v>
       </c>
       <c r="Q457" t="n">
-        <v>6422500</v>
+        <v>4172500</v>
       </c>
     </row>
     <row r="458">
@@ -21407,10 +21407,10 @@
         <v>1976</v>
       </c>
       <c r="N476" t="n">
-        <v>7046.9398299681</v>
+        <v>7046.939829932</v>
       </c>
       <c r="O476" t="n">
-        <v>13924753.10401697</v>
+        <v>13924753.10394563</v>
       </c>
       <c r="P476" t="n">
         <v>9900</v>
@@ -22250,10 +22250,10 @@
         <v>198</v>
       </c>
       <c r="N495" t="n">
-        <v>5577.2680778032</v>
+        <v>5577.2680733945</v>
       </c>
       <c r="O495" t="n">
-        <v>1104299.079405033</v>
+        <v>1104299.078532111</v>
       </c>
       <c r="P495" t="n">
         <v>6500</v>
@@ -22804,22 +22804,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M508" t="n">
-        <v>478</v>
+        <v>278</v>
       </c>
       <c r="N508" t="n">
         <v>3181.9</v>
       </c>
       <c r="O508" t="n">
-        <v>1520948.2</v>
+        <v>884568.2000000001</v>
       </c>
       <c r="P508" t="n">
         <v>5100</v>
       </c>
       <c r="Q508" t="n">
-        <v>2437800</v>
+        <v>1417800</v>
       </c>
     </row>
     <row r="509">
@@ -23115,10 +23115,10 @@
         <v>1329</v>
       </c>
       <c r="N515" t="n">
-        <v>2523.3377476715</v>
+        <v>2523.3377470356</v>
       </c>
       <c r="O515" t="n">
-        <v>3353515.866655423</v>
+        <v>3353515.865810312</v>
       </c>
       <c r="P515" t="n">
         <v>2800</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -968,10 +968,10 @@
         <v>860</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O14" t="n">
-        <v>1557721.855323498</v>
+        <v>1557722.110809374</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1085,10 +1085,10 @@
         <v>244</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O17" t="n">
-        <v>823926.14566938</v>
+        <v>823926.1454377996</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.55944797</v>
+        <v>1271651.560042531</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2513,10 +2513,10 @@
         <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O53" t="n">
-        <v>356582.956460184</v>
+        <v>356582.9568</v>
       </c>
       <c r="P53" t="n">
         <v>34900</v>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O54" t="n">
-        <v>594415.4858517055</v>
+        <v>594415.4853012073</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -2808,10 +2808,10 @@
         <v>136</v>
       </c>
       <c r="N60" t="n">
-        <v>7407.7300524934</v>
+        <v>7407.7300526316</v>
       </c>
       <c r="O60" t="n">
-        <v>1007451.287139102</v>
+        <v>1007451.287157898</v>
       </c>
       <c r="P60" t="n">
         <v>10900</v>
@@ -3155,10 +3155,10 @@
         <v>27</v>
       </c>
       <c r="N68" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O68" t="n">
-        <v>5401949.4</v>
+        <v>5401949.402109239</v>
       </c>
       <c r="P68" t="n">
         <v>312000</v>
@@ -3600,10 +3600,10 @@
         <v>91</v>
       </c>
       <c r="N78" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O78" t="n">
-        <v>5611685.533518519</v>
+        <v>5611685.534482755</v>
       </c>
       <c r="P78" t="n">
         <v>98900</v>
@@ -4114,10 +4114,10 @@
         <v>200</v>
       </c>
       <c r="N90" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O90" t="n">
-        <v>987462.0322344401</v>
+        <v>987462.0322580601</v>
       </c>
       <c r="P90" t="n">
         <v>7500</v>
@@ -5056,10 +5056,10 @@
         <v>1080</v>
       </c>
       <c r="N112" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O112" t="n">
-        <v>2788836.49211058</v>
+        <v>2788836.468693372</v>
       </c>
       <c r="P112" t="n">
         <v>4500</v>
@@ -5148,10 +5148,10 @@
         <v>1986</v>
       </c>
       <c r="N114" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O114" t="n">
-        <v>10360755.38740515</v>
+        <v>10360755.38024145</v>
       </c>
       <c r="P114" t="n">
         <v>8500</v>
@@ -5281,10 +5281,10 @@
         <v>6298</v>
       </c>
       <c r="N117" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O117" t="n">
-        <v>19894505.41147814</v>
+        <v>19894505.41569528</v>
       </c>
       <c r="P117" t="n">
         <v>5600</v>
@@ -5511,10 +5511,10 @@
         <v>224</v>
       </c>
       <c r="N122" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O122" t="n">
-        <v>603640.4542586657</v>
+        <v>603640.4429427903</v>
       </c>
       <c r="P122" t="n">
         <v>4900</v>
@@ -5831,10 +5831,10 @@
         <v>3024</v>
       </c>
       <c r="N129" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O129" t="n">
-        <v>11478227.06135579</v>
+        <v>11478227.06137091</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -5969,10 +5969,10 @@
         <v>64</v>
       </c>
       <c r="N132" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O132" t="n">
-        <v>313019.5229715584</v>
+        <v>313019.5229819456</v>
       </c>
       <c r="P132" t="n">
         <v>8200</v>
@@ -6246,10 +6246,10 @@
         <v>24</v>
       </c>
       <c r="N138" t="n">
-        <v>2267.0481598668</v>
+        <v>2267.0481583333</v>
       </c>
       <c r="O138" t="n">
-        <v>54409.1558368032</v>
+        <v>54409.15579999919</v>
       </c>
       <c r="P138" t="n">
         <v>3900</v>
@@ -6506,22 +6506,22 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M144" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="N144" t="n">
         <v>10716.34</v>
       </c>
       <c r="O144" t="n">
-        <v>1275244.46</v>
+        <v>1071634</v>
       </c>
       <c r="P144" t="n">
         <v>39000</v>
       </c>
       <c r="Q144" t="n">
-        <v>4641000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="145">
@@ -6602,10 +6602,10 @@
         <v>264</v>
       </c>
       <c r="N146" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O146" t="n">
-        <v>948883.0927472424</v>
+        <v>948883.088959608</v>
       </c>
       <c r="P146" t="n">
         <v>6500</v>
@@ -6827,10 +6827,10 @@
         <v>384</v>
       </c>
       <c r="N151" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O151" t="n">
-        <v>5691793.483222656</v>
+        <v>5691793.48296384</v>
       </c>
       <c r="P151" t="n">
         <v>24900</v>
@@ -6909,22 +6909,22 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M153" t="n">
-        <v>1095</v>
+        <v>903</v>
       </c>
       <c r="N153" t="n">
         <v>2090.85</v>
       </c>
       <c r="O153" t="n">
-        <v>2289480.75</v>
+        <v>1888037.55</v>
       </c>
       <c r="P153" t="n">
         <v>2900</v>
       </c>
       <c r="Q153" t="n">
-        <v>3175500</v>
+        <v>2618700</v>
       </c>
     </row>
     <row r="154">
@@ -7230,10 +7230,10 @@
         <v>78</v>
       </c>
       <c r="N160" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O160" t="n">
-        <v>237249.4809867156</v>
+        <v>237249.4809948978</v>
       </c>
       <c r="P160" t="n">
         <v>5500</v>
@@ -8410,22 +8410,22 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M187" t="n">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="N187" t="n">
         <v>9903</v>
       </c>
       <c r="O187" t="n">
-        <v>5139657</v>
+        <v>5020821</v>
       </c>
       <c r="P187" t="n">
         <v>15900</v>
       </c>
       <c r="Q187" t="n">
-        <v>8252100</v>
+        <v>8061300</v>
       </c>
     </row>
     <row r="188">
@@ -8462,10 +8462,10 @@
         <v>1152</v>
       </c>
       <c r="N188" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O188" t="n">
-        <v>1878823.478890944</v>
+        <v>1878823.495407514</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8508,10 +8508,10 @@
         <v>768</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.6026503973</v>
+        <v>1690.6023498845</v>
       </c>
       <c r="O189" t="n">
-        <v>1298382.835505127</v>
+        <v>1298382.604711296</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8554,10 +8554,10 @@
         <v>5472</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O190" t="n">
-        <v>8482656.948978644</v>
+        <v>8482657.101578496</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8600,10 +8600,10 @@
         <v>2016</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O191" t="n">
-        <v>4845476.910781585</v>
+        <v>4845477.086857612</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -10232,10 +10232,10 @@
         <v>1254</v>
       </c>
       <c r="N229" t="n">
-        <v>880.3293685687599</v>
+        <v>880.32937295274</v>
       </c>
       <c r="O229" t="n">
-        <v>1103933.028185225</v>
+        <v>1103933.033682736</v>
       </c>
       <c r="P229" t="n">
         <v>1200</v>
@@ -10539,10 +10539,10 @@
         <v>523</v>
       </c>
       <c r="N236" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O236" t="n">
-        <v>522352.1389200956</v>
+        <v>522352.1394596067</v>
       </c>
       <c r="P236" t="n">
         <v>1600</v>
@@ -10716,10 +10716,10 @@
         <v>390</v>
       </c>
       <c r="N240" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O240" t="n">
-        <v>1671226.157320863</v>
+        <v>1671226.159459467</v>
       </c>
       <c r="P240" t="n">
         <v>6900</v>
@@ -11313,10 +11313,10 @@
         <v>95</v>
       </c>
       <c r="N254" t="n">
-        <v>12005.159831933</v>
+        <v>12005.159831224</v>
       </c>
       <c r="O254" t="n">
-        <v>1140490.184033635</v>
+        <v>1140490.18396628</v>
       </c>
       <c r="P254" t="n">
         <v>19500</v>
@@ -12930,10 +12930,10 @@
         <v>399</v>
       </c>
       <c r="N291" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O291" t="n">
-        <v>2082050.036056328</v>
+        <v>2082050.038009473</v>
       </c>
       <c r="P291" t="n">
         <v>8500</v>
@@ -12976,10 +12976,10 @@
         <v>206</v>
       </c>
       <c r="N292" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="O292" t="n">
-        <v>328571.9465507324</v>
+        <v>328571.9462209264</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
@@ -13022,10 +13022,10 @@
         <v>541</v>
       </c>
       <c r="N293" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O293" t="n">
-        <v>1953361.6634577</v>
+        <v>1953361.663508121</v>
       </c>
       <c r="P293" t="n">
         <v>5800</v>
@@ -13338,22 +13338,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M300" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="N300" t="n">
         <v>6058.52</v>
       </c>
       <c r="O300" t="n">
-        <v>920895.04</v>
+        <v>617969.04</v>
       </c>
       <c r="P300" t="n">
         <v>9700</v>
       </c>
       <c r="Q300" t="n">
-        <v>1474400</v>
+        <v>989400</v>
       </c>
     </row>
     <row r="301">
@@ -13436,10 +13436,10 @@
         <v>384</v>
       </c>
       <c r="N302" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O302" t="n">
-        <v>639113.9343820416</v>
+        <v>639113.8673263488</v>
       </c>
       <c r="P302" t="n">
         <v>2900</v>
@@ -14954,10 +14954,10 @@
         <v>28</v>
       </c>
       <c r="N335" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O335" t="n">
-        <v>63064.303341522</v>
+        <v>63064.3035670368</v>
       </c>
       <c r="P335" t="n">
         <v>3900</v>
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -16779,19 +16779,19 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="N375" t="n">
         <v>59834</v>
       </c>
       <c r="O375" t="n">
-        <v>15197836</v>
+        <v>21241070</v>
       </c>
       <c r="P375" t="n">
         <v>7900</v>
       </c>
       <c r="Q375" t="n">
-        <v>2006600</v>
+        <v>2804500</v>
       </c>
     </row>
     <row r="376">
@@ -17659,10 +17659,10 @@
         <v>4224</v>
       </c>
       <c r="N394" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O394" t="n">
-        <v>6403747.9380336</v>
+        <v>6403747.934636237</v>
       </c>
       <c r="P394" t="n">
         <v>2300</v>
@@ -17705,10 +17705,10 @@
         <v>1152</v>
       </c>
       <c r="N395" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O395" t="n">
-        <v>2832207.417168192</v>
+        <v>2832207.405076109</v>
       </c>
       <c r="P395" t="n">
         <v>3500</v>
@@ -17751,10 +17751,10 @@
         <v>480</v>
       </c>
       <c r="N396" t="n">
-        <v>1907.3941918295</v>
+        <v>1907.3940437158</v>
       </c>
       <c r="O396" t="n">
-        <v>915549.21207816</v>
+        <v>915549.140983584</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17797,10 +17797,10 @@
         <v>576</v>
       </c>
       <c r="N397" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O397" t="n">
-        <v>1020148.493341536</v>
+        <v>1020148.483931194</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
@@ -17843,10 +17843,10 @@
         <v>960</v>
       </c>
       <c r="N398" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O398" t="n">
-        <v>1996208.821368096</v>
+        <v>1996208.814090048</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -17889,10 +17889,10 @@
         <v>1344</v>
       </c>
       <c r="N399" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O399" t="n">
-        <v>2423252.370574963</v>
+        <v>2423252.391724147</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -17981,10 +17981,10 @@
         <v>1440</v>
       </c>
       <c r="N401" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O401" t="n">
-        <v>3055916.170588176</v>
+        <v>3055916.165297328</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -18027,10 +18027,10 @@
         <v>612</v>
       </c>
       <c r="N402" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O402" t="n">
-        <v>1290579.472997741</v>
+        <v>1290579.511709862</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
@@ -18073,10 +18073,10 @@
         <v>684</v>
       </c>
       <c r="N403" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O403" t="n">
-        <v>1406361.334390888</v>
+        <v>1406361.263664056</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
@@ -18119,10 +18119,10 @@
         <v>714</v>
       </c>
       <c r="N404" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O404" t="n">
-        <v>2302341.756944418</v>
+        <v>2302341.767922096</v>
       </c>
       <c r="P404" t="n">
         <v>4500</v>
@@ -18165,10 +18165,10 @@
         <v>1152</v>
       </c>
       <c r="N405" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O405" t="n">
-        <v>1907632.577924352</v>
+        <v>1907632.537799386</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -19634,10 +19634,10 @@
         <v>7572</v>
       </c>
       <c r="N437" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O437" t="n">
-        <v>3916905.907319192</v>
+        <v>3916906.610992345</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -19683,10 +19683,10 @@
         <v>504</v>
       </c>
       <c r="N438" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O438" t="n">
-        <v>1567864.756564394</v>
+        <v>1567864.717403897</v>
       </c>
       <c r="P438" t="n">
         <v>4500</v>
@@ -19815,10 +19815,10 @@
         <v>18248</v>
       </c>
       <c r="N441" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O441" t="n">
-        <v>12842857.22201443</v>
+        <v>12842857.002568</v>
       </c>
       <c r="P441" t="n">
         <v>900</v>
@@ -20392,10 +20392,10 @@
         <v>1669</v>
       </c>
       <c r="N454" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O454" t="n">
-        <v>2662915.461558034</v>
+        <v>2662915.4183064</v>
       </c>
       <c r="P454" t="n">
         <v>2500</v>
@@ -21269,10 +21269,10 @@
         <v>1976</v>
       </c>
       <c r="N473" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O473" t="n">
-        <v>13924753.10394563</v>
+        <v>13924753.1038741</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -22848,10 +22848,10 @@
         <v>68</v>
       </c>
       <c r="N509" t="n">
-        <v>2830.2251183432</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O509" t="n">
-        <v>192455.3080473376</v>
+        <v>192455.310119046</v>
       </c>
       <c r="P509" t="n">
         <v>2400</v>
@@ -23185,10 +23185,10 @@
         <v>427</v>
       </c>
       <c r="N517" t="n">
-        <v>3153.2320501475</v>
+        <v>3153.2320511559</v>
       </c>
       <c r="O517" t="n">
-        <v>1346430.085412983</v>
+        <v>1346430.085843569</v>
       </c>
       <c r="P517" t="n">
         <v>3300</v>
@@ -23399,10 +23399,10 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="O522" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="P522" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>100</v>
@@ -6903,13 +6903,13 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>1095</v>
+        <v>903</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>903</v>
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
         <v>507</v>
@@ -13332,13 +13332,13 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
         <v>102</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -962,22 +962,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M14" t="n">
-        <v>860</v>
+        <v>360</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3047800109</v>
+        <v>1811.3053012048</v>
       </c>
       <c r="O14" t="n">
-        <v>1557722.110809374</v>
+        <v>652069.9084337279</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>2236000</v>
+        <v>936000</v>
       </c>
     </row>
     <row r="15">
@@ -1085,10 +1085,10 @@
         <v>244</v>
       </c>
       <c r="N17" t="n">
-        <v>3376.7464976959</v>
+        <v>3376.7464891304</v>
       </c>
       <c r="O17" t="n">
-        <v>823926.1454377996</v>
+        <v>823926.1433478176</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
@@ -1881,10 +1881,10 @@
         <v>216</v>
       </c>
       <c r="N37" t="n">
-        <v>6272.8545786963</v>
+        <v>6272.8545933014</v>
       </c>
       <c r="O37" t="n">
-        <v>1354936.588998401</v>
+        <v>1354936.592153102</v>
       </c>
       <c r="P37" t="n">
         <v>7900</v>
@@ -1920,10 +1920,10 @@
         <v>649</v>
       </c>
       <c r="N38" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O38" t="n">
-        <v>2548517.29333335</v>
+        <v>2548517.281757137</v>
       </c>
       <c r="P38" t="n">
         <v>4800</v>
@@ -2045,10 +2045,10 @@
         <v>527</v>
       </c>
       <c r="N41" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="O41" t="n">
-        <v>1271651.560042531</v>
+        <v>1271651.563034205</v>
       </c>
       <c r="P41" t="n">
         <v>4700</v>
@@ -2123,10 +2123,10 @@
         <v>144</v>
       </c>
       <c r="N43" t="n">
-        <v>3716.3301892744</v>
+        <v>3716.3301923077</v>
       </c>
       <c r="O43" t="n">
-        <v>535151.5472555136</v>
+        <v>535151.5476923088</v>
       </c>
       <c r="P43" t="n">
         <v>9500</v>
@@ -2552,10 +2552,10 @@
         <v>152</v>
       </c>
       <c r="N54" t="n">
-        <v>3910.6281927711</v>
+        <v>3910.6281818182</v>
       </c>
       <c r="O54" t="n">
-        <v>594415.4853012073</v>
+        <v>594415.4836363664</v>
       </c>
       <c r="P54" t="n">
         <v>9100</v>
@@ -2594,10 +2594,10 @@
         <v>60</v>
       </c>
       <c r="N55" t="n">
-        <v>16486.409172932</v>
+        <v>16486.409090909</v>
       </c>
       <c r="O55" t="n">
-        <v>989184.5503759199</v>
+        <v>989184.5454545401</v>
       </c>
       <c r="P55" t="n">
         <v>30500</v>
@@ -3155,10 +3155,10 @@
         <v>27</v>
       </c>
       <c r="N68" t="n">
-        <v>200072.20007812</v>
+        <v>200072.20015748</v>
       </c>
       <c r="O68" t="n">
-        <v>5401949.402109239</v>
+        <v>5401949.40425196</v>
       </c>
       <c r="P68" t="n">
         <v>312000</v>
@@ -3600,10 +3600,10 @@
         <v>91</v>
       </c>
       <c r="N78" t="n">
-        <v>61666.874005305</v>
+        <v>61666.874015957</v>
       </c>
       <c r="O78" t="n">
-        <v>5611685.534482755</v>
+        <v>5611685.535452087</v>
       </c>
       <c r="P78" t="n">
         <v>98900</v>
@@ -3986,10 +3986,10 @@
         <v>1440</v>
       </c>
       <c r="N87" t="n">
-        <v>1950.2147262682</v>
+        <v>1950.2147103275</v>
       </c>
       <c r="O87" t="n">
-        <v>2808309.205826208</v>
+        <v>2808309.1828716</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -5056,10 +5056,10 @@
         <v>1080</v>
       </c>
       <c r="N112" t="n">
-        <v>2582.2559895309</v>
+        <v>2582.2559749444</v>
       </c>
       <c r="O112" t="n">
-        <v>2788836.468693372</v>
+        <v>2788836.452939952</v>
       </c>
       <c r="P112" t="n">
         <v>4500</v>
@@ -5148,10 +5148,10 @@
         <v>1986</v>
       </c>
       <c r="N114" t="n">
-        <v>5216.8959618537</v>
+        <v>5216.8962134973</v>
       </c>
       <c r="O114" t="n">
-        <v>10360755.38024145</v>
+        <v>10360755.88000564</v>
       </c>
       <c r="P114" t="n">
         <v>8500</v>
@@ -5281,10 +5281,10 @@
         <v>6298</v>
       </c>
       <c r="N117" t="n">
-        <v>3158.8608154486</v>
+        <v>3158.8608230874</v>
       </c>
       <c r="O117" t="n">
-        <v>19894505.41569528</v>
+        <v>19894505.46380445</v>
       </c>
       <c r="P117" t="n">
         <v>5600</v>
@@ -5511,10 +5511,10 @@
         <v>224</v>
       </c>
       <c r="N122" t="n">
-        <v>2694.8234059946</v>
+        <v>2694.8233333333</v>
       </c>
       <c r="O122" t="n">
-        <v>603640.4429427903</v>
+        <v>603640.4266666592</v>
       </c>
       <c r="P122" t="n">
         <v>4900</v>
@@ -5831,10 +5831,10 @@
         <v>3024</v>
       </c>
       <c r="N129" t="n">
-        <v>3795.7100070671</v>
+        <v>3795.7100070822</v>
       </c>
       <c r="O129" t="n">
-        <v>11478227.06137091</v>
+        <v>11478227.06141657</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -5969,10 +5969,10 @@
         <v>64</v>
       </c>
       <c r="N132" t="n">
-        <v>4890.9300465929</v>
+        <v>4890.9300467563</v>
       </c>
       <c r="O132" t="n">
-        <v>313019.5229819456</v>
+        <v>313019.5229924032</v>
       </c>
       <c r="P132" t="n">
         <v>8200</v>
@@ -6602,10 +6602,10 @@
         <v>264</v>
       </c>
       <c r="N146" t="n">
-        <v>3594.254124847</v>
+        <v>3594.2541140405</v>
       </c>
       <c r="O146" t="n">
-        <v>948883.088959608</v>
+        <v>948883.086106692</v>
       </c>
       <c r="P146" t="n">
         <v>6500</v>
@@ -7230,10 +7230,10 @@
         <v>78</v>
       </c>
       <c r="N160" t="n">
-        <v>3041.6600127551</v>
+        <v>3041.6600128617</v>
       </c>
       <c r="O160" t="n">
-        <v>237249.4809948978</v>
+        <v>237249.4810032126</v>
       </c>
       <c r="P160" t="n">
         <v>5500</v>
@@ -7317,10 +7317,10 @@
         <v>809</v>
       </c>
       <c r="N162" t="n">
-        <v>4372.2107877711</v>
+        <v>4372.2107879391</v>
       </c>
       <c r="O162" t="n">
-        <v>3537118.52730682</v>
+        <v>3537118.527442731</v>
       </c>
       <c r="P162" t="n">
         <v>7500</v>
@@ -8462,10 +8462,10 @@
         <v>1152</v>
       </c>
       <c r="N188" t="n">
-        <v>1630.9231730968</v>
+        <v>1630.9233118002</v>
       </c>
       <c r="O188" t="n">
-        <v>1878823.495407514</v>
+        <v>1878823.65519383</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8508,10 +8508,10 @@
         <v>768</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.6023498845</v>
+        <v>1690.6006518987</v>
       </c>
       <c r="O189" t="n">
-        <v>1298382.604711296</v>
+        <v>1298381.300658202</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8554,10 +8554,10 @@
         <v>5472</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.193183768</v>
+        <v>1550.1933219945</v>
       </c>
       <c r="O190" t="n">
-        <v>8482657.101578496</v>
+        <v>8482657.857953904</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8600,10 +8600,10 @@
         <v>2016</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5104597508</v>
+        <v>2403.5107961064</v>
       </c>
       <c r="O191" t="n">
-        <v>4845477.086857612</v>
+        <v>4845477.764950503</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -10716,10 +10716,10 @@
         <v>390</v>
       </c>
       <c r="N240" t="n">
-        <v>4285.1952806653</v>
+        <v>4285.1953699789</v>
       </c>
       <c r="O240" t="n">
-        <v>1671226.159459467</v>
+        <v>1671226.194291771</v>
       </c>
       <c r="P240" t="n">
         <v>6900</v>
@@ -12562,10 +12562,10 @@
         <v>433</v>
       </c>
       <c r="N283" t="n">
-        <v>3113.8900262812</v>
+        <v>3113.8900265957</v>
       </c>
       <c r="O283" t="n">
-        <v>1348314.38137976</v>
+        <v>1348314.381515938</v>
       </c>
       <c r="P283" t="n">
         <v>5000</v>
@@ -12930,10 +12930,10 @@
         <v>399</v>
       </c>
       <c r="N291" t="n">
-        <v>5218.170521327</v>
+        <v>5218.1705238095</v>
       </c>
       <c r="O291" t="n">
-        <v>2082050.038009473</v>
+        <v>2082050.038999991</v>
       </c>
       <c r="P291" t="n">
         <v>8500</v>
@@ -12976,10 +12976,10 @@
         <v>206</v>
       </c>
       <c r="N292" t="n">
-        <v>1595.0094476744</v>
+        <v>1595.0094378698</v>
       </c>
       <c r="O292" t="n">
-        <v>328571.9462209264</v>
+        <v>328571.9442011788</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
@@ -13022,10 +13022,10 @@
         <v>541</v>
       </c>
       <c r="N293" t="n">
-        <v>3610.6500249688</v>
+        <v>3610.6500252207</v>
       </c>
       <c r="O293" t="n">
-        <v>1953361.663508121</v>
+        <v>1953361.663644399</v>
       </c>
       <c r="P293" t="n">
         <v>5800</v>
@@ -13436,10 +13436,10 @@
         <v>384</v>
       </c>
       <c r="N302" t="n">
-        <v>1664.3590294957</v>
+        <v>1664.3585273632</v>
       </c>
       <c r="O302" t="n">
-        <v>639113.8673263488</v>
+        <v>639113.6745074688</v>
       </c>
       <c r="P302" t="n">
         <v>2900</v>
@@ -14126,10 +14126,10 @@
         <v>1145</v>
       </c>
       <c r="N317" t="n">
-        <v>1778.4725680247</v>
+        <v>1778.4725740823</v>
       </c>
       <c r="O317" t="n">
-        <v>2036351.090388282</v>
+        <v>2036351.097324234</v>
       </c>
       <c r="P317" t="n">
         <v>4900</v>
@@ -17659,10 +17659,10 @@
         <v>4224</v>
       </c>
       <c r="N394" t="n">
-        <v>1516.0388102832</v>
+        <v>1516.0388052024</v>
       </c>
       <c r="O394" t="n">
-        <v>6403747.934636237</v>
+        <v>6403747.913174937</v>
       </c>
       <c r="P394" t="n">
         <v>2300</v>
@@ -17751,10 +17751,10 @@
         <v>480</v>
       </c>
       <c r="N396" t="n">
-        <v>1907.3940437158</v>
+        <v>1907.394010989</v>
       </c>
       <c r="O396" t="n">
-        <v>915549.140983584</v>
+        <v>915549.12527472</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17797,10 +17797,10 @@
         <v>576</v>
       </c>
       <c r="N397" t="n">
-        <v>1771.0911179361</v>
+        <v>1771.0908132147</v>
       </c>
       <c r="O397" t="n">
-        <v>1020148.483931194</v>
+        <v>1020148.308411667</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
@@ -17843,10 +17843,10 @@
         <v>960</v>
       </c>
       <c r="N398" t="n">
-        <v>2079.3841813438</v>
+        <v>2079.3841354372</v>
       </c>
       <c r="O398" t="n">
-        <v>1996208.814090048</v>
+        <v>1996208.770019712</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -17889,10 +17889,10 @@
         <v>1344</v>
       </c>
       <c r="N399" t="n">
-        <v>1803.0151724138</v>
+        <v>1803.0152234206</v>
       </c>
       <c r="O399" t="n">
-        <v>2423252.391724147</v>
+        <v>2423252.460277286</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -17935,10 +17935,10 @@
         <v>144</v>
       </c>
       <c r="N400" t="n">
-        <v>3306.5953488372</v>
+        <v>3306.5953246753</v>
       </c>
       <c r="O400" t="n">
-        <v>476149.7302325568</v>
+        <v>476149.7267532432</v>
       </c>
       <c r="P400" t="n">
         <v>4900</v>
@@ -17981,10 +17981,10 @@
         <v>1440</v>
       </c>
       <c r="N401" t="n">
-        <v>2122.1640036787</v>
+        <v>2122.164</v>
       </c>
       <c r="O401" t="n">
-        <v>3055916.165297328</v>
+        <v>3055916.16</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -18027,10 +18027,10 @@
         <v>612</v>
       </c>
       <c r="N402" t="n">
-        <v>2108.7900518135</v>
+        <v>2108.7900692042</v>
       </c>
       <c r="O402" t="n">
-        <v>1290579.511709862</v>
+        <v>1290579.52235297</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
@@ -18073,10 +18073,10 @@
         <v>684</v>
       </c>
       <c r="N403" t="n">
-        <v>2056.0837188071</v>
+        <v>2056.0837111517</v>
       </c>
       <c r="O403" t="n">
-        <v>1406361.263664056</v>
+        <v>1406361.258427763</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
@@ -18165,10 +18165,10 @@
         <v>1152</v>
       </c>
       <c r="N405" t="n">
-        <v>1655.9310223953</v>
+        <v>1655.9309931618</v>
       </c>
       <c r="O405" t="n">
-        <v>1907632.537799386</v>
+        <v>1907632.504122394</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -18964,10 +18964,10 @@
         <v>2</v>
       </c>
       <c r="N422" t="n">
-        <v>1530.4499206034</v>
+        <v>1530.4499195171</v>
       </c>
       <c r="O422" t="n">
-        <v>3060.8998412068</v>
+        <v>3060.8998390342</v>
       </c>
       <c r="P422" t="n">
         <v>2600</v>
@@ -19634,10 +19634,10 @@
         <v>7572</v>
       </c>
       <c r="N437" t="n">
-        <v>517.28824762181</v>
+        <v>517.28836312001</v>
       </c>
       <c r="O437" t="n">
-        <v>3916906.610992345</v>
+        <v>3916907.485544716</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -19683,10 +19683,10 @@
         <v>504</v>
       </c>
       <c r="N438" t="n">
-        <v>3110.8426932617</v>
+        <v>3110.8426185007</v>
       </c>
       <c r="O438" t="n">
-        <v>1567864.717403897</v>
+        <v>1567864.679724353</v>
       </c>
       <c r="P438" t="n">
         <v>4500</v>
@@ -19815,10 +19815,10 @@
         <v>18248</v>
       </c>
       <c r="N441" t="n">
-        <v>703.7953201758</v>
+        <v>703.79529676406</v>
       </c>
       <c r="O441" t="n">
-        <v>12842857.002568</v>
+        <v>12842856.57535057</v>
       </c>
       <c r="P441" t="n">
         <v>900</v>
@@ -20392,10 +20392,10 @@
         <v>1669</v>
       </c>
       <c r="N454" t="n">
-        <v>1595.5155292429</v>
+        <v>1595.5153131828</v>
       </c>
       <c r="O454" t="n">
-        <v>2662915.4183064</v>
+        <v>2662915.057702093</v>
       </c>
       <c r="P454" t="n">
         <v>2500</v>
@@ -20897,10 +20897,10 @@
         <v>4</v>
       </c>
       <c r="N465" t="n">
-        <v>1783.7988843537</v>
+        <v>1783.7988833409</v>
       </c>
       <c r="O465" t="n">
-        <v>7135.1955374148</v>
+        <v>7135.1955333636</v>
       </c>
       <c r="P465" t="n">
         <v>1500</v>
@@ -21269,10 +21269,10 @@
         <v>1976</v>
       </c>
       <c r="N473" t="n">
-        <v>7046.9398298958</v>
+        <v>7046.9398286204</v>
       </c>
       <c r="O473" t="n">
-        <v>13924753.1038741</v>
+        <v>13924753.10135391</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -22112,10 +22112,10 @@
         <v>198</v>
       </c>
       <c r="N492" t="n">
-        <v>5577.2680733945</v>
+        <v>5577.2680465116</v>
       </c>
       <c r="O492" t="n">
-        <v>1104299.078532111</v>
+        <v>1104299.073209297</v>
       </c>
       <c r="P492" t="n">
         <v>6500</v>
@@ -23399,10 +23399,10 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>4985.4047058824</v>
+        <v>4985.4047808765</v>
       </c>
       <c r="O522" t="n">
-        <v>4985.4047058824</v>
+        <v>4985.4047808765</v>
       </c>
       <c r="P522" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>860</v>
+        <v>360</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>360</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>6966000</v>
+        <v>6804000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5160000</v>
+        <v>5040000</v>
       </c>
     </row>
     <row r="5">
@@ -962,22 +962,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M14" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O14" t="n">
-        <v>652069.9084337279</v>
+        <v>326034.959999994</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>936000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="15">
@@ -2123,10 +2123,10 @@
         <v>144</v>
       </c>
       <c r="N43" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O43" t="n">
-        <v>535151.5476923088</v>
+        <v>535151.5478709696</v>
       </c>
       <c r="P43" t="n">
         <v>9500</v>
@@ -2722,10 +2722,10 @@
         <v>48</v>
       </c>
       <c r="N58" t="n">
-        <v>30238.812535211</v>
+        <v>30238.812571429</v>
       </c>
       <c r="O58" t="n">
-        <v>1451463.001690128</v>
+        <v>1451463.003428592</v>
       </c>
       <c r="P58" t="n">
         <v>51100</v>
@@ -2808,10 +2808,10 @@
         <v>136</v>
       </c>
       <c r="N60" t="n">
-        <v>7407.7300526316</v>
+        <v>7407.7300533333</v>
       </c>
       <c r="O60" t="n">
-        <v>1007451.287157898</v>
+        <v>1007451.287253329</v>
       </c>
       <c r="P60" t="n">
         <v>10900</v>
@@ -3113,10 +3113,10 @@
         <v>112</v>
       </c>
       <c r="N67" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O67" t="n">
-        <v>15838691.0690904</v>
+        <v>15838691.07074912</v>
       </c>
       <c r="P67" t="n">
         <v>251900</v>
@@ -3986,10 +3986,10 @@
         <v>1440</v>
       </c>
       <c r="N87" t="n">
-        <v>1950.2147103275</v>
+        <v>1950.21469429</v>
       </c>
       <c r="O87" t="n">
-        <v>2808309.1828716</v>
+        <v>2808309.1597776</v>
       </c>
       <c r="P87" t="n">
         <v>2900</v>
@@ -4375,10 +4375,10 @@
         <v>244</v>
       </c>
       <c r="N96" t="n">
-        <v>21084.771458886</v>
+        <v>21084.771462766</v>
       </c>
       <c r="O96" t="n">
-        <v>5144684.235968184</v>
+        <v>5144684.236914904</v>
       </c>
       <c r="P96" t="n">
         <v>30000</v>
@@ -4457,10 +4457,10 @@
         <v>157</v>
       </c>
       <c r="N98" t="n">
-        <v>31233.611793893</v>
+        <v>31233.611800766</v>
       </c>
       <c r="O98" t="n">
-        <v>4903677.051641201</v>
+        <v>4903677.052720262</v>
       </c>
       <c r="P98" t="n">
         <v>45500</v>
@@ -5056,10 +5056,10 @@
         <v>1080</v>
       </c>
       <c r="N112" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O112" t="n">
-        <v>2788836.452939952</v>
+        <v>2788836.44237388</v>
       </c>
       <c r="P112" t="n">
         <v>4500</v>
@@ -5281,10 +5281,10 @@
         <v>6298</v>
       </c>
       <c r="N117" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O117" t="n">
-        <v>19894505.46380445</v>
+        <v>19894505.4673477</v>
       </c>
       <c r="P117" t="n">
         <v>5600</v>
@@ -5373,10 +5373,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O119" t="n">
-        <v>553193.9627707296</v>
+        <v>553193.9667909648</v>
       </c>
       <c r="P119" t="n">
         <v>6900</v>
@@ -5511,10 +5511,10 @@
         <v>224</v>
       </c>
       <c r="N122" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O122" t="n">
-        <v>603640.4266666592</v>
+        <v>603640.4156151712</v>
       </c>
       <c r="P122" t="n">
         <v>4900</v>
@@ -5831,10 +5831,10 @@
         <v>3024</v>
       </c>
       <c r="N129" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O129" t="n">
-        <v>11478227.06141657</v>
+        <v>11478227.06143169</v>
       </c>
       <c r="P129" t="n">
         <v>6200</v>
@@ -5969,10 +5969,10 @@
         <v>64</v>
       </c>
       <c r="N132" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O132" t="n">
-        <v>313019.5229924032</v>
+        <v>313019.5229976576</v>
       </c>
       <c r="P132" t="n">
         <v>8200</v>
@@ -6327,22 +6327,22 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M140" t="n">
-        <v>2452</v>
+        <v>2406</v>
       </c>
       <c r="N140" t="n">
         <v>5667.94</v>
       </c>
       <c r="O140" t="n">
-        <v>13897788.88</v>
+        <v>13637063.64</v>
       </c>
       <c r="P140" t="n">
         <v>9500</v>
       </c>
       <c r="Q140" t="n">
-        <v>23294000</v>
+        <v>22857000</v>
       </c>
     </row>
     <row r="141">
@@ -6827,10 +6827,10 @@
         <v>384</v>
       </c>
       <c r="N151" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O151" t="n">
-        <v>5691793.48296384</v>
+        <v>5691793.481664767</v>
       </c>
       <c r="P151" t="n">
         <v>24900</v>
@@ -6909,22 +6909,22 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="M153" t="n">
-        <v>903</v>
+        <v>519</v>
       </c>
       <c r="N153" t="n">
         <v>2090.85</v>
       </c>
       <c r="O153" t="n">
-        <v>1888037.55</v>
+        <v>1085151.15</v>
       </c>
       <c r="P153" t="n">
         <v>2900</v>
       </c>
       <c r="Q153" t="n">
-        <v>2618700</v>
+        <v>1505100</v>
       </c>
     </row>
     <row r="154">
@@ -7230,10 +7230,10 @@
         <v>78</v>
       </c>
       <c r="N160" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O160" t="n">
-        <v>237249.4810032126</v>
+        <v>237249.48100971</v>
       </c>
       <c r="P160" t="n">
         <v>5500</v>
@@ -8012,10 +8012,10 @@
         <v>200</v>
       </c>
       <c r="N178" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O178" t="n">
-        <v>404344.22450212</v>
+        <v>404344.22463768</v>
       </c>
       <c r="P178" t="n">
         <v>2400</v>
@@ -8462,10 +8462,10 @@
         <v>1152</v>
       </c>
       <c r="N188" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O188" t="n">
-        <v>1878823.65519383</v>
+        <v>1878823.684999987</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8508,10 +8508,10 @@
         <v>768</v>
       </c>
       <c r="N189" t="n">
-        <v>1690.6006518987</v>
+        <v>1690.6000587084</v>
       </c>
       <c r="O189" t="n">
-        <v>1298381.300658202</v>
+        <v>1298380.845088051</v>
       </c>
       <c r="P189" t="n">
         <v>2900</v>
@@ -8554,10 +8554,10 @@
         <v>5472</v>
       </c>
       <c r="N190" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O190" t="n">
-        <v>8482657.857953904</v>
+        <v>8482658.037071068</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -8600,10 +8600,10 @@
         <v>2016</v>
       </c>
       <c r="N191" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O191" t="n">
-        <v>4845477.764950503</v>
+        <v>4845478.087451031</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -8720,22 +8720,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M194" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N194" t="n">
         <v>101770.01727273</v>
       </c>
       <c r="O194" t="n">
-        <v>1831860.31090914</v>
+        <v>1221240.20727276</v>
       </c>
       <c r="P194" t="n">
         <v>136900</v>
       </c>
       <c r="Q194" t="n">
-        <v>2464200</v>
+        <v>1642800</v>
       </c>
     </row>
     <row r="195">
@@ -11267,10 +11267,10 @@
         <v>150</v>
       </c>
       <c r="N253" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O253" t="n">
-        <v>1734305.7789474</v>
+        <v>1734305.77836405</v>
       </c>
       <c r="P253" t="n">
         <v>18500</v>
@@ -12562,10 +12562,10 @@
         <v>433</v>
       </c>
       <c r="N283" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O283" t="n">
-        <v>1348314.381515938</v>
+        <v>1348314.381750321</v>
       </c>
       <c r="P283" t="n">
         <v>5000</v>
@@ -12746,10 +12746,10 @@
         <v>69</v>
       </c>
       <c r="N287" t="n">
-        <v>4163.1601818182</v>
+        <v>4163.1601960784</v>
       </c>
       <c r="O287" t="n">
-        <v>287258.0525454558</v>
+        <v>287258.0535294096</v>
       </c>
       <c r="P287" t="n">
         <v>6700</v>
@@ -12930,10 +12930,10 @@
         <v>399</v>
       </c>
       <c r="N291" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O291" t="n">
-        <v>2082050.038999991</v>
+        <v>2082050.040251494</v>
       </c>
       <c r="P291" t="n">
         <v>8500</v>
@@ -12976,10 +12976,10 @@
         <v>206</v>
       </c>
       <c r="N292" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="O292" t="n">
-        <v>328571.9442011788</v>
+        <v>328571.9403058012</v>
       </c>
       <c r="P292" t="n">
         <v>2600</v>
@@ -13022,10 +13022,10 @@
         <v>541</v>
       </c>
       <c r="N293" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O293" t="n">
-        <v>1953361.663644399</v>
+        <v>1953361.663730959</v>
       </c>
       <c r="P293" t="n">
         <v>5800</v>
@@ -13292,22 +13292,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M299" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="N299" t="n">
         <v>1812.57</v>
       </c>
       <c r="O299" t="n">
-        <v>349826.01</v>
+        <v>168569.01</v>
       </c>
       <c r="P299" t="n">
         <v>2900</v>
       </c>
       <c r="Q299" t="n">
-        <v>559700</v>
+        <v>269700</v>
       </c>
     </row>
     <row r="300">
@@ -13436,10 +13436,10 @@
         <v>384</v>
       </c>
       <c r="N302" t="n">
-        <v>1664.3585273632</v>
+        <v>1664.3584236948</v>
       </c>
       <c r="O302" t="n">
-        <v>639113.6745074688</v>
+        <v>639113.6346988032</v>
       </c>
       <c r="P302" t="n">
         <v>2900</v>
@@ -14126,10 +14126,10 @@
         <v>1145</v>
       </c>
       <c r="N317" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O317" t="n">
-        <v>2036351.097324234</v>
+        <v>2036351.105166338</v>
       </c>
       <c r="P317" t="n">
         <v>4900</v>
@@ -14672,22 +14672,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M329" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N329" t="n">
         <v>28116</v>
       </c>
       <c r="O329" t="n">
-        <v>534204</v>
+        <v>0</v>
       </c>
       <c r="P329" t="n">
         <v>45900</v>
       </c>
       <c r="Q329" t="n">
-        <v>872100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -15136,10 +15136,10 @@
         <v>864</v>
       </c>
       <c r="N339" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O339" t="n">
-        <v>2011494.599039405</v>
+        <v>2011494.590967744</v>
       </c>
       <c r="P339" t="n">
         <v>4500</v>
@@ -15544,22 +15544,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M348" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N348" t="n">
         <v>100129</v>
       </c>
       <c r="O348" t="n">
-        <v>1602064</v>
+        <v>801032</v>
       </c>
       <c r="P348" t="n">
         <v>159900</v>
       </c>
       <c r="Q348" t="n">
-        <v>2558400</v>
+        <v>1279200</v>
       </c>
     </row>
     <row r="349">
@@ -17193,22 +17193,22 @@
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M384" t="n">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="N384" t="n">
         <v>8700</v>
       </c>
       <c r="O384" t="n">
-        <v>3706200</v>
+        <v>3532200</v>
       </c>
       <c r="P384" t="n">
         <v>14900</v>
       </c>
       <c r="Q384" t="n">
-        <v>6347400</v>
+        <v>6049400</v>
       </c>
     </row>
     <row r="385">
@@ -17843,10 +17843,10 @@
         <v>960</v>
       </c>
       <c r="N398" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O398" t="n">
-        <v>1996208.770019712</v>
+        <v>1996208.75703456</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -17889,10 +17889,10 @@
         <v>1344</v>
       </c>
       <c r="N399" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O399" t="n">
-        <v>2423252.460277286</v>
+        <v>2423252.466773645</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
@@ -17935,10 +17935,10 @@
         <v>144</v>
       </c>
       <c r="N400" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O400" t="n">
-        <v>476149.7267532432</v>
+        <v>476149.7142857088</v>
       </c>
       <c r="P400" t="n">
         <v>4900</v>
@@ -17981,10 +17981,10 @@
         <v>1440</v>
       </c>
       <c r="N401" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O401" t="n">
-        <v>3055916.16</v>
+        <v>3055916.136081168</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -18027,10 +18027,10 @@
         <v>612</v>
       </c>
       <c r="N402" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O402" t="n">
-        <v>1290579.52235297</v>
+        <v>1290579.641904784</v>
       </c>
       <c r="P402" t="n">
         <v>2900</v>
@@ -18073,10 +18073,10 @@
         <v>684</v>
       </c>
       <c r="N403" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O403" t="n">
-        <v>1406361.258427763</v>
+        <v>1406361.232053954</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
@@ -19453,10 +19453,10 @@
         <v>1</v>
       </c>
       <c r="N433" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="O433" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="P433" t="n">
         <v>1900</v>
@@ -19634,10 +19634,10 @@
         <v>7572</v>
       </c>
       <c r="N437" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O437" t="n">
-        <v>3916907.485544716</v>
+        <v>3916908.073891766</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -19683,10 +19683,10 @@
         <v>504</v>
       </c>
       <c r="N438" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O438" t="n">
-        <v>1567864.679724353</v>
+        <v>1567864.652334876</v>
       </c>
       <c r="P438" t="n">
         <v>4500</v>
@@ -19809,22 +19809,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="M441" t="n">
-        <v>18248</v>
+        <v>17096</v>
       </c>
       <c r="N441" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O441" t="n">
-        <v>12842856.57535057</v>
+        <v>12032083.90633845</v>
       </c>
       <c r="P441" t="n">
         <v>900</v>
       </c>
       <c r="Q441" t="n">
-        <v>16423200</v>
+        <v>15386400</v>
       </c>
     </row>
     <row r="442">
@@ -20392,10 +20392,10 @@
         <v>1669</v>
       </c>
       <c r="N454" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O454" t="n">
-        <v>2662915.057702093</v>
+        <v>2662914.768684534</v>
       </c>
       <c r="P454" t="n">
         <v>2500</v>
@@ -23399,10 +23399,10 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="O522" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="P522" t="n">
         <v>7900</v>
@@ -23670,10 +23670,10 @@
         <v>5</v>
       </c>
       <c r="N528" t="n">
-        <v>21664.371428571</v>
+        <v>21664.371538462</v>
       </c>
       <c r="O528" t="n">
-        <v>108321.857142855</v>
+        <v>108321.85769231</v>
       </c>
       <c r="P528" t="n">
         <v>30000</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>25</v>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5010,10 +5010,10 @@
         <v>382</v>
       </c>
       <c r="N111" t="n">
-        <v>3250.4653148346</v>
+        <v>3247</v>
       </c>
       <c r="O111" t="n">
-        <v>1241677.750266817</v>
+        <v>1240354</v>
       </c>
       <c r="P111" t="n">
         <v>5200</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6640,10 +6640,10 @@
         <v>57</v>
       </c>
       <c r="N147" t="n">
-        <v>9237.463157894699</v>
+        <v>9047</v>
       </c>
       <c r="O147" t="n">
-        <v>526535.3999999978</v>
+        <v>515679</v>
       </c>
       <c r="P147" t="n">
         <v>5900</v>
@@ -7300,10 +7300,10 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="K186" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K211" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9694,10 +9694,10 @@
         <v>384</v>
       </c>
       <c r="N216" t="n">
-        <v>2679.7246188341</v>
+        <v>2661.82</v>
       </c>
       <c r="O216" t="n">
-        <v>1029014.253632294</v>
+        <v>1022138.88</v>
       </c>
       <c r="P216" t="n">
         <v>3200</v>
@@ -10022,10 +10022,10 @@
         <v>576</v>
       </c>
       <c r="N224" t="n">
-        <v>8799.395863611</v>
+        <v>8794.48</v>
       </c>
       <c r="O224" t="n">
-        <v>5068452.017439936</v>
+        <v>5065620.48</v>
       </c>
       <c r="P224" t="n">
         <v>14500</v>
@@ -10532,10 +10532,10 @@
         <v>2738</v>
       </c>
       <c r="N236" t="n">
-        <v>1733.4632374328</v>
+        <v>1732.9153651597</v>
       </c>
       <c r="O236" t="n">
-        <v>4746222.344091007</v>
+        <v>4744722.269807259</v>
       </c>
       <c r="P236" t="n">
         <v>1900</v>
@@ -12016,10 +12016,10 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K271" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -12241,10 +12241,10 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -12328,10 +12328,10 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -12543,10 +12543,10 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K283" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -15971,10 +15971,10 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K358" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -16162,10 +16162,10 @@
         <v>240</v>
       </c>
       <c r="N362" t="n">
-        <v>2637.9574105622</v>
+        <v>2629</v>
       </c>
       <c r="O362" t="n">
-        <v>633109.778534928</v>
+        <v>630960</v>
       </c>
       <c r="P362" t="n">
         <v>4500</v>
@@ -16300,10 +16300,10 @@
         <v>1134</v>
       </c>
       <c r="N365" t="n">
-        <v>5775.9026369168</v>
+        <v>5772</v>
       </c>
       <c r="O365" t="n">
-        <v>6549873.590263651</v>
+        <v>6545448</v>
       </c>
       <c r="P365" t="n">
         <v>9900</v>
@@ -16346,10 +16346,10 @@
         <v>738</v>
       </c>
       <c r="N366" t="n">
-        <v>6283.164516129</v>
+        <v>6268</v>
       </c>
       <c r="O366" t="n">
-        <v>4636975.412903202</v>
+        <v>4625784</v>
       </c>
       <c r="P366" t="n">
         <v>10900</v>
@@ -16622,10 +16622,10 @@
         <v>480</v>
       </c>
       <c r="N372" t="n">
-        <v>3904.1097178683</v>
+        <v>3898</v>
       </c>
       <c r="O372" t="n">
-        <v>1873972.664576784</v>
+        <v>1871040</v>
       </c>
       <c r="P372" t="n">
         <v>6900</v>
@@ -18138,10 +18138,10 @@
         <v>576</v>
       </c>
       <c r="N405" t="n">
-        <v>1775.6031464968</v>
+        <v>1771.0907898089</v>
       </c>
       <c r="O405" t="n">
-        <v>1022747.412382157</v>
+        <v>1020148.294929926</v>
       </c>
       <c r="P405" t="n">
         <v>2500</v>
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
@@ -19485,10 +19485,10 @@
         <v>1</v>
       </c>
       <c r="N434" t="n">
-        <v>2474.8947826087</v>
+        <v>2357.74</v>
       </c>
       <c r="O434" t="n">
-        <v>2474.8947826087</v>
+        <v>2357.74</v>
       </c>
       <c r="P434" t="n">
         <v>3000</v>
@@ -19750,10 +19750,10 @@
         <v>386</v>
       </c>
       <c r="N440" t="n">
-        <v>5100.8048289738</v>
+        <v>5050</v>
       </c>
       <c r="O440" t="n">
-        <v>1968910.663983887</v>
+        <v>1949300</v>
       </c>
       <c r="P440" t="n">
         <v>2000</v>
@@ -20765,13 +20765,13 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>1669</v>
+        <v>1369</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
       </c>
       <c r="L463" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M463" t="n">
         <v>1369</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.056000006</v>
+        <v>326035.074626874</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1433478176</v>
+        <v>823926.1421823028</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1116,10 +1116,10 @@
         <v>162</v>
       </c>
       <c r="N18" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O18" t="n">
-        <v>932951.4841592982</v>
+        <v>932951.4840798209</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8546153846</v>
+        <v>6272.8546302251</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.596923074</v>
+        <v>1354936.600128622</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -1998,10 +1998,10 @@
         <v>527</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O40" t="n">
-        <v>1271651.563034205</v>
+        <v>1271651.564239823</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2031,22 +2031,22 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M41" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="N41" t="n">
         <v>3526.1</v>
       </c>
       <c r="O41" t="n">
-        <v>451340.8</v>
+        <v>197461.6</v>
       </c>
       <c r="P41" t="n">
         <v>6300</v>
       </c>
       <c r="Q41" t="n">
-        <v>806400</v>
+        <v>352800</v>
       </c>
     </row>
     <row r="42">
@@ -2505,10 +2505,10 @@
         <v>152</v>
       </c>
       <c r="N53" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O53" t="n">
-        <v>594415.4836363664</v>
+        <v>594415.4819512183</v>
       </c>
       <c r="P53" t="n">
         <v>9100</v>
@@ -2628,10 +2628,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.3700000159</v>
+        <v>754174.3684033439</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -2925,10 +2925,10 @@
         <v>28</v>
       </c>
       <c r="N63" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O63" t="n">
-        <v>1593390.471186444</v>
+        <v>1593390.483508768</v>
       </c>
       <c r="P63" t="n">
         <v>95900</v>
@@ -2972,10 +2972,10 @@
         <v>6</v>
       </c>
       <c r="N64" t="n">
-        <v>62349.658857143</v>
+        <v>62349.657575758</v>
       </c>
       <c r="O64" t="n">
-        <v>374097.953142858</v>
+        <v>374097.945454548</v>
       </c>
       <c r="P64" t="n">
         <v>109900</v>
@@ -3108,10 +3108,10 @@
         <v>27</v>
       </c>
       <c r="N67" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O67" t="n">
-        <v>5401949.4131706</v>
+        <v>5401949.415491791</v>
       </c>
       <c r="P67" t="n">
         <v>312000</v>
@@ -3939,10 +3939,10 @@
         <v>1440</v>
       </c>
       <c r="N86" t="n">
-        <v>1950.2146835443</v>
+        <v>1950.2146537678</v>
       </c>
       <c r="O86" t="n">
-        <v>2808309.144303792</v>
+        <v>2808309.101425632</v>
       </c>
       <c r="P86" t="n">
         <v>2900</v>
@@ -4067,10 +4067,10 @@
         <v>200</v>
       </c>
       <c r="N89" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O89" t="n">
-        <v>987462.0323291599</v>
+        <v>987462.03247232</v>
       </c>
       <c r="P89" t="n">
         <v>7500</v>
@@ -4328,10 +4328,10 @@
         <v>244</v>
       </c>
       <c r="N95" t="n">
-        <v>21084.771462766</v>
+        <v>21084.771466667</v>
       </c>
       <c r="O95" t="n">
-        <v>5144684.236914904</v>
+        <v>5144684.237866748</v>
       </c>
       <c r="P95" t="n">
         <v>30000</v>
@@ -4963,10 +4963,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O110" t="n">
-        <v>2788836.36329142</v>
+        <v>2788836.325457616</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5055,10 +5055,10 @@
         <v>1986</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O112" t="n">
-        <v>10360755.81322242</v>
+        <v>10360755.78423655</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5188,10 +5188,10 @@
         <v>6298</v>
       </c>
       <c r="N115" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O115" t="n">
-        <v>19894505.47368727</v>
+        <v>19894505.475719</v>
       </c>
       <c r="P115" t="n">
         <v>5600</v>
@@ -5418,10 +5418,10 @@
         <v>224</v>
       </c>
       <c r="N120" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O120" t="n">
-        <v>603640.4086245344</v>
+        <v>603640.406514656</v>
       </c>
       <c r="P120" t="n">
         <v>4900</v>
@@ -5876,10 +5876,10 @@
         <v>64</v>
       </c>
       <c r="N130" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O130" t="n">
-        <v>313019.5230494336</v>
+        <v>313019.5230806272</v>
       </c>
       <c r="P130" t="n">
         <v>8200</v>
@@ -6509,10 +6509,10 @@
         <v>264</v>
       </c>
       <c r="N144" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O144" t="n">
-        <v>948883.07940888</v>
+        <v>948883.0755555624</v>
       </c>
       <c r="P144" t="n">
         <v>6500</v>
@@ -6734,10 +6734,10 @@
         <v>361</v>
       </c>
       <c r="N149" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O149" t="n">
-        <v>5350878.766690378</v>
+        <v>5350878.766443815</v>
       </c>
       <c r="P149" t="n">
         <v>24900</v>
@@ -6816,22 +6816,22 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="M151" t="n">
-        <v>519</v>
+        <v>39</v>
       </c>
       <c r="N151" t="n">
         <v>2090.85</v>
       </c>
       <c r="O151" t="n">
-        <v>1085151.15</v>
+        <v>81543.14999999999</v>
       </c>
       <c r="P151" t="n">
         <v>2900</v>
       </c>
       <c r="Q151" t="n">
-        <v>1505100</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="152">
@@ -7137,10 +7137,10 @@
         <v>78</v>
       </c>
       <c r="N158" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O158" t="n">
-        <v>237249.4810110204</v>
+        <v>237249.4810123308</v>
       </c>
       <c r="P158" t="n">
         <v>5500</v>
@@ -7172,22 +7172,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M159" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
         <v>3981.47</v>
       </c>
       <c r="O159" t="n">
-        <v>597220.5</v>
+        <v>0</v>
       </c>
       <c r="P159" t="n">
         <v>7000</v>
       </c>
       <c r="Q159" t="n">
-        <v>1050000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -7224,10 +7224,10 @@
         <v>809</v>
       </c>
       <c r="N160" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O160" t="n">
-        <v>3537118.527941804</v>
+        <v>3537118.528032573</v>
       </c>
       <c r="P160" t="n">
         <v>7500</v>
@@ -7573,10 +7573,10 @@
         <v>10357</v>
       </c>
       <c r="N168" t="n">
-        <v>1532.6290283636</v>
+        <v>1532.6290281516</v>
       </c>
       <c r="O168" t="n">
-        <v>15873438.8467618</v>
+        <v>15873438.84456612</v>
       </c>
       <c r="P168" t="n">
         <v>1200</v>
@@ -8369,10 +8369,10 @@
         <v>1152</v>
       </c>
       <c r="N186" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O186" t="n">
-        <v>1878823.775530829</v>
+        <v>1878823.828689754</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8415,10 +8415,10 @@
         <v>768</v>
       </c>
       <c r="N187" t="n">
-        <v>1690.5995518395</v>
+        <v>1690.5992886179</v>
       </c>
       <c r="O187" t="n">
-        <v>1298380.455812736</v>
+        <v>1298380.253658547</v>
       </c>
       <c r="P187" t="n">
         <v>2900</v>
@@ -8461,10 +8461,10 @@
         <v>5472</v>
       </c>
       <c r="N188" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O188" t="n">
-        <v>8482658.51378952</v>
+        <v>8482658.944388313</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8507,10 +8507,10 @@
         <v>2016</v>
       </c>
       <c r="N189" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O189" t="n">
-        <v>4845478.803452985</v>
+        <v>4845479.15771398</v>
       </c>
       <c r="P189" t="n">
         <v>3500</v>
@@ -9079,22 +9079,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M202" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="N202" t="n">
         <v>17328</v>
       </c>
       <c r="O202" t="n">
-        <v>3119040</v>
+        <v>1559520</v>
       </c>
       <c r="P202" t="n">
         <v>32900</v>
       </c>
       <c r="Q202" t="n">
-        <v>5922000</v>
+        <v>2961000</v>
       </c>
     </row>
     <row r="203">
@@ -9166,22 +9166,22 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M204" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N204" t="n">
         <v>7028</v>
       </c>
       <c r="O204" t="n">
-        <v>2150568</v>
+        <v>2122456</v>
       </c>
       <c r="P204" t="n">
         <v>15900</v>
       </c>
       <c r="Q204" t="n">
-        <v>4865400</v>
+        <v>4801800</v>
       </c>
     </row>
     <row r="205">
@@ -9967,10 +9967,10 @@
         <v>90</v>
       </c>
       <c r="N223" t="n">
-        <v>22485.695890411</v>
+        <v>22485.695885714</v>
       </c>
       <c r="O223" t="n">
-        <v>2023712.63013699</v>
+        <v>2023712.62971426</v>
       </c>
       <c r="P223" t="n">
         <v>36500</v>
@@ -10098,10 +10098,10 @@
         <v>381</v>
       </c>
       <c r="N226" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O226" t="n">
-        <v>1021361.825676683</v>
+        <v>1021361.825536475</v>
       </c>
       <c r="P226" t="n">
         <v>4900</v>
@@ -10139,10 +10139,10 @@
         <v>1254</v>
       </c>
       <c r="N227" t="n">
-        <v>880.32945034206</v>
+        <v>880.3295131797699</v>
       </c>
       <c r="O227" t="n">
-        <v>1103933.130728943</v>
+        <v>1103933.209527432</v>
       </c>
       <c r="P227" t="n">
         <v>1200</v>
@@ -10617,22 +10617,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M238" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O238" t="n">
-        <v>1671226.203184707</v>
+        <v>642779.31323373</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
       </c>
       <c r="Q238" t="n">
-        <v>2691000</v>
+        <v>1035000</v>
       </c>
     </row>
     <row r="239">
@@ -10666,22 +10666,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M239" t="n">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="N239" t="n">
         <v>9776.99</v>
       </c>
       <c r="O239" t="n">
-        <v>3167744.76</v>
+        <v>821267.16</v>
       </c>
       <c r="P239" t="n">
         <v>15900</v>
       </c>
       <c r="Q239" t="n">
-        <v>5151600</v>
+        <v>1335600</v>
       </c>
     </row>
     <row r="240">
@@ -10754,10 +10754,10 @@
         <v>248</v>
       </c>
       <c r="N241" t="n">
-        <v>12132.858149466</v>
+        <v>12132.858122744</v>
       </c>
       <c r="O241" t="n">
-        <v>3008948.821067568</v>
+        <v>3008948.814440512</v>
       </c>
       <c r="P241" t="n">
         <v>15900</v>
@@ -11174,10 +11174,10 @@
         <v>150</v>
       </c>
       <c r="N251" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O251" t="n">
-        <v>1734305.77836405</v>
+        <v>1734305.77777785</v>
       </c>
       <c r="P251" t="n">
         <v>18500</v>
@@ -11220,10 +11220,10 @@
         <v>95</v>
       </c>
       <c r="N252" t="n">
-        <v>12005.159831224</v>
+        <v>12005.159830508</v>
       </c>
       <c r="O252" t="n">
-        <v>1140490.18396628</v>
+        <v>1140490.18389826</v>
       </c>
       <c r="P252" t="n">
         <v>19500</v>
@@ -12121,10 +12121,10 @@
         <v>480</v>
       </c>
       <c r="N273" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O273" t="n">
-        <v>3825576.079698096</v>
+        <v>3825576.07993944</v>
       </c>
       <c r="P273" t="n">
         <v>12900</v>
@@ -12428,10 +12428,10 @@
         <v>433</v>
       </c>
       <c r="N280" t="n">
-        <v>3113.8900273598</v>
+        <v>3113.8900274725</v>
       </c>
       <c r="O280" t="n">
-        <v>1348314.381846793</v>
+        <v>1348314.381895593</v>
       </c>
       <c r="P280" t="n">
         <v>5000</v>
@@ -12612,10 +12612,10 @@
         <v>69</v>
       </c>
       <c r="N284" t="n">
-        <v>4163.1602</v>
+        <v>4163.1602061856</v>
       </c>
       <c r="O284" t="n">
-        <v>287258.0538</v>
+        <v>287258.0542268064</v>
       </c>
       <c r="P284" t="n">
         <v>6700</v>
@@ -12796,10 +12796,10 @@
         <v>399</v>
       </c>
       <c r="N288" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O288" t="n">
-        <v>2082050.043317131</v>
+        <v>2082050.045940954</v>
       </c>
       <c r="P288" t="n">
         <v>8500</v>
@@ -12842,10 +12842,10 @@
         <v>206</v>
       </c>
       <c r="N289" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="O289" t="n">
-        <v>328571.9382581612</v>
+        <v>328571.935548499</v>
       </c>
       <c r="P289" t="n">
         <v>2600</v>
@@ -13302,10 +13302,10 @@
         <v>384</v>
       </c>
       <c r="N299" t="n">
-        <v>1664.3579393305</v>
+        <v>1664.3571460424</v>
       </c>
       <c r="O299" t="n">
-        <v>639113.448702912</v>
+        <v>639113.1440802816</v>
       </c>
       <c r="P299" t="n">
         <v>2900</v>
@@ -13992,10 +13992,10 @@
         <v>1145</v>
       </c>
       <c r="N314" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O314" t="n">
-        <v>2036351.124070174</v>
+        <v>2036351.124512716</v>
       </c>
       <c r="P314" t="n">
         <v>4900</v>
@@ -16377,10 +16377,10 @@
         <v>192</v>
       </c>
       <c r="N366" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O366" t="n">
-        <v>3278589.98857152</v>
+        <v>3278589.988508352</v>
       </c>
       <c r="P366" t="n">
         <v>27500</v>
@@ -17479,10 +17479,10 @@
         <v>4224</v>
       </c>
       <c r="N390" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O390" t="n">
-        <v>6403747.904342132</v>
+        <v>6403747.898929497</v>
       </c>
       <c r="P390" t="n">
         <v>2300</v>
@@ -17525,10 +17525,10 @@
         <v>1152</v>
       </c>
       <c r="N391" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O391" t="n">
-        <v>2832207.29947895</v>
+        <v>2832207.264465293</v>
       </c>
       <c r="P391" t="n">
         <v>3500</v>
@@ -17571,10 +17571,10 @@
         <v>480</v>
       </c>
       <c r="N392" t="n">
-        <v>1907.3938243626</v>
+        <v>1907.3938009479</v>
       </c>
       <c r="O392" t="n">
-        <v>915549.035694048</v>
+        <v>915549.024454992</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
@@ -17617,10 +17617,10 @@
         <v>576</v>
       </c>
       <c r="N393" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O393" t="n">
-        <v>1020148.212574368</v>
+        <v>1020148.184551392</v>
       </c>
       <c r="P393" t="n">
         <v>2500</v>
@@ -17663,10 +17663,10 @@
         <v>960</v>
       </c>
       <c r="N394" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O394" t="n">
-        <v>1996208.691199968</v>
+        <v>1996208.685485472</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -17709,10 +17709,10 @@
         <v>1344</v>
       </c>
       <c r="N395" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O395" t="n">
-        <v>2423252.904220243</v>
+        <v>2423252.911564397</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
@@ -17755,10 +17755,10 @@
         <v>144</v>
       </c>
       <c r="N396" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O396" t="n">
-        <v>476149.7142857088</v>
+        <v>476149.707877176</v>
       </c>
       <c r="P396" t="n">
         <v>4900</v>
@@ -17801,10 +17801,10 @@
         <v>1440</v>
       </c>
       <c r="N397" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O397" t="n">
-        <v>3055916.049953472</v>
+        <v>3055916.044513584</v>
       </c>
       <c r="P397" t="n">
         <v>2900</v>
@@ -17841,22 +17841,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M398" t="n">
-        <v>612</v>
+        <v>432</v>
       </c>
       <c r="N398" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O398" t="n">
-        <v>1290580.148767468</v>
+        <v>910997.8963350912</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
       </c>
       <c r="Q398" t="n">
-        <v>1774800</v>
+        <v>1252800</v>
       </c>
     </row>
     <row r="399">
@@ -17893,10 +17893,10 @@
         <v>684</v>
       </c>
       <c r="N399" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O399" t="n">
-        <v>1406361.093767827</v>
+        <v>1406361.058163233</v>
       </c>
       <c r="P399" t="n">
         <v>2900</v>
@@ -17939,10 +17939,10 @@
         <v>714</v>
       </c>
       <c r="N400" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O400" t="n">
-        <v>2302341.91154391</v>
+        <v>2302341.925999983</v>
       </c>
       <c r="P400" t="n">
         <v>4500</v>
@@ -17985,10 +17985,10 @@
         <v>1152</v>
       </c>
       <c r="N401" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O401" t="n">
-        <v>1907632.48381079</v>
+        <v>1907632.473625037</v>
       </c>
       <c r="P401" t="n">
         <v>2500</v>
@@ -19098,10 +19098,10 @@
         <v>216</v>
       </c>
       <c r="N425" t="n">
-        <v>2286.1648032937</v>
+        <v>2286.1647937672</v>
       </c>
       <c r="O425" t="n">
-        <v>493811.5975114392</v>
+        <v>493811.5954537152</v>
       </c>
       <c r="P425" t="n">
         <v>3000</v>
@@ -19273,10 +19273,10 @@
         <v>1</v>
       </c>
       <c r="N429" t="n">
-        <v>1283.6539261745</v>
+        <v>1283.6538013699</v>
       </c>
       <c r="O429" t="n">
-        <v>1283.6539261745</v>
+        <v>1283.6538013699</v>
       </c>
       <c r="P429" t="n">
         <v>1900</v>
@@ -19454,10 +19454,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O433" t="n">
-        <v>3916912.017579121</v>
+        <v>3916912.930477537</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -19503,10 +19503,10 @@
         <v>504</v>
       </c>
       <c r="N434" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O434" t="n">
-        <v>1567864.534432644</v>
+        <v>1567864.530234576</v>
       </c>
       <c r="P434" t="n">
         <v>4500</v>
@@ -19635,10 +19635,10 @@
         <v>17096</v>
       </c>
       <c r="N437" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O437" t="n">
-        <v>12032083.20037281</v>
+        <v>12032082.91901829</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -19684,10 +19684,10 @@
         <v>127</v>
       </c>
       <c r="N438" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O438" t="n">
-        <v>404145.8905904097</v>
+        <v>404145.8924299031</v>
       </c>
       <c r="P438" t="n">
         <v>6900</v>
@@ -20212,10 +20212,10 @@
         <v>1369</v>
       </c>
       <c r="N450" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O450" t="n">
-        <v>2184257.68903437</v>
+        <v>2184257.468840987</v>
       </c>
       <c r="P450" t="n">
         <v>2500</v>
@@ -20859,10 +20859,10 @@
         <v>50</v>
       </c>
       <c r="N464" t="n">
-        <v>4159.0002941176</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O464" t="n">
-        <v>207950.01470588</v>
+        <v>207950.01476015</v>
       </c>
       <c r="P464" t="n">
         <v>8900</v>
@@ -21456,22 +21456,22 @@
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M477" t="n">
-        <v>798</v>
+        <v>498</v>
       </c>
       <c r="N477" t="n">
         <v>4581.84</v>
       </c>
       <c r="O477" t="n">
-        <v>3656308.32</v>
+        <v>2281756.32</v>
       </c>
       <c r="P477" t="n">
         <v>7900</v>
       </c>
       <c r="Q477" t="n">
-        <v>6304200</v>
+        <v>3934200</v>
       </c>
     </row>
     <row r="478">
@@ -21505,22 +21505,22 @@
         <v>0</v>
       </c>
       <c r="L478" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M478" t="n">
-        <v>870</v>
+        <v>470</v>
       </c>
       <c r="N478" t="n">
         <v>3155</v>
       </c>
       <c r="O478" t="n">
-        <v>2744850</v>
+        <v>1482850</v>
       </c>
       <c r="P478" t="n">
         <v>5900</v>
       </c>
       <c r="Q478" t="n">
-        <v>5133000</v>
+        <v>2773000</v>
       </c>
     </row>
     <row r="479">
@@ -22234,10 +22234,10 @@
         <v>955</v>
       </c>
       <c r="N495" t="n">
-        <v>2129.8331598174</v>
+        <v>2129.8331627057</v>
       </c>
       <c r="O495" t="n">
-        <v>2033990.667625617</v>
+        <v>2033990.670383943</v>
       </c>
       <c r="P495" t="n">
         <v>2700</v>
@@ -23049,10 +23049,10 @@
         <v>1</v>
       </c>
       <c r="N514" t="n">
-        <v>6035.6648529412</v>
+        <v>6035.665</v>
       </c>
       <c r="O514" t="n">
-        <v>6035.6648529412</v>
+        <v>6035.665</v>
       </c>
       <c r="P514" t="n">
         <v>8500</v>
@@ -23219,10 +23219,10 @@
         <v>1</v>
       </c>
       <c r="N518" t="n">
-        <v>4985.4051948052</v>
+        <v>4985.4053097345</v>
       </c>
       <c r="O518" t="n">
-        <v>4985.4051948052</v>
+        <v>4985.4053097345</v>
       </c>
       <c r="P518" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3059701493</v>
+        <v>1811.3062015504</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.074626874</v>
+        <v>326035.116279072</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1421823028</v>
+        <v>823926.1393721059</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1116,10 +1116,10 @@
         <v>162</v>
       </c>
       <c r="N18" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O18" t="n">
-        <v>932951.4840798209</v>
+        <v>932951.4840000035</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8546302251</v>
+        <v>6272.8546451613</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.600128622</v>
+        <v>1354936.603354841</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2466,10 +2466,10 @@
         <v>24</v>
       </c>
       <c r="N52" t="n">
-        <v>14857.623214286</v>
+        <v>14857.623243243</v>
       </c>
       <c r="O52" t="n">
-        <v>356582.957142864</v>
+        <v>356582.957837832</v>
       </c>
       <c r="P52" t="n">
         <v>34900</v>
@@ -2547,10 +2547,10 @@
         <v>52</v>
       </c>
       <c r="N54" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="O54" t="n">
-        <v>857293.264000004</v>
+        <v>863938.9482170719</v>
       </c>
       <c r="P54" t="n">
         <v>30500</v>
@@ -2628,10 +2628,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.3684033439</v>
+        <v>754174.3659574561</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -2925,10 +2925,10 @@
         <v>28</v>
       </c>
       <c r="N63" t="n">
-        <v>56906.802982456</v>
+        <v>56906.803962264</v>
       </c>
       <c r="O63" t="n">
-        <v>1593390.483508768</v>
+        <v>1593390.510943392</v>
       </c>
       <c r="P63" t="n">
         <v>95900</v>
@@ -3291,10 +3291,10 @@
         <v>14</v>
       </c>
       <c r="N71" t="n">
-        <v>263530.17666667</v>
+        <v>263530.17529412</v>
       </c>
       <c r="O71" t="n">
-        <v>3689422.47333338</v>
+        <v>3689422.45411768</v>
       </c>
       <c r="P71" t="n">
         <v>402900</v>
@@ -4963,10 +4963,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2558569052</v>
+        <v>2582.2558256496</v>
       </c>
       <c r="O110" t="n">
-        <v>2788836.325457616</v>
+        <v>2788836.291701568</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5055,10 +5055,10 @@
         <v>1986</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.8961652752</v>
+        <v>5216.8961603854</v>
       </c>
       <c r="O112" t="n">
-        <v>10360755.78423655</v>
+        <v>10360755.77452541</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5136,22 +5136,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M114" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
         <v>6713.08</v>
       </c>
       <c r="O114" t="n">
-        <v>503481</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
         <v>9900</v>
       </c>
       <c r="Q114" t="n">
-        <v>742500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5188,10 +5188,10 @@
         <v>6298</v>
       </c>
       <c r="N115" t="n">
-        <v>3158.8608249792</v>
+        <v>3158.860825504</v>
       </c>
       <c r="O115" t="n">
-        <v>19894505.475719</v>
+        <v>19894505.47902419</v>
       </c>
       <c r="P115" t="n">
         <v>5600</v>
@@ -5280,10 +5280,10 @@
         <v>144</v>
       </c>
       <c r="N117" t="n">
-        <v>3841.6247787611</v>
+        <v>3841.6247928994</v>
       </c>
       <c r="O117" t="n">
-        <v>553193.9681415984</v>
+        <v>553193.9701775135</v>
       </c>
       <c r="P117" t="n">
         <v>6900</v>
@@ -5418,10 +5418,10 @@
         <v>224</v>
       </c>
       <c r="N120" t="n">
-        <v>2694.823243369</v>
+        <v>2694.8232244517</v>
       </c>
       <c r="O120" t="n">
-        <v>603640.406514656</v>
+        <v>603640.4022771808</v>
       </c>
       <c r="P120" t="n">
         <v>4900</v>
@@ -5464,10 +5464,10 @@
         <v>288</v>
       </c>
       <c r="N121" t="n">
-        <v>1026.13</v>
+        <v>1032.527319202</v>
       </c>
       <c r="O121" t="n">
-        <v>295525.4400000001</v>
+        <v>297367.867930176</v>
       </c>
       <c r="P121" t="n">
         <v>1900</v>
@@ -5599,22 +5599,22 @@
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M124" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="N124" t="n">
         <v>8796</v>
       </c>
       <c r="O124" t="n">
-        <v>1935120</v>
+        <v>1266624</v>
       </c>
       <c r="P124" t="n">
         <v>14900</v>
       </c>
       <c r="Q124" t="n">
-        <v>3278000</v>
+        <v>2145600</v>
       </c>
     </row>
     <row r="125">
@@ -5738,10 +5738,10 @@
         <v>3024</v>
       </c>
       <c r="N127" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O127" t="n">
-        <v>11478227.06149247</v>
+        <v>11478227.0628055</v>
       </c>
       <c r="P127" t="n">
         <v>6200</v>
@@ -5876,10 +5876,10 @@
         <v>64</v>
       </c>
       <c r="N130" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O130" t="n">
-        <v>313019.5230806272</v>
+        <v>314533.5231922624</v>
       </c>
       <c r="P130" t="n">
         <v>8200</v>
@@ -6014,22 +6014,22 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M133" t="n">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="N133" t="n">
         <v>5888</v>
       </c>
       <c r="O133" t="n">
-        <v>877312</v>
+        <v>559360</v>
       </c>
       <c r="P133" t="n">
         <v>9500</v>
       </c>
       <c r="Q133" t="n">
-        <v>1415500</v>
+        <v>902500</v>
       </c>
     </row>
     <row r="134">
@@ -6509,10 +6509,10 @@
         <v>264</v>
       </c>
       <c r="N144" t="n">
-        <v>3594.2540740741</v>
+        <v>3594.2540520446</v>
       </c>
       <c r="O144" t="n">
-        <v>948883.0755555624</v>
+        <v>948883.0697397745</v>
       </c>
       <c r="P144" t="n">
         <v>6500</v>
@@ -6642,10 +6642,10 @@
         <v>599</v>
       </c>
       <c r="N147" t="n">
-        <v>4891</v>
+        <v>4913.5912240185</v>
       </c>
       <c r="O147" t="n">
-        <v>2929709</v>
+        <v>2943241.143187081</v>
       </c>
       <c r="P147" t="n">
         <v>8200</v>
@@ -6682,22 +6682,22 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M148" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="N148" t="n">
         <v>8154</v>
       </c>
       <c r="O148" t="n">
-        <v>782784</v>
+        <v>391392</v>
       </c>
       <c r="P148" t="n">
         <v>13500</v>
       </c>
       <c r="Q148" t="n">
-        <v>1296000</v>
+        <v>648000</v>
       </c>
     </row>
     <row r="149">
@@ -7183,10 +7183,10 @@
         <v>809</v>
       </c>
       <c r="N159" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O159" t="n">
-        <v>3537118.528032573</v>
+        <v>3539134.267464053</v>
       </c>
       <c r="P159" t="n">
         <v>7500</v>
@@ -8015,10 +8015,10 @@
         <v>238</v>
       </c>
       <c r="N178" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="O178" t="n">
-        <v>895260.7999999999</v>
+        <v>901558.0623681113</v>
       </c>
       <c r="P178" t="n">
         <v>6900</v>
@@ -8328,10 +8328,10 @@
         <v>1152</v>
       </c>
       <c r="N185" t="n">
-        <v>1630.9234624043</v>
+        <v>1630.9234875283</v>
       </c>
       <c r="O185" t="n">
-        <v>1878823.828689754</v>
+        <v>1878823.857632602</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8374,10 +8374,10 @@
         <v>768</v>
       </c>
       <c r="N186" t="n">
-        <v>1690.5992886179</v>
+        <v>1690.5983498584</v>
       </c>
       <c r="O186" t="n">
-        <v>1298380.253658547</v>
+        <v>1298379.532691251</v>
       </c>
       <c r="P186" t="n">
         <v>2900</v>
@@ -8420,10 +8420,10 @@
         <v>5472</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.1935205388</v>
+        <v>1550.1935332762</v>
       </c>
       <c r="O187" t="n">
-        <v>8482658.944388313</v>
+        <v>8482659.014087366</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8466,10 +8466,10 @@
         <v>2016</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5114869613</v>
+        <v>2403.5115510508</v>
       </c>
       <c r="O188" t="n">
-        <v>4845479.15771398</v>
+        <v>4845479.286918413</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9297,22 +9297,22 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="M207" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
         <v>9338</v>
       </c>
       <c r="O207" t="n">
-        <v>1036518</v>
+        <v>0</v>
       </c>
       <c r="P207" t="n">
         <v>15500</v>
       </c>
       <c r="Q207" t="n">
-        <v>1720500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -9885,10 +9885,10 @@
         <v>216</v>
       </c>
       <c r="N221" t="n">
-        <v>2517.22</v>
+        <v>2528.6359637188</v>
       </c>
       <c r="O221" t="n">
-        <v>543719.5199999999</v>
+        <v>546185.3681632609</v>
       </c>
       <c r="P221" t="n">
         <v>4200</v>
@@ -9926,10 +9926,10 @@
         <v>90</v>
       </c>
       <c r="N222" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="O222" t="n">
-        <v>2023712.62971426</v>
+        <v>2023712.62929063</v>
       </c>
       <c r="P222" t="n">
         <v>36500</v>
@@ -10582,10 +10582,10 @@
         <v>150</v>
       </c>
       <c r="N237" t="n">
-        <v>4285.1954215582</v>
+        <v>4285.1954682454</v>
       </c>
       <c r="O237" t="n">
-        <v>642779.31323373</v>
+        <v>642779.32023681</v>
       </c>
       <c r="P237" t="n">
         <v>6900</v>
@@ -11087,10 +11087,10 @@
         <v>2329</v>
       </c>
       <c r="N249" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O249" t="n">
-        <v>8363741.77</v>
+        <v>8381169.257626286</v>
       </c>
       <c r="P249" t="n">
         <v>6300</v>
@@ -12519,22 +12519,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M282" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
         <v>10911.29</v>
       </c>
       <c r="O282" t="n">
-        <v>676499.9800000001</v>
+        <v>0</v>
       </c>
       <c r="P282" t="n">
         <v>17400</v>
       </c>
       <c r="Q282" t="n">
-        <v>1078800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -12755,10 +12755,10 @@
         <v>399</v>
       </c>
       <c r="N287" t="n">
-        <v>5218.1705412054</v>
+        <v>5218.1705479452</v>
       </c>
       <c r="O287" t="n">
-        <v>2082050.045940954</v>
+        <v>2082050.048630135</v>
       </c>
       <c r="P287" t="n">
         <v>8500</v>
@@ -12801,10 +12801,10 @@
         <v>206</v>
       </c>
       <c r="N288" t="n">
-        <v>1595.0093958665</v>
+        <v>1595.0093800979</v>
       </c>
       <c r="O288" t="n">
-        <v>328571.935548499</v>
+        <v>328571.9323001674</v>
       </c>
       <c r="P288" t="n">
         <v>2600</v>
@@ -13261,10 +13261,10 @@
         <v>384</v>
       </c>
       <c r="N298" t="n">
-        <v>1664.3571460424</v>
+        <v>1664.3569717514</v>
       </c>
       <c r="O298" t="n">
-        <v>639113.1440802816</v>
+        <v>639113.0771525375</v>
       </c>
       <c r="P298" t="n">
         <v>2900</v>
@@ -13951,10 +13951,10 @@
         <v>1145</v>
       </c>
       <c r="N313" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O313" t="n">
-        <v>2036351.124512716</v>
+        <v>2036351.146807126</v>
       </c>
       <c r="P313" t="n">
         <v>4900</v>
@@ -14733,10 +14733,10 @@
         <v>28</v>
       </c>
       <c r="N330" t="n">
-        <v>2252.2966541823</v>
+        <v>2252.2966708385</v>
       </c>
       <c r="O330" t="n">
-        <v>63064.30631710439</v>
+        <v>63064.30678347801</v>
       </c>
       <c r="P330" t="n">
         <v>3900</v>
@@ -14915,10 +14915,10 @@
         <v>864</v>
       </c>
       <c r="N334" t="n">
-        <v>2328.1187258454</v>
+        <v>2328.1187254606</v>
       </c>
       <c r="O334" t="n">
-        <v>2011494.579130426</v>
+        <v>2011494.578797959</v>
       </c>
       <c r="P334" t="n">
         <v>4500</v>
@@ -15185,22 +15185,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M340" t="n">
-        <v>1152</v>
+        <v>960</v>
       </c>
       <c r="N340" t="n">
         <v>4544</v>
       </c>
       <c r="O340" t="n">
-        <v>5234688</v>
+        <v>4362240</v>
       </c>
       <c r="P340" t="n">
         <v>7900</v>
       </c>
       <c r="Q340" t="n">
-        <v>9100800</v>
+        <v>7584000</v>
       </c>
     </row>
     <row r="341">
@@ -15830,10 +15830,10 @@
         <v>10</v>
       </c>
       <c r="N354" t="n">
-        <v>8637</v>
+        <v>9422.1818181818</v>
       </c>
       <c r="O354" t="n">
-        <v>86370</v>
+        <v>94221.818181818</v>
       </c>
       <c r="P354" t="n">
         <v>14500</v>
@@ -15922,10 +15922,10 @@
         <v>2016</v>
       </c>
       <c r="N356" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O356" t="n">
-        <v>13396320</v>
+        <v>13440266.37506831</v>
       </c>
       <c r="P356" t="n">
         <v>10900</v>
@@ -17484,10 +17484,10 @@
         <v>1152</v>
       </c>
       <c r="N390" t="n">
-        <v>2458.5132504039</v>
+        <v>2477.7391560769</v>
       </c>
       <c r="O390" t="n">
-        <v>2832207.264465293</v>
+        <v>2854355.507800589</v>
       </c>
       <c r="P390" t="n">
         <v>3500</v>
@@ -17530,10 +17530,10 @@
         <v>480</v>
       </c>
       <c r="N391" t="n">
-        <v>1907.3938009479</v>
+        <v>1951.7948205626</v>
       </c>
       <c r="O391" t="n">
-        <v>915549.024454992</v>
+        <v>936861.513870048</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -17576,10 +17576,10 @@
         <v>576</v>
       </c>
       <c r="N392" t="n">
-        <v>1771.0905981795</v>
+        <v>1799.166010568</v>
       </c>
       <c r="O392" t="n">
-        <v>1020148.184551392</v>
+        <v>1036319.622087168</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
@@ -17622,10 +17622,10 @@
         <v>960</v>
       </c>
       <c r="N393" t="n">
-        <v>2079.3840473807</v>
+        <v>2079.3840374332</v>
       </c>
       <c r="O393" t="n">
-        <v>1996208.685485472</v>
+        <v>1996208.675935872</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -17662,22 +17662,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M394" t="n">
-        <v>1344</v>
+        <v>1152</v>
       </c>
       <c r="N394" t="n">
-        <v>1803.0155591997</v>
+        <v>1817.3204760331</v>
       </c>
       <c r="O394" t="n">
-        <v>2423252.911564397</v>
+        <v>2093553.188390131</v>
       </c>
       <c r="P394" t="n">
         <v>2500</v>
       </c>
       <c r="Q394" t="n">
-        <v>3360000</v>
+        <v>2880000</v>
       </c>
     </row>
     <row r="395">
@@ -17714,10 +17714,10 @@
         <v>144</v>
       </c>
       <c r="N395" t="n">
-        <v>3306.5951935915</v>
+        <v>3306.5951807229</v>
       </c>
       <c r="O395" t="n">
-        <v>476149.707877176</v>
+        <v>476149.7060240976</v>
       </c>
       <c r="P395" t="n">
         <v>4900</v>
@@ -17760,10 +17760,10 @@
         <v>1440</v>
       </c>
       <c r="N396" t="n">
-        <v>2122.1639198011</v>
+        <v>2138.1701634192</v>
       </c>
       <c r="O396" t="n">
-        <v>3055916.044513584</v>
+        <v>3078965.035323648</v>
       </c>
       <c r="P396" t="n">
         <v>2900</v>
@@ -17800,22 +17800,22 @@
         <v>0</v>
       </c>
       <c r="L397" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M397" t="n">
-        <v>432</v>
+        <v>216</v>
       </c>
       <c r="N397" t="n">
-        <v>2108.7914267016</v>
+        <v>2142.8043145161</v>
       </c>
       <c r="O397" t="n">
-        <v>910997.8963350912</v>
+        <v>462845.7319354776</v>
       </c>
       <c r="P397" t="n">
         <v>2900</v>
       </c>
       <c r="Q397" t="n">
-        <v>1252800</v>
+        <v>626400</v>
       </c>
     </row>
     <row r="398">
@@ -17852,10 +17852,10 @@
         <v>684</v>
       </c>
       <c r="N398" t="n">
-        <v>2056.0834183673</v>
+        <v>2056.0833654773</v>
       </c>
       <c r="O398" t="n">
-        <v>1406361.058163233</v>
+        <v>1406361.021986473</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
@@ -17898,10 +17898,10 @@
         <v>714</v>
       </c>
       <c r="N399" t="n">
-        <v>3224.5685238095</v>
+        <v>3224.5685400763</v>
       </c>
       <c r="O399" t="n">
-        <v>2302341.925999983</v>
+        <v>2302341.937614478</v>
       </c>
       <c r="P399" t="n">
         <v>4500</v>
@@ -17944,10 +17944,10 @@
         <v>1152</v>
       </c>
       <c r="N400" t="n">
-        <v>1655.9309666884</v>
+        <v>1669.0127123107</v>
       </c>
       <c r="O400" t="n">
-        <v>1907632.473625037</v>
+        <v>1922702.644581926</v>
       </c>
       <c r="P400" t="n">
         <v>2500</v>
@@ -19057,10 +19057,10 @@
         <v>216</v>
       </c>
       <c r="N424" t="n">
-        <v>2286.1647937672</v>
+        <v>2286.1647358665</v>
       </c>
       <c r="O424" t="n">
-        <v>493811.5954537152</v>
+        <v>493811.582947164</v>
       </c>
       <c r="P424" t="n">
         <v>3000</v>
@@ -19413,10 +19413,10 @@
         <v>7572</v>
       </c>
       <c r="N432" t="n">
-        <v>517.28908220781</v>
+        <v>517.28922545101</v>
       </c>
       <c r="O432" t="n">
-        <v>3916912.930477537</v>
+        <v>3916914.015115048</v>
       </c>
       <c r="P432" t="n">
         <v>900</v>
@@ -19462,10 +19462,10 @@
         <v>504</v>
       </c>
       <c r="N433" t="n">
-        <v>3110.842321894</v>
+        <v>3110.8421999117</v>
       </c>
       <c r="O433" t="n">
-        <v>1567864.530234576</v>
+        <v>1567864.468755497</v>
       </c>
       <c r="P433" t="n">
         <v>4500</v>
@@ -19594,10 +19594,10 @@
         <v>17096</v>
       </c>
       <c r="N436" t="n">
-        <v>703.79521051815</v>
+        <v>703.79520622865</v>
       </c>
       <c r="O436" t="n">
-        <v>12032082.91901829</v>
+        <v>12032082.845685</v>
       </c>
       <c r="P436" t="n">
         <v>900</v>
@@ -20171,10 +20171,10 @@
         <v>1369</v>
       </c>
       <c r="N449" t="n">
-        <v>1595.513125523</v>
+        <v>1595.5130117944</v>
       </c>
       <c r="O449" t="n">
-        <v>2184257.468840987</v>
+        <v>2184257.313146533</v>
       </c>
       <c r="P449" t="n">
         <v>2500</v>
@@ -20676,10 +20676,10 @@
         <v>4</v>
       </c>
       <c r="N460" t="n">
-        <v>1783.798877225</v>
+        <v>1783.7988767123</v>
       </c>
       <c r="O460" t="n">
-        <v>7135.1955089</v>
+        <v>7135.1955068492</v>
       </c>
       <c r="P460" t="n">
         <v>1500</v>
@@ -21274,10 +21274,10 @@
         <v>40</v>
       </c>
       <c r="N473" t="n">
-        <v>44113.603820225</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O473" t="n">
-        <v>1764544.152809</v>
+        <v>1764544.15367232</v>
       </c>
       <c r="P473" t="n">
         <v>71900</v>
@@ -22407,10 +22407,10 @@
         <v>5</v>
       </c>
       <c r="N499" t="n">
-        <v>1176.57</v>
+        <v>1179.3131202642</v>
       </c>
       <c r="O499" t="n">
-        <v>5882.849999999999</v>
+        <v>5896.565601321</v>
       </c>
       <c r="P499" t="n">
         <v>1900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3062015504</v>
+        <v>1811.3067953668</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.116279072</v>
+        <v>326035.223166024</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -999,10 +999,10 @@
         <v>112</v>
       </c>
       <c r="N15" t="n">
-        <v>1990.0435416667</v>
+        <v>1990.0435294118</v>
       </c>
       <c r="O15" t="n">
-        <v>222884.8766666704</v>
+        <v>222884.8752941216</v>
       </c>
       <c r="P15" t="n">
         <v>4400</v>
@@ -1914,22 +1914,22 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>22510.483333333</v>
       </c>
       <c r="O38" t="n">
-        <v>135062.899999998</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>44900</v>
       </c>
       <c r="Q38" t="n">
-        <v>269400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2076,10 +2076,10 @@
         <v>144</v>
       </c>
       <c r="N42" t="n">
-        <v>3716.3301935484</v>
+        <v>3716.3301938611</v>
       </c>
       <c r="O42" t="n">
-        <v>535151.5478709696</v>
+        <v>535151.5479159984</v>
       </c>
       <c r="P42" t="n">
         <v>9500</v>
@@ -2505,10 +2505,10 @@
         <v>152</v>
       </c>
       <c r="N53" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="O53" t="n">
-        <v>594415.4819512183</v>
+        <v>594415.4808163256</v>
       </c>
       <c r="P53" t="n">
         <v>9100</v>
@@ -3013,22 +3013,22 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M65" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="N65" t="n">
         <v>77455.737927928</v>
       </c>
       <c r="O65" t="n">
-        <v>7900485.268648656</v>
+        <v>7435750.841081088</v>
       </c>
       <c r="P65" t="n">
         <v>122900</v>
       </c>
       <c r="Q65" t="n">
-        <v>12535800</v>
+        <v>11798400</v>
       </c>
     </row>
     <row r="66">
@@ -3060,22 +3060,22 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N66" t="n">
         <v>141416.88456026</v>
       </c>
       <c r="O66" t="n">
-        <v>15838691.07074912</v>
+        <v>15697274.18618886</v>
       </c>
       <c r="P66" t="n">
         <v>251900</v>
       </c>
       <c r="Q66" t="n">
-        <v>28212800</v>
+        <v>27960900</v>
       </c>
     </row>
     <row r="67">
@@ -3553,10 +3553,10 @@
         <v>85</v>
       </c>
       <c r="N77" t="n">
-        <v>61666.874026667</v>
+        <v>61666.874048257</v>
       </c>
       <c r="O77" t="n">
-        <v>5241684.292266695</v>
+        <v>5241684.294101845</v>
       </c>
       <c r="P77" t="n">
         <v>98900</v>
@@ -3630,22 +3630,22 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M79" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="N79" t="n">
         <v>3865.67</v>
       </c>
       <c r="O79" t="n">
-        <v>1163566.67</v>
+        <v>1113312.96</v>
       </c>
       <c r="P79" t="n">
         <v>5500</v>
       </c>
       <c r="Q79" t="n">
-        <v>1655500</v>
+        <v>1584000</v>
       </c>
     </row>
     <row r="80">
@@ -3939,10 +3939,10 @@
         <v>1440</v>
       </c>
       <c r="N86" t="n">
-        <v>1950.2146537678</v>
+        <v>1950.2145987654</v>
       </c>
       <c r="O86" t="n">
-        <v>2808309.101425632</v>
+        <v>2808309.022222176</v>
       </c>
       <c r="P86" t="n">
         <v>2900</v>
@@ -4963,10 +4963,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2558256496</v>
+        <v>2582.2557662062</v>
       </c>
       <c r="O110" t="n">
-        <v>2788836.291701568</v>
+        <v>2788836.227502696</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5055,10 +5055,10 @@
         <v>1986</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.8961603854</v>
+        <v>5216.8961467368</v>
       </c>
       <c r="O112" t="n">
-        <v>10360755.77452541</v>
+        <v>10360755.74741928</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5835,10 +5835,10 @@
         <v>64</v>
       </c>
       <c r="N129" t="n">
-        <v>4890.9300483676</v>
+        <v>4890.9300485437</v>
       </c>
       <c r="O129" t="n">
-        <v>313019.5230955264</v>
+        <v>313019.5231067968</v>
       </c>
       <c r="P129" t="n">
         <v>8200</v>
@@ -6468,10 +6468,10 @@
         <v>264</v>
       </c>
       <c r="N143" t="n">
-        <v>3594.2540520446</v>
+        <v>3594.2540372671</v>
       </c>
       <c r="O143" t="n">
-        <v>948883.0697397745</v>
+        <v>948883.0658385145</v>
       </c>
       <c r="P143" t="n">
         <v>6500</v>
@@ -6693,10 +6693,10 @@
         <v>361</v>
       </c>
       <c r="N148" t="n">
-        <v>14822.378854415</v>
+        <v>14822.378852361</v>
       </c>
       <c r="O148" t="n">
-        <v>5350878.766443815</v>
+        <v>5350878.765702321</v>
       </c>
       <c r="P148" t="n">
         <v>24900</v>
@@ -6772,25 +6772,25 @@
         <v>39</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M150" t="n">
-        <v>39</v>
+        <v>576</v>
       </c>
       <c r="N150" t="n">
         <v>2090.85</v>
       </c>
       <c r="O150" t="n">
-        <v>81543.14999999999</v>
+        <v>1204329.6</v>
       </c>
       <c r="P150" t="n">
         <v>2900</v>
       </c>
       <c r="Q150" t="n">
-        <v>113100</v>
+        <v>1670400</v>
       </c>
     </row>
     <row r="151">
@@ -7096,10 +7096,10 @@
         <v>78</v>
       </c>
       <c r="N157" t="n">
-        <v>3041.6600129786</v>
+        <v>3041.6600130804</v>
       </c>
       <c r="O157" t="n">
-        <v>237249.4810123308</v>
+        <v>237249.4810202712</v>
       </c>
       <c r="P157" t="n">
         <v>5500</v>
@@ -7142,10 +7142,10 @@
         <v>809</v>
       </c>
       <c r="N158" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O158" t="n">
-        <v>3537118.528532536</v>
+        <v>3537118.528805573</v>
       </c>
       <c r="P158" t="n">
         <v>7500</v>
@@ -7400,22 +7400,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M164" t="n">
-        <v>5706</v>
+        <v>5616</v>
       </c>
       <c r="N164" t="n">
         <v>4648.6</v>
       </c>
       <c r="O164" t="n">
-        <v>26524911.6</v>
+        <v>26106537.6</v>
       </c>
       <c r="P164" t="n">
         <v>8900</v>
       </c>
       <c r="Q164" t="n">
-        <v>50783400</v>
+        <v>49982400</v>
       </c>
     </row>
     <row r="165">
@@ -8287,10 +8287,10 @@
         <v>1152</v>
       </c>
       <c r="N184" t="n">
-        <v>1630.9234875283</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="O184" t="n">
-        <v>1878823.857632602</v>
+        <v>1878823.932806707</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8333,10 +8333,10 @@
         <v>768</v>
       </c>
       <c r="N185" t="n">
-        <v>1690.5983498584</v>
+        <v>1690.5981330472</v>
       </c>
       <c r="O185" t="n">
-        <v>1298379.532691251</v>
+        <v>1298379.366180249</v>
       </c>
       <c r="P185" t="n">
         <v>2900</v>
@@ -8379,10 +8379,10 @@
         <v>5472</v>
       </c>
       <c r="N186" t="n">
-        <v>1550.1935332762</v>
+        <v>1550.1935823921</v>
       </c>
       <c r="O186" t="n">
-        <v>8482659.014087366</v>
+        <v>8482659.282849573</v>
       </c>
       <c r="P186" t="n">
         <v>2500</v>
@@ -8425,10 +8425,10 @@
         <v>2016</v>
       </c>
       <c r="N187" t="n">
-        <v>2403.5115510508</v>
+        <v>2403.5116616598</v>
       </c>
       <c r="O187" t="n">
-        <v>4845479.286918413</v>
+        <v>4845479.509906157</v>
       </c>
       <c r="P187" t="n">
         <v>3500</v>
@@ -9833,22 +9833,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M220" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N220" t="n">
-        <v>22485.695881007</v>
+        <v>22485.695577396</v>
       </c>
       <c r="O220" t="n">
-        <v>2023712.62929063</v>
+        <v>674570.86732188</v>
       </c>
       <c r="P220" t="n">
         <v>36500</v>
       </c>
       <c r="Q220" t="n">
-        <v>3285000</v>
+        <v>1095000</v>
       </c>
     </row>
     <row r="221">
@@ -10495,10 +10495,10 @@
         <v>150</v>
       </c>
       <c r="N235" t="n">
-        <v>4285.1954682454</v>
+        <v>4285.1954741379</v>
       </c>
       <c r="O235" t="n">
-        <v>642779.32023681</v>
+        <v>642779.3211206851</v>
       </c>
       <c r="P235" t="n">
         <v>6900</v>
@@ -10959,10 +10959,10 @@
         <v>1</v>
       </c>
       <c r="N246" t="n">
-        <v>30244.600034702</v>
+        <v>30244.600034722</v>
       </c>
       <c r="O246" t="n">
-        <v>30244.600034702</v>
+        <v>30244.600034722</v>
       </c>
       <c r="P246" t="n">
         <v>48900</v>
@@ -11046,10 +11046,10 @@
         <v>150</v>
       </c>
       <c r="N248" t="n">
-        <v>11562.038518519</v>
+        <v>11562.038494624</v>
       </c>
       <c r="O248" t="n">
-        <v>1734305.77777785</v>
+        <v>1734305.7741936</v>
       </c>
       <c r="P248" t="n">
         <v>18500</v>
@@ -12622,10 +12622,10 @@
         <v>399</v>
       </c>
       <c r="N284" t="n">
-        <v>5218.1705479452</v>
+        <v>5218.1705520703</v>
       </c>
       <c r="O284" t="n">
-        <v>2082050.048630135</v>
+        <v>2082050.05027605</v>
       </c>
       <c r="P284" t="n">
         <v>8500</v>
@@ -12668,10 +12668,10 @@
         <v>206</v>
       </c>
       <c r="N285" t="n">
-        <v>1595.0093800979</v>
+        <v>1595.0093780687</v>
       </c>
       <c r="O285" t="n">
-        <v>328571.9323001674</v>
+        <v>328571.9318821522</v>
       </c>
       <c r="P285" t="n">
         <v>2600</v>
@@ -12714,10 +12714,10 @@
         <v>541</v>
       </c>
       <c r="N286" t="n">
-        <v>3610.650025641</v>
+        <v>3610.65002574</v>
       </c>
       <c r="O286" t="n">
-        <v>1953361.663871781</v>
+        <v>1953361.66392534</v>
       </c>
       <c r="P286" t="n">
         <v>5800</v>
@@ -13128,10 +13128,10 @@
         <v>384</v>
       </c>
       <c r="N295" t="n">
-        <v>1664.3569717514</v>
+        <v>1664.3568077803</v>
       </c>
       <c r="O295" t="n">
-        <v>639113.0771525375</v>
+        <v>639113.0141876352</v>
       </c>
       <c r="P295" t="n">
         <v>2900</v>
@@ -14600,10 +14600,10 @@
         <v>28</v>
       </c>
       <c r="N327" t="n">
-        <v>2252.2966708385</v>
+        <v>2252.2968774194</v>
       </c>
       <c r="O327" t="n">
-        <v>63064.30678347801</v>
+        <v>63064.3125677432</v>
       </c>
       <c r="P327" t="n">
         <v>3900</v>
@@ -14782,10 +14782,10 @@
         <v>864</v>
       </c>
       <c r="N331" t="n">
-        <v>2328.1187254606</v>
+        <v>2328.1187184938</v>
       </c>
       <c r="O331" t="n">
-        <v>2011494.578797959</v>
+        <v>2011494.572778643</v>
       </c>
       <c r="P331" t="n">
         <v>4500</v>
@@ -17305,10 +17305,10 @@
         <v>4224</v>
       </c>
       <c r="N386" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O386" t="n">
-        <v>6403747.898929497</v>
+        <v>6403747.891035264</v>
       </c>
       <c r="P386" t="n">
         <v>2300</v>
@@ -17351,10 +17351,10 @@
         <v>1152</v>
       </c>
       <c r="N387" t="n">
-        <v>2458.5131932225</v>
+        <v>2458.5131821149</v>
       </c>
       <c r="O387" t="n">
-        <v>2832207.19859232</v>
+        <v>2832207.185796365</v>
       </c>
       <c r="P387" t="n">
         <v>3500</v>
@@ -17535,10 +17535,10 @@
         <v>1152</v>
       </c>
       <c r="N391" t="n">
-        <v>1803.0156033058</v>
+        <v>1803.0156051587</v>
       </c>
       <c r="O391" t="n">
-        <v>2077073.975008281</v>
+        <v>2077073.977142822</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -17581,10 +17581,10 @@
         <v>144</v>
       </c>
       <c r="N392" t="n">
-        <v>3306.5951807229</v>
+        <v>3306.5951742627</v>
       </c>
       <c r="O392" t="n">
-        <v>476149.7060240976</v>
+        <v>476149.7050938288</v>
       </c>
       <c r="P392" t="n">
         <v>4900</v>
@@ -17673,10 +17673,10 @@
         <v>216</v>
       </c>
       <c r="N394" t="n">
-        <v>2108.791733871</v>
+        <v>2108.7917654987</v>
       </c>
       <c r="O394" t="n">
-        <v>455499.014516136</v>
+        <v>455499.0213477192</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -17719,10 +17719,10 @@
         <v>684</v>
       </c>
       <c r="N395" t="n">
-        <v>2056.0833654773</v>
+        <v>2056.0833612094</v>
       </c>
       <c r="O395" t="n">
-        <v>1406361.021986473</v>
+        <v>1406361.01906723</v>
       </c>
       <c r="P395" t="n">
         <v>2900</v>
@@ -17765,10 +17765,10 @@
         <v>714</v>
       </c>
       <c r="N396" t="n">
-        <v>3224.5685400763</v>
+        <v>3224.5685727969</v>
       </c>
       <c r="O396" t="n">
-        <v>2302341.937614478</v>
+        <v>2302341.960976987</v>
       </c>
       <c r="P396" t="n">
         <v>4500</v>
@@ -17811,10 +17811,10 @@
         <v>1152</v>
       </c>
       <c r="N397" t="n">
-        <v>1655.9308953259</v>
+        <v>1655.9308833223</v>
       </c>
       <c r="O397" t="n">
-        <v>1907632.391415437</v>
+        <v>1907632.37758729</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
@@ -18128,22 +18128,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M404" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N404" t="n">
         <v>5347.73</v>
       </c>
       <c r="O404" t="n">
-        <v>267386.5</v>
+        <v>0</v>
       </c>
       <c r="P404" t="n">
         <v>9500</v>
       </c>
       <c r="Q404" t="n">
-        <v>475000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -18226,10 +18226,10 @@
         <v>8400</v>
       </c>
       <c r="N406" t="n">
-        <v>1955.2371159315</v>
+        <v>1955.2371140003</v>
       </c>
       <c r="O406" t="n">
-        <v>16423991.7738246</v>
+        <v>16423991.75760252</v>
       </c>
       <c r="P406" t="n">
         <v>3000</v>
@@ -18924,10 +18924,10 @@
         <v>216</v>
       </c>
       <c r="N421" t="n">
-        <v>2286.1647358665</v>
+        <v>2286.1647064306</v>
       </c>
       <c r="O421" t="n">
-        <v>493811.582947164</v>
+        <v>493811.5765890095</v>
       </c>
       <c r="P421" t="n">
         <v>3000</v>
@@ -19280,10 +19280,10 @@
         <v>7572</v>
       </c>
       <c r="N429" t="n">
-        <v>517.28922545101</v>
+        <v>517.2892916984</v>
       </c>
       <c r="O429" t="n">
-        <v>3916914.015115048</v>
+        <v>3916914.516740285</v>
       </c>
       <c r="P429" t="n">
         <v>900</v>
@@ -19323,22 +19323,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="M430" t="n">
-        <v>504</v>
+        <v>252</v>
       </c>
       <c r="N430" t="n">
-        <v>3110.8421999117</v>
+        <v>3110.8418772978</v>
       </c>
       <c r="O430" t="n">
-        <v>1567864.468755497</v>
+        <v>783932.1530790456</v>
       </c>
       <c r="P430" t="n">
         <v>4500</v>
       </c>
       <c r="Q430" t="n">
-        <v>2268000</v>
+        <v>1134000</v>
       </c>
     </row>
     <row r="431">
@@ -19461,10 +19461,10 @@
         <v>17096</v>
       </c>
       <c r="N433" t="n">
-        <v>703.79520622865</v>
+        <v>703.79518726322</v>
       </c>
       <c r="O433" t="n">
-        <v>12032082.845685</v>
+        <v>12032082.52145201</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -20038,10 +20038,10 @@
         <v>1369</v>
       </c>
       <c r="N446" t="n">
-        <v>1595.5130117944</v>
+        <v>1595.5128965225</v>
       </c>
       <c r="O446" t="n">
-        <v>2184257.313146533</v>
+        <v>2184257.155339302</v>
       </c>
       <c r="P446" t="n">
         <v>2500</v>
@@ -20955,22 +20955,22 @@
         <v>0</v>
       </c>
       <c r="L466" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M466" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="N466" t="n">
         <v>24338.47</v>
       </c>
       <c r="O466" t="n">
-        <v>2482523.94</v>
+        <v>1362954.32</v>
       </c>
       <c r="P466" t="n">
         <v>27900</v>
       </c>
       <c r="Q466" t="n">
-        <v>2845800</v>
+        <v>1562400</v>
       </c>
     </row>
     <row r="467">

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -839,10 +839,10 @@
         <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>8642.2268253968</v>
+        <v>8642.226774193499</v>
       </c>
       <c r="O11" t="n">
-        <v>207413.4438095232</v>
+        <v>207413.442580644</v>
       </c>
       <c r="P11" t="n">
         <v>13900</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3067953668</v>
+        <v>1811.3069785884</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.223166024</v>
+        <v>326035.256145912</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464728365</v>
+        <v>3376.7464699454</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1393721059</v>
+        <v>823926.1386666775</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8546451613</v>
+        <v>6272.8546905537</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.603354841</v>
+        <v>1354936.613159599</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2458,10 +2458,10 @@
         <v>152</v>
       </c>
       <c r="N52" t="n">
-        <v>3910.6281632653</v>
+        <v>3910.6281595092</v>
       </c>
       <c r="O52" t="n">
-        <v>594415.4808163256</v>
+        <v>594415.4802453984</v>
       </c>
       <c r="P52" t="n">
         <v>9100</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.965957447</v>
+        <v>15711.965922747</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.3659574561</v>
+        <v>754174.3642918561</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2675,10 +2675,10 @@
         <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>13712.844516129</v>
+        <v>13712.844</v>
       </c>
       <c r="O57" t="n">
-        <v>27425.689032258</v>
+        <v>27425.688</v>
       </c>
       <c r="P57" t="n">
         <v>22600</v>
@@ -2714,10 +2714,10 @@
         <v>136</v>
       </c>
       <c r="N58" t="n">
-        <v>7407.7300542005</v>
+        <v>7407.7300543478</v>
       </c>
       <c r="O58" t="n">
-        <v>1007451.287371268</v>
+        <v>1007451.287391301</v>
       </c>
       <c r="P58" t="n">
         <v>10900</v>
@@ -3061,10 +3061,10 @@
         <v>27</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20057377</v>
+        <v>200072.20066116</v>
       </c>
       <c r="O66" t="n">
-        <v>5401949.415491791</v>
+        <v>5401949.41785132</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.79407407</v>
+        <v>174389.795</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.76444442</v>
+        <v>1046338.77</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3150,10 +3150,10 @@
         <v>16</v>
       </c>
       <c r="N68" t="n">
-        <v>251809.29393939</v>
+        <v>251809.29375</v>
       </c>
       <c r="O68" t="n">
-        <v>4028948.70303024</v>
+        <v>4028948.7</v>
       </c>
       <c r="P68" t="n">
         <v>584000</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874048257</v>
+        <v>61666.874070081</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.294101845</v>
+        <v>5241684.295956885</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4916,10 +4916,10 @@
         <v>1080</v>
       </c>
       <c r="N109" t="n">
-        <v>2582.2557662062</v>
+        <v>2582.2557508532</v>
       </c>
       <c r="O109" t="n">
-        <v>2788836.227502696</v>
+        <v>2788836.210921456</v>
       </c>
       <c r="P109" t="n">
         <v>4500</v>
@@ -5008,10 +5008,10 @@
         <v>1986</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8961467368</v>
+        <v>5216.8961296772</v>
       </c>
       <c r="O111" t="n">
-        <v>10360755.74741928</v>
+        <v>10360755.71353892</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
@@ -5100,10 +5100,10 @@
         <v>6298</v>
       </c>
       <c r="N113" t="n">
-        <v>3158.860825504</v>
+        <v>3158.8608260699</v>
       </c>
       <c r="O113" t="n">
-        <v>19894505.47902419</v>
+        <v>19894505.48258823</v>
       </c>
       <c r="P113" t="n">
         <v>5600</v>
@@ -5330,10 +5330,10 @@
         <v>224</v>
       </c>
       <c r="N118" t="n">
-        <v>2694.8232244517</v>
+        <v>2694.8231862975</v>
       </c>
       <c r="O118" t="n">
-        <v>603640.4022771808</v>
+        <v>603640.3937306399</v>
       </c>
       <c r="P118" t="n">
         <v>4900</v>
@@ -5650,10 +5650,10 @@
         <v>3024</v>
       </c>
       <c r="N125" t="n">
-        <v>3795.7100075415</v>
+        <v>3795.7100075514</v>
       </c>
       <c r="O125" t="n">
-        <v>11478227.0628055</v>
+        <v>11478227.06283543</v>
       </c>
       <c r="P125" t="n">
         <v>6200</v>
@@ -5788,10 +5788,10 @@
         <v>64</v>
       </c>
       <c r="N128" t="n">
-        <v>4890.9300485437</v>
+        <v>4890.9300486322</v>
       </c>
       <c r="O128" t="n">
-        <v>313019.5231067968</v>
+        <v>313019.5231124608</v>
       </c>
       <c r="P128" t="n">
         <v>8200</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.2540372671</v>
+        <v>3594.2540224159</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.0658385145</v>
+        <v>948883.0619177977</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -6646,10 +6646,10 @@
         <v>361</v>
       </c>
       <c r="N147" t="n">
-        <v>14822.378852361</v>
+        <v>14822.378850987</v>
       </c>
       <c r="O147" t="n">
-        <v>5350878.765702321</v>
+        <v>5350878.765206306</v>
       </c>
       <c r="P147" t="n">
         <v>24900</v>
@@ -7049,10 +7049,10 @@
         <v>78</v>
       </c>
       <c r="N156" t="n">
-        <v>3041.6600130804</v>
+        <v>3041.6600131579</v>
       </c>
       <c r="O156" t="n">
-        <v>237249.4810202712</v>
+        <v>237249.4810263162</v>
       </c>
       <c r="P156" t="n">
         <v>5500</v>
@@ -7444,10 +7444,10 @@
         <v>10357</v>
       </c>
       <c r="N165" t="n">
-        <v>1532.6290281516</v>
+        <v>1532.62902709</v>
       </c>
       <c r="O165" t="n">
-        <v>15873438.84456612</v>
+        <v>15873438.83357113</v>
       </c>
       <c r="P165" t="n">
         <v>1200</v>
@@ -7790,10 +7790,10 @@
         <v>200</v>
       </c>
       <c r="N173" t="n">
-        <v>2021.7211231884</v>
+        <v>2021.7211300122</v>
       </c>
       <c r="O173" t="n">
-        <v>404344.22463768</v>
+        <v>404344.22600244</v>
       </c>
       <c r="P173" t="n">
         <v>2400</v>
@@ -8240,10 +8240,10 @@
         <v>1152</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9235527836</v>
+        <v>1630.9235742505</v>
       </c>
       <c r="O183" t="n">
-        <v>1878823.932806707</v>
+        <v>1878823.957536576</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8286,10 +8286,10 @@
         <v>768</v>
       </c>
       <c r="N184" t="n">
-        <v>1690.5981330472</v>
+        <v>1690.5974723655</v>
       </c>
       <c r="O184" t="n">
-        <v>1298379.366180249</v>
+        <v>1298378.858776704</v>
       </c>
       <c r="P184" t="n">
         <v>2900</v>
@@ -8332,10 +8332,10 @@
         <v>5472</v>
       </c>
       <c r="N185" t="n">
-        <v>1550.1935823921</v>
+        <v>1550.1936350279</v>
       </c>
       <c r="O185" t="n">
-        <v>8482659.282849573</v>
+        <v>8482659.570872668</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8378,10 +8378,10 @@
         <v>2016</v>
       </c>
       <c r="N186" t="n">
-        <v>2403.5116616598</v>
+        <v>2403.5118666412</v>
       </c>
       <c r="O186" t="n">
-        <v>4845479.509906157</v>
+        <v>4845479.923148659</v>
       </c>
       <c r="P186" t="n">
         <v>3500</v>
@@ -8592,10 +8592,10 @@
         <v>40</v>
       </c>
       <c r="N191" t="n">
-        <v>1020.1698591549</v>
+        <v>1020.1698412698</v>
       </c>
       <c r="O191" t="n">
-        <v>40806.794366196</v>
+        <v>40806.793650792</v>
       </c>
       <c r="P191" t="n">
         <v>1350</v>
@@ -9213,10 +9213,10 @@
         <v>1415</v>
       </c>
       <c r="N205" t="n">
-        <v>4196.872528417</v>
+        <v>4196.8725291181</v>
       </c>
       <c r="O205" t="n">
-        <v>5938574.627710055</v>
+        <v>5938574.628702112</v>
       </c>
       <c r="P205" t="n">
         <v>5900</v>
@@ -9792,10 +9792,10 @@
         <v>30</v>
       </c>
       <c r="N219" t="n">
-        <v>22485.695577396</v>
+        <v>22485.695571956</v>
       </c>
       <c r="O219" t="n">
-        <v>674570.86732188</v>
+        <v>674570.86715868</v>
       </c>
       <c r="P219" t="n">
         <v>36500</v>
@@ -9964,10 +9964,10 @@
         <v>1254</v>
       </c>
       <c r="N223" t="n">
-        <v>880.3295131797699</v>
+        <v>880.32952448883</v>
       </c>
       <c r="O223" t="n">
-        <v>1103933.209527432</v>
+        <v>1103933.223708993</v>
       </c>
       <c r="P223" t="n">
         <v>1200</v>
@@ -10051,10 +10051,10 @@
         <v>50</v>
       </c>
       <c r="N225" t="n">
-        <v>11431.604756098</v>
+        <v>11431.604691358</v>
       </c>
       <c r="O225" t="n">
-        <v>571580.2378049</v>
+        <v>571580.2345679</v>
       </c>
       <c r="P225" t="n">
         <v>48900</v>
@@ -10448,10 +10448,10 @@
         <v>150</v>
       </c>
       <c r="N234" t="n">
-        <v>4285.1954741379</v>
+        <v>4285.1954859611</v>
       </c>
       <c r="O234" t="n">
-        <v>642779.3211206851</v>
+        <v>642779.3228941649</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -10912,10 +10912,10 @@
         <v>1</v>
       </c>
       <c r="N245" t="n">
-        <v>30244.600034722</v>
+        <v>30244.600034762</v>
       </c>
       <c r="O245" t="n">
-        <v>30244.600034722</v>
+        <v>30244.600034762</v>
       </c>
       <c r="P245" t="n">
         <v>48900</v>
@@ -10999,10 +10999,10 @@
         <v>150</v>
       </c>
       <c r="N247" t="n">
-        <v>11562.038494624</v>
+        <v>11562.038478261</v>
       </c>
       <c r="O247" t="n">
-        <v>1734305.7741936</v>
+        <v>1734305.77173915</v>
       </c>
       <c r="P247" t="n">
         <v>18500</v>
@@ -11685,10 +11685,10 @@
         <v>34</v>
       </c>
       <c r="N263" t="n">
-        <v>27123.765232775</v>
+        <v>27123.765223881</v>
       </c>
       <c r="O263" t="n">
-        <v>922208.01791435</v>
+        <v>922208.017611954</v>
       </c>
       <c r="P263" t="n">
         <v>44500</v>
@@ -11813,10 +11813,10 @@
         <v>23</v>
       </c>
       <c r="N266" t="n">
-        <v>31771.063719008</v>
+        <v>31771.063781513</v>
       </c>
       <c r="O266" t="n">
-        <v>730734.465537184</v>
+        <v>730734.4669747989</v>
       </c>
       <c r="P266" t="n">
         <v>68900</v>
@@ -11946,10 +11946,10 @@
         <v>480</v>
       </c>
       <c r="N269" t="n">
-        <v>7969.9501665405</v>
+        <v>7969.9501669196</v>
       </c>
       <c r="O269" t="n">
-        <v>3825576.07993944</v>
+        <v>3825576.080121408</v>
       </c>
       <c r="P269" t="n">
         <v>12900</v>
@@ -12621,10 +12621,10 @@
         <v>206</v>
       </c>
       <c r="N284" t="n">
-        <v>1595.0093780687</v>
+        <v>1595.009375</v>
       </c>
       <c r="O284" t="n">
-        <v>328571.9318821522</v>
+        <v>328571.93125</v>
       </c>
       <c r="P284" t="n">
         <v>2600</v>
@@ -12667,10 +12667,10 @@
         <v>541</v>
       </c>
       <c r="N285" t="n">
-        <v>3610.65002574</v>
+        <v>3610.6500258065</v>
       </c>
       <c r="O285" t="n">
-        <v>1953361.66392534</v>
+        <v>1953361.663961316</v>
       </c>
       <c r="P285" t="n">
         <v>5800</v>
@@ -13081,10 +13081,10 @@
         <v>384</v>
       </c>
       <c r="N294" t="n">
-        <v>1664.3568077803</v>
+        <v>1664.355973236</v>
       </c>
       <c r="O294" t="n">
-        <v>639113.0141876352</v>
+        <v>639112.693722624</v>
       </c>
       <c r="P294" t="n">
         <v>2900</v>
@@ -13771,10 +13771,10 @@
         <v>1145</v>
       </c>
       <c r="N309" t="n">
-        <v>1778.4726172988</v>
+        <v>1778.4726251691</v>
       </c>
       <c r="O309" t="n">
-        <v>2036351.146807126</v>
+        <v>2036351.15581862</v>
       </c>
       <c r="P309" t="n">
         <v>4900</v>
@@ -14735,10 +14735,10 @@
         <v>864</v>
       </c>
       <c r="N330" t="n">
-        <v>2328.1187184938</v>
+        <v>2328.1187161545</v>
       </c>
       <c r="O330" t="n">
-        <v>2011494.572778643</v>
+        <v>2011494.570757488</v>
       </c>
       <c r="P330" t="n">
         <v>4500</v>
@@ -17258,10 +17258,10 @@
         <v>4224</v>
       </c>
       <c r="N385" t="n">
-        <v>1516.038799961</v>
+        <v>1516.0387986728</v>
       </c>
       <c r="O385" t="n">
-        <v>6403747.891035264</v>
+        <v>6403747.885593908</v>
       </c>
       <c r="P385" t="n">
         <v>2300</v>
@@ -17350,10 +17350,10 @@
         <v>480</v>
       </c>
       <c r="N387" t="n">
-        <v>1907.393656644</v>
+        <v>1907.3930202775</v>
       </c>
       <c r="O387" t="n">
-        <v>915548.95518912</v>
+        <v>915548.6497332</v>
       </c>
       <c r="P387" t="n">
         <v>2500</v>
@@ -17442,10 +17442,10 @@
         <v>960</v>
       </c>
       <c r="N389" t="n">
-        <v>2079.3840374332</v>
+        <v>2079.3840254521</v>
       </c>
       <c r="O389" t="n">
-        <v>1996208.675935872</v>
+        <v>1996208.664434016</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17534,10 +17534,10 @@
         <v>144</v>
       </c>
       <c r="N391" t="n">
-        <v>3306.5951742627</v>
+        <v>3306.5951351351</v>
       </c>
       <c r="O391" t="n">
-        <v>476149.7050938288</v>
+        <v>476149.6994594544</v>
       </c>
       <c r="P391" t="n">
         <v>4900</v>
@@ -17626,10 +17626,10 @@
         <v>216</v>
       </c>
       <c r="N393" t="n">
-        <v>2108.7917654987</v>
+        <v>2108.7918292683</v>
       </c>
       <c r="O393" t="n">
-        <v>455499.0213477192</v>
+        <v>455499.0351219528</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -17718,10 +17718,10 @@
         <v>714</v>
       </c>
       <c r="N395" t="n">
-        <v>3224.5685727969</v>
+        <v>3224.5688003933</v>
       </c>
       <c r="O395" t="n">
-        <v>2302341.960976987</v>
+        <v>2302342.123480816</v>
       </c>
       <c r="P395" t="n">
         <v>4500</v>
@@ -17764,10 +17764,10 @@
         <v>1152</v>
       </c>
       <c r="N396" t="n">
-        <v>1655.9308833223</v>
+        <v>1655.9308652576</v>
       </c>
       <c r="O396" t="n">
-        <v>1907632.37758729</v>
+        <v>1907632.356776755</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -19189,10 +19189,10 @@
         <v>7572</v>
       </c>
       <c r="N427" t="n">
-        <v>517.2892916984</v>
+        <v>517.28943177426</v>
       </c>
       <c r="O427" t="n">
-        <v>3916914.516740285</v>
+        <v>3916915.577394697</v>
       </c>
       <c r="P427" t="n">
         <v>900</v>
@@ -19238,10 +19238,10 @@
         <v>252</v>
       </c>
       <c r="N428" t="n">
-        <v>3110.8418772978</v>
+        <v>3110.8416960301</v>
       </c>
       <c r="O428" t="n">
-        <v>783932.1530790456</v>
+        <v>783932.1073995852</v>
       </c>
       <c r="P428" t="n">
         <v>4500</v>
@@ -19326,10 +19326,10 @@
         <v>5</v>
       </c>
       <c r="N430" t="n">
-        <v>3002.0209957326</v>
+        <v>3002.021</v>
       </c>
       <c r="O430" t="n">
-        <v>15010.104978663</v>
+        <v>15010.105</v>
       </c>
       <c r="P430" t="n">
         <v>4500</v>
@@ -19370,10 +19370,10 @@
         <v>17096</v>
       </c>
       <c r="N431" t="n">
-        <v>703.79518726322</v>
+        <v>703.79518287415</v>
       </c>
       <c r="O431" t="n">
-        <v>12032082.52145201</v>
+        <v>12032082.44641647</v>
       </c>
       <c r="P431" t="n">
         <v>900</v>
@@ -19772,10 +19772,10 @@
         <v>381</v>
       </c>
       <c r="N440" t="n">
-        <v>3629.7161041667</v>
+        <v>3629.7160714286</v>
       </c>
       <c r="O440" t="n">
-        <v>1382921.835687513</v>
+        <v>1382921.823214297</v>
       </c>
       <c r="P440" t="n">
         <v>4900</v>
@@ -19947,10 +19947,10 @@
         <v>1369</v>
       </c>
       <c r="N444" t="n">
-        <v>1595.5128965225</v>
+        <v>1595.5127943686</v>
       </c>
       <c r="O444" t="n">
-        <v>2184257.155339302</v>
+        <v>2184257.015490613</v>
       </c>
       <c r="P444" t="n">
         <v>2500</v>
@@ -21626,10 +21626,10 @@
         <v>1198</v>
       </c>
       <c r="N481" t="n">
-        <v>4282.1072467371</v>
+        <v>4282.1072450249</v>
       </c>
       <c r="O481" t="n">
-        <v>5129964.481591045</v>
+        <v>5129964.47953983</v>
       </c>
       <c r="P481" t="n">
         <v>5300</v>
@@ -21667,10 +21667,10 @@
         <v>198</v>
       </c>
       <c r="N482" t="n">
-        <v>5577.2680465116</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O482" t="n">
-        <v>1104299.073209297</v>
+        <v>1104299.071401874</v>
       </c>
       <c r="P482" t="n">
         <v>6500</v>
@@ -21969,10 +21969,10 @@
         <v>955</v>
       </c>
       <c r="N489" t="n">
-        <v>2129.8331627057</v>
+        <v>2129.8331714024</v>
       </c>
       <c r="O489" t="n">
-        <v>2033990.670383943</v>
+        <v>2033990.678689292</v>
       </c>
       <c r="P489" t="n">
         <v>2700</v>
@@ -22013,10 +22013,10 @@
         <v>1010</v>
       </c>
       <c r="N490" t="n">
-        <v>2106.9511305147</v>
+        <v>2106.9511336406</v>
       </c>
       <c r="O490" t="n">
-        <v>2128020.641819847</v>
+        <v>2128020.644977006</v>
       </c>
       <c r="P490" t="n">
         <v>2700</v>
@@ -22142,10 +22142,10 @@
         <v>436</v>
       </c>
       <c r="N493" t="n">
-        <v>5497.1753314121</v>
+        <v>5497.1753179191</v>
       </c>
       <c r="O493" t="n">
-        <v>2396768.444495676</v>
+        <v>2396768.438612727</v>
       </c>
       <c r="P493" t="n">
         <v>6500</v>
@@ -22271,10 +22271,10 @@
         <v>5129</v>
       </c>
       <c r="N496" t="n">
-        <v>1794.2879721384</v>
+        <v>1794.2879692219</v>
       </c>
       <c r="O496" t="n">
-        <v>9202903.009097854</v>
+        <v>9202902.994139126</v>
       </c>
       <c r="P496" t="n">
         <v>1600</v>
@@ -22315,10 +22315,10 @@
         <v>481</v>
       </c>
       <c r="N497" t="n">
-        <v>2181.4248974943</v>
+        <v>2181.4247785548</v>
       </c>
       <c r="O497" t="n">
-        <v>1049265.375694758</v>
+        <v>1049265.318484859</v>
       </c>
       <c r="P497" t="n">
         <v>2900</v>
@@ -22828,10 +22828,10 @@
         <v>5</v>
       </c>
       <c r="N509" t="n">
-        <v>3683.6327020785</v>
+        <v>3683.6327400468</v>
       </c>
       <c r="O509" t="n">
-        <v>18418.1635103925</v>
+        <v>18418.163700234</v>
       </c>
       <c r="P509" t="n">
         <v>3600</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -792,22 +792,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="N10" t="n">
         <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>1944000</v>
+        <v>1620000</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1440000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="11">
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.256145912</v>
+        <v>326035.29942576</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1386666775</v>
+        <v>823926.1377243008</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -2458,10 +2458,10 @@
         <v>152</v>
       </c>
       <c r="N52" t="n">
-        <v>3910.6281595092</v>
+        <v>3910.6281481481</v>
       </c>
       <c r="O52" t="n">
-        <v>594415.4802453984</v>
+        <v>594415.4785185112</v>
       </c>
       <c r="P52" t="n">
         <v>9100</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.295956885</v>
+        <v>5241684.296891885</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4916,10 +4916,10 @@
         <v>1080</v>
       </c>
       <c r="N109" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O109" t="n">
-        <v>2788836.210921456</v>
+        <v>2788836.194219688</v>
       </c>
       <c r="P109" t="n">
         <v>4500</v>
@@ -4956,22 +4956,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M110" t="n">
-        <v>3379</v>
+        <v>3279</v>
       </c>
       <c r="N110" t="n">
         <v>10600</v>
       </c>
       <c r="O110" t="n">
-        <v>35817400</v>
+        <v>34757400</v>
       </c>
       <c r="P110" t="n">
         <v>17200</v>
       </c>
       <c r="Q110" t="n">
-        <v>58118800</v>
+        <v>56398800</v>
       </c>
     </row>
     <row r="111">
@@ -5002,22 +5002,22 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M111" t="n">
-        <v>1986</v>
+        <v>1898</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O111" t="n">
-        <v>10360755.71353892</v>
+        <v>9901668.846776182</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
       </c>
       <c r="Q111" t="n">
-        <v>16881000</v>
+        <v>16133000</v>
       </c>
     </row>
     <row r="112">
@@ -5650,10 +5650,10 @@
         <v>3024</v>
       </c>
       <c r="N125" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O125" t="n">
-        <v>11478227.06283543</v>
+        <v>11478227.06283997</v>
       </c>
       <c r="P125" t="n">
         <v>6200</v>
@@ -5788,10 +5788,10 @@
         <v>64</v>
       </c>
       <c r="N128" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O128" t="n">
-        <v>313019.5231124608</v>
+        <v>313019.523121952</v>
       </c>
       <c r="P128" t="n">
         <v>8200</v>
@@ -6065,10 +6065,10 @@
         <v>24</v>
       </c>
       <c r="N134" t="n">
-        <v>2267.0481451951</v>
+        <v>2267.0481436371</v>
       </c>
       <c r="O134" t="n">
-        <v>54409.1554846824</v>
+        <v>54409.1554472904</v>
       </c>
       <c r="P134" t="n">
         <v>3900</v>
@@ -6646,10 +6646,10 @@
         <v>361</v>
       </c>
       <c r="N147" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O147" t="n">
-        <v>5350878.765206306</v>
+        <v>5350878.76470957</v>
       </c>
       <c r="P147" t="n">
         <v>24900</v>
@@ -7049,10 +7049,10 @@
         <v>78</v>
       </c>
       <c r="N156" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O156" t="n">
-        <v>237249.4810263162</v>
+        <v>237249.48103311</v>
       </c>
       <c r="P156" t="n">
         <v>5500</v>
@@ -7095,10 +7095,10 @@
         <v>809</v>
       </c>
       <c r="N157" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O157" t="n">
-        <v>3537118.528805573</v>
+        <v>3537118.529215574</v>
       </c>
       <c r="P157" t="n">
         <v>7500</v>
@@ -7258,22 +7258,22 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M161" t="n">
-        <v>2655</v>
+        <v>2487</v>
       </c>
       <c r="N161" t="n">
         <v>3655.96</v>
       </c>
       <c r="O161" t="n">
-        <v>9706573.800000001</v>
+        <v>9092372.52</v>
       </c>
       <c r="P161" t="n">
         <v>5500</v>
       </c>
       <c r="Q161" t="n">
-        <v>14602500</v>
+        <v>13678500</v>
       </c>
     </row>
     <row r="162">
@@ -8240,10 +8240,10 @@
         <v>1152</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O183" t="n">
-        <v>1878823.957536576</v>
+        <v>1878823.996171661</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8286,10 +8286,10 @@
         <v>768</v>
       </c>
       <c r="N184" t="n">
-        <v>1690.5974723655</v>
+        <v>1690.5973219585</v>
       </c>
       <c r="O184" t="n">
-        <v>1298378.858776704</v>
+        <v>1298378.743264128</v>
       </c>
       <c r="P184" t="n">
         <v>2900</v>
@@ -8332,10 +8332,10 @@
         <v>5472</v>
       </c>
       <c r="N185" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O185" t="n">
-        <v>8482659.570872668</v>
+        <v>8482659.787527205</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8378,10 +8378,10 @@
         <v>2016</v>
       </c>
       <c r="N186" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O186" t="n">
-        <v>4845479.923148659</v>
+        <v>4845480.121317629</v>
       </c>
       <c r="P186" t="n">
         <v>3500</v>
@@ -9923,10 +9923,10 @@
         <v>381</v>
       </c>
       <c r="N222" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O222" t="n">
-        <v>1021361.825536475</v>
+        <v>1021361.825395962</v>
       </c>
       <c r="P222" t="n">
         <v>4900</v>
@@ -10448,10 +10448,10 @@
         <v>150</v>
       </c>
       <c r="N234" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O234" t="n">
-        <v>642779.3228941649</v>
+        <v>642779.324675325</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -10999,10 +10999,10 @@
         <v>150</v>
       </c>
       <c r="N247" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O247" t="n">
-        <v>1734305.77173915</v>
+        <v>1734305.7711171</v>
       </c>
       <c r="P247" t="n">
         <v>18500</v>
@@ -11685,10 +11685,10 @@
         <v>34</v>
       </c>
       <c r="N263" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O263" t="n">
-        <v>922208.017611954</v>
+        <v>922208.0170037621</v>
       </c>
       <c r="P263" t="n">
         <v>44500</v>
@@ -11946,10 +11946,10 @@
         <v>480</v>
       </c>
       <c r="N269" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O269" t="n">
-        <v>3825576.080121408</v>
+        <v>3825576.080243184</v>
       </c>
       <c r="P269" t="n">
         <v>12900</v>
@@ -12575,10 +12575,10 @@
         <v>399</v>
       </c>
       <c r="N283" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O283" t="n">
-        <v>2082050.05027605</v>
+        <v>2082050.051108324</v>
       </c>
       <c r="P283" t="n">
         <v>8500</v>
@@ -12621,10 +12621,10 @@
         <v>206</v>
       </c>
       <c r="N284" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="O284" t="n">
-        <v>328571.93125</v>
+        <v>328571.9299667848</v>
       </c>
       <c r="P284" t="n">
         <v>2600</v>
@@ -12667,10 +12667,10 @@
         <v>541</v>
       </c>
       <c r="N285" t="n">
-        <v>3610.6500258065</v>
+        <v>3610.6500258732</v>
       </c>
       <c r="O285" t="n">
-        <v>1953361.663961316</v>
+        <v>1953361.663997401</v>
       </c>
       <c r="P285" t="n">
         <v>5800</v>
@@ -13081,10 +13081,10 @@
         <v>384</v>
       </c>
       <c r="N294" t="n">
-        <v>1664.355973236</v>
+        <v>1664.355782984</v>
       </c>
       <c r="O294" t="n">
-        <v>639112.693722624</v>
+        <v>639112.6206658559</v>
       </c>
       <c r="P294" t="n">
         <v>2900</v>
@@ -13771,10 +13771,10 @@
         <v>1145</v>
       </c>
       <c r="N309" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O309" t="n">
-        <v>2036351.15581862</v>
+        <v>2036351.172176891</v>
       </c>
       <c r="P309" t="n">
         <v>4900</v>
@@ -14553,10 +14553,10 @@
         <v>28</v>
       </c>
       <c r="N326" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O326" t="n">
-        <v>63064.3125677432</v>
+        <v>63064.31559632959</v>
       </c>
       <c r="P326" t="n">
         <v>3900</v>
@@ -14735,10 +14735,10 @@
         <v>864</v>
       </c>
       <c r="N330" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O330" t="n">
-        <v>2011494.570757488</v>
+        <v>2011494.566693146</v>
       </c>
       <c r="P330" t="n">
         <v>4500</v>
@@ -16156,10 +16156,10 @@
         <v>192</v>
       </c>
       <c r="N361" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O361" t="n">
-        <v>3278589.988508352</v>
+        <v>3278589.988444992</v>
       </c>
       <c r="P361" t="n">
         <v>27500</v>
@@ -17258,10 +17258,10 @@
         <v>4224</v>
       </c>
       <c r="N385" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O385" t="n">
-        <v>6403747.885593908</v>
+        <v>6403747.871690189</v>
       </c>
       <c r="P385" t="n">
         <v>2300</v>
@@ -17304,10 +17304,10 @@
         <v>1152</v>
       </c>
       <c r="N386" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O386" t="n">
-        <v>2832207.185796365</v>
+        <v>2832207.06608352</v>
       </c>
       <c r="P386" t="n">
         <v>3500</v>
@@ -17396,10 +17396,10 @@
         <v>576</v>
       </c>
       <c r="N388" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O388" t="n">
-        <v>1020148.098705389</v>
+        <v>1020148.076816986</v>
       </c>
       <c r="P388" t="n">
         <v>2500</v>
@@ -17442,10 +17442,10 @@
         <v>960</v>
       </c>
       <c r="N389" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O389" t="n">
-        <v>1996208.664434016</v>
+        <v>1996208.6179608</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17534,10 +17534,10 @@
         <v>144</v>
       </c>
       <c r="N391" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O391" t="n">
-        <v>476149.6994594544</v>
+        <v>476149.635398232</v>
       </c>
       <c r="P391" t="n">
         <v>4900</v>
@@ -17626,10 +17626,10 @@
         <v>216</v>
       </c>
       <c r="N393" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O393" t="n">
-        <v>455499.0351219528</v>
+        <v>455499.0791454096</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -17672,10 +17672,10 @@
         <v>684</v>
       </c>
       <c r="N394" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O394" t="n">
-        <v>1406361.01906723</v>
+        <v>1406360.902210481</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -17764,10 +17764,10 @@
         <v>1152</v>
       </c>
       <c r="N396" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O396" t="n">
-        <v>1907632.356776755</v>
+        <v>1907632.349821555</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -18565,10 +18565,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>527.91977777778</v>
+        <v>527.92037313433</v>
       </c>
       <c r="O413" t="n">
-        <v>1055.83955555556</v>
+        <v>1055.84074626866</v>
       </c>
       <c r="P413" t="n">
         <v>1300</v>
@@ -19189,10 +19189,10 @@
         <v>7572</v>
       </c>
       <c r="N427" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O427" t="n">
-        <v>3916915.577394697</v>
+        <v>3916918.232027497</v>
       </c>
       <c r="P427" t="n">
         <v>900</v>
@@ -19238,10 +19238,10 @@
         <v>252</v>
       </c>
       <c r="N428" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O428" t="n">
-        <v>783932.1073995852</v>
+        <v>783932.0713978572</v>
       </c>
       <c r="P428" t="n">
         <v>4500</v>
@@ -19370,10 +19370,10 @@
         <v>17096</v>
       </c>
       <c r="N431" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O431" t="n">
-        <v>12032082.44641647</v>
+        <v>12032082.32369557</v>
       </c>
       <c r="P431" t="n">
         <v>900</v>
@@ -19947,10 +19947,10 @@
         <v>1369</v>
       </c>
       <c r="N444" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O444" t="n">
-        <v>2184257.015490613</v>
+        <v>2184256.009604037</v>
       </c>
       <c r="P444" t="n">
         <v>2500</v>
@@ -21626,10 +21626,10 @@
         <v>1198</v>
       </c>
       <c r="N481" t="n">
-        <v>4282.1072450249</v>
+        <v>4282.1072260488</v>
       </c>
       <c r="O481" t="n">
-        <v>5129964.47953983</v>
+        <v>5129964.456806462</v>
       </c>
       <c r="P481" t="n">
         <v>5300</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>60</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8546905537</v>
+        <v>6272.8547682119</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.613159599</v>
+        <v>1354936.62993377</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -1873,10 +1873,10 @@
         <v>649</v>
       </c>
       <c r="N37" t="n">
-        <v>3926.8371059432</v>
+        <v>3926.8370969414</v>
       </c>
       <c r="O37" t="n">
-        <v>2548517.281757137</v>
+        <v>2548517.275914968</v>
       </c>
       <c r="P37" t="n">
         <v>4800</v>
@@ -1951,10 +1951,10 @@
         <v>527</v>
       </c>
       <c r="N39" t="n">
-        <v>2413.0010706638</v>
+        <v>2413.0010741139</v>
       </c>
       <c r="O39" t="n">
-        <v>1271651.564239823</v>
+        <v>1271651.566058025</v>
       </c>
       <c r="P39" t="n">
         <v>4700</v>
@@ -2419,10 +2419,10 @@
         <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>14857.623243243</v>
+        <v>14857.623257919</v>
       </c>
       <c r="O51" t="n">
-        <v>356582.957837832</v>
+        <v>356582.958190056</v>
       </c>
       <c r="P51" t="n">
         <v>34900</v>
@@ -2458,10 +2458,10 @@
         <v>152</v>
       </c>
       <c r="N52" t="n">
-        <v>3910.6281481481</v>
+        <v>3910.6281404959</v>
       </c>
       <c r="O52" t="n">
-        <v>594415.4785185112</v>
+        <v>594415.4773553768</v>
       </c>
       <c r="P52" t="n">
         <v>9100</v>
@@ -2628,10 +2628,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>30238.812571429</v>
+        <v>30238.812608696</v>
       </c>
       <c r="O56" t="n">
-        <v>1451463.003428592</v>
+        <v>1451463.005217408</v>
       </c>
       <c r="P56" t="n">
         <v>51100</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.795</v>
+        <v>174389.79826087</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.77</v>
+        <v>1046338.78956522</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874081081</v>
+        <v>61666.874092141</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.296891885</v>
+        <v>5241684.297831985</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4020,10 +4020,10 @@
         <v>200</v>
       </c>
       <c r="N88" t="n">
-        <v>4937.3101623616</v>
+        <v>4937.3101635688</v>
       </c>
       <c r="O88" t="n">
-        <v>987462.03247232</v>
+        <v>987462.0327137599</v>
       </c>
       <c r="P88" t="n">
         <v>7500</v>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>3379</v>
+        <v>3279</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>3279</v>
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>1986</v>
+        <v>1898</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>1898</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8961258041</v>
+        <v>5216.8961202577</v>
       </c>
       <c r="O111" t="n">
-        <v>9901668.846776182</v>
+        <v>9901668.836249115</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.2540224159</v>
+        <v>3594.2540186916</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.0619177977</v>
+        <v>948883.0609345824</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -7095,10 +7095,10 @@
         <v>809</v>
       </c>
       <c r="N157" t="n">
-        <v>4372.2107901305</v>
+        <v>4372.2107902432</v>
       </c>
       <c r="O157" t="n">
-        <v>3537118.529215574</v>
+        <v>3537118.529306749</v>
       </c>
       <c r="P157" t="n">
         <v>7500</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>2655</v>
+        <v>2487</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>2487</v>
@@ -8240,10 +8240,10 @@
         <v>1152</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9236077879</v>
+        <v>1630.9235901027</v>
       </c>
       <c r="O183" t="n">
-        <v>1878823.996171661</v>
+        <v>1878823.97579831</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8286,10 +8286,10 @@
         <v>768</v>
       </c>
       <c r="N184" t="n">
-        <v>1690.5973219585</v>
+        <v>1690.5972035794</v>
       </c>
       <c r="O184" t="n">
-        <v>1298378.743264128</v>
+        <v>1298378.652348979</v>
       </c>
       <c r="P184" t="n">
         <v>2900</v>
@@ -8332,10 +8332,10 @@
         <v>5472</v>
       </c>
       <c r="N185" t="n">
-        <v>1550.1936746212</v>
+        <v>1550.1936753491</v>
       </c>
       <c r="O185" t="n">
-        <v>8482659.787527205</v>
+        <v>8482659.791510275</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8378,10 +8378,10 @@
         <v>2016</v>
       </c>
       <c r="N186" t="n">
-        <v>2403.5119649393</v>
+        <v>2403.5119996136</v>
       </c>
       <c r="O186" t="n">
-        <v>4845480.121317629</v>
+        <v>4845480.191221017</v>
       </c>
       <c r="P186" t="n">
         <v>3500</v>
@@ -9923,10 +9923,10 @@
         <v>381</v>
       </c>
       <c r="N222" t="n">
-        <v>2680.739699202</v>
+        <v>2680.7396988322</v>
       </c>
       <c r="O222" t="n">
-        <v>1021361.825395962</v>
+        <v>1021361.825255068</v>
       </c>
       <c r="P222" t="n">
         <v>4900</v>
@@ -10448,10 +10448,10 @@
         <v>150</v>
       </c>
       <c r="N234" t="n">
-        <v>4285.1954978355</v>
+        <v>4285.1955097614</v>
       </c>
       <c r="O234" t="n">
-        <v>642779.324675325</v>
+        <v>642779.3264642101</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -12575,10 +12575,10 @@
         <v>399</v>
       </c>
       <c r="N283" t="n">
-        <v>5218.1705541562</v>
+        <v>5218.170554855</v>
       </c>
       <c r="O283" t="n">
-        <v>2082050.051108324</v>
+        <v>2082050.051387145</v>
       </c>
       <c r="P283" t="n">
         <v>8500</v>
@@ -12621,10 +12621,10 @@
         <v>206</v>
       </c>
       <c r="N284" t="n">
-        <v>1595.0093687708</v>
+        <v>1595.0093634841</v>
       </c>
       <c r="O284" t="n">
-        <v>328571.9299667848</v>
+        <v>328571.9288777246</v>
       </c>
       <c r="P284" t="n">
         <v>2600</v>
@@ -13081,10 +13081,10 @@
         <v>384</v>
       </c>
       <c r="N294" t="n">
-        <v>1664.355782984</v>
+        <v>1664.355659204</v>
       </c>
       <c r="O294" t="n">
-        <v>639112.6206658559</v>
+        <v>639112.5731343359</v>
       </c>
       <c r="P294" t="n">
         <v>2900</v>
@@ -13771,10 +13771,10 @@
         <v>1145</v>
       </c>
       <c r="N309" t="n">
-        <v>1778.4726394558</v>
+        <v>1778.4726299141</v>
       </c>
       <c r="O309" t="n">
-        <v>2036351.172176891</v>
+        <v>2036351.161251645</v>
       </c>
       <c r="P309" t="n">
         <v>4900</v>
@@ -17258,10 +17258,10 @@
         <v>4224</v>
       </c>
       <c r="N385" t="n">
-        <v>1516.0387953812</v>
+        <v>1516.0387982037</v>
       </c>
       <c r="O385" t="n">
-        <v>6403747.871690189</v>
+        <v>6403747.883612429</v>
       </c>
       <c r="P385" t="n">
         <v>2300</v>
@@ -17304,10 +17304,10 @@
         <v>1152</v>
       </c>
       <c r="N386" t="n">
-        <v>2458.5130781975</v>
+        <v>2458.5131328074</v>
       </c>
       <c r="O386" t="n">
-        <v>2832207.06608352</v>
+        <v>2832207.128994124</v>
       </c>
       <c r="P386" t="n">
         <v>3500</v>
@@ -17442,10 +17442,10 @@
         <v>960</v>
       </c>
       <c r="N389" t="n">
-        <v>2079.3839770425</v>
+        <v>2079.3840254521</v>
       </c>
       <c r="O389" t="n">
-        <v>1996208.6179608</v>
+        <v>1996208.664434016</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17534,10 +17534,10 @@
         <v>144</v>
       </c>
       <c r="N391" t="n">
-        <v>3306.5946902655</v>
+        <v>3306.5951153324</v>
       </c>
       <c r="O391" t="n">
-        <v>476149.635398232</v>
+        <v>476149.6966078656</v>
       </c>
       <c r="P391" t="n">
         <v>4900</v>
@@ -17672,10 +17672,10 @@
         <v>684</v>
       </c>
       <c r="N394" t="n">
-        <v>2056.0831903662</v>
+        <v>2056.0831723454</v>
       </c>
       <c r="O394" t="n">
-        <v>1406360.902210481</v>
+        <v>1406360.889884253</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -19189,10 +19189,10 @@
         <v>7572</v>
       </c>
       <c r="N427" t="n">
-        <v>517.28978235968</v>
+        <v>517.2898138359</v>
       </c>
       <c r="O427" t="n">
-        <v>3916918.232027497</v>
+        <v>3916918.470365434</v>
       </c>
       <c r="P427" t="n">
         <v>900</v>
@@ -19238,10 +19238,10 @@
         <v>252</v>
       </c>
       <c r="N428" t="n">
-        <v>3110.8415531661</v>
+        <v>3110.8415227818</v>
       </c>
       <c r="O428" t="n">
-        <v>783932.0713978572</v>
+        <v>783932.0637410136</v>
       </c>
       <c r="P428" t="n">
         <v>4500</v>
@@ -19370,10 +19370,10 @@
         <v>17096</v>
       </c>
       <c r="N431" t="n">
-        <v>703.79517569581</v>
+        <v>703.795175</v>
       </c>
       <c r="O431" t="n">
-        <v>12032082.32369557</v>
+        <v>12032082.3118</v>
       </c>
       <c r="P431" t="n">
         <v>900</v>
@@ -19419,10 +19419,10 @@
         <v>127</v>
       </c>
       <c r="N432" t="n">
-        <v>3182.2511214953</v>
+        <v>3182.2511235955</v>
       </c>
       <c r="O432" t="n">
-        <v>404145.8924299031</v>
+        <v>404145.8926966285</v>
       </c>
       <c r="P432" t="n">
         <v>6900</v>
@@ -19947,10 +19947,10 @@
         <v>1369</v>
       </c>
       <c r="N444" t="n">
-        <v>1595.5120596085</v>
+        <v>1595.5123423818</v>
       </c>
       <c r="O444" t="n">
-        <v>2184256.009604037</v>
+        <v>2184256.396720684</v>
       </c>
       <c r="P444" t="n">
         <v>2500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.29942576</v>
+        <v>326035.32220368</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1377243008</v>
+        <v>823926.1374883772</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8547682119</v>
+        <v>6272.8547761194</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.62993377</v>
+        <v>1354936.631641791</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -3019,10 +3019,10 @@
         <v>111</v>
       </c>
       <c r="N65" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O65" t="n">
-        <v>15697274.18618886</v>
+        <v>15697274.18784276</v>
       </c>
       <c r="P65" t="n">
         <v>251900</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.297831985</v>
+        <v>5241684.299727486</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4020,10 +4020,10 @@
         <v>200</v>
       </c>
       <c r="N88" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O88" t="n">
-        <v>987462.0327137599</v>
+        <v>987462.0327381</v>
       </c>
       <c r="P88" t="n">
         <v>7500</v>
@@ -4916,10 +4916,10 @@
         <v>1080</v>
       </c>
       <c r="N109" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O109" t="n">
-        <v>2788836.194219688</v>
+        <v>2788836.171428556</v>
       </c>
       <c r="P109" t="n">
         <v>4500</v>
@@ -5008,10 +5008,10 @@
         <v>1898</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O111" t="n">
-        <v>9901668.836249115</v>
+        <v>9901668.821460279</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
@@ -5100,10 +5100,10 @@
         <v>6298</v>
       </c>
       <c r="N113" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O113" t="n">
-        <v>19894505.48258823</v>
+        <v>19894505.48360788</v>
       </c>
       <c r="P113" t="n">
         <v>5600</v>
@@ -5192,10 +5192,10 @@
         <v>144</v>
       </c>
       <c r="N115" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O115" t="n">
-        <v>553193.9701775135</v>
+        <v>553193.9742857184</v>
       </c>
       <c r="P115" t="n">
         <v>6900</v>
@@ -5788,10 +5788,10 @@
         <v>64</v>
       </c>
       <c r="N128" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O128" t="n">
-        <v>313019.523121952</v>
+        <v>313019.52312576</v>
       </c>
       <c r="P128" t="n">
         <v>8200</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.0609345824</v>
+        <v>948883.056</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -6728,22 +6728,22 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="M149" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
         <v>2090.85</v>
       </c>
       <c r="O149" t="n">
-        <v>1204329.6</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
         <v>2900</v>
       </c>
       <c r="Q149" t="n">
-        <v>1670400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -7049,10 +7049,10 @@
         <v>78</v>
       </c>
       <c r="N156" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O156" t="n">
-        <v>237249.48103311</v>
+        <v>237249.4810358556</v>
       </c>
       <c r="P156" t="n">
         <v>5500</v>
@@ -8240,10 +8240,10 @@
         <v>1152</v>
       </c>
       <c r="N183" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O183" t="n">
-        <v>1878823.97579831</v>
+        <v>1878824.029586227</v>
       </c>
       <c r="P183" t="n">
         <v>2500</v>
@@ -8286,10 +8286,10 @@
         <v>768</v>
       </c>
       <c r="N184" t="n">
-        <v>1690.5972035794</v>
+        <v>1690.5971524664</v>
       </c>
       <c r="O184" t="n">
-        <v>1298378.652348979</v>
+        <v>1298378.613094195</v>
       </c>
       <c r="P184" t="n">
         <v>2900</v>
@@ -8332,10 +8332,10 @@
         <v>5472</v>
       </c>
       <c r="N185" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O185" t="n">
-        <v>8482659.791510275</v>
+        <v>8482659.911734492</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8378,10 +8378,10 @@
         <v>2016</v>
       </c>
       <c r="N186" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O186" t="n">
-        <v>4845480.191221017</v>
+        <v>4845480.341710781</v>
       </c>
       <c r="P186" t="n">
         <v>3500</v>
@@ -8904,22 +8904,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M198" t="n">
-        <v>1007</v>
+        <v>719</v>
       </c>
       <c r="N198" t="n">
         <v>3253</v>
       </c>
       <c r="O198" t="n">
-        <v>3275771</v>
+        <v>2338907</v>
       </c>
       <c r="P198" t="n">
         <v>3900</v>
       </c>
       <c r="Q198" t="n">
-        <v>3927300</v>
+        <v>2804100</v>
       </c>
     </row>
     <row r="199">
@@ -9078,22 +9078,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="M202" t="n">
-        <v>700</v>
+        <v>489</v>
       </c>
       <c r="N202" t="n">
         <v>3253</v>
       </c>
       <c r="O202" t="n">
-        <v>2277100</v>
+        <v>1590717</v>
       </c>
       <c r="P202" t="n">
         <v>3900</v>
       </c>
       <c r="Q202" t="n">
-        <v>2730000</v>
+        <v>1907100</v>
       </c>
     </row>
     <row r="203">
@@ -9213,10 +9213,10 @@
         <v>1415</v>
       </c>
       <c r="N205" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O205" t="n">
-        <v>5938574.628702112</v>
+        <v>5938574.629694875</v>
       </c>
       <c r="P205" t="n">
         <v>5900</v>
@@ -10448,10 +10448,10 @@
         <v>150</v>
       </c>
       <c r="N234" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O234" t="n">
-        <v>642779.3264642101</v>
+        <v>642779.3300653649</v>
       </c>
       <c r="P234" t="n">
         <v>6900</v>
@@ -13081,10 +13081,10 @@
         <v>384</v>
       </c>
       <c r="N294" t="n">
-        <v>1664.355659204</v>
+        <v>1664.3554968553</v>
       </c>
       <c r="O294" t="n">
-        <v>639112.5731343359</v>
+        <v>639112.5107924353</v>
       </c>
       <c r="P294" t="n">
         <v>2900</v>
@@ -13771,10 +13771,10 @@
         <v>1145</v>
       </c>
       <c r="N309" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O309" t="n">
-        <v>2036351.161251645</v>
+        <v>2036351.179504433</v>
       </c>
       <c r="P309" t="n">
         <v>4900</v>
@@ -14735,10 +14735,10 @@
         <v>864</v>
       </c>
       <c r="N330" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O330" t="n">
-        <v>2011494.566693146</v>
+        <v>2011494.565331741</v>
       </c>
       <c r="P330" t="n">
         <v>4500</v>
@@ -16156,10 +16156,10 @@
         <v>192</v>
       </c>
       <c r="N361" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O361" t="n">
-        <v>3278589.988444992</v>
+        <v>3278589.988381824</v>
       </c>
       <c r="P361" t="n">
         <v>27500</v>
@@ -17258,10 +17258,10 @@
         <v>4224</v>
       </c>
       <c r="N385" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O385" t="n">
-        <v>6403747.883612429</v>
+        <v>6403747.870693747</v>
       </c>
       <c r="P385" t="n">
         <v>2300</v>
@@ -17304,10 +17304,10 @@
         <v>1152</v>
       </c>
       <c r="N386" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O386" t="n">
-        <v>2832207.128994124</v>
+        <v>2832207.063440486</v>
       </c>
       <c r="P386" t="n">
         <v>3500</v>
@@ -17442,10 +17442,10 @@
         <v>960</v>
       </c>
       <c r="N389" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O389" t="n">
-        <v>1996208.664434016</v>
+        <v>1996208.612098656</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17488,10 +17488,10 @@
         <v>1152</v>
       </c>
       <c r="N390" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O390" t="n">
-        <v>2077073.977142822</v>
+        <v>2077073.998566682</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
@@ -17534,10 +17534,10 @@
         <v>144</v>
       </c>
       <c r="N391" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O391" t="n">
-        <v>476149.6966078656</v>
+        <v>476149.6331360928</v>
       </c>
       <c r="P391" t="n">
         <v>4900</v>
@@ -17580,10 +17580,10 @@
         <v>1440</v>
       </c>
       <c r="N392" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O392" t="n">
-        <v>3055915.948208688</v>
+        <v>3055915.945426032</v>
       </c>
       <c r="P392" t="n">
         <v>2900</v>
@@ -17626,10 +17626,10 @@
         <v>216</v>
       </c>
       <c r="N393" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O393" t="n">
-        <v>455499.0791454096</v>
+        <v>455499.08993772</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -17672,10 +17672,10 @@
         <v>684</v>
       </c>
       <c r="N394" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O394" t="n">
-        <v>1406360.889884253</v>
+        <v>1406360.764565194</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
@@ -17718,10 +17718,10 @@
         <v>714</v>
       </c>
       <c r="N395" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O395" t="n">
-        <v>2302342.123480816</v>
+        <v>2302342.129665341</v>
       </c>
       <c r="P395" t="n">
         <v>4500</v>
@@ -17764,10 +17764,10 @@
         <v>1152</v>
       </c>
       <c r="N396" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O396" t="n">
-        <v>1907632.349821555</v>
+        <v>1907632.286808538</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -19189,10 +19189,10 @@
         <v>7572</v>
       </c>
       <c r="N427" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O427" t="n">
-        <v>3916918.470365434</v>
+        <v>3916919.129427847</v>
       </c>
       <c r="P427" t="n">
         <v>900</v>
@@ -19238,10 +19238,10 @@
         <v>252</v>
       </c>
       <c r="N428" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O428" t="n">
-        <v>783932.0637410136</v>
+        <v>783932.0336089452</v>
       </c>
       <c r="P428" t="n">
         <v>4500</v>
@@ -19370,10 +19370,10 @@
         <v>17096</v>
       </c>
       <c r="N431" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O431" t="n">
-        <v>12032082.3118</v>
+        <v>12032082.21253618</v>
       </c>
       <c r="P431" t="n">
         <v>900</v>
@@ -19947,10 +19947,10 @@
         <v>1369</v>
       </c>
       <c r="N444" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O444" t="n">
-        <v>2184256.396720684</v>
+        <v>2184255.877795211</v>
       </c>
       <c r="P444" t="n">
         <v>2500</v>
@@ -20824,10 +20824,10 @@
         <v>1976</v>
       </c>
       <c r="N463" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O463" t="n">
-        <v>13924753.1004082</v>
+        <v>13924753.09996992</v>
       </c>
       <c r="P463" t="n">
         <v>9900</v>
@@ -22221,22 +22221,22 @@
         <v>0</v>
       </c>
       <c r="L495" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M495" t="n">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="N495" t="n">
         <v>3181.9</v>
       </c>
       <c r="O495" t="n">
-        <v>884568.2000000001</v>
+        <v>248188.2</v>
       </c>
       <c r="P495" t="n">
         <v>5100</v>
       </c>
       <c r="Q495" t="n">
-        <v>1417800</v>
+        <v>397800</v>
       </c>
     </row>
     <row r="496">
@@ -22954,10 +22954,10 @@
         <v>1</v>
       </c>
       <c r="N512" t="n">
-        <v>4985.4053097345</v>
+        <v>4985.4053571429</v>
       </c>
       <c r="O512" t="n">
-        <v>4985.4053097345</v>
+        <v>4985.4053571429</v>
       </c>
       <c r="P512" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.32220368</v>
+        <v>326035.333333332</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1873,10 +1873,10 @@
         <v>649</v>
       </c>
       <c r="N37" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O37" t="n">
-        <v>2548517.275914968</v>
+        <v>2548517.274937769</v>
       </c>
       <c r="P37" t="n">
         <v>4800</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.3642918561</v>
+        <v>754174.3634482559</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -5100,10 +5100,10 @@
         <v>6298</v>
       </c>
       <c r="N113" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O113" t="n">
-        <v>19894505.48360788</v>
+        <v>19903278.60082804</v>
       </c>
       <c r="P113" t="n">
         <v>5600</v>
@@ -5192,10 +5192,10 @@
         <v>144</v>
       </c>
       <c r="N115" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O115" t="n">
-        <v>553193.9742857184</v>
+        <v>555397.9343426304</v>
       </c>
       <c r="P115" t="n">
         <v>6900</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.056</v>
+        <v>948883.0550093928</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -7051,10 +7051,10 @@
         <v>809</v>
       </c>
       <c r="N156" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O156" t="n">
-        <v>3537118.529397923</v>
+        <v>3537118.529443551</v>
       </c>
       <c r="P156" t="n">
         <v>7500</v>
@@ -7883,10 +7883,10 @@
         <v>238</v>
       </c>
       <c r="N175" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O175" t="n">
-        <v>895260.7999999999</v>
+        <v>898540.1435897544</v>
       </c>
       <c r="P175" t="n">
         <v>6900</v>
@@ -8196,10 +8196,10 @@
         <v>1152</v>
       </c>
       <c r="N182" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O182" t="n">
-        <v>1878824.04150816</v>
+        <v>1878824.052496397</v>
       </c>
       <c r="P182" t="n">
         <v>2500</v>
@@ -8242,10 +8242,10 @@
         <v>768</v>
       </c>
       <c r="N183" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O183" t="n">
-        <v>1298378.494266394</v>
+        <v>1298378.467641293</v>
       </c>
       <c r="P183" t="n">
         <v>2900</v>
@@ -8288,10 +8288,10 @@
         <v>5472</v>
       </c>
       <c r="N184" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O184" t="n">
-        <v>8482659.923836367</v>
+        <v>8482659.954153437</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8334,10 +8334,10 @@
         <v>2016</v>
       </c>
       <c r="N185" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O185" t="n">
-        <v>4845480.393874982</v>
+        <v>4845480.427186963</v>
       </c>
       <c r="P185" t="n">
         <v>3500</v>
@@ -9879,10 +9879,10 @@
         <v>381</v>
       </c>
       <c r="N221" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O221" t="n">
-        <v>1021361.823827004</v>
+        <v>1021361.823754652</v>
       </c>
       <c r="P221" t="n">
         <v>4900</v>
@@ -12209,10 +12209,10 @@
         <v>433</v>
       </c>
       <c r="N275" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O275" t="n">
-        <v>1348314.381895593</v>
+        <v>1348314.381961322</v>
       </c>
       <c r="P275" t="n">
         <v>5000</v>
@@ -12623,10 +12623,10 @@
         <v>541</v>
       </c>
       <c r="N284" t="n">
-        <v>3610.6500258732</v>
+        <v>3610.6500261438</v>
       </c>
       <c r="O284" t="n">
-        <v>1953361.663997401</v>
+        <v>1953361.664143796</v>
       </c>
       <c r="P284" t="n">
         <v>5800</v>
@@ -17444,10 +17444,10 @@
         <v>1152</v>
       </c>
       <c r="N389" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O389" t="n">
-        <v>2077073.998566682</v>
+        <v>2077074.013648205</v>
       </c>
       <c r="P389" t="n">
         <v>2500</v>
@@ -17490,10 +17490,10 @@
         <v>144</v>
       </c>
       <c r="N390" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O390" t="n">
-        <v>476149.6331360928</v>
+        <v>476149.6320000048</v>
       </c>
       <c r="P390" t="n">
         <v>4900</v>
@@ -17628,10 +17628,10 @@
         <v>684</v>
       </c>
       <c r="N393" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O393" t="n">
-        <v>1406360.76130525</v>
+        <v>1406360.759673568</v>
       </c>
       <c r="P393" t="n">
         <v>2900</v>
@@ -17720,10 +17720,10 @@
         <v>1152</v>
       </c>
       <c r="N395" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O395" t="n">
-        <v>1907632.286808538</v>
+        <v>1907632.265636275</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
@@ -19145,10 +19145,10 @@
         <v>7572</v>
       </c>
       <c r="N426" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O426" t="n">
-        <v>3916919.443636999</v>
+        <v>3916919.658984223</v>
       </c>
       <c r="P426" t="n">
         <v>900</v>
@@ -19194,10 +19194,10 @@
         <v>252</v>
       </c>
       <c r="N427" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O427" t="n">
-        <v>783932.0283276552</v>
+        <v>783932.0256773208</v>
       </c>
       <c r="P427" t="n">
         <v>4500</v>
@@ -19326,10 +19326,10 @@
         <v>17096</v>
       </c>
       <c r="N430" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O430" t="n">
-        <v>12032082.15783924</v>
+        <v>12032082.12399035</v>
       </c>
       <c r="P430" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -597,22 +597,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.407702703</v>
+        <v>96741.42375</v>
       </c>
       <c r="O5" t="n">
-        <v>5224036.015945962</v>
+        <v>386965.695</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
       </c>
       <c r="Q5" t="n">
-        <v>10200600</v>
+        <v>755600</v>
       </c>
     </row>
     <row r="6">
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3076124567</v>
+        <v>1811.3076256499</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.370242206</v>
+        <v>326035.372616982</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.40875</v>
+        <v>16486.408661417</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.2549999999</v>
+        <v>857293.250393684</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -4916,10 +4916,10 @@
         <v>1080</v>
       </c>
       <c r="N109" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O109" t="n">
-        <v>2788836.087272688</v>
+        <v>2788836.056096976</v>
       </c>
       <c r="P109" t="n">
         <v>4500</v>
@@ -5008,10 +5008,10 @@
         <v>1898</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O111" t="n">
-        <v>9901668.793837355</v>
+        <v>9901668.78636493</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
@@ -5788,10 +5788,10 @@
         <v>64</v>
       </c>
       <c r="N128" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O128" t="n">
-        <v>313019.5231315008</v>
+        <v>313019.5231334144</v>
       </c>
       <c r="P128" t="n">
         <v>8200</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.0490395607</v>
+        <v>948883.0480401888</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -6690,10 +6690,10 @@
         <v>15671</v>
       </c>
       <c r="N148" t="n">
-        <v>616.01871898278</v>
+        <v>616.01871837471</v>
       </c>
       <c r="O148" t="n">
-        <v>9653629.345179146</v>
+        <v>9653629.335650081</v>
       </c>
       <c r="P148" t="n">
         <v>800</v>
@@ -7005,10 +7005,10 @@
         <v>78</v>
       </c>
       <c r="N155" t="n">
-        <v>3041.6600134228</v>
+        <v>3041.660013459</v>
       </c>
       <c r="O155" t="n">
-        <v>237249.4810469784</v>
+        <v>237249.481049802</v>
       </c>
       <c r="P155" t="n">
         <v>5500</v>
@@ -7051,10 +7051,10 @@
         <v>809</v>
       </c>
       <c r="N156" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O156" t="n">
-        <v>3537118.529717397</v>
+        <v>3537118.529991406</v>
       </c>
       <c r="P156" t="n">
         <v>7500</v>
@@ -8196,10 +8196,10 @@
         <v>1152</v>
       </c>
       <c r="N182" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O182" t="n">
-        <v>1878824.141471232</v>
+        <v>1878824.159297856</v>
       </c>
       <c r="P182" t="n">
         <v>2500</v>
@@ -8242,10 +8242,10 @@
         <v>384</v>
       </c>
       <c r="N183" t="n">
-        <v>1690.5964846154</v>
+        <v>1690.5964302236</v>
       </c>
       <c r="O183" t="n">
-        <v>649189.0500923136</v>
+        <v>649189.0292058624</v>
       </c>
       <c r="P183" t="n">
         <v>2900</v>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>5472</v>
+        <v>4608</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8285,19 +8285,19 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>5472</v>
+        <v>4608</v>
       </c>
       <c r="N184" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O184" t="n">
-        <v>8482660.422177974</v>
+        <v>7143292.992451277</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
       </c>
       <c r="Q184" t="n">
-        <v>13680000</v>
+        <v>11520000</v>
       </c>
     </row>
     <row r="185">
@@ -8334,10 +8334,10 @@
         <v>1632</v>
       </c>
       <c r="N185" t="n">
-        <v>2403.5124244849</v>
+        <v>2403.5125045299</v>
       </c>
       <c r="O185" t="n">
-        <v>3922532.276759357</v>
+        <v>3922532.407392797</v>
       </c>
       <c r="P185" t="n">
         <v>3500</v>
@@ -10404,10 +10404,10 @@
         <v>150</v>
       </c>
       <c r="N233" t="n">
-        <v>4285.1956570156</v>
+        <v>4285.195701459</v>
       </c>
       <c r="O233" t="n">
-        <v>642779.3485523399</v>
+        <v>642779.35521885</v>
       </c>
       <c r="P233" t="n">
         <v>6900</v>
@@ -12163,10 +12163,10 @@
         <v>433</v>
       </c>
       <c r="N274" t="n">
-        <v>3113.8900276243</v>
+        <v>3113.8900280899</v>
       </c>
       <c r="O274" t="n">
-        <v>1348314.381961322</v>
+        <v>1348314.382162927</v>
       </c>
       <c r="P274" t="n">
         <v>5000</v>
@@ -12301,10 +12301,10 @@
         <v>69</v>
       </c>
       <c r="N277" t="n">
-        <v>4163.1602061856</v>
+        <v>4163.160212766</v>
       </c>
       <c r="O277" t="n">
-        <v>287258.0542268064</v>
+        <v>287258.054680854</v>
       </c>
       <c r="P277" t="n">
         <v>6700</v>
@@ -14417,10 +14417,10 @@
         <v>28</v>
       </c>
       <c r="N323" t="n">
-        <v>2252.2972418478</v>
+        <v>2252.2973618785</v>
       </c>
       <c r="O323" t="n">
-        <v>63064.32277173839</v>
+        <v>63064.326132598</v>
       </c>
       <c r="P323" t="n">
         <v>3900</v>
@@ -14599,10 +14599,10 @@
         <v>864</v>
       </c>
       <c r="N327" t="n">
-        <v>2328.1187082951</v>
+        <v>2328.1186987357</v>
       </c>
       <c r="O327" t="n">
-        <v>2011494.563966966</v>
+        <v>2011494.555707645</v>
       </c>
       <c r="P327" t="n">
         <v>4500</v>
@@ -17168,10 +17168,10 @@
         <v>1152</v>
       </c>
       <c r="N383" t="n">
-        <v>2458.5130528766</v>
+        <v>2458.5130063609</v>
       </c>
       <c r="O383" t="n">
-        <v>2832207.036913843</v>
+        <v>2832206.983327757</v>
       </c>
       <c r="P383" t="n">
         <v>3500</v>
@@ -17260,10 +17260,10 @@
         <v>576</v>
       </c>
       <c r="N385" t="n">
-        <v>1771.0904111406</v>
+        <v>1771.0903664224</v>
       </c>
       <c r="O385" t="n">
-        <v>1020148.076816986</v>
+        <v>1020148.051059302</v>
       </c>
       <c r="P385" t="n">
         <v>2500</v>
@@ -17352,10 +17352,10 @@
         <v>1152</v>
       </c>
       <c r="N387" t="n">
-        <v>1803.0156556557</v>
+        <v>1803.0157013118</v>
       </c>
       <c r="O387" t="n">
-        <v>2077074.035315366</v>
+        <v>2077074.087911194</v>
       </c>
       <c r="P387" t="n">
         <v>2500</v>
@@ -17444,10 +17444,10 @@
         <v>396</v>
       </c>
       <c r="N389" t="n">
-        <v>2056.0829556314</v>
+        <v>2056.0829120879</v>
       </c>
       <c r="O389" t="n">
-        <v>814208.8504300345</v>
+        <v>814208.8331868083</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -18961,10 +18961,10 @@
         <v>7572</v>
       </c>
       <c r="N422" t="n">
-        <v>517.29010591089</v>
+        <v>517.2904197169401</v>
       </c>
       <c r="O422" t="n">
-        <v>3916920.681957259</v>
+        <v>3916923.05809667</v>
       </c>
       <c r="P422" t="n">
         <v>900</v>
@@ -19010,10 +19010,10 @@
         <v>252</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O423" t="n">
-        <v>783931.9762855729</v>
+        <v>783931.843956618</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -19142,10 +19142,10 @@
         <v>17096</v>
       </c>
       <c r="N426" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O426" t="n">
-        <v>12032081.73574139</v>
+        <v>12032081.41480793</v>
       </c>
       <c r="P426" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3076256499</v>
+        <v>1811.3076655052</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.372616982</v>
+        <v>326035.379790936</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464631809</v>
+        <v>3376.746460274</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1370161396</v>
+        <v>823926.1363068561</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8548484848</v>
+        <v>6272.8549315068</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.647272717</v>
+        <v>1354936.665205469</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2029,10 +2029,10 @@
         <v>144</v>
       </c>
       <c r="N41" t="n">
-        <v>3716.3301954397</v>
+        <v>3716.3301957586</v>
       </c>
       <c r="O41" t="n">
-        <v>535151.5481433169</v>
+        <v>535151.5481892384</v>
       </c>
       <c r="P41" t="n">
         <v>9500</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4483,19 +4483,19 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="N99" t="n">
         <v>2331</v>
       </c>
       <c r="O99" t="n">
-        <v>505827</v>
+        <v>477855</v>
       </c>
       <c r="P99" t="n">
         <v>3500</v>
       </c>
       <c r="Q99" t="n">
-        <v>759500</v>
+        <v>717500</v>
       </c>
     </row>
     <row r="100">
@@ -4916,10 +4916,10 @@
         <v>1080</v>
       </c>
       <c r="N109" t="n">
-        <v>2582.2556074972</v>
+        <v>2582.2555674232</v>
       </c>
       <c r="O109" t="n">
-        <v>2788836.056096976</v>
+        <v>2788836.012817056</v>
       </c>
       <c r="P109" t="n">
         <v>4500</v>
@@ -5008,10 +5008,10 @@
         <v>1898</v>
       </c>
       <c r="N111" t="n">
-        <v>5216.8960939752</v>
+        <v>5216.8960872076</v>
       </c>
       <c r="O111" t="n">
-        <v>9901668.78636493</v>
+        <v>9901668.773520026</v>
       </c>
       <c r="P111" t="n">
         <v>8500</v>
@@ -6421,10 +6421,10 @@
         <v>264</v>
       </c>
       <c r="N142" t="n">
-        <v>3594.2539698492</v>
+        <v>3594.2539622642</v>
       </c>
       <c r="O142" t="n">
-        <v>948883.0480401888</v>
+        <v>948883.0460377487</v>
       </c>
       <c r="P142" t="n">
         <v>6500</v>
@@ -6646,10 +6646,10 @@
         <v>361</v>
       </c>
       <c r="N147" t="n">
-        <v>14822.37884823</v>
+        <v>14822.378847539</v>
       </c>
       <c r="O147" t="n">
-        <v>5350878.764211031</v>
+        <v>5350878.763961579</v>
       </c>
       <c r="P147" t="n">
         <v>24900</v>
@@ -7005,10 +7005,10 @@
         <v>78</v>
       </c>
       <c r="N155" t="n">
-        <v>3041.660013459</v>
+        <v>3041.6600135135</v>
       </c>
       <c r="O155" t="n">
-        <v>237249.481049802</v>
+        <v>237249.481054053</v>
       </c>
       <c r="P155" t="n">
         <v>5500</v>
@@ -8196,10 +8196,10 @@
         <v>1152</v>
       </c>
       <c r="N182" t="n">
-        <v>1630.9237493905</v>
+        <v>1630.9237512195</v>
       </c>
       <c r="O182" t="n">
-        <v>1878824.159297856</v>
+        <v>1878824.161404864</v>
       </c>
       <c r="P182" t="n">
         <v>2500</v>
@@ -8242,10 +8242,10 @@
         <v>384</v>
       </c>
       <c r="N183" t="n">
-        <v>1690.5964302236</v>
+        <v>1690.5961358314</v>
       </c>
       <c r="O183" t="n">
-        <v>649189.0292058624</v>
+        <v>649188.9161592576</v>
       </c>
       <c r="P183" t="n">
         <v>2900</v>
@@ -8288,10 +8288,10 @@
         <v>4608</v>
       </c>
       <c r="N184" t="n">
-        <v>1550.1937917646</v>
+        <v>1550.193804203</v>
       </c>
       <c r="O184" t="n">
-        <v>7143292.992451277</v>
+        <v>7143293.049767423</v>
       </c>
       <c r="P184" t="n">
         <v>2500</v>
@@ -8334,10 +8334,10 @@
         <v>1632</v>
       </c>
       <c r="N185" t="n">
-        <v>2403.5125045299</v>
+        <v>2403.5125525465</v>
       </c>
       <c r="O185" t="n">
-        <v>3922532.407392797</v>
+        <v>3922532.485755888</v>
       </c>
       <c r="P185" t="n">
         <v>3500</v>
@@ -10404,10 +10404,10 @@
         <v>150</v>
       </c>
       <c r="N233" t="n">
-        <v>4285.195701459</v>
+        <v>4285.1957207207</v>
       </c>
       <c r="O233" t="n">
-        <v>642779.35521885</v>
+        <v>642779.3581081049</v>
       </c>
       <c r="P233" t="n">
         <v>6900</v>
@@ -12531,10 +12531,10 @@
         <v>206</v>
       </c>
       <c r="N282" t="n">
-        <v>1595.0093425606</v>
+        <v>1595.0093402778</v>
       </c>
       <c r="O282" t="n">
-        <v>328571.9245674836</v>
+        <v>328571.9240972268</v>
       </c>
       <c r="P282" t="n">
         <v>2600</v>
@@ -14599,10 +14599,10 @@
         <v>864</v>
       </c>
       <c r="N327" t="n">
-        <v>2328.1186987357</v>
+        <v>2328.1186979327</v>
       </c>
       <c r="O327" t="n">
-        <v>2011494.555707645</v>
+        <v>2011494.555013853</v>
       </c>
       <c r="P327" t="n">
         <v>4500</v>
@@ -17122,10 +17122,10 @@
         <v>4224</v>
       </c>
       <c r="N382" t="n">
-        <v>1516.0387934921</v>
+        <v>1516.0387920714</v>
       </c>
       <c r="O382" t="n">
-        <v>6403747.863710631</v>
+        <v>6403747.857709593</v>
       </c>
       <c r="P382" t="n">
         <v>2300</v>
@@ -17168,10 +17168,10 @@
         <v>1152</v>
       </c>
       <c r="N383" t="n">
-        <v>2458.5130063609</v>
+        <v>2458.5129946345</v>
       </c>
       <c r="O383" t="n">
-        <v>2832206.983327757</v>
+        <v>2832206.969818944</v>
       </c>
       <c r="P383" t="n">
         <v>3500</v>
@@ -17490,10 +17490,10 @@
         <v>714</v>
       </c>
       <c r="N390" t="n">
-        <v>3224.5688526212</v>
+        <v>3224.5688613861</v>
       </c>
       <c r="O390" t="n">
-        <v>2302342.160771537</v>
+        <v>2302342.167029675</v>
       </c>
       <c r="P390" t="n">
         <v>4500</v>
@@ -17536,10 +17536,10 @@
         <v>864</v>
       </c>
       <c r="N391" t="n">
-        <v>1655.9307707708</v>
+        <v>1655.9307676903</v>
       </c>
       <c r="O391" t="n">
-        <v>1430724.185945971</v>
+        <v>1430724.183284419</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -18961,10 +18961,10 @@
         <v>7572</v>
       </c>
       <c r="N422" t="n">
-        <v>517.2904197169401</v>
+        <v>517.29054581378</v>
       </c>
       <c r="O422" t="n">
-        <v>3916923.05809667</v>
+        <v>3916924.012901942</v>
       </c>
       <c r="P422" t="n">
         <v>900</v>
@@ -19010,10 +19010,10 @@
         <v>252</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8406506215</v>
+        <v>3110.8406407201</v>
       </c>
       <c r="O423" t="n">
-        <v>783931.843956618</v>
+        <v>783931.8414614652</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -19142,10 +19142,10 @@
         <v>17096</v>
       </c>
       <c r="N426" t="n">
-        <v>703.79512253205</v>
+        <v>703.79511760843</v>
       </c>
       <c r="O426" t="n">
-        <v>12032081.41480793</v>
+        <v>12032081.33063372</v>
       </c>
       <c r="P426" t="n">
         <v>900</v>
@@ -22726,10 +22726,10 @@
         <v>1</v>
       </c>
       <c r="N507" t="n">
-        <v>4985.4055045872</v>
+        <v>4985.4056872038</v>
       </c>
       <c r="O507" t="n">
-        <v>4985.4055045872</v>
+        <v>4985.4056872038</v>
       </c>
       <c r="P507" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3076655052</v>
+        <v>1811.3078361532</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.379790936</v>
+        <v>326035.410507576</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.746460274</v>
+        <v>3376.7464583333</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1363068561</v>
+        <v>823926.1358333252</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -1990,10 +1990,10 @@
         <v>527</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010834236</v>
+        <v>2413.0010857763</v>
       </c>
       <c r="O40" t="n">
-        <v>1271651.570964237</v>
+        <v>1271651.57220411</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2068,10 +2068,10 @@
         <v>144</v>
       </c>
       <c r="N42" t="n">
-        <v>3716.3301957586</v>
+        <v>3716.3301963993</v>
       </c>
       <c r="O42" t="n">
-        <v>535151.5481892384</v>
+        <v>535151.5482814992</v>
       </c>
       <c r="P42" t="n">
         <v>9500</v>
@@ -2497,10 +2497,10 @@
         <v>152</v>
       </c>
       <c r="N53" t="n">
-        <v>3910.628089172</v>
+        <v>3910.6280686695</v>
       </c>
       <c r="O53" t="n">
-        <v>594415.469554144</v>
+        <v>594415.466437764</v>
       </c>
       <c r="P53" t="n">
         <v>9100</v>
@@ -2620,10 +2620,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.965851528</v>
+        <v>15711.965814978</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.360873344</v>
+        <v>754174.359118944</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -2753,10 +2753,10 @@
         <v>136</v>
       </c>
       <c r="N59" t="n">
-        <v>7407.7300543478</v>
+        <v>7407.7300550964</v>
       </c>
       <c r="O59" t="n">
-        <v>1007451.287391301</v>
+        <v>1007451.28749311</v>
       </c>
       <c r="P59" t="n">
         <v>10900</v>
@@ -3100,10 +3100,10 @@
         <v>27</v>
       </c>
       <c r="N67" t="n">
-        <v>200072.20066116</v>
+        <v>200072.20075</v>
       </c>
       <c r="O67" t="n">
-        <v>5401949.41785132</v>
+        <v>5401949.42025</v>
       </c>
       <c r="P67" t="n">
         <v>312000</v>
@@ -4059,10 +4059,10 @@
         <v>200</v>
       </c>
       <c r="N89" t="n">
-        <v>4937.3101636905</v>
+        <v>4937.3101649175</v>
       </c>
       <c r="O89" t="n">
-        <v>987462.0327381</v>
+        <v>987462.0329834999</v>
       </c>
       <c r="P89" t="n">
         <v>7500</v>
@@ -4955,10 +4955,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2555674232</v>
+        <v>2582.2555555556</v>
       </c>
       <c r="O110" t="n">
-        <v>2788836.012817056</v>
+        <v>2788836.000000048</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5047,10 +5047,10 @@
         <v>1898</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.8960872076</v>
+        <v>5216.89608155</v>
       </c>
       <c r="O112" t="n">
-        <v>9901668.773520026</v>
+        <v>9901668.762781901</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5139,10 +5139,10 @@
         <v>6298</v>
       </c>
       <c r="N114" t="n">
-        <v>3158.8608272041</v>
+        <v>3158.8608285041</v>
       </c>
       <c r="O114" t="n">
-        <v>19894505.48973142</v>
+        <v>19894505.49791882</v>
       </c>
       <c r="P114" t="n">
         <v>5600</v>
@@ -5689,10 +5689,10 @@
         <v>3024</v>
       </c>
       <c r="N126" t="n">
-        <v>3795.7100075657</v>
+        <v>3795.7100075672</v>
       </c>
       <c r="O126" t="n">
-        <v>11478227.06287868</v>
+        <v>11478227.06288321</v>
       </c>
       <c r="P126" t="n">
         <v>6200</v>
@@ -6460,10 +6460,10 @@
         <v>264</v>
       </c>
       <c r="N143" t="n">
-        <v>3594.2539546599</v>
+        <v>3594.2538892425</v>
       </c>
       <c r="O143" t="n">
-        <v>948883.0440302136</v>
+        <v>948883.0267600201</v>
       </c>
       <c r="P143" t="n">
         <v>6500</v>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -7131,10 +7131,10 @@
         <v>809</v>
       </c>
       <c r="N158" t="n">
-        <v>4372.2107910895</v>
+        <v>4372.2107914851</v>
       </c>
       <c r="O158" t="n">
-        <v>3537118.529991406</v>
+        <v>3537118.530311446</v>
       </c>
       <c r="P158" t="n">
         <v>7500</v>
@@ -7480,10 +7480,10 @@
         <v>10357</v>
       </c>
       <c r="N166" t="n">
-        <v>1532.6290268774</v>
+        <v>1532.6290268065</v>
       </c>
       <c r="O166" t="n">
-        <v>15873438.83136923</v>
+        <v>15873438.83063492</v>
       </c>
       <c r="P166" t="n">
         <v>1200</v>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -8317,10 +8317,10 @@
         <v>1152</v>
       </c>
       <c r="N185" t="n">
-        <v>1630.9237512195</v>
+        <v>1630.9238354115</v>
       </c>
       <c r="O185" t="n">
-        <v>1878824.161404864</v>
+        <v>1878824.258394048</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8363,10 +8363,10 @@
         <v>384</v>
       </c>
       <c r="N186" t="n">
-        <v>1690.5961358314</v>
+        <v>1690.5953666398</v>
       </c>
       <c r="O186" t="n">
-        <v>649188.9161592576</v>
+        <v>649188.6207896832</v>
       </c>
       <c r="P186" t="n">
         <v>2900</v>
@@ -8409,10 +8409,10 @@
         <v>4608</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.193804203</v>
+        <v>1550.1938475894</v>
       </c>
       <c r="O187" t="n">
-        <v>7143293.049767423</v>
+        <v>7143293.249691956</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8455,10 +8455,10 @@
         <v>1632</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5125525465</v>
+        <v>2403.5129584811</v>
       </c>
       <c r="O188" t="n">
-        <v>3922532.485755888</v>
+        <v>3922533.148241156</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -8798,10 +8798,10 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -9380,10 +9380,10 @@
         <v>1415</v>
       </c>
       <c r="N209" t="n">
-        <v>4196.8725298197</v>
+        <v>4196.8725305216</v>
       </c>
       <c r="O209" t="n">
-        <v>5938574.629694875</v>
+        <v>5938574.630688065</v>
       </c>
       <c r="P209" t="n">
         <v>5900</v>
@@ -9959,10 +9959,10 @@
         <v>30</v>
       </c>
       <c r="N223" t="n">
-        <v>22485.695571956</v>
+        <v>22485.695561036</v>
       </c>
       <c r="O223" t="n">
-        <v>674570.86715868</v>
+        <v>674570.8668310799</v>
       </c>
       <c r="P223" t="n">
         <v>36500</v>
@@ -10615,10 +10615,10 @@
         <v>150</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.1957207207</v>
+        <v>4285.195740113</v>
       </c>
       <c r="O238" t="n">
-        <v>642779.3581081049</v>
+        <v>642779.36101695</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -12096,10 +12096,10 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K273" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -12195,10 +12195,10 @@
         <v>480</v>
       </c>
       <c r="N275" t="n">
-        <v>7969.9501671733</v>
+        <v>7969.9501675552</v>
       </c>
       <c r="O275" t="n">
-        <v>3825576.080243184</v>
+        <v>3825576.080426496</v>
       </c>
       <c r="P275" t="n">
         <v>12900</v>
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -12628,10 +12628,10 @@
         <v>433</v>
       </c>
       <c r="N285" t="n">
-        <v>3113.8900280899</v>
+        <v>3113.8900281294</v>
       </c>
       <c r="O285" t="n">
-        <v>1348314.382162927</v>
+        <v>1348314.38218003</v>
       </c>
       <c r="P285" t="n">
         <v>5000</v>
@@ -12950,10 +12950,10 @@
         <v>399</v>
       </c>
       <c r="N292" t="n">
-        <v>5218.1705662806</v>
+        <v>5218.1705677419</v>
       </c>
       <c r="O292" t="n">
-        <v>2082050.055945959</v>
+        <v>2082050.056529018</v>
       </c>
       <c r="P292" t="n">
         <v>8500</v>
@@ -12996,10 +12996,10 @@
         <v>206</v>
       </c>
       <c r="N293" t="n">
-        <v>1595.0093402778</v>
+        <v>1595.0093238434</v>
       </c>
       <c r="O293" t="n">
-        <v>328571.9240972268</v>
+        <v>328571.9207117404</v>
       </c>
       <c r="P293" t="n">
         <v>2600</v>
@@ -17587,10 +17587,10 @@
         <v>4224</v>
       </c>
       <c r="N393" t="n">
-        <v>1516.0387920714</v>
+        <v>1516.0387919529</v>
       </c>
       <c r="O393" t="n">
-        <v>6403747.857709593</v>
+        <v>6403747.85720905</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
@@ -17633,10 +17633,10 @@
         <v>1152</v>
       </c>
       <c r="N394" t="n">
-        <v>2458.5129946345</v>
+        <v>2458.5129828687</v>
       </c>
       <c r="O394" t="n">
-        <v>2832206.969818944</v>
+        <v>2832206.956264742</v>
       </c>
       <c r="P394" t="n">
         <v>3500</v>
@@ -17725,10 +17725,10 @@
         <v>576</v>
       </c>
       <c r="N396" t="n">
-        <v>1771.0903664224</v>
+        <v>1771.0903406814</v>
       </c>
       <c r="O396" t="n">
-        <v>1020148.051059302</v>
+        <v>1020148.036232486</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17771,10 +17771,10 @@
         <v>960</v>
       </c>
       <c r="N397" t="n">
-        <v>2079.3839648173</v>
+        <v>2079.383962775</v>
       </c>
       <c r="O397" t="n">
-        <v>1996208.606224608</v>
+        <v>1996208.604264</v>
       </c>
       <c r="P397" t="n">
         <v>2900</v>
@@ -17817,10 +17817,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>1803.0157128413</v>
+        <v>1803.0157988368</v>
       </c>
       <c r="O398" t="n">
-        <v>2077074.101193178</v>
+        <v>2077074.200259994</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -17863,10 +17863,10 @@
         <v>1440</v>
       </c>
       <c r="N399" t="n">
-        <v>2122.163800317</v>
+        <v>2122.1637428023</v>
       </c>
       <c r="O399" t="n">
-        <v>3055915.87245648</v>
+        <v>3055915.789635312</v>
       </c>
       <c r="P399" t="n">
         <v>2900</v>
@@ -17909,10 +17909,10 @@
         <v>396</v>
       </c>
       <c r="N400" t="n">
-        <v>2056.0828974535</v>
+        <v>2056.0828901137</v>
       </c>
       <c r="O400" t="n">
-        <v>814208.827391586</v>
+        <v>814208.8244850253</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -17955,10 +17955,10 @@
         <v>714</v>
       </c>
       <c r="N401" t="n">
-        <v>3224.5688613861</v>
+        <v>3224.5688657751</v>
       </c>
       <c r="O401" t="n">
-        <v>2302342.167029675</v>
+        <v>2302342.170163421</v>
       </c>
       <c r="P401" t="n">
         <v>4500</v>
@@ -18001,10 +18001,10 @@
         <v>864</v>
       </c>
       <c r="N402" t="n">
-        <v>1655.9307676903</v>
+        <v>1655.9307118872</v>
       </c>
       <c r="O402" t="n">
-        <v>1430724.183284419</v>
+        <v>1430724.135070541</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -18756,10 +18756,10 @@
         <v>2</v>
       </c>
       <c r="N418" t="n">
-        <v>1530.4499195171</v>
+        <v>1530.4499191266</v>
       </c>
       <c r="O418" t="n">
-        <v>3060.8998390342</v>
+        <v>3060.8998382532</v>
       </c>
       <c r="P418" t="n">
         <v>2600</v>
@@ -19426,10 +19426,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.29054581378</v>
+        <v>517.29069907291</v>
       </c>
       <c r="O433" t="n">
-        <v>3916924.012901942</v>
+        <v>3916925.173380075</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -19475,10 +19475,10 @@
         <v>252</v>
       </c>
       <c r="N434" t="n">
-        <v>3110.8406407201</v>
+        <v>3110.8404252438</v>
       </c>
       <c r="O434" t="n">
-        <v>783931.8414614652</v>
+        <v>783931.7871614376</v>
       </c>
       <c r="P434" t="n">
         <v>4500</v>
@@ -19607,10 +19607,10 @@
         <v>17096</v>
       </c>
       <c r="N437" t="n">
-        <v>703.79511689575</v>
+        <v>703.79510612101</v>
       </c>
       <c r="O437" t="n">
-        <v>12032081.31844974</v>
+        <v>12032081.13424479</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -20184,10 +20184,10 @@
         <v>1369</v>
       </c>
       <c r="N450" t="n">
-        <v>1595.5118087506</v>
+        <v>1595.5116515014</v>
       </c>
       <c r="O450" t="n">
-        <v>2184255.666179571</v>
+        <v>2184255.450905417</v>
       </c>
       <c r="P450" t="n">
         <v>2500</v>
@@ -21061,10 +21061,10 @@
         <v>1976</v>
       </c>
       <c r="N469" t="n">
-        <v>7046.939827883</v>
+        <v>7046.9398275862</v>
       </c>
       <c r="O469" t="n">
-        <v>13924753.09989681</v>
+        <v>13924753.09931033</v>
       </c>
       <c r="P469" t="n">
         <v>9900</v>
@@ -21095,10 +21095,10 @@
         </is>
       </c>
       <c r="J470" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -21699,10 +21699,10 @@
         <v>20</v>
       </c>
       <c r="N483" t="n">
-        <v>1619.568255102</v>
+        <v>1619.5682224532</v>
       </c>
       <c r="O483" t="n">
-        <v>32391.36510204</v>
+        <v>32391.364449064</v>
       </c>
       <c r="P483" t="n">
         <v>1900</v>
@@ -22379,10 +22379,10 @@
         <v>436</v>
       </c>
       <c r="N499" t="n">
-        <v>5497.1753179191</v>
+        <v>5497.1753111433</v>
       </c>
       <c r="O499" t="n">
-        <v>2396768.438612727</v>
+        <v>2396768.435658479</v>
       </c>
       <c r="P499" t="n">
         <v>6500</v>
@@ -23191,10 +23191,10 @@
         <v>1</v>
       </c>
       <c r="N518" t="n">
-        <v>4985.4056872038</v>
+        <v>4985.40591133</v>
       </c>
       <c r="O518" t="n">
-        <v>4985.4056872038</v>
+        <v>4985.40591133</v>
       </c>
       <c r="P518" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -2539,10 +2539,10 @@
         <v>52</v>
       </c>
       <c r="N54" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O54" t="n">
-        <v>857293.250393684</v>
+        <v>857293.2457143081</v>
       </c>
       <c r="P54" t="n">
         <v>30500</v>
@@ -2620,10 +2620,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.359118944</v>
+        <v>754174.35823008</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -4955,10 +4955,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O110" t="n">
-        <v>2788836.000000048</v>
+        <v>2788835.997857112</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -18001,10 +18001,10 @@
         <v>864</v>
       </c>
       <c r="N402" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O402" t="n">
-        <v>1430724.135070541</v>
+        <v>1430724.124277107</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -19475,10 +19475,10 @@
         <v>252</v>
       </c>
       <c r="N434" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O434" t="n">
-        <v>783931.7871614376</v>
+        <v>783931.7845444679</v>
       </c>
       <c r="P434" t="n">
         <v>4500</v>
@@ -20184,10 +20184,10 @@
         <v>1369</v>
       </c>
       <c r="N450" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O450" t="n">
-        <v>2184255.450905417</v>
+        <v>2184255.38214876</v>
       </c>
       <c r="P450" t="n">
         <v>2500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -880,10 +880,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>14490.384928571</v>
+        <v>14490.384892086</v>
       </c>
       <c r="O12" t="n">
-        <v>246336.543785707</v>
+        <v>246336.543165462</v>
       </c>
       <c r="P12" t="n">
         <v>23600</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3078361532</v>
+        <v>1811.3078994614</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.410507576</v>
+        <v>326035.421903052</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464583333</v>
+        <v>3376.7464524986</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1358333252</v>
+        <v>823926.1344096584</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -2497,10 +2497,10 @@
         <v>152</v>
       </c>
       <c r="N53" t="n">
-        <v>3910.6280686695</v>
+        <v>3910.6280519481</v>
       </c>
       <c r="O53" t="n">
-        <v>594415.466437764</v>
+        <v>594415.4638961112</v>
       </c>
       <c r="P53" t="n">
         <v>9100</v>
@@ -2620,10 +2620,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.96579646</v>
+        <v>15711.965777778</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.35823008</v>
+        <v>754174.3573333439</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -3931,10 +3931,10 @@
         <v>1440</v>
       </c>
       <c r="N86" t="n">
-        <v>1950.2145987654</v>
+        <v>1950.214568029</v>
       </c>
       <c r="O86" t="n">
-        <v>2808309.022222176</v>
+        <v>2808308.97796176</v>
       </c>
       <c r="P86" t="n">
         <v>2900</v>
@@ -4955,10 +4955,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2555535714</v>
+        <v>2582.255546613</v>
       </c>
       <c r="O110" t="n">
-        <v>2788835.997857112</v>
+        <v>2788835.99034204</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5047,10 +5047,10 @@
         <v>1898</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.89608155</v>
+        <v>5216.8960627633</v>
       </c>
       <c r="O112" t="n">
-        <v>9901668.762781901</v>
+        <v>9901668.727124743</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5139,10 +5139,10 @@
         <v>6298</v>
       </c>
       <c r="N114" t="n">
-        <v>3158.8608285041</v>
+        <v>3158.8608303391</v>
       </c>
       <c r="O114" t="n">
-        <v>19894505.49791882</v>
+        <v>19894505.50947565</v>
       </c>
       <c r="P114" t="n">
         <v>5600</v>
@@ -5231,10 +5231,10 @@
         <v>144</v>
       </c>
       <c r="N116" t="n">
-        <v>3841.6248454636</v>
+        <v>3841.62486</v>
       </c>
       <c r="O116" t="n">
-        <v>553193.9777467584</v>
+        <v>553193.9798399999</v>
       </c>
       <c r="P116" t="n">
         <v>6900</v>
@@ -5689,10 +5689,10 @@
         <v>3024</v>
       </c>
       <c r="N126" t="n">
-        <v>3795.7100075672</v>
+        <v>3795.7100075815</v>
       </c>
       <c r="O126" t="n">
-        <v>11478227.06288321</v>
+        <v>11478227.06292646</v>
       </c>
       <c r="P126" t="n">
         <v>6200</v>
@@ -6104,10 +6104,10 @@
         <v>24</v>
       </c>
       <c r="N135" t="n">
-        <v>2267.0481436371</v>
+        <v>2267.0481247348</v>
       </c>
       <c r="O135" t="n">
-        <v>54409.1554472904</v>
+        <v>54409.15499363519</v>
       </c>
       <c r="P135" t="n">
         <v>3900</v>
@@ -6460,10 +6460,10 @@
         <v>264</v>
       </c>
       <c r="N143" t="n">
-        <v>3594.2538892425</v>
+        <v>3594.2538618926</v>
       </c>
       <c r="O143" t="n">
-        <v>948883.0267600201</v>
+        <v>948883.0195396465</v>
       </c>
       <c r="P143" t="n">
         <v>6500</v>
@@ -7085,10 +7085,10 @@
         <v>78</v>
       </c>
       <c r="N157" t="n">
-        <v>3041.6600135135</v>
+        <v>3041.660013541</v>
       </c>
       <c r="O157" t="n">
-        <v>237249.481054053</v>
+        <v>237249.481056198</v>
       </c>
       <c r="P157" t="n">
         <v>5500</v>
@@ -7131,10 +7131,10 @@
         <v>809</v>
       </c>
       <c r="N158" t="n">
-        <v>4372.2107914851</v>
+        <v>4372.2107916548</v>
       </c>
       <c r="O158" t="n">
-        <v>3537118.530311446</v>
+        <v>3537118.530448733</v>
       </c>
       <c r="P158" t="n">
         <v>7500</v>
@@ -8317,10 +8317,10 @@
         <v>1152</v>
       </c>
       <c r="N185" t="n">
-        <v>1630.9238354115</v>
+        <v>1630.9238750315</v>
       </c>
       <c r="O185" t="n">
-        <v>1878824.258394048</v>
+        <v>1878824.304036288</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8363,10 +8363,10 @@
         <v>384</v>
       </c>
       <c r="N186" t="n">
-        <v>1690.5953666398</v>
+        <v>1690.5947980214</v>
       </c>
       <c r="O186" t="n">
-        <v>649188.6207896832</v>
+        <v>649188.4024402176</v>
       </c>
       <c r="P186" t="n">
         <v>2900</v>
@@ -8409,10 +8409,10 @@
         <v>4608</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.1938475894</v>
+        <v>1550.1938919769</v>
       </c>
       <c r="O187" t="n">
-        <v>7143293.249691956</v>
+        <v>7143293.454229555</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8455,10 +8455,10 @@
         <v>1632</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5129584811</v>
+        <v>2403.5131199831</v>
       </c>
       <c r="O188" t="n">
-        <v>3922533.148241156</v>
+        <v>3922533.411812419</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9380,10 +9380,10 @@
         <v>1415</v>
       </c>
       <c r="N209" t="n">
-        <v>4196.8725305216</v>
+        <v>4196.872531224</v>
       </c>
       <c r="O209" t="n">
-        <v>5938574.630688065</v>
+        <v>5938574.63168196</v>
       </c>
       <c r="P209" t="n">
         <v>5900</v>
@@ -10131,10 +10131,10 @@
         <v>1254</v>
       </c>
       <c r="N227" t="n">
-        <v>880.32953355545</v>
+        <v>880.32956085919</v>
       </c>
       <c r="O227" t="n">
-        <v>1103933.235078534</v>
+        <v>1103933.269317424</v>
       </c>
       <c r="P227" t="n">
         <v>1200</v>
@@ -10615,10 +10615,10 @@
         <v>150</v>
       </c>
       <c r="N238" t="n">
-        <v>4285.195740113</v>
+        <v>4285.1957531144</v>
       </c>
       <c r="O238" t="n">
-        <v>642779.36101695</v>
+        <v>642779.3629671599</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
@@ -11934,10 +11934,10 @@
         <v>34</v>
       </c>
       <c r="N269" t="n">
-        <v>27123.765196998</v>
+        <v>27123.76518797</v>
       </c>
       <c r="O269" t="n">
-        <v>922208.016697932</v>
+        <v>922208.01639098</v>
       </c>
       <c r="P269" t="n">
         <v>44500</v>
@@ -12950,10 +12950,10 @@
         <v>399</v>
       </c>
       <c r="N292" t="n">
-        <v>5218.1705677419</v>
+        <v>5218.1705692109</v>
       </c>
       <c r="O292" t="n">
-        <v>2082050.056529018</v>
+        <v>2082050.057115149</v>
       </c>
       <c r="P292" t="n">
         <v>8500</v>
@@ -12996,10 +12996,10 @@
         <v>206</v>
       </c>
       <c r="N293" t="n">
-        <v>1595.0093238434</v>
+        <v>1595.0093202147</v>
       </c>
       <c r="O293" t="n">
-        <v>328571.9207117404</v>
+        <v>328571.9199642282</v>
       </c>
       <c r="P293" t="n">
         <v>2600</v>
@@ -14100,10 +14100,10 @@
         <v>1145</v>
       </c>
       <c r="N317" t="n">
-        <v>1778.4726494689</v>
+        <v>1778.4726526892</v>
       </c>
       <c r="O317" t="n">
-        <v>2036351.183641891</v>
+        <v>2036351.187329134</v>
       </c>
       <c r="P317" t="n">
         <v>4900</v>
@@ -14882,10 +14882,10 @@
         <v>28</v>
       </c>
       <c r="N334" t="n">
-        <v>2252.2973618785</v>
+        <v>2252.2974859551</v>
       </c>
       <c r="O334" t="n">
-        <v>63064.326132598</v>
+        <v>63064.3296067428</v>
       </c>
       <c r="P334" t="n">
         <v>3900</v>
@@ -15064,10 +15064,10 @@
         <v>864</v>
       </c>
       <c r="N338" t="n">
-        <v>2328.1186979327</v>
+        <v>2328.1186975309</v>
       </c>
       <c r="O338" t="n">
-        <v>2011494.555013853</v>
+        <v>2011494.554666698</v>
       </c>
       <c r="P338" t="n">
         <v>4500</v>
@@ -17587,10 +17587,10 @@
         <v>4224</v>
       </c>
       <c r="N393" t="n">
-        <v>1516.0387919529</v>
+        <v>1516.0387905286</v>
       </c>
       <c r="O393" t="n">
-        <v>6403747.85720905</v>
+        <v>6403747.851192806</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
@@ -17633,10 +17633,10 @@
         <v>1152</v>
       </c>
       <c r="N394" t="n">
-        <v>2458.5129828687</v>
+        <v>2458.5129162428</v>
       </c>
       <c r="O394" t="n">
-        <v>2832206.956264742</v>
+        <v>2832206.879511706</v>
       </c>
       <c r="P394" t="n">
         <v>3500</v>
@@ -17725,10 +17725,10 @@
         <v>576</v>
       </c>
       <c r="N396" t="n">
-        <v>1771.0903406814</v>
+        <v>1771.0902822581</v>
       </c>
       <c r="O396" t="n">
-        <v>1020148.036232486</v>
+        <v>1020148.002580666</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17817,10 +17817,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>1803.0157988368</v>
+        <v>1803.015867082</v>
       </c>
       <c r="O398" t="n">
-        <v>2077074.200259994</v>
+        <v>2077074.278878464</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -17863,10 +17863,10 @@
         <v>1440</v>
       </c>
       <c r="N399" t="n">
-        <v>2122.1637428023</v>
+        <v>2122.163732778</v>
       </c>
       <c r="O399" t="n">
-        <v>3055915.789635312</v>
+        <v>3055915.77520032</v>
       </c>
       <c r="P399" t="n">
         <v>2900</v>
@@ -17909,10 +17909,10 @@
         <v>396</v>
       </c>
       <c r="N400" t="n">
-        <v>2056.0828901137</v>
+        <v>2056.0828704663</v>
       </c>
       <c r="O400" t="n">
-        <v>814208.8244850253</v>
+        <v>814208.8167046548</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -17955,10 +17955,10 @@
         <v>714</v>
       </c>
       <c r="N401" t="n">
-        <v>3224.5688657751</v>
+        <v>3224.5689232303</v>
       </c>
       <c r="O401" t="n">
-        <v>2302342.170163421</v>
+        <v>2302342.211186434</v>
       </c>
       <c r="P401" t="n">
         <v>4500</v>
@@ -18001,10 +18001,10 @@
         <v>864</v>
       </c>
       <c r="N402" t="n">
-        <v>1655.9306993948</v>
+        <v>1655.9305693829</v>
       </c>
       <c r="O402" t="n">
-        <v>1430724.124277107</v>
+        <v>1430724.011946826</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -19070,10 +19070,10 @@
         <v>216</v>
       </c>
       <c r="N425" t="n">
-        <v>2286.1647064306</v>
+        <v>2286.1646666667</v>
       </c>
       <c r="O425" t="n">
-        <v>493811.5765890095</v>
+        <v>493811.5680000072</v>
       </c>
       <c r="P425" t="n">
         <v>3000</v>
@@ -19426,10 +19426,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.29069907291</v>
+        <v>517.29096206919</v>
       </c>
       <c r="O433" t="n">
-        <v>3916925.173380075</v>
+        <v>3916927.164787906</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -19475,10 +19475,10 @@
         <v>252</v>
       </c>
       <c r="N434" t="n">
-        <v>3110.840414859</v>
+        <v>3110.8403177212</v>
       </c>
       <c r="O434" t="n">
-        <v>783931.7845444679</v>
+        <v>783931.7600657424</v>
       </c>
       <c r="P434" t="n">
         <v>4500</v>
@@ -19607,10 +19607,10 @@
         <v>17096</v>
       </c>
       <c r="N437" t="n">
-        <v>703.79510612101</v>
+        <v>703.79509062003</v>
       </c>
       <c r="O437" t="n">
-        <v>12032081.13424479</v>
+        <v>12032080.86924003</v>
       </c>
       <c r="P437" t="n">
         <v>900</v>
@@ -22977,10 +22977,10 @@
         <v>427</v>
       </c>
       <c r="N513" t="n">
-        <v>3153.2320511559</v>
+        <v>3153.2320521654</v>
       </c>
       <c r="O513" t="n">
-        <v>1346430.085843569</v>
+        <v>1346430.086274626</v>
       </c>
       <c r="P513" t="n">
         <v>3300</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -4955,10 +4955,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O110" t="n">
-        <v>2788835.99034204</v>
+        <v>2788835.987114136</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -8409,10 +8409,10 @@
         <v>4608</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O187" t="n">
-        <v>7143293.454229555</v>
+        <v>7143293.461756262</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -16485,10 +16485,10 @@
         <v>192</v>
       </c>
       <c r="N369" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O369" t="n">
-        <v>3278589.988318272</v>
+        <v>3278589.988254912</v>
       </c>
       <c r="P369" t="n">
         <v>27500</v>
@@ -19426,10 +19426,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O433" t="n">
-        <v>3916927.164787906</v>
+        <v>3916927.244774501</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q525"/>
+  <dimension ref="A1:Q524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -603,10 +603,10 @@
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>96741.42375</v>
+        <v>96741.43166666701</v>
       </c>
       <c r="O5" t="n">
-        <v>386965.695</v>
+        <v>386965.726666668</v>
       </c>
       <c r="P5" t="n">
         <v>188900</v>
@@ -999,10 +999,10 @@
         <v>112</v>
       </c>
       <c r="N15" t="n">
-        <v>1990.0435171103</v>
+        <v>1990.0434548944</v>
       </c>
       <c r="O15" t="n">
-        <v>222884.8739163536</v>
+        <v>222884.8669481728</v>
       </c>
       <c r="P15" t="n">
         <v>4400</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464524986</v>
+        <v>3376.7464515243</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1344096584</v>
+        <v>823926.1341719292</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8549315068</v>
+        <v>6272.8549740933</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.665205469</v>
+        <v>1354936.674404153</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -1873,10 +1873,10 @@
         <v>649</v>
       </c>
       <c r="N37" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O37" t="n">
-        <v>2548517.274937769</v>
+        <v>2548517.272000006</v>
       </c>
       <c r="P37" t="n">
         <v>4800</v>
@@ -2458,10 +2458,10 @@
         <v>24</v>
       </c>
       <c r="N52" t="n">
-        <v>14857.623257919</v>
+        <v>14857.623272727</v>
       </c>
       <c r="O52" t="n">
-        <v>356582.958190056</v>
+        <v>356582.958545448</v>
       </c>
       <c r="P52" t="n">
         <v>34900</v>
@@ -2497,10 +2497,10 @@
         <v>152</v>
       </c>
       <c r="N53" t="n">
-        <v>3910.6280519481</v>
+        <v>3910.6280349345</v>
       </c>
       <c r="O53" t="n">
-        <v>594415.4638961112</v>
+        <v>594415.461310044</v>
       </c>
       <c r="P53" t="n">
         <v>9100</v>
@@ -2539,10 +2539,10 @@
         <v>52</v>
       </c>
       <c r="N54" t="n">
-        <v>16486.408571429</v>
+        <v>16486.40848</v>
       </c>
       <c r="O54" t="n">
-        <v>857293.2457143081</v>
+        <v>857293.2409599999</v>
       </c>
       <c r="P54" t="n">
         <v>30500</v>
@@ -2620,10 +2620,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>15711.965777778</v>
+        <v>15711.96573991</v>
       </c>
       <c r="O56" t="n">
-        <v>754174.3573333439</v>
+        <v>754174.35551568</v>
       </c>
       <c r="P56" t="n">
         <v>28500</v>
@@ -2667,10 +2667,10 @@
         <v>48</v>
       </c>
       <c r="N57" t="n">
-        <v>30238.812647059</v>
+        <v>30238.813103448</v>
       </c>
       <c r="O57" t="n">
-        <v>1451463.007058832</v>
+        <v>1451463.028965504</v>
       </c>
       <c r="P57" t="n">
         <v>51100</v>
@@ -3100,10 +3100,10 @@
         <v>27</v>
       </c>
       <c r="N67" t="n">
-        <v>200072.20075</v>
+        <v>200072.20121739</v>
       </c>
       <c r="O67" t="n">
-        <v>5401949.42025</v>
+        <v>5401949.432869529</v>
       </c>
       <c r="P67" t="n">
         <v>312000</v>
@@ -3931,10 +3931,10 @@
         <v>1440</v>
       </c>
       <c r="N86" t="n">
-        <v>1950.214568029</v>
+        <v>1950.2145482866</v>
       </c>
       <c r="O86" t="n">
-        <v>2808308.97796176</v>
+        <v>2808308.949532704</v>
       </c>
       <c r="P86" t="n">
         <v>2900</v>
@@ -4955,10 +4955,10 @@
         <v>1080</v>
       </c>
       <c r="N110" t="n">
-        <v>2582.2555436242</v>
+        <v>2582.2555195682</v>
       </c>
       <c r="O110" t="n">
-        <v>2788835.987114136</v>
+        <v>2788835.961133656</v>
       </c>
       <c r="P110" t="n">
         <v>4500</v>
@@ -5047,10 +5047,10 @@
         <v>1898</v>
       </c>
       <c r="N112" t="n">
-        <v>5216.8960627633</v>
+        <v>5216.8960541642</v>
       </c>
       <c r="O112" t="n">
-        <v>9901668.727124743</v>
+        <v>9901668.710803652</v>
       </c>
       <c r="P112" t="n">
         <v>8500</v>
@@ -5369,10 +5369,10 @@
         <v>224</v>
       </c>
       <c r="N119" t="n">
-        <v>2694.8231670588</v>
+        <v>2694.8231638418</v>
       </c>
       <c r="O119" t="n">
-        <v>603640.3894211713</v>
+        <v>603640.3887005632</v>
       </c>
       <c r="P119" t="n">
         <v>4900</v>
@@ -5689,10 +5689,10 @@
         <v>3024</v>
       </c>
       <c r="N126" t="n">
-        <v>3795.7100075815</v>
+        <v>3795.7100075887</v>
       </c>
       <c r="O126" t="n">
-        <v>11478227.06292646</v>
+        <v>11478227.06294823</v>
       </c>
       <c r="P126" t="n">
         <v>6200</v>
@@ -5827,10 +5827,10 @@
         <v>64</v>
       </c>
       <c r="N129" t="n">
-        <v>4890.9300489596</v>
+        <v>4890.9300493218</v>
       </c>
       <c r="O129" t="n">
-        <v>313019.5231334144</v>
+        <v>313019.5231565952</v>
       </c>
       <c r="P129" t="n">
         <v>8200</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6457,19 +6457,19 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="N143" t="n">
-        <v>3594.2538618926</v>
+        <v>3594.2537131631</v>
       </c>
       <c r="O143" t="n">
-        <v>948883.0195396465</v>
+        <v>603834.6238114008</v>
       </c>
       <c r="P143" t="n">
         <v>6500</v>
       </c>
       <c r="Q143" t="n">
-        <v>1716000</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="144">
@@ -6770,10 +6770,10 @@
         <v>15671</v>
       </c>
       <c r="N150" t="n">
-        <v>616.01871837471</v>
+        <v>616.01871807046</v>
       </c>
       <c r="O150" t="n">
-        <v>9653629.335650081</v>
+        <v>9653629.330882179</v>
       </c>
       <c r="P150" t="n">
         <v>800</v>
@@ -7131,10 +7131,10 @@
         <v>809</v>
       </c>
       <c r="N158" t="n">
-        <v>4372.2107916548</v>
+        <v>4372.2107917679</v>
       </c>
       <c r="O158" t="n">
-        <v>3537118.530448733</v>
+        <v>3537118.530540232</v>
       </c>
       <c r="P158" t="n">
         <v>7500</v>
@@ -7480,10 +7480,10 @@
         <v>10357</v>
       </c>
       <c r="N166" t="n">
-        <v>1532.6290268065</v>
+        <v>1532.6290266647</v>
       </c>
       <c r="O166" t="n">
-        <v>15873438.83063492</v>
+        <v>15873438.8291663</v>
       </c>
       <c r="P166" t="n">
         <v>1200</v>
@@ -8317,10 +8317,10 @@
         <v>1152</v>
       </c>
       <c r="N185" t="n">
-        <v>1630.9238750315</v>
+        <v>1630.9238760081</v>
       </c>
       <c r="O185" t="n">
-        <v>1878824.304036288</v>
+        <v>1878824.305161331</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8363,10 +8363,10 @@
         <v>384</v>
       </c>
       <c r="N186" t="n">
-        <v>1690.5947980214</v>
+        <v>1690.5946096346</v>
       </c>
       <c r="O186" t="n">
-        <v>649188.4024402176</v>
+        <v>649188.3300996864</v>
       </c>
       <c r="P186" t="n">
         <v>2900</v>
@@ -8409,10 +8409,10 @@
         <v>4608</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.1938936103</v>
+        <v>1550.1939063158</v>
       </c>
       <c r="O187" t="n">
-        <v>7143293.461756262</v>
+        <v>7143293.520303207</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8455,10 +8455,10 @@
         <v>1632</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5131199831</v>
+        <v>2403.5134379057</v>
       </c>
       <c r="O188" t="n">
-        <v>3922533.411812419</v>
+        <v>3922533.930662102</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9380,10 +9380,10 @@
         <v>1415</v>
       </c>
       <c r="N209" t="n">
-        <v>4196.872531224</v>
+        <v>4196.8725319267</v>
       </c>
       <c r="O209" t="n">
-        <v>5938574.63168196</v>
+        <v>5938574.63267628</v>
       </c>
       <c r="P209" t="n">
         <v>5900</v>
@@ -9959,10 +9959,10 @@
         <v>30</v>
       </c>
       <c r="N223" t="n">
-        <v>22485.695561036</v>
+        <v>22485.695555556</v>
       </c>
       <c r="O223" t="n">
-        <v>674570.8668310799</v>
+        <v>674570.8666666801</v>
       </c>
       <c r="P223" t="n">
         <v>36500</v>
@@ -10090,10 +10090,10 @@
         <v>381</v>
       </c>
       <c r="N226" t="n">
-        <v>2680.7396948941</v>
+        <v>2680.739694704</v>
       </c>
       <c r="O226" t="n">
-        <v>1021361.823754652</v>
+        <v>1021361.823682224</v>
       </c>
       <c r="P226" t="n">
         <v>4900</v>
@@ -10131,10 +10131,10 @@
         <v>1254</v>
       </c>
       <c r="N227" t="n">
-        <v>880.32956085919</v>
+        <v>880.32956314156</v>
       </c>
       <c r="O227" t="n">
-        <v>1103933.269317424</v>
+        <v>1103933.272179516</v>
       </c>
       <c r="P227" t="n">
         <v>1200</v>
@@ -11166,10 +11166,10 @@
         <v>150</v>
       </c>
       <c r="N251" t="n">
-        <v>11562.038465753</v>
+        <v>11562.038444444</v>
       </c>
       <c r="O251" t="n">
-        <v>1734305.76986295</v>
+        <v>1734305.7666666</v>
       </c>
       <c r="P251" t="n">
         <v>18500</v>
@@ -11934,10 +11934,10 @@
         <v>34</v>
       </c>
       <c r="N269" t="n">
-        <v>27123.76518797</v>
+        <v>27123.765160681</v>
       </c>
       <c r="O269" t="n">
-        <v>922208.01639098</v>
+        <v>922208.0154631539</v>
       </c>
       <c r="P269" t="n">
         <v>44500</v>
@@ -12277,10 +12277,10 @@
         <v>12</v>
       </c>
       <c r="N277" t="n">
-        <v>9994.7101470588</v>
+        <v>9994.710151515201</v>
       </c>
       <c r="O277" t="n">
-        <v>119936.5217647056</v>
+        <v>119936.5218181824</v>
       </c>
       <c r="P277" t="n">
         <v>20800</v>
@@ -14100,10 +14100,10 @@
         <v>1145</v>
       </c>
       <c r="N317" t="n">
-        <v>1778.4726526892</v>
+        <v>1778.4726559172</v>
       </c>
       <c r="O317" t="n">
-        <v>2036351.187329134</v>
+        <v>2036351.191025194</v>
       </c>
       <c r="P317" t="n">
         <v>4900</v>
@@ -16793,7 +16793,7 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="K376" t="n">
         <v>0</v>
@@ -16802,19 +16802,19 @@
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="N376" t="n">
         <v>10755</v>
       </c>
       <c r="O376" t="n">
-        <v>2570445</v>
+        <v>2247795</v>
       </c>
       <c r="P376" t="n">
         <v>17900</v>
       </c>
       <c r="Q376" t="n">
-        <v>4278100</v>
+        <v>3741100</v>
       </c>
     </row>
     <row r="377">
@@ -17587,10 +17587,10 @@
         <v>4224</v>
       </c>
       <c r="N393" t="n">
-        <v>1516.0387905286</v>
+        <v>1516.0387891009</v>
       </c>
       <c r="O393" t="n">
-        <v>6403747.851192806</v>
+        <v>6403747.845162202</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
@@ -17633,10 +17633,10 @@
         <v>1152</v>
       </c>
       <c r="N394" t="n">
-        <v>2458.5129162428</v>
+        <v>2458.5128483396</v>
       </c>
       <c r="O394" t="n">
-        <v>2832206.879511706</v>
+        <v>2832206.801287219</v>
       </c>
       <c r="P394" t="n">
         <v>3500</v>
@@ -17679,10 +17679,10 @@
         <v>240</v>
       </c>
       <c r="N395" t="n">
-        <v>1907.3929220779</v>
+        <v>1907.392860262</v>
       </c>
       <c r="O395" t="n">
-        <v>457774.301298696</v>
+        <v>457774.28646288</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
@@ -17725,10 +17725,10 @@
         <v>576</v>
       </c>
       <c r="N396" t="n">
-        <v>1771.0902822581</v>
+        <v>1771.0902626263</v>
       </c>
       <c r="O396" t="n">
-        <v>1020148.002580666</v>
+        <v>1020147.991272749</v>
       </c>
       <c r="P396" t="n">
         <v>2500</v>
@@ -17771,10 +17771,10 @@
         <v>960</v>
       </c>
       <c r="N397" t="n">
-        <v>2079.383962775</v>
+        <v>2079.3839381583</v>
       </c>
       <c r="O397" t="n">
-        <v>1996208.604264</v>
+        <v>1996208.580631968</v>
       </c>
       <c r="P397" t="n">
         <v>2900</v>
@@ -17817,10 +17817,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>1803.015867082</v>
+        <v>1803.0158874609</v>
       </c>
       <c r="O398" t="n">
-        <v>2077074.278878464</v>
+        <v>2077074.302354957</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -17863,10 +17863,10 @@
         <v>1440</v>
       </c>
       <c r="N399" t="n">
-        <v>2122.163732778</v>
+        <v>2122.1637267479</v>
       </c>
       <c r="O399" t="n">
-        <v>3055915.77520032</v>
+        <v>3055915.766516976</v>
       </c>
       <c r="P399" t="n">
         <v>2900</v>
@@ -17909,10 +17909,10 @@
         <v>396</v>
       </c>
       <c r="N400" t="n">
-        <v>2056.0828704663</v>
+        <v>2056.0827781666</v>
       </c>
       <c r="O400" t="n">
-        <v>814208.8167046548</v>
+        <v>814208.7801539735</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -17955,10 +17955,10 @@
         <v>714</v>
       </c>
       <c r="N401" t="n">
-        <v>3224.5689232303</v>
+        <v>3224.5689410589</v>
       </c>
       <c r="O401" t="n">
-        <v>2302342.211186434</v>
+        <v>2302342.223916054</v>
       </c>
       <c r="P401" t="n">
         <v>4500</v>
@@ -18001,10 +18001,10 @@
         <v>864</v>
       </c>
       <c r="N402" t="n">
-        <v>1655.9305693829</v>
+        <v>1655.9305111492</v>
       </c>
       <c r="O402" t="n">
-        <v>1430724.011946826</v>
+        <v>1430723.961632909</v>
       </c>
       <c r="P402" t="n">
         <v>2500</v>
@@ -19111,10 +19111,10 @@
         <v>1</v>
       </c>
       <c r="N426" t="n">
-        <v>2590.4171296296</v>
+        <v>2590.4171028037</v>
       </c>
       <c r="O426" t="n">
-        <v>2590.4171296296</v>
+        <v>2590.4171028037</v>
       </c>
       <c r="P426" t="n">
         <v>2800</v>
@@ -19426,10 +19426,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.29097263266</v>
+        <v>517.29128286432</v>
       </c>
       <c r="O433" t="n">
-        <v>3916927.244774501</v>
+        <v>3916929.593848631</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -19441,20 +19441,15 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>C620</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>7700154271143</v>
+        <v>6978454510649</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>BURBUJERO 4 BOQUILLAS</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MATRACA LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -19463,7 +19458,7 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>252</v>
+        <v>1386</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
@@ -19472,33 +19467,33 @@
         <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>252</v>
+        <v>1386</v>
       </c>
       <c r="N434" t="n">
-        <v>3110.8403177212</v>
+        <v>2030.02</v>
       </c>
       <c r="O434" t="n">
-        <v>783931.7600657424</v>
+        <v>2813607.72</v>
       </c>
       <c r="P434" t="n">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="Q434" t="n">
-        <v>1134000</v>
+        <v>4989600</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>C620</t>
+          <t>C627</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>6978454510649</v>
+        <v>6916312021166</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>MATRACA LUZ Y SONIDO</t>
+          <t>BOUQUET FELIZ CUMPLEAOS CAPTUS,DONA.GAFA Y PIA</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -19507,7 +19502,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>1386</v>
+        <v>5</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -19516,33 +19511,33 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>1386</v>
+        <v>5</v>
       </c>
       <c r="N435" t="n">
-        <v>2030.02</v>
+        <v>3002.021</v>
       </c>
       <c r="O435" t="n">
-        <v>2813607.72</v>
+        <v>15010.105</v>
       </c>
       <c r="P435" t="n">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="Q435" t="n">
-        <v>4989600</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>C627</t>
+          <t>C629</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>6916312021166</v>
+        <v>7791638082188</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>BOUQUET FELIZ CUMPLEAOS CAPTUS,DONA.GAFA Y PIA</t>
+          <t>BURBUJERO PITO STD</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -19551,7 +19546,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>5</v>
+        <v>15368</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -19560,42 +19555,47 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>5</v>
+        <v>15368</v>
       </c>
       <c r="N436" t="n">
-        <v>3002.021</v>
+        <v>703.79502188713</v>
       </c>
       <c r="O436" t="n">
-        <v>15010.105</v>
+        <v>10815921.89636141</v>
       </c>
       <c r="P436" t="n">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="Q436" t="n">
-        <v>22500</v>
+        <v>13831200</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>C629</t>
+          <t>C6331</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>7791638082188</v>
+        <v>6558502124150</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>BURBUJERO PITO STD</t>
+          <t>RELOJ PROYECTOR DINOSAURIO C6331</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J437" t="n">
-        <v>17096</v>
+        <v>127</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -19604,47 +19604,42 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>17096</v>
+        <v>127</v>
       </c>
       <c r="N437" t="n">
-        <v>703.79509062003</v>
+        <v>3182.251119403</v>
       </c>
       <c r="O437" t="n">
-        <v>12032080.86924003</v>
+        <v>404145.892164181</v>
       </c>
       <c r="P437" t="n">
-        <v>900</v>
+        <v>6900</v>
       </c>
       <c r="Q437" t="n">
-        <v>15386400</v>
+        <v>876300</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>C6331</t>
+          <t>C634</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>6558502124150</v>
+        <v>6916312021258</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>RELOJ PROYECTOR DINOSAURIO C6331</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>GLOBO BOUQUET BABY SHOWER</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J438" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -19653,42 +19648,47 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="N438" t="n">
-        <v>3182.2511173184</v>
+        <v>3920.1054098361</v>
       </c>
       <c r="O438" t="n">
-        <v>404145.8918994368</v>
+        <v>196005.270491805</v>
       </c>
       <c r="P438" t="n">
-        <v>6900</v>
+        <v>5500</v>
       </c>
       <c r="Q438" t="n">
-        <v>876300</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>C634</t>
+          <t>C6406</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>6916312021258</v>
+        <v>6820212541115</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET BABY SHOWER</t>
+          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J439" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -19697,47 +19697,39 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="N439" t="n">
-        <v>3920.1054098361</v>
+        <v>14260.14</v>
       </c>
       <c r="O439" t="n">
-        <v>196005.270491805</v>
+        <v>2053460.16</v>
       </c>
       <c r="P439" t="n">
-        <v>5500</v>
+        <v>15900</v>
       </c>
       <c r="Q439" t="n">
-        <v>275000</v>
+        <v>2289600</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>C6406</t>
-        </is>
-      </c>
-      <c r="B440" t="n">
-        <v>6820212541115</v>
+          <t>C642</t>
+        </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PAJAROS MUSICALES DECORATIVOS C6406</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>MICELANEOS</t>
+          <t>LANZADOR AGUA</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J440" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -19746,30 +19738,33 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="N440" t="n">
-        <v>14260.14</v>
+        <v>2529.19</v>
       </c>
       <c r="O440" t="n">
-        <v>2053460.16</v>
+        <v>328794.7</v>
       </c>
       <c r="P440" t="n">
-        <v>15900</v>
+        <v>5100</v>
       </c>
       <c r="Q440" t="n">
-        <v>2289600</v>
+        <v>663000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>C642</t>
-        </is>
+          <t>C645</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>6916312021265</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>LANZADOR AGUA</t>
+          <t>GLOBO BOUQUET CANDY</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -19778,7 +19773,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>130</v>
+        <v>501</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -19787,42 +19782,44 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>130</v>
+        <v>501</v>
       </c>
       <c r="N441" t="n">
-        <v>2529.19</v>
+        <v>3384.9037623762</v>
       </c>
       <c r="O441" t="n">
-        <v>328794.7</v>
+        <v>1695836.784950476</v>
       </c>
       <c r="P441" t="n">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="Q441" t="n">
-        <v>663000</v>
+        <v>2254500</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>C645</t>
-        </is>
-      </c>
-      <c r="B442" t="n">
-        <v>6916312021265</v>
+          <t>C659</t>
+        </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET CANDY</t>
+          <t>SLIME BOLSITA STD C659</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J442" t="n">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -19831,44 +19828,39 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="N442" t="n">
-        <v>3384.9037623762</v>
+        <v>1300</v>
       </c>
       <c r="O442" t="n">
-        <v>1695836.784950476</v>
+        <v>624000</v>
       </c>
       <c r="P442" t="n">
-        <v>4500</v>
+        <v>2200</v>
       </c>
       <c r="Q442" t="n">
-        <v>2254500</v>
+        <v>1056000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>C659</t>
+          <t>C678</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>SLIME BOLSITA STD C659</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>GLOBOS BOUQUET PERSONAJES</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J443" t="n">
-        <v>480</v>
+        <v>10</v>
       </c>
       <c r="K443" t="n">
         <v>0</v>
@@ -19877,30 +19869,33 @@
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>480</v>
+        <v>10</v>
       </c>
       <c r="N443" t="n">
-        <v>1300</v>
+        <v>2717.1178965517</v>
       </c>
       <c r="O443" t="n">
-        <v>624000</v>
+        <v>27171.178965517</v>
       </c>
       <c r="P443" t="n">
-        <v>2200</v>
+        <v>3500</v>
       </c>
       <c r="Q443" t="n">
-        <v>1056000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>C678</t>
-        </is>
+          <t>C68</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>5899989622175</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET PERSONAJES</t>
+          <t>INFLABLE VARA ANIMALES</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -19909,7 +19904,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>10</v>
+        <v>616</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -19918,33 +19913,33 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>10</v>
+        <v>616</v>
       </c>
       <c r="N444" t="n">
-        <v>2717.1178965517</v>
+        <v>1950.51</v>
       </c>
       <c r="O444" t="n">
-        <v>27171.178965517</v>
+        <v>1201514.16</v>
       </c>
       <c r="P444" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="Q444" t="n">
-        <v>35000</v>
+        <v>924000</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>C68</t>
+          <t>C683</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>5899989622175</v>
+        <v>6916312021326</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>INFLABLE VARA ANIMALES</t>
+          <t>GLOBO BOUQUET CHEERS</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -19953,7 +19948,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>616</v>
+        <v>381</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -19962,33 +19957,30 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>616</v>
+        <v>381</v>
       </c>
       <c r="N445" t="n">
-        <v>1950.51</v>
+        <v>3629.7160212766</v>
       </c>
       <c r="O445" t="n">
-        <v>1201514.16</v>
+        <v>1382921.804106385</v>
       </c>
       <c r="P445" t="n">
-        <v>1500</v>
+        <v>4900</v>
       </c>
       <c r="Q445" t="n">
-        <v>924000</v>
+        <v>1866900</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>C683</t>
-        </is>
-      </c>
-      <c r="B446" t="n">
-        <v>6916312021326</v>
+          <t>C687</t>
+        </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET CHEERS</t>
+          <t>GLOBO NARUTO</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -19997,7 +19989,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>381</v>
+        <v>878</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20006,30 +19998,33 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>381</v>
+        <v>878</v>
       </c>
       <c r="N446" t="n">
-        <v>3629.716029724</v>
+        <v>1000</v>
       </c>
       <c r="O446" t="n">
-        <v>1382921.807324844</v>
+        <v>878000</v>
       </c>
       <c r="P446" t="n">
-        <v>4900</v>
+        <v>1300</v>
       </c>
       <c r="Q446" t="n">
-        <v>1866900</v>
+        <v>1141400</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>C687</t>
-        </is>
+          <t>C69</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>5899989622182</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>GLOBO NARUTO</t>
+          <t>INFLABLE VARA JIRAFA</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -20038,7 +20033,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>878</v>
+        <v>295</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20047,33 +20042,30 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>878</v>
+        <v>295</v>
       </c>
       <c r="N447" t="n">
-        <v>1000</v>
+        <v>1755.74</v>
       </c>
       <c r="O447" t="n">
-        <v>878000</v>
+        <v>517943.3</v>
       </c>
       <c r="P447" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Q447" t="n">
-        <v>1141400</v>
+        <v>442500</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>C69</t>
-        </is>
-      </c>
-      <c r="B448" t="n">
-        <v>5899989622182</v>
+          <t>C691</t>
+        </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>INFLABLE VARA JIRAFA</t>
+          <t>GLOBO BOUQUET H.B UNICORNIO</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -20082,7 +20074,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>295</v>
+        <v>28</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -20091,30 +20083,38 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>295</v>
+        <v>28</v>
       </c>
       <c r="N448" t="n">
-        <v>1755.74</v>
+        <v>2230.77</v>
       </c>
       <c r="O448" t="n">
-        <v>517943.3</v>
+        <v>62461.56</v>
       </c>
       <c r="P448" t="n">
-        <v>1500</v>
+        <v>2900</v>
       </c>
       <c r="Q448" t="n">
-        <v>442500</v>
+        <v>81200</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>C691</t>
-        </is>
+          <t>C694</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>8411083181340</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET H.B UNICORNIO</t>
+          <t>BOLITRON OJON  MULTICOLOR</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -20123,7 +20123,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>28</v>
+        <v>569</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -20132,33 +20132,30 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>28</v>
+        <v>569</v>
       </c>
       <c r="N449" t="n">
-        <v>2230.77</v>
+        <v>1595.5115507777</v>
       </c>
       <c r="O449" t="n">
-        <v>62461.56</v>
+        <v>907846.0723925113</v>
       </c>
       <c r="P449" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q449" t="n">
-        <v>81200</v>
+        <v>1422500</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>C694</t>
-        </is>
-      </c>
-      <c r="B450" t="n">
-        <v>8411083181340</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>BOLITRON OJON  MULTICOLOR</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -20172,7 +20169,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>1369</v>
+        <v>241</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -20181,44 +20178,47 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>1369</v>
+        <v>241</v>
       </c>
       <c r="N450" t="n">
-        <v>1595.5116012774</v>
+        <v>1567.02</v>
       </c>
       <c r="O450" t="n">
-        <v>2184255.38214876</v>
+        <v>377651.82</v>
       </c>
       <c r="P450" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q450" t="n">
-        <v>3422500</v>
+        <v>698900</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>C698</t>
-        </is>
+          <t>C7005</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>6874123039124</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>MAQUINA DE COSER C7005</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J451" t="n">
-        <v>241</v>
+        <v>122</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -20227,38 +20227,38 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>241</v>
+        <v>122</v>
       </c>
       <c r="N451" t="n">
-        <v>1567.02</v>
+        <v>6078.9925934066</v>
       </c>
       <c r="O451" t="n">
-        <v>377651.82</v>
+        <v>741637.0963956051</v>
       </c>
       <c r="P451" t="n">
-        <v>2900</v>
+        <v>18500</v>
       </c>
       <c r="Q451" t="n">
-        <v>698900</v>
+        <v>2257000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>C7005</t>
+          <t>C7066</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>6874123039124</v>
+        <v>6920241270663</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER C7005</t>
+          <t>LANZADOR DE DARDOS C7066</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -20267,7 +20267,7 @@
         </is>
       </c>
       <c r="J452" t="n">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="K452" t="n">
         <v>0</v>
@@ -20276,47 +20276,42 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="N452" t="n">
-        <v>6078.9925934066</v>
+        <v>10548.76</v>
       </c>
       <c r="O452" t="n">
-        <v>741637.0963956051</v>
+        <v>369206.6</v>
       </c>
       <c r="P452" t="n">
-        <v>18500</v>
+        <v>35900</v>
       </c>
       <c r="Q452" t="n">
-        <v>2257000</v>
+        <v>1256500</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>C7066</t>
+          <t>C707</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>6920241270663</v>
+        <v>6.91369e+17</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>LANZADOR DE DARDOS C7066</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
+          <t>CUADRO FESTIN 30 CM</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J453" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -20325,33 +20320,33 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="N453" t="n">
-        <v>10548.76</v>
+        <v>7779.21</v>
       </c>
       <c r="O453" t="n">
-        <v>369206.6</v>
+        <v>15558.42</v>
       </c>
       <c r="P453" t="n">
-        <v>35900</v>
+        <v>10900</v>
       </c>
       <c r="Q453" t="n">
-        <v>1256500</v>
+        <v>21800</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>C707</t>
+          <t>C71</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>6.91369e+17</v>
+        <v>5899989622205</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>CUADRO FESTIN 30 CM</t>
+          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -20360,7 +20355,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>2</v>
+        <v>1322</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -20369,42 +20364,44 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>2</v>
+        <v>1322</v>
       </c>
       <c r="N454" t="n">
-        <v>7779.21</v>
+        <v>1669.6</v>
       </c>
       <c r="O454" t="n">
-        <v>15558.42</v>
+        <v>2207211.2</v>
       </c>
       <c r="P454" t="n">
-        <v>10900</v>
+        <v>2900</v>
       </c>
       <c r="Q454" t="n">
-        <v>21800</v>
+        <v>3833800</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>C71</t>
-        </is>
-      </c>
-      <c r="B455" t="n">
-        <v>5899989622205</v>
+          <t>C7276</t>
+        </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>C71 INFLABLE PONY ROSADO-AZUL</t>
+          <t>CARTUCHERA 3D OSO HELADO C7276/5518</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J455" t="n">
-        <v>1322</v>
+        <v>36</v>
       </c>
       <c r="K455" t="n">
         <v>0</v>
@@ -20413,30 +20410,33 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>1322</v>
+        <v>36</v>
       </c>
       <c r="N455" t="n">
-        <v>1669.6</v>
+        <v>1322.925</v>
       </c>
       <c r="O455" t="n">
-        <v>2207211.2</v>
+        <v>47625.3</v>
       </c>
       <c r="P455" t="n">
-        <v>2900</v>
+        <v>7900</v>
       </c>
       <c r="Q455" t="n">
-        <v>3833800</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>C7276</t>
-        </is>
+          <t>C7293</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>6895675680015</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>CARTUCHERA 3D OSO HELADO C7276/5518</t>
+          <t>JUEGO DE ARCO Y FLECHA C7293</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -20462,35 +20462,35 @@
         <v>36</v>
       </c>
       <c r="N456" t="n">
-        <v>1322.925</v>
+        <v>11229.38</v>
       </c>
       <c r="O456" t="n">
-        <v>47625.3</v>
+        <v>404257.68</v>
       </c>
       <c r="P456" t="n">
-        <v>7900</v>
+        <v>23900</v>
       </c>
       <c r="Q456" t="n">
-        <v>284400</v>
+        <v>860400</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>C7293</t>
+          <t>C7301</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>6895675680015</v>
+        <v>6925262535258</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>JUEGO DE ARCO Y FLECHA C7293</t>
+          <t>MUÑECA CON CABALLO JIANI  C7301</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>36</v>
+        <v>1728</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
@@ -20508,47 +20508,39 @@
         <v>0</v>
       </c>
       <c r="M457" t="n">
-        <v>36</v>
+        <v>1728</v>
       </c>
       <c r="N457" t="n">
-        <v>11229.38</v>
+        <v>24538</v>
       </c>
       <c r="O457" t="n">
-        <v>404257.68</v>
+        <v>42401664</v>
       </c>
       <c r="P457" t="n">
-        <v>23900</v>
+        <v>31900</v>
       </c>
       <c r="Q457" t="n">
-        <v>860400</v>
+        <v>55123200</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>C7301</t>
-        </is>
-      </c>
-      <c r="B458" t="n">
-        <v>6925262535258</v>
+          <t>C737</t>
+        </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>MUÑECA CON CABALLO JIANI  C7301</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>MUÑECA</t>
+          <t>GLOBO BOUQUET HAPPY NEW YEAR</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J458" t="n">
-        <v>1728</v>
+        <v>91</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
@@ -20557,30 +20549,33 @@
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>1728</v>
+        <v>91</v>
       </c>
       <c r="N458" t="n">
-        <v>24538</v>
+        <v>2505.7605194805</v>
       </c>
       <c r="O458" t="n">
-        <v>42401664</v>
+        <v>228024.2072727255</v>
       </c>
       <c r="P458" t="n">
-        <v>31900</v>
+        <v>3000</v>
       </c>
       <c r="Q458" t="n">
-        <v>55123200</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>C737</t>
-        </is>
+          <t>C739</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>8596162180152</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET HAPPY NEW YEAR</t>
+          <t>C739 GLOBO SILUETA UNICORNIO GDE</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -20589,7 +20584,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>91</v>
+        <v>2082</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -20598,33 +20593,33 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>91</v>
+        <v>2082</v>
       </c>
       <c r="N459" t="n">
-        <v>2505.760516129</v>
+        <v>1309.0790925756</v>
       </c>
       <c r="O459" t="n">
-        <v>228024.206967739</v>
+        <v>2725502.670742399</v>
       </c>
       <c r="P459" t="n">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="Q459" t="n">
-        <v>273000</v>
+        <v>3539400</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>C739</t>
+          <t>C74</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>8596162180152</v>
+        <v>7891276129716</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>C739 GLOBO SILUETA UNICORNIO GDE</t>
+          <t>INFLABLE BATE USA</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -20633,7 +20628,7 @@
         </is>
       </c>
       <c r="J460" t="n">
-        <v>2082</v>
+        <v>4</v>
       </c>
       <c r="K460" t="n">
         <v>0</v>
@@ -20642,33 +20637,33 @@
         <v>0</v>
       </c>
       <c r="M460" t="n">
-        <v>2082</v>
+        <v>4</v>
       </c>
       <c r="N460" t="n">
-        <v>1309.0790925756</v>
+        <v>1783.7988767123</v>
       </c>
       <c r="O460" t="n">
-        <v>2725502.670742399</v>
+        <v>7135.1955068492</v>
       </c>
       <c r="P460" t="n">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="Q460" t="n">
-        <v>3539400</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>C74</t>
+          <t>C740</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>7891276129716</v>
+        <v>8596162180169</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>INFLABLE BATE USA</t>
+          <t>GLOBO SILUETA UNICORNIO MEDIANO</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -20677,7 +20672,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>4</v>
+        <v>6000</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -20686,42 +20681,47 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>4</v>
+        <v>6000</v>
       </c>
       <c r="N461" t="n">
-        <v>1783.7988767123</v>
+        <v>460.04140858356</v>
       </c>
       <c r="O461" t="n">
-        <v>7135.1955068492</v>
+        <v>2760248.45150136</v>
       </c>
       <c r="P461" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="Q461" t="n">
-        <v>6000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>C740</t>
+          <t>C7402</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>8596162180169</v>
+        <v>6920601877891</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>GLOBO SILUETA UNICORNIO MEDIANO</t>
+          <t>PANDERETA X 3 C7402</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J462" t="n">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
@@ -20730,38 +20730,38 @@
         <v>0</v>
       </c>
       <c r="M462" t="n">
-        <v>6000</v>
+        <v>1</v>
       </c>
       <c r="N462" t="n">
-        <v>460.04140858356</v>
+        <v>2356.29</v>
       </c>
       <c r="O462" t="n">
-        <v>2760248.45150136</v>
+        <v>2356.29</v>
       </c>
       <c r="P462" t="n">
-        <v>600</v>
+        <v>6500</v>
       </c>
       <c r="Q462" t="n">
-        <v>3600000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>C7402</t>
+          <t>C7413</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>6920601877891</v>
+        <v>6921202412870</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>PANDERETA X 3 C7402</t>
+          <t>DIDACTICO TORRE DE AROS C7413</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -20770,7 +20770,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
@@ -20779,47 +20779,42 @@
         <v>0</v>
       </c>
       <c r="M463" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="N463" t="n">
-        <v>2356.29</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O463" t="n">
-        <v>2356.29</v>
+        <v>207950.01476015</v>
       </c>
       <c r="P463" t="n">
-        <v>6500</v>
+        <v>8900</v>
       </c>
       <c r="Q463" t="n">
-        <v>6500</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>C7413</t>
+          <t>C743</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>6921202412870</v>
+        <v>8596162180329</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DIDACTICO TORRE DE AROS C7413</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
+          <t>GLOBO MENSAJE 10 STD</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J464" t="n">
-        <v>50</v>
+        <v>728</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -20828,33 +20823,33 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>50</v>
+        <v>728</v>
       </c>
       <c r="N464" t="n">
-        <v>4159.000295203</v>
+        <v>286.61333044868</v>
       </c>
       <c r="O464" t="n">
-        <v>207950.01476015</v>
+        <v>208654.5045666391</v>
       </c>
       <c r="P464" t="n">
-        <v>8900</v>
+        <v>350</v>
       </c>
       <c r="Q464" t="n">
-        <v>445000</v>
+        <v>254800</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>C743</t>
+          <t>C745</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>8596162180329</v>
+        <v>8596162180343</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE 10 STD</t>
+          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -20863,7 +20858,7 @@
         </is>
       </c>
       <c r="J465" t="n">
-        <v>728</v>
+        <v>35</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
@@ -20872,33 +20867,33 @@
         <v>0</v>
       </c>
       <c r="M465" t="n">
-        <v>728</v>
+        <v>35</v>
       </c>
       <c r="N465" t="n">
-        <v>286.61333044868</v>
+        <v>3097.9492241379</v>
       </c>
       <c r="O465" t="n">
-        <v>208654.5045666391</v>
+        <v>108428.2228448265</v>
       </c>
       <c r="P465" t="n">
-        <v>350</v>
+        <v>2400</v>
       </c>
       <c r="Q465" t="n">
-        <v>254800</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>C745</t>
+          <t>C752</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>8596162180343</v>
+        <v>8596162180497</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>GLOBO BIENVENIDO COLORES PUNTOS</t>
+          <t>GLOBO UNICORNIO MED 4 PATAS</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -20907,7 +20902,7 @@
         </is>
       </c>
       <c r="J466" t="n">
-        <v>35</v>
+        <v>1721</v>
       </c>
       <c r="K466" t="n">
         <v>0</v>
@@ -20916,42 +20911,47 @@
         <v>0</v>
       </c>
       <c r="M466" t="n">
-        <v>35</v>
+        <v>1721</v>
       </c>
       <c r="N466" t="n">
-        <v>3097.9492241379</v>
+        <v>1163.7447787403</v>
       </c>
       <c r="O466" t="n">
-        <v>108428.2228448265</v>
+        <v>2002804.764212056</v>
       </c>
       <c r="P466" t="n">
-        <v>2400</v>
+        <v>1500</v>
       </c>
       <c r="Q466" t="n">
-        <v>84000</v>
+        <v>2581500</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>C752</t>
+          <t>C7527</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>8596162180497</v>
+        <v>8823306251417</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>GLOBO UNICORNIO MED 4 PATAS</t>
+          <t>ARCO Y FLECHA BLISTER SENCILLO C7527</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J467" t="n">
-        <v>1721</v>
+        <v>16</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -20960,33 +20960,33 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>1721</v>
+        <v>16</v>
       </c>
       <c r="N467" t="n">
-        <v>1163.7447787403</v>
+        <v>7465.9</v>
       </c>
       <c r="O467" t="n">
-        <v>2002804.764212056</v>
+        <v>119454.4</v>
       </c>
       <c r="P467" t="n">
-        <v>1500</v>
+        <v>11900</v>
       </c>
       <c r="Q467" t="n">
-        <v>2581500</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>C7527</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>8823306251417</v>
+        <v>6951241752002</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>ARCO Y FLECHA BLISTER SENCILLO C7527</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>16</v>
+        <v>1976</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21009,38 +21009,35 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>16</v>
+        <v>1976</v>
       </c>
       <c r="N468" t="n">
-        <v>7465.9</v>
+        <v>7046.9398275862</v>
       </c>
       <c r="O468" t="n">
-        <v>119454.4</v>
+        <v>13924753.09931033</v>
       </c>
       <c r="P468" t="n">
-        <v>11900</v>
+        <v>9900</v>
       </c>
       <c r="Q468" t="n">
-        <v>190400</v>
+        <v>19562400</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>C7534</t>
-        </is>
-      </c>
-      <c r="B469" t="n">
-        <v>6951241752002</v>
+          <t>C7535</t>
+        </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>CARRO METALICO X13 CON CAMION C7535</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -21049,7 +21046,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>1976</v>
+        <v>57</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -21058,44 +21055,42 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>1976</v>
+        <v>57</v>
       </c>
       <c r="N469" t="n">
-        <v>7046.9398275862</v>
+        <v>24338.47</v>
       </c>
       <c r="O469" t="n">
-        <v>13924753.09931033</v>
+        <v>1387292.79</v>
       </c>
       <c r="P469" t="n">
-        <v>9900</v>
+        <v>27900</v>
       </c>
       <c r="Q469" t="n">
-        <v>19562400</v>
+        <v>1590300</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>C7535</t>
-        </is>
+          <t>C755</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>8602001374085</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>CARRO METALICO X13 CON CAMION C7535</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr">
-        <is>
-          <t>CARROS</t>
+          <t>FOMMY LETRAS</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J470" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="K470" t="n">
         <v>0</v>
@@ -21104,33 +21099,33 @@
         <v>0</v>
       </c>
       <c r="M470" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N470" t="n">
-        <v>24338.47</v>
+        <v>10197</v>
       </c>
       <c r="O470" t="n">
-        <v>1387292.79</v>
+        <v>805563</v>
       </c>
       <c r="P470" t="n">
-        <v>27900</v>
+        <v>14300</v>
       </c>
       <c r="Q470" t="n">
-        <v>1590300</v>
+        <v>1129700</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>C755</t>
+          <t>C756</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>8602001374085</v>
+        <v>8602001374092</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>FOMMY LETRAS</t>
+          <t>FOMMY NUMEROS</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -21139,7 +21134,7 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
@@ -21148,42 +21143,44 @@
         <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="N471" t="n">
-        <v>10197</v>
+        <v>10301.17</v>
       </c>
       <c r="O471" t="n">
-        <v>805563</v>
+        <v>113312.87</v>
       </c>
       <c r="P471" t="n">
         <v>14300</v>
       </c>
       <c r="Q471" t="n">
-        <v>1129700</v>
+        <v>157300</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>C756</t>
-        </is>
-      </c>
-      <c r="B472" t="n">
-        <v>8602001374092</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>FOMMY NUMEROS</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J472" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -21192,35 +21189,35 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="N472" t="n">
-        <v>10301.17</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O472" t="n">
-        <v>113312.87</v>
+        <v>20704.06</v>
       </c>
       <c r="P472" t="n">
-        <v>14300</v>
+        <v>2500</v>
       </c>
       <c r="Q472" t="n">
-        <v>157300</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>C7560</t>
+          <t>C7560AC</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>TRICICLO INFANTIL OSITO C756AC</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -21229,7 +21226,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -21238,35 +21235,38 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N473" t="n">
-        <v>796.3099999999999</v>
+        <v>44113.603953488</v>
       </c>
       <c r="O473" t="n">
-        <v>20704.06</v>
+        <v>1764544.15813952</v>
       </c>
       <c r="P473" t="n">
-        <v>2500</v>
+        <v>71900</v>
       </c>
       <c r="Q473" t="n">
-        <v>65000</v>
+        <v>2876000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>C7560AC</t>
-        </is>
+          <t>C7587</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>7587228020247</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>TRICICLO INFANTIL OSITO C756AC</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -21284,38 +21284,38 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="N474" t="n">
-        <v>44113.603841808</v>
+        <v>1080.18</v>
       </c>
       <c r="O474" t="n">
-        <v>1764544.15367232</v>
+        <v>259243.2</v>
       </c>
       <c r="P474" t="n">
-        <v>71900</v>
+        <v>4900</v>
       </c>
       <c r="Q474" t="n">
-        <v>2876000</v>
+        <v>1176000</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>C7587</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>7587228020247</v>
+        <v>6999899236093</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -21333,33 +21333,33 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="N475" t="n">
-        <v>1080.18</v>
+        <v>7811.9</v>
       </c>
       <c r="O475" t="n">
-        <v>259243.2</v>
+        <v>9374280</v>
       </c>
       <c r="P475" t="n">
-        <v>4900</v>
+        <v>13900</v>
       </c>
       <c r="Q475" t="n">
-        <v>1176000</v>
+        <v>16680000</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA PATO C7614</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -21373,7 +21373,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>1200</v>
+        <v>498</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -21382,25 +21382,25 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>1200</v>
+        <v>498</v>
       </c>
       <c r="N476" t="n">
-        <v>7811.9</v>
+        <v>4581.84</v>
       </c>
       <c r="O476" t="n">
-        <v>9374280</v>
+        <v>2281756.32</v>
       </c>
       <c r="P476" t="n">
-        <v>13900</v>
+        <v>7900</v>
       </c>
       <c r="Q476" t="n">
-        <v>16680000</v>
+        <v>3934200</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>C7614</t>
+          <t>C7614-F</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -21408,12 +21408,12 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA PATO C7614</t>
+          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -21422,7 +21422,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -21431,38 +21431,38 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="N477" t="n">
-        <v>4581.84</v>
+        <v>3155</v>
       </c>
       <c r="O477" t="n">
-        <v>2281756.32</v>
+        <v>1482850</v>
       </c>
       <c r="P477" t="n">
-        <v>7900</v>
+        <v>5900</v>
       </c>
       <c r="Q477" t="n">
-        <v>3934200</v>
+        <v>2773000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>C7614-F</t>
+          <t>C7619</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>6999899236130</v>
+        <v>6999899236215</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA FLAMINGO C7614-F</t>
+          <t>DONA INFLABLE FLORES  ESCARCHADAS 70# C7619</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -21471,7 +21471,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>470</v>
+        <v>10</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -21480,47 +21480,39 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>470</v>
+        <v>10</v>
       </c>
       <c r="N478" t="n">
-        <v>3155</v>
+        <v>2010.71</v>
       </c>
       <c r="O478" t="n">
-        <v>1482850</v>
+        <v>20107.1</v>
       </c>
       <c r="P478" t="n">
-        <v>5900</v>
+        <v>7200</v>
       </c>
       <c r="Q478" t="n">
-        <v>2773000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>C7619</t>
-        </is>
-      </c>
-      <c r="B479" t="n">
-        <v>6999899236215</v>
+          <t>C771</t>
+        </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DONA INFLABLE FLORES  ESCARCHADAS 70# C7619</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO LOVE YOU</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J479" t="n">
-        <v>10</v>
+        <v>1670</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -21529,30 +21521,33 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>10</v>
+        <v>1670</v>
       </c>
       <c r="N479" t="n">
-        <v>2010.71</v>
+        <v>1244.5992565056</v>
       </c>
       <c r="O479" t="n">
-        <v>20107.1</v>
+        <v>2078480.758364352</v>
       </c>
       <c r="P479" t="n">
-        <v>7200</v>
+        <v>1500</v>
       </c>
       <c r="Q479" t="n">
-        <v>72000</v>
+        <v>2505000</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>C771</t>
-        </is>
+          <t>C784</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>8913992935507</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>GLOBO LOVE YOU</t>
+          <t>GLOBO MENSAJE CUADRADO</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -21561,7 +21556,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>1670</v>
+        <v>100</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -21570,33 +21565,30 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>1670</v>
+        <v>100</v>
       </c>
       <c r="N480" t="n">
-        <v>1244.5992565056</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O480" t="n">
-        <v>2078480.758364352</v>
+        <v>70489.68946963899</v>
       </c>
       <c r="P480" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="Q480" t="n">
-        <v>2505000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>C784</t>
-        </is>
-      </c>
-      <c r="B481" t="n">
-        <v>8913992935507</v>
+          <t>C787</t>
+        </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>GLOBO MENSAJE CUADRADO</t>
+          <t>GLOBO RATONA</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -21605,7 +21597,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>100</v>
+        <v>4850</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -21614,30 +21606,30 @@
         <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>100</v>
+        <v>4850</v>
       </c>
       <c r="N481" t="n">
-        <v>704.8968946963899</v>
+        <v>1153.85</v>
       </c>
       <c r="O481" t="n">
-        <v>70489.68946963899</v>
+        <v>5596172.5</v>
       </c>
       <c r="P481" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="Q481" t="n">
-        <v>90000</v>
+        <v>7275000</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>C787</t>
+          <t>C811</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>GLOBO RATONA</t>
+          <t>GLOBO NUMERO 100CM</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -21646,7 +21638,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>4850</v>
+        <v>20</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -21655,30 +21647,30 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>4850</v>
+        <v>20</v>
       </c>
       <c r="N482" t="n">
-        <v>1153.85</v>
+        <v>1619.5682224532</v>
       </c>
       <c r="O482" t="n">
-        <v>5596172.5</v>
+        <v>32391.364449064</v>
       </c>
       <c r="P482" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q482" t="n">
-        <v>7275000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>C811</t>
+          <t>C815</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>GLOBO NUMERO 100CM</t>
+          <t>SCOOTER HUMO</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -21687,7 +21679,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -21696,30 +21688,30 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="N483" t="n">
-        <v>1619.5682224532</v>
+        <v>110520.77</v>
       </c>
       <c r="O483" t="n">
-        <v>32391.364449064</v>
+        <v>1436770.01</v>
       </c>
       <c r="P483" t="n">
-        <v>1900</v>
+        <v>176900</v>
       </c>
       <c r="Q483" t="n">
-        <v>38000</v>
+        <v>2299700</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>C815</t>
+          <t>C816</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>SCOOTER HUMO</t>
+          <t>GLOBO SET FC</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -21728,7 +21720,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>13</v>
+        <v>357</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21737,30 +21729,30 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>13</v>
+        <v>357</v>
       </c>
       <c r="N484" t="n">
-        <v>110520.77</v>
+        <v>6172.7748309179</v>
       </c>
       <c r="O484" t="n">
-        <v>1436770.01</v>
+        <v>2203680.61463769</v>
       </c>
       <c r="P484" t="n">
-        <v>176900</v>
+        <v>8000</v>
       </c>
       <c r="Q484" t="n">
-        <v>2299700</v>
+        <v>2856000</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>C816</t>
+          <t>C820</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>GLOBO SET FC</t>
+          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -21769,7 +21761,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>357</v>
+        <v>1989</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -21778,30 +21770,30 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>357</v>
+        <v>1989</v>
       </c>
       <c r="N485" t="n">
-        <v>6172.7748309179</v>
+        <v>3461.54</v>
       </c>
       <c r="O485" t="n">
-        <v>2203680.61463769</v>
+        <v>6885003.06</v>
       </c>
       <c r="P485" t="n">
-        <v>8000</v>
+        <v>4500</v>
       </c>
       <c r="Q485" t="n">
-        <v>2856000</v>
+        <v>8950500</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>C820</t>
+          <t>C821</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FELIZ CUMPLEANOS</t>
+          <t>GLOBO BOUQUET HAPPY BIRTHDAY DOS COLORES</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -21810,7 +21802,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>1989</v>
+        <v>1198</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -21819,30 +21811,30 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>1989</v>
+        <v>1198</v>
       </c>
       <c r="N486" t="n">
-        <v>3461.54</v>
+        <v>4282.1072225705</v>
       </c>
       <c r="O486" t="n">
-        <v>6885003.06</v>
+        <v>5129964.45263946</v>
       </c>
       <c r="P486" t="n">
-        <v>4500</v>
+        <v>5300</v>
       </c>
       <c r="Q486" t="n">
-        <v>8950500</v>
+        <v>6349400</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>C821</t>
+          <t>C822</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET HAPPY BIRTHDAY DOS COLORES</t>
+          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -21851,7 +21843,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>1198</v>
+        <v>198</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21860,30 +21852,33 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>1198</v>
+        <v>198</v>
       </c>
       <c r="N487" t="n">
-        <v>4282.1072225705</v>
+        <v>5577.2680373832</v>
       </c>
       <c r="O487" t="n">
-        <v>5129964.45263946</v>
+        <v>1104299.071401874</v>
       </c>
       <c r="P487" t="n">
-        <v>5300</v>
+        <v>6500</v>
       </c>
       <c r="Q487" t="n">
-        <v>6349400</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>C822</t>
-        </is>
+          <t>C831</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>2021071411029</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET NEGRO CON PLATA</t>
+          <t>GLOBO NINANINO</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -21892,7 +21887,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>198</v>
+        <v>2463</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -21901,33 +21896,30 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>198</v>
+        <v>2463</v>
       </c>
       <c r="N488" t="n">
-        <v>5577.2680373832</v>
+        <v>824.64111075024</v>
       </c>
       <c r="O488" t="n">
-        <v>1104299.071401874</v>
+        <v>2031091.055777841</v>
       </c>
       <c r="P488" t="n">
-        <v>6500</v>
+        <v>1000</v>
       </c>
       <c r="Q488" t="n">
-        <v>1287000</v>
+        <v>2463000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>C831</t>
-        </is>
-      </c>
-      <c r="B489" t="n">
-        <v>2021071411029</v>
+          <t>C833</t>
+        </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>GLOBO NINANINO</t>
+          <t>GLOBO BURBUJA MENSAJE 20</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -21936,7 +21928,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>2463</v>
+        <v>20</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -21945,30 +21937,33 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>2463</v>
+        <v>20</v>
       </c>
       <c r="N489" t="n">
-        <v>824.64111075024</v>
+        <v>921.36630630631</v>
       </c>
       <c r="O489" t="n">
-        <v>2031091.055777841</v>
+        <v>18427.3261261262</v>
       </c>
       <c r="P489" t="n">
         <v>1000</v>
       </c>
       <c r="Q489" t="n">
-        <v>2463000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>C833</t>
-        </is>
+          <t>C848</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>6900159908483</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>GLOBO BURBUJA MENSAJE 20</t>
+          <t>BLOBO GRANDE SORPRESA NINONINA</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -21977,7 +21972,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>20</v>
+        <v>1446</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -21986,33 +21981,33 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>20</v>
+        <v>1446</v>
       </c>
       <c r="N490" t="n">
-        <v>921.36630630631</v>
+        <v>2489.1752653486</v>
       </c>
       <c r="O490" t="n">
-        <v>18427.3261261262</v>
+        <v>3599347.433694076</v>
       </c>
       <c r="P490" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="Q490" t="n">
-        <v>20000</v>
+        <v>4338000</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>C848</t>
+          <t>C851</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>6900159908483</v>
+        <v>2021071411227</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>BLOBO GRANDE SORPRESA NINONINA</t>
+          <t>GLOBO BOUQUET FIESTA</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -22021,7 +22016,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>1446</v>
+        <v>499</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22030,33 +22025,33 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>1446</v>
+        <v>499</v>
       </c>
       <c r="N491" t="n">
-        <v>2489.1752678107</v>
+        <v>2952.0877378815</v>
       </c>
       <c r="O491" t="n">
-        <v>3599347.437254272</v>
+        <v>1473091.781202868</v>
       </c>
       <c r="P491" t="n">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="Q491" t="n">
-        <v>4338000</v>
+        <v>1896200</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>C851</t>
+          <t>C852</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>2021071411227</v>
+        <v>2021071411203</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FIESTA</t>
+          <t>GLOBO BUQUET LABIOS</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -22065,7 +22060,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>499</v>
+        <v>650</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -22074,33 +22069,33 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>499</v>
+        <v>650</v>
       </c>
       <c r="N492" t="n">
-        <v>2952.0877378815</v>
+        <v>3167.0258208955</v>
       </c>
       <c r="O492" t="n">
-        <v>1473091.781202868</v>
+        <v>2058566.783582075</v>
       </c>
       <c r="P492" t="n">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="Q492" t="n">
-        <v>1896200</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>C852</t>
+          <t>C854</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2021071411203</v>
+        <v>2021071411210</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>GLOBO BUQUET LABIOS</t>
+          <t>GLOBO BUQUET CORAZON Y Y ESTRELLA</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -22109,7 +22104,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>650</v>
+        <v>1367</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -22118,33 +22113,30 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>650</v>
+        <v>1367</v>
       </c>
       <c r="N493" t="n">
-        <v>3167.0258208955</v>
+        <v>2307.69</v>
       </c>
       <c r="O493" t="n">
-        <v>2058566.783582075</v>
+        <v>3154612.23</v>
       </c>
       <c r="P493" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="Q493" t="n">
-        <v>2600000</v>
+        <v>4101000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>C854</t>
-        </is>
-      </c>
-      <c r="B494" t="n">
-        <v>2021071411210</v>
+          <t>C855</t>
+        </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>GLOBO BUQUET CORAZON Y Y ESTRELLA</t>
+          <t>GLOBOS BUQUET CERVEZA</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -22153,7 +22145,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>1367</v>
+        <v>955</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -22162,30 +22154,33 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>1367</v>
+        <v>955</v>
       </c>
       <c r="N494" t="n">
-        <v>2307.69</v>
+        <v>2129.8331714024</v>
       </c>
       <c r="O494" t="n">
-        <v>3154612.23</v>
+        <v>2033990.678689292</v>
       </c>
       <c r="P494" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="Q494" t="n">
-        <v>4101000</v>
+        <v>2578500</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>C855</t>
-        </is>
+          <t>C856</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>2021071411272</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>GLOBOS BUQUET CERVEZA</t>
+          <t>GLOBO BOUQUET</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -22194,7 +22189,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>955</v>
+        <v>1010</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -22203,33 +22198,33 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>955</v>
+        <v>1010</v>
       </c>
       <c r="N495" t="n">
-        <v>2129.8331714024</v>
+        <v>2106.9511336406</v>
       </c>
       <c r="O495" t="n">
-        <v>2033990.678689292</v>
+        <v>2128020.644977006</v>
       </c>
       <c r="P495" t="n">
         <v>2700</v>
       </c>
       <c r="Q495" t="n">
-        <v>2578500</v>
+        <v>2727000</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>C856</t>
+          <t>C860</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>2021071411272</v>
+        <v>2021071411173</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET</t>
+          <t>GLOBO BOUQUET FELIZ CIMPLEANOS</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -22238,7 +22233,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>1010</v>
+        <v>820</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -22247,33 +22242,33 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>1010</v>
+        <v>820</v>
       </c>
       <c r="N496" t="n">
-        <v>2106.9511336406</v>
+        <v>2988.7998653199</v>
       </c>
       <c r="O496" t="n">
-        <v>2128020.644977006</v>
+        <v>2450815.889562318</v>
       </c>
       <c r="P496" t="n">
-        <v>2700</v>
+        <v>3800</v>
       </c>
       <c r="Q496" t="n">
-        <v>2727000</v>
+        <v>3116000</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>C860</t>
+          <t>C862</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>2021071411173</v>
+        <v>2021071411319</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET FELIZ CIMPLEANOS</t>
+          <t>GLOBO BOUQUET MENSAJE</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -22282,7 +22277,7 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>820</v>
+        <v>746</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -22291,33 +22286,30 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>820</v>
+        <v>746</v>
       </c>
       <c r="N497" t="n">
-        <v>2988.7998653199</v>
+        <v>1769.23</v>
       </c>
       <c r="O497" t="n">
-        <v>2450815.889562318</v>
+        <v>1319845.58</v>
       </c>
       <c r="P497" t="n">
-        <v>3800</v>
+        <v>2300</v>
       </c>
       <c r="Q497" t="n">
-        <v>3116000</v>
+        <v>1715800</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>C862</t>
-        </is>
-      </c>
-      <c r="B498" t="n">
-        <v>2021071411319</v>
+          <t>C863</t>
+        </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET MENSAJE</t>
+          <t>GLOBOS BOUQUET FELIZ DIA</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -22326,7 +22318,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>746</v>
+        <v>436</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -22335,30 +22327,30 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>746</v>
+        <v>436</v>
       </c>
       <c r="N498" t="n">
-        <v>1769.23</v>
+        <v>5497.1753111433</v>
       </c>
       <c r="O498" t="n">
-        <v>1319845.58</v>
+        <v>2396768.435658479</v>
       </c>
       <c r="P498" t="n">
-        <v>2300</v>
+        <v>6500</v>
       </c>
       <c r="Q498" t="n">
-        <v>1715800</v>
+        <v>2834000</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>C863</t>
+          <t>C866</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET FELIZ DIA</t>
+          <t>YOYO SURTIDO</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -22367,7 +22359,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>436</v>
+        <v>5</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -22376,30 +22368,33 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>436</v>
+        <v>5</v>
       </c>
       <c r="N499" t="n">
-        <v>5497.1753111433</v>
+        <v>1176.57</v>
       </c>
       <c r="O499" t="n">
-        <v>2396768.435658479</v>
+        <v>5882.849999999999</v>
       </c>
       <c r="P499" t="n">
-        <v>6500</v>
+        <v>1900</v>
       </c>
       <c r="Q499" t="n">
-        <v>2834000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>C866</t>
-        </is>
+          <t>C887</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>6920210213929</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>YOYO SURTIDO</t>
+          <t>BALON FOOTBALL SURTIDO #2</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -22408,7 +22403,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -22417,33 +22412,33 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="N500" t="n">
-        <v>1176.57</v>
+        <v>3181.9</v>
       </c>
       <c r="O500" t="n">
-        <v>5882.849999999999</v>
+        <v>248188.2</v>
       </c>
       <c r="P500" t="n">
-        <v>1900</v>
+        <v>5100</v>
       </c>
       <c r="Q500" t="n">
-        <v>9500</v>
+        <v>397800</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>C887</t>
+          <t>C890</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>6920210213929</v>
+        <v>6913545113699</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL SURTIDO #2</t>
+          <t>CORTINA FEST</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -22452,7 +22447,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>78</v>
+        <v>5129</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -22461,33 +22456,33 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>78</v>
+        <v>5129</v>
       </c>
       <c r="N501" t="n">
-        <v>3181.9</v>
+        <v>1794.287966297</v>
       </c>
       <c r="O501" t="n">
-        <v>248188.2</v>
+        <v>9202902.979137313</v>
       </c>
       <c r="P501" t="n">
-        <v>5100</v>
+        <v>1600</v>
       </c>
       <c r="Q501" t="n">
-        <v>397800</v>
+        <v>8206400</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>C890</t>
+          <t>C891</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>6913545113699</v>
+        <v>1233031565180</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>CORTINA FEST</t>
+          <t>TOP PASTEL NUMERO</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -22496,7 +22491,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>5129</v>
+        <v>481</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -22505,33 +22500,33 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>5129</v>
+        <v>481</v>
       </c>
       <c r="N502" t="n">
-        <v>1794.287968053</v>
+        <v>2181.4247724621</v>
       </c>
       <c r="O502" t="n">
-        <v>9202902.988143837</v>
+        <v>1049265.31555427</v>
       </c>
       <c r="P502" t="n">
-        <v>1600</v>
+        <v>2900</v>
       </c>
       <c r="Q502" t="n">
-        <v>8206400</v>
+        <v>1394900</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>C891</t>
+          <t>C893</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>1233031565180</v>
+        <v>6910050641082</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>TOP PASTEL NUMERO</t>
+          <t>CUBO MAGICO</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -22540,7 +22535,7 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>481</v>
+        <v>1440</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -22549,33 +22544,33 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>481</v>
+        <v>1440</v>
       </c>
       <c r="N503" t="n">
-        <v>2181.4247724621</v>
+        <v>1727.31</v>
       </c>
       <c r="O503" t="n">
-        <v>1049265.31555427</v>
+        <v>2487326.4</v>
       </c>
       <c r="P503" t="n">
-        <v>2900</v>
+        <v>2850</v>
       </c>
       <c r="Q503" t="n">
-        <v>1394900</v>
+        <v>4104000</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>C893</t>
+          <t>C895</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>6910050641082</v>
+        <v>6913545115815</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CUBO MAGICO</t>
+          <t>CORTINA FESTIN TORNASOL</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -22584,7 +22579,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>1440</v>
+        <v>68</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -22593,33 +22588,33 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>1440</v>
+        <v>68</v>
       </c>
       <c r="N504" t="n">
-        <v>1727.31</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O504" t="n">
-        <v>2487326.4</v>
+        <v>192455.310119046</v>
       </c>
       <c r="P504" t="n">
-        <v>2850</v>
+        <v>2400</v>
       </c>
       <c r="Q504" t="n">
-        <v>4104000</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>C895</t>
+          <t>C902</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>6913545115815</v>
+        <v>2021071411180</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CORTINA FESTIN TORNASOL</t>
+          <t>GLOBOS BOUQUET NINONINA</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -22628,7 +22623,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -22637,33 +22632,30 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="N505" t="n">
-        <v>2830.2251488095</v>
+        <v>2153.85</v>
       </c>
       <c r="O505" t="n">
-        <v>192455.310119046</v>
+        <v>21538.5</v>
       </c>
       <c r="P505" t="n">
-        <v>2400</v>
+        <v>2800</v>
       </c>
       <c r="Q505" t="n">
-        <v>163200</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>C902</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>2021071411180</v>
+          <t>C905</t>
+        </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>GLOBOS BOUQUET NINONINA</t>
+          <t>GLOBO BOUQUET CORAZON</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -22672,7 +22664,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>10</v>
+        <v>1119</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -22681,30 +22673,33 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>10</v>
+        <v>1119</v>
       </c>
       <c r="N506" t="n">
-        <v>2153.85</v>
+        <v>2564.431520417</v>
       </c>
       <c r="O506" t="n">
-        <v>21538.5</v>
+        <v>2869598.871346623</v>
       </c>
       <c r="P506" t="n">
-        <v>2800</v>
+        <v>3300</v>
       </c>
       <c r="Q506" t="n">
-        <v>28000</v>
+        <v>3692700</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>C905</t>
-        </is>
+          <t>C91</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>6803012120018</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET CORAZON</t>
+          <t>GLOBO BOUQUET SURTIDO</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -22713,7 +22708,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>1119</v>
+        <v>1329</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -22722,33 +22717,30 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>1119</v>
+        <v>1329</v>
       </c>
       <c r="N507" t="n">
-        <v>2564.431520417</v>
+        <v>2523.3377457627</v>
       </c>
       <c r="O507" t="n">
-        <v>2869598.871346623</v>
+        <v>3353515.864118628</v>
       </c>
       <c r="P507" t="n">
-        <v>3300</v>
+        <v>2800</v>
       </c>
       <c r="Q507" t="n">
-        <v>3692700</v>
+        <v>3721200</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>C91</t>
-        </is>
-      </c>
-      <c r="B508" t="n">
-        <v>6803012120018</v>
+          <t>C911</t>
+        </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET SURTIDO</t>
+          <t>GLOBO BOUQUET I LOVE YOU</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -22757,7 +22749,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>1329</v>
+        <v>940</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -22766,30 +22758,30 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>1329</v>
+        <v>940</v>
       </c>
       <c r="N508" t="n">
-        <v>2523.3377457627</v>
+        <v>2076.92</v>
       </c>
       <c r="O508" t="n">
-        <v>3353515.864118628</v>
+        <v>1952304.8</v>
       </c>
       <c r="P508" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="Q508" t="n">
-        <v>3721200</v>
+        <v>2538000</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>C911</t>
+          <t>C915</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET I LOVE YOU</t>
+          <t>GLOBOS M¡SCARAS EN PIJAMAS</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -22798,7 +22790,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>940</v>
+        <v>4386</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -22807,30 +22799,30 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>940</v>
+        <v>4386</v>
       </c>
       <c r="N509" t="n">
-        <v>2076.92</v>
+        <v>923.08</v>
       </c>
       <c r="O509" t="n">
-        <v>1952304.8</v>
+        <v>4048628.88</v>
       </c>
       <c r="P509" t="n">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="Q509" t="n">
-        <v>2538000</v>
+        <v>5263200</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>C915</t>
+          <t>C917</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>GLOBOS M¡SCARAS EN PIJAMAS</t>
+          <t>GLOBO BOUQUET PRINCESA</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -22839,7 +22831,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>4386</v>
+        <v>1130</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -22848,30 +22840,30 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>4386</v>
+        <v>1130</v>
       </c>
       <c r="N510" t="n">
-        <v>923.08</v>
+        <v>2271.5972749591</v>
       </c>
       <c r="O510" t="n">
-        <v>4048628.88</v>
+        <v>2566904.920703783</v>
       </c>
       <c r="P510" t="n">
-        <v>1200</v>
+        <v>2900</v>
       </c>
       <c r="Q510" t="n">
-        <v>5263200</v>
+        <v>3277000</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>C917</t>
+          <t>C919</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET PRINCESA</t>
+          <t>GLOBOS RATN</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -22880,7 +22872,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>1130</v>
+        <v>6195</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -22889,30 +22881,33 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>1130</v>
+        <v>6195</v>
       </c>
       <c r="N511" t="n">
-        <v>2271.5972749591</v>
+        <v>1230.77</v>
       </c>
       <c r="O511" t="n">
-        <v>2566904.920703783</v>
+        <v>7624620.149999999</v>
       </c>
       <c r="P511" t="n">
-        <v>2900</v>
+        <v>1600</v>
       </c>
       <c r="Q511" t="n">
-        <v>3277000</v>
+        <v>9912000</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>C919</t>
-        </is>
+          <t>C92</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>6803012120100</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>GLOBOS RATN</t>
+          <t>GLOBO BOUQUET SURTIDO</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -22921,7 +22916,7 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>6195</v>
+        <v>427</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -22930,33 +22925,33 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>6195</v>
+        <v>427</v>
       </c>
       <c r="N512" t="n">
-        <v>1230.77</v>
+        <v>3153.2320521654</v>
       </c>
       <c r="O512" t="n">
-        <v>7624620.149999999</v>
+        <v>1346430.086274626</v>
       </c>
       <c r="P512" t="n">
-        <v>1600</v>
+        <v>3300</v>
       </c>
       <c r="Q512" t="n">
-        <v>9912000</v>
+        <v>1409100</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>C92</t>
+          <t>C930</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>6803012120100</v>
+        <v>6920202109308</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET SURTIDO</t>
+          <t>GLOBO BOUQUET BASE</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -22965,7 +22960,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>427</v>
+        <v>1</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -22974,33 +22969,33 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>427</v>
+        <v>1</v>
       </c>
       <c r="N513" t="n">
-        <v>3153.2320521654</v>
+        <v>6035.6650381679</v>
       </c>
       <c r="O513" t="n">
-        <v>1346430.086274626</v>
+        <v>6035.6650381679</v>
       </c>
       <c r="P513" t="n">
-        <v>3300</v>
+        <v>8500</v>
       </c>
       <c r="Q513" t="n">
-        <v>1409100</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>C930</t>
+          <t>C935</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>6920202109308</v>
+        <v>6920202109353</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET BASE</t>
+          <t>GLOBO BOUQUET</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -23009,7 +23004,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -23018,33 +23013,33 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N514" t="n">
-        <v>6035.6650381679</v>
+        <v>3683.6327400468</v>
       </c>
       <c r="O514" t="n">
-        <v>6035.6650381679</v>
+        <v>18418.163700234</v>
       </c>
       <c r="P514" t="n">
-        <v>8500</v>
+        <v>3600</v>
       </c>
       <c r="Q514" t="n">
-        <v>8500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>C935</t>
+          <t>C953</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>6920202109353</v>
+        <v>6952365109536</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET</t>
+          <t>GLOBO ARCOIRIS NUBE</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -23053,7 +23048,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23062,33 +23057,30 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="N515" t="n">
-        <v>3683.6327400468</v>
+        <v>923.08</v>
       </c>
       <c r="O515" t="n">
-        <v>18418.163700234</v>
+        <v>110769.6</v>
       </c>
       <c r="P515" t="n">
-        <v>3600</v>
+        <v>1200</v>
       </c>
       <c r="Q515" t="n">
-        <v>18000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>C953</t>
-        </is>
-      </c>
-      <c r="B516" t="n">
-        <v>6952365109536</v>
+          <t>C956</t>
+        </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>GLOBO ARCOIRIS NUBE</t>
+          <t>PABLO GLOBO 40CM</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -23097,7 +23089,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>120</v>
+        <v>2985</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23106,30 +23098,30 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>120</v>
+        <v>2985</v>
       </c>
       <c r="N516" t="n">
-        <v>923.08</v>
+        <v>264</v>
       </c>
       <c r="O516" t="n">
-        <v>110769.6</v>
+        <v>788040</v>
       </c>
       <c r="P516" t="n">
-        <v>1200</v>
+        <v>390</v>
       </c>
       <c r="Q516" t="n">
-        <v>144000</v>
+        <v>1164150</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>C956</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PABLO GLOBO 40CM</t>
+          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -23138,7 +23130,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>2985</v>
+        <v>1</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23147,30 +23139,30 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>2985</v>
+        <v>1</v>
       </c>
       <c r="N517" t="n">
-        <v>264</v>
+        <v>4985.40591133</v>
       </c>
       <c r="O517" t="n">
-        <v>788040</v>
+        <v>4985.40591133</v>
       </c>
       <c r="P517" t="n">
-        <v>390</v>
+        <v>7900</v>
       </c>
       <c r="Q517" t="n">
-        <v>1164150</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>CM2199</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
+          <t>JUEGO DE MESA ASTRONAUTA</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -23179,7 +23171,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -23188,39 +23180,44 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="N518" t="n">
-        <v>4985.40591133</v>
+        <v>7589.9229901269</v>
       </c>
       <c r="O518" t="n">
-        <v>4985.40591133</v>
+        <v>3187767.655853298</v>
       </c>
       <c r="P518" t="n">
-        <v>7900</v>
+        <v>10900</v>
       </c>
       <c r="Q518" t="n">
-        <v>7900</v>
+        <v>4578000</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>CM2199</t>
+          <t>FG024</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>JUEGO DE MESA ASTRONAUTA</t>
+          <t>CARRO MEZCLADOR DINOSAURIO 6588-2</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J519" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -23229,35 +23226,35 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>420</v>
+        <v>1</v>
       </c>
       <c r="N519" t="n">
-        <v>7589.9229901269</v>
+        <v>15482.98</v>
       </c>
       <c r="O519" t="n">
-        <v>3187767.655853298</v>
+        <v>15482.98</v>
       </c>
       <c r="P519" t="n">
-        <v>10900</v>
+        <v>18500</v>
       </c>
       <c r="Q519" t="n">
-        <v>4578000</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>FG024</t>
+          <t>FG034</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>CARRO MEZCLADOR DINOSAURIO 6588-2</t>
+          <t>CHILLONES X6 PELOTAS 2502-18</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -23278,32 +23275,32 @@
         <v>1</v>
       </c>
       <c r="N520" t="n">
-        <v>15482.98</v>
+        <v>7384.25</v>
       </c>
       <c r="O520" t="n">
-        <v>15482.98</v>
+        <v>7384.25</v>
       </c>
       <c r="P520" t="n">
-        <v>18500</v>
+        <v>9500</v>
       </c>
       <c r="Q520" t="n">
-        <v>18500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>FG034</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>CHILLONES X6 PELOTAS 2502-18</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -23312,7 +23309,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -23321,35 +23318,35 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="N521" t="n">
-        <v>7384.25</v>
+        <v>2644.9</v>
       </c>
       <c r="O521" t="n">
-        <v>7384.25</v>
+        <v>904555.8</v>
       </c>
       <c r="P521" t="n">
-        <v>9500</v>
+        <v>3900</v>
       </c>
       <c r="Q521" t="n">
-        <v>9500</v>
+        <v>1333800</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -23358,7 +23355,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>342</v>
+        <v>60</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -23367,44 +23364,44 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>342</v>
+        <v>60</v>
       </c>
       <c r="N522" t="n">
-        <v>2644.9</v>
+        <v>1952.66</v>
       </c>
       <c r="O522" t="n">
-        <v>904555.8</v>
+        <v>117159.6</v>
       </c>
       <c r="P522" t="n">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="Q522" t="n">
-        <v>1333800</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>GPH18148/VE</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>CICCIOBELLO ARRE ARRE</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J523" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -23413,44 +23410,49 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="N523" t="n">
-        <v>1952.66</v>
+        <v>21664.371538462</v>
       </c>
       <c r="O523" t="n">
-        <v>117159.6</v>
+        <v>108321.85769231</v>
       </c>
       <c r="P523" t="n">
-        <v>3500</v>
+        <v>30000</v>
       </c>
       <c r="Q523" t="n">
-        <v>210000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>GPH18148/VE</t>
+          <t>MG29023</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>MG29023</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>CICCIOBELLO ARRE ARRE</t>
+          <t>MAQUILLAJE SIRENA CON BRILLOS Y SOMBRAS MG29023</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -23459,69 +23461,18 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N524" t="n">
-        <v>21664.371538462</v>
+        <v>2932.64</v>
       </c>
       <c r="O524" t="n">
-        <v>108321.85769231</v>
+        <v>8797.92</v>
       </c>
       <c r="P524" t="n">
-        <v>30000</v>
+        <v>10900</v>
       </c>
       <c r="Q524" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>MG29023</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>MG29023</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>MAQUILLAJE SIRENA CON BRILLOS Y SOMBRAS MG29023</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>MUÑECA</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J525" t="n">
-        <v>3</v>
-      </c>
-      <c r="K525" t="n">
-        <v>0</v>
-      </c>
-      <c r="L525" t="n">
-        <v>0</v>
-      </c>
-      <c r="M525" t="n">
-        <v>3</v>
-      </c>
-      <c r="N525" t="n">
-        <v>2932.64</v>
-      </c>
-      <c r="O525" t="n">
-        <v>8797.92</v>
-      </c>
-      <c r="P525" t="n">
-        <v>10900</v>
-      </c>
-      <c r="Q525" t="n">
         <v>32700</v>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -5827,10 +5827,10 @@
         <v>64</v>
       </c>
       <c r="N129" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O129" t="n">
-        <v>313019.5231565952</v>
+        <v>313019.5231604928</v>
       </c>
       <c r="P129" t="n">
         <v>8200</v>
@@ -7131,10 +7131,10 @@
         <v>809</v>
       </c>
       <c r="N158" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O158" t="n">
-        <v>3537118.530540232</v>
+        <v>3537118.53063181</v>
       </c>
       <c r="P158" t="n">
         <v>7500</v>
@@ -8317,10 +8317,10 @@
         <v>1152</v>
       </c>
       <c r="N185" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O185" t="n">
-        <v>1878824.305161331</v>
+        <v>1878824.317573901</v>
       </c>
       <c r="P185" t="n">
         <v>2500</v>
@@ -8409,10 +8409,10 @@
         <v>4608</v>
       </c>
       <c r="N187" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O187" t="n">
-        <v>7143293.520303207</v>
+        <v>7143293.552572109</v>
       </c>
       <c r="P187" t="n">
         <v>2500</v>
@@ -8455,10 +8455,10 @@
         <v>1632</v>
       </c>
       <c r="N188" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O188" t="n">
-        <v>3922533.930662102</v>
+        <v>3922533.96868656</v>
       </c>
       <c r="P188" t="n">
         <v>3500</v>
@@ -9918,10 +9918,10 @@
         <v>216</v>
       </c>
       <c r="N222" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O222" t="n">
-        <v>543719.5199999999</v>
+        <v>549002.6246477808</v>
       </c>
       <c r="P222" t="n">
         <v>4200</v>
@@ -12950,10 +12950,10 @@
         <v>399</v>
       </c>
       <c r="N292" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O292" t="n">
-        <v>2082050.057115149</v>
+        <v>2082050.057704273</v>
       </c>
       <c r="P292" t="n">
         <v>8500</v>
@@ -12996,10 +12996,10 @@
         <v>206</v>
       </c>
       <c r="N293" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="O293" t="n">
-        <v>328571.9199642282</v>
+        <v>328571.9174134744</v>
       </c>
       <c r="P293" t="n">
         <v>2600</v>
@@ -17587,10 +17587,10 @@
         <v>4224</v>
       </c>
       <c r="N393" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O393" t="n">
-        <v>6403747.845162202</v>
+        <v>6411315.796131418</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
@@ -17817,10 +17817,10 @@
         <v>1152</v>
       </c>
       <c r="N398" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O398" t="n">
-        <v>2077074.302354957</v>
+        <v>2077074.309429734</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -19426,10 +19426,10 @@
         <v>7572</v>
       </c>
       <c r="N433" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O433" t="n">
-        <v>3916929.593848631</v>
+        <v>3923151.914662397</v>
       </c>
       <c r="P433" t="n">
         <v>900</v>
@@ -19558,10 +19558,10 @@
         <v>15368</v>
       </c>
       <c r="N436" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O436" t="n">
-        <v>10815921.89636141</v>
+        <v>10815921.84414756</v>
       </c>
       <c r="P436" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.955685704</v>
+        <v>2788835.94913194</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -5151,10 +5151,10 @@
         <v>144</v>
       </c>
       <c r="N114" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O114" t="n">
-        <v>553193.9798399999</v>
+        <v>553193.9819458416</v>
       </c>
       <c r="P114" t="n">
         <v>6900</v>
@@ -8014,10 +8014,10 @@
         <v>1152</v>
       </c>
       <c r="N178" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O178" t="n">
-        <v>1878824.343751949</v>
+        <v>1878824.350631347</v>
       </c>
       <c r="P178" t="n">
         <v>2500</v>
@@ -8152,10 +8152,10 @@
         <v>1632</v>
       </c>
       <c r="N181" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O181" t="n">
-        <v>3922534.346455066</v>
+        <v>3922534.420597152</v>
       </c>
       <c r="P181" t="n">
         <v>3500</v>
@@ -18809,10 +18809,10 @@
         <v>15368</v>
       </c>
       <c r="N419" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O419" t="n">
-        <v>10815921.69184699</v>
+        <v>10815921.68135403</v>
       </c>
       <c r="P419" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -798,10 +798,10 @@
         <v>60</v>
       </c>
       <c r="N10" t="n">
-        <v>27000</v>
+        <v>27035.809018568</v>
       </c>
       <c r="O10" t="n">
-        <v>1620000</v>
+        <v>1622148.54111408</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3079710145</v>
+        <v>1811.3080365297</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.43478261</v>
+        <v>326035.446575346</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464515243</v>
+        <v>3376.746444689</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1341719292</v>
+        <v>823926.1325041159</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8549913345</v>
+        <v>6272.8550437828</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.678128252</v>
+        <v>1354936.689457085</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2458,10 +2458,10 @@
         <v>152</v>
       </c>
       <c r="N52" t="n">
-        <v>3910.6280306346</v>
+        <v>3910.6280263158</v>
       </c>
       <c r="O52" t="n">
-        <v>594415.4606564592</v>
+        <v>594415.4600000016</v>
       </c>
       <c r="P52" t="n">
         <v>9100</v>
@@ -3019,10 +3019,10 @@
         <v>111</v>
       </c>
       <c r="N65" t="n">
-        <v>141416.88457516</v>
+        <v>141416.88459016</v>
       </c>
       <c r="O65" t="n">
-        <v>15697274.18784276</v>
+        <v>15697274.18950776</v>
       </c>
       <c r="P65" t="n">
         <v>251900</v>
@@ -3061,10 +3061,10 @@
         <v>27</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20172727</v>
+        <v>200072.20183486</v>
       </c>
       <c r="O66" t="n">
-        <v>5401949.44663629</v>
+        <v>5401949.44954122</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.79826087</v>
+        <v>174389.79954545</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.78956522</v>
+        <v>1046338.7972727</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874114441</v>
+        <v>61666.874148352</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.299727486</v>
+        <v>5241684.30260992</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -3892,10 +3892,10 @@
         <v>1440</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2145482866</v>
+        <v>1950.2145369407</v>
       </c>
       <c r="O85" t="n">
-        <v>2808308.949532704</v>
+        <v>2808308.933194608</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4020,10 +4020,10 @@
         <v>200</v>
       </c>
       <c r="N88" t="n">
-        <v>4937.3101649175</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O88" t="n">
-        <v>987462.0329834999</v>
+        <v>987462.0330827</v>
       </c>
       <c r="P88" t="n">
         <v>7500</v>
@@ -4655,10 +4655,10 @@
         <v>101</v>
       </c>
       <c r="N103" t="n">
-        <v>17207.41</v>
+        <v>17234.854035088</v>
       </c>
       <c r="O103" t="n">
-        <v>1737948.41</v>
+        <v>1740720.257543888</v>
       </c>
       <c r="P103" t="n">
         <v>20000</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2555084555</v>
+        <v>2582.2554768392</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.94913194</v>
+        <v>2788835.914986336</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8960524399</v>
+        <v>5216.8960380117</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.707530931</v>
+        <v>9901668.680146206</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608305026</v>
+        <v>3158.860831485</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.51050537</v>
+        <v>19894505.51669253</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5243,10 +5243,10 @@
         <v>224</v>
       </c>
       <c r="N116" t="n">
-        <v>2694.8231638418</v>
+        <v>2694.8231444759</v>
       </c>
       <c r="O116" t="n">
-        <v>603640.3887005632</v>
+        <v>603640.3843626016</v>
       </c>
       <c r="P116" t="n">
         <v>4900</v>
@@ -5384,10 +5384,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>8796</v>
+        <v>8807.6968085106</v>
       </c>
       <c r="O119" t="n">
-        <v>1266624</v>
+        <v>1268308.340425526</v>
       </c>
       <c r="P119" t="n">
         <v>14900</v>
@@ -5517,10 +5517,10 @@
         <v>3024</v>
       </c>
       <c r="N122" t="n">
-        <v>3795.7100075887</v>
+        <v>3795.7100075916</v>
       </c>
       <c r="O122" t="n">
-        <v>11478227.06294823</v>
+        <v>11478227.062957</v>
       </c>
       <c r="P122" t="n">
         <v>6200</v>
@@ -5655,10 +5655,10 @@
         <v>64</v>
       </c>
       <c r="N125" t="n">
-        <v>4890.9300493827</v>
+        <v>4890.930049597</v>
       </c>
       <c r="O125" t="n">
-        <v>313019.5231604928</v>
+        <v>313019.523174208</v>
       </c>
       <c r="P125" t="n">
         <v>8200</v>
@@ -5750,10 +5750,10 @@
         <v>95</v>
       </c>
       <c r="N127" t="n">
-        <v>5888</v>
+        <v>5946.1052631579</v>
       </c>
       <c r="O127" t="n">
-        <v>559360</v>
+        <v>564880.0000000005</v>
       </c>
       <c r="P127" t="n">
         <v>9500</v>
@@ -6239,10 +6239,10 @@
         <v>168</v>
       </c>
       <c r="N138" t="n">
-        <v>3594.2536883629</v>
+        <v>3594.253608522</v>
       </c>
       <c r="O138" t="n">
-        <v>603834.6196449671</v>
+        <v>603834.606231696</v>
       </c>
       <c r="P138" t="n">
         <v>6500</v>
@@ -6464,10 +6464,10 @@
         <v>361</v>
       </c>
       <c r="N143" t="n">
-        <v>14822.378847539</v>
+        <v>14822.378837068</v>
       </c>
       <c r="O143" t="n">
-        <v>5350878.763961579</v>
+        <v>5350878.760181548</v>
       </c>
       <c r="P143" t="n">
         <v>24900</v>
@@ -6640,10 +6640,10 @@
         <v>180</v>
       </c>
       <c r="N147" t="n">
-        <v>2665.4</v>
+        <v>2667.0463248919</v>
       </c>
       <c r="O147" t="n">
-        <v>479772</v>
+        <v>480068.338480542</v>
       </c>
       <c r="P147" t="n">
         <v>20900</v>
@@ -6823,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600136054</v>
+        <v>3041.6600136893</v>
       </c>
       <c r="O151" t="n">
-        <v>237249.4810612212</v>
+        <v>237249.4810677654</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.2107921642</v>
+        <v>4372.5234503719</v>
       </c>
       <c r="O152" t="n">
-        <v>3537118.530860838</v>
+        <v>3537371.471350867</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7259,10 +7259,10 @@
         <v>4579</v>
       </c>
       <c r="N161" t="n">
-        <v>17472.91</v>
+        <v>17473.953844316</v>
       </c>
       <c r="O161" t="n">
-        <v>80008454.89</v>
+        <v>80013234.65312298</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -7347,10 +7347,10 @@
         <v>5378</v>
       </c>
       <c r="N163" t="n">
-        <v>1530.63</v>
+        <v>1530.7162764218</v>
       </c>
       <c r="O163" t="n">
-        <v>8231728.140000001</v>
+        <v>8232192.134596441</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8014,10 +8014,10 @@
         <v>1152</v>
       </c>
       <c r="N178" t="n">
-        <v>1630.9239154786</v>
+        <v>1630.9239476386</v>
       </c>
       <c r="O178" t="n">
-        <v>1878824.350631347</v>
+        <v>1878824.387679667</v>
       </c>
       <c r="P178" t="n">
         <v>2500</v>
@@ -8060,10 +8060,10 @@
         <v>384</v>
       </c>
       <c r="N179" t="n">
-        <v>1690.5944611529</v>
+        <v>1690.5922846782</v>
       </c>
       <c r="O179" t="n">
-        <v>649188.2730827136</v>
+        <v>649187.4373164289</v>
       </c>
       <c r="P179" t="n">
         <v>2900</v>
@@ -8106,10 +8106,10 @@
         <v>4608</v>
       </c>
       <c r="N180" t="n">
-        <v>1550.1939407455</v>
+        <v>1550.1940319426</v>
       </c>
       <c r="O180" t="n">
-        <v>7143293.678955263</v>
+        <v>7143294.099191501</v>
       </c>
       <c r="P180" t="n">
         <v>2500</v>
@@ -8152,10 +8152,10 @@
         <v>1632</v>
       </c>
       <c r="N181" t="n">
-        <v>2403.513738111</v>
+        <v>2403.5140171519</v>
       </c>
       <c r="O181" t="n">
-        <v>3922534.420597152</v>
+        <v>3922534.875991901</v>
       </c>
       <c r="P181" t="n">
         <v>3500</v>
@@ -8987,10 +8987,10 @@
         <v>1415</v>
       </c>
       <c r="N200" t="n">
-        <v>4196.8725326298</v>
+        <v>4196.8725382689</v>
       </c>
       <c r="O200" t="n">
-        <v>5938574.633671167</v>
+        <v>5938574.641650493</v>
       </c>
       <c r="P200" t="n">
         <v>5900</v>
@@ -9402,10 +9402,10 @@
         <v>864</v>
       </c>
       <c r="N210" t="n">
-        <v>2567</v>
+        <v>2569.7269830028</v>
       </c>
       <c r="O210" t="n">
-        <v>2217888</v>
+        <v>2220244.113314419</v>
       </c>
       <c r="P210" t="n">
         <v>4500</v>
@@ -9738,10 +9738,10 @@
         <v>1254</v>
       </c>
       <c r="N218" t="n">
-        <v>880.32958602536</v>
+        <v>880.32962749339</v>
       </c>
       <c r="O218" t="n">
-        <v>1103933.300875801</v>
+        <v>1103933.352876711</v>
       </c>
       <c r="P218" t="n">
         <v>1200</v>
@@ -10222,10 +10222,10 @@
         <v>150</v>
       </c>
       <c r="N229" t="n">
-        <v>4285.1957990868</v>
+        <v>4285.1958525346</v>
       </c>
       <c r="O229" t="n">
-        <v>642779.36986302</v>
+        <v>642779.37788019</v>
       </c>
       <c r="P229" t="n">
         <v>6900</v>
@@ -10353,10 +10353,10 @@
         <v>248</v>
       </c>
       <c r="N232" t="n">
-        <v>12132.858122744</v>
+        <v>12132.858109091</v>
       </c>
       <c r="O232" t="n">
-        <v>3008948.814440512</v>
+        <v>3008948.811054568</v>
       </c>
       <c r="P232" t="n">
         <v>15900</v>
@@ -10686,10 +10686,10 @@
         <v>1</v>
       </c>
       <c r="N240" t="n">
-        <v>30244.600034742</v>
+        <v>30244.600034762</v>
       </c>
       <c r="O240" t="n">
-        <v>30244.600034742</v>
+        <v>30244.600034762</v>
       </c>
       <c r="P240" t="n">
         <v>48900</v>
@@ -11459,10 +11459,10 @@
         <v>34</v>
       </c>
       <c r="N258" t="n">
-        <v>27123.765142315</v>
+        <v>27123.765105163</v>
       </c>
       <c r="O258" t="n">
-        <v>922208.01483871</v>
+        <v>922208.0135755419</v>
       </c>
       <c r="P258" t="n">
         <v>44500</v>
@@ -11720,10 +11720,10 @@
         <v>480</v>
       </c>
       <c r="N264" t="n">
-        <v>7969.9501675552</v>
+        <v>7982.1180305344</v>
       </c>
       <c r="O264" t="n">
-        <v>3825576.080426496</v>
+        <v>3831416.654656512</v>
       </c>
       <c r="P264" t="n">
         <v>12900</v>
@@ -11802,10 +11802,10 @@
         <v>12</v>
       </c>
       <c r="N266" t="n">
-        <v>9994.710151515201</v>
+        <v>10148.474923077</v>
       </c>
       <c r="O266" t="n">
-        <v>119936.5218181824</v>
+        <v>121781.699076924</v>
       </c>
       <c r="P266" t="n">
         <v>20800</v>
@@ -12431,10 +12431,10 @@
         <v>399</v>
       </c>
       <c r="N280" t="n">
-        <v>5218.1705736636</v>
+        <v>5218.1705744125</v>
       </c>
       <c r="O280" t="n">
-        <v>2082050.058891776</v>
+        <v>2082050.059190588</v>
       </c>
       <c r="P280" t="n">
         <v>8500</v>
@@ -12891,10 +12891,10 @@
         <v>108</v>
       </c>
       <c r="N290" t="n">
-        <v>14380</v>
+        <v>14447.670588235</v>
       </c>
       <c r="O290" t="n">
-        <v>1553040</v>
+        <v>1560348.42352938</v>
       </c>
       <c r="P290" t="n">
         <v>23000</v>
@@ -13397,10 +13397,10 @@
         <v>1145</v>
       </c>
       <c r="N301" t="n">
-        <v>1778.4726787358</v>
+        <v>1778.4726973583</v>
       </c>
       <c r="O301" t="n">
-        <v>2036351.217152491</v>
+        <v>2036351.238475253</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -14271,10 +14271,10 @@
         <v>36</v>
       </c>
       <c r="N320" t="n">
-        <v>22942</v>
+        <v>23400.84</v>
       </c>
       <c r="O320" t="n">
-        <v>825912</v>
+        <v>842430.24</v>
       </c>
       <c r="P320" t="n">
         <v>36900</v>
@@ -14361,10 +14361,10 @@
         <v>864</v>
       </c>
       <c r="N322" t="n">
-        <v>2328.1186963238</v>
+        <v>2328.1186869944</v>
       </c>
       <c r="O322" t="n">
-        <v>2011494.553623763</v>
+        <v>2011494.545563162</v>
       </c>
       <c r="P322" t="n">
         <v>4500</v>
@@ -15782,10 +15782,10 @@
         <v>192</v>
       </c>
       <c r="N353" t="n">
-        <v>17075.989522161</v>
+        <v>17075.98952183</v>
       </c>
       <c r="O353" t="n">
-        <v>3278589.988254912</v>
+        <v>3278589.98819136</v>
       </c>
       <c r="P353" t="n">
         <v>27500</v>
@@ -16007,10 +16007,10 @@
         <v>355</v>
       </c>
       <c r="N358" t="n">
-        <v>59834</v>
+        <v>59958.524453694</v>
       </c>
       <c r="O358" t="n">
-        <v>21241070</v>
+        <v>21285276.18106137</v>
       </c>
       <c r="P358" t="n">
         <v>7900</v>
@@ -16562,10 +16562,10 @@
         <v>528</v>
       </c>
       <c r="N370" t="n">
-        <v>3821</v>
+        <v>3821.6520477816</v>
       </c>
       <c r="O370" t="n">
-        <v>2017488</v>
+        <v>2017832.281228685</v>
       </c>
       <c r="P370" t="n">
         <v>5900</v>
@@ -16608,10 +16608,10 @@
         <v>180</v>
       </c>
       <c r="N371" t="n">
-        <v>15472</v>
+        <v>15512.291666667</v>
       </c>
       <c r="O371" t="n">
-        <v>2784960</v>
+        <v>2792212.50000006</v>
       </c>
       <c r="P371" t="n">
         <v>25900</v>
@@ -16746,10 +16746,10 @@
         <v>576</v>
       </c>
       <c r="N374" t="n">
-        <v>5476</v>
+        <v>5486.9301397206</v>
       </c>
       <c r="O374" t="n">
-        <v>3154176</v>
+        <v>3160471.760479066</v>
       </c>
       <c r="P374" t="n">
         <v>8900</v>
@@ -16884,10 +16884,10 @@
         <v>4224</v>
       </c>
       <c r="N377" t="n">
-        <v>1516.0387847976</v>
+        <v>1516.0387762203</v>
       </c>
       <c r="O377" t="n">
-        <v>6403747.826985063</v>
+        <v>6403747.790754547</v>
       </c>
       <c r="P377" t="n">
         <v>2300</v>
@@ -16930,10 +16930,10 @@
         <v>864</v>
       </c>
       <c r="N378" t="n">
-        <v>2458.5128483396</v>
+        <v>2458.5128385327</v>
       </c>
       <c r="O378" t="n">
-        <v>2124155.100965415</v>
+        <v>2124155.092492253</v>
       </c>
       <c r="P378" t="n">
         <v>3500</v>
@@ -16976,10 +16976,10 @@
         <v>240</v>
       </c>
       <c r="N379" t="n">
-        <v>1907.392860262</v>
+        <v>1907.3928289474</v>
       </c>
       <c r="O379" t="n">
-        <v>457774.28646288</v>
+        <v>457774.278947376</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
@@ -17022,10 +17022,10 @@
         <v>288</v>
       </c>
       <c r="N380" t="n">
-        <v>1771.090242915</v>
+        <v>1771.0901699524</v>
       </c>
       <c r="O380" t="n">
-        <v>510073.9899595201</v>
+        <v>510073.9689462912</v>
       </c>
       <c r="P380" t="n">
         <v>2500</v>
@@ -17068,10 +17068,10 @@
         <v>720</v>
       </c>
       <c r="N381" t="n">
-        <v>2079.3838525155</v>
+        <v>2079.3837839721</v>
       </c>
       <c r="O381" t="n">
-        <v>1497156.37381116</v>
+        <v>1497156.324459912</v>
       </c>
       <c r="P381" t="n">
         <v>2900</v>
@@ -17114,10 +17114,10 @@
         <v>864</v>
       </c>
       <c r="N382" t="n">
-        <v>1803.0158997564</v>
+        <v>1803.0159162304</v>
       </c>
       <c r="O382" t="n">
-        <v>1557805.73738953</v>
+        <v>1557805.751623066</v>
       </c>
       <c r="P382" t="n">
         <v>2500</v>
@@ -17206,10 +17206,10 @@
         <v>396</v>
       </c>
       <c r="N384" t="n">
-        <v>2056.0827629734</v>
+        <v>2056.082714437</v>
       </c>
       <c r="O384" t="n">
-        <v>814208.7741374663</v>
+        <v>814208.754917052</v>
       </c>
       <c r="P384" t="n">
         <v>2900</v>
@@ -17252,10 +17252,10 @@
         <v>714</v>
       </c>
       <c r="N385" t="n">
-        <v>3224.56895</v>
+        <v>3224.5689724311</v>
       </c>
       <c r="O385" t="n">
-        <v>2302342.2303</v>
+        <v>2302342.246315805</v>
       </c>
       <c r="P385" t="n">
         <v>4500</v>
@@ -17298,10 +17298,10 @@
         <v>864</v>
       </c>
       <c r="N386" t="n">
-        <v>1655.9303958333</v>
+        <v>1655.9303421788</v>
       </c>
       <c r="O386" t="n">
-        <v>1430723.861999971</v>
+        <v>1430723.815642483</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
@@ -18189,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="N405" t="n">
-        <v>2357.74</v>
+        <v>2407.2030769231</v>
       </c>
       <c r="O405" t="n">
-        <v>2357.74</v>
+        <v>2407.2030769231</v>
       </c>
       <c r="P405" t="n">
         <v>3000</v>
@@ -18321,10 +18321,10 @@
         <v>216</v>
       </c>
       <c r="N408" t="n">
-        <v>2286.1646666667</v>
+        <v>2286.16463138</v>
       </c>
       <c r="O408" t="n">
-        <v>493811.5680000072</v>
+        <v>493811.5603780801</v>
       </c>
       <c r="P408" t="n">
         <v>3000</v>
@@ -18496,10 +18496,10 @@
         <v>1</v>
       </c>
       <c r="N412" t="n">
-        <v>1283.6532462687</v>
+        <v>1283.6530916031</v>
       </c>
       <c r="O412" t="n">
-        <v>1283.6532462687</v>
+        <v>1283.6530916031</v>
       </c>
       <c r="P412" t="n">
         <v>1900</v>
@@ -18677,10 +18677,10 @@
         <v>6996</v>
       </c>
       <c r="N416" t="n">
-        <v>517.29151641831</v>
+        <v>517.2923857868</v>
       </c>
       <c r="O416" t="n">
-        <v>3618971.448862497</v>
+        <v>3618977.530964453</v>
       </c>
       <c r="P416" t="n">
         <v>900</v>
@@ -18809,10 +18809,10 @@
         <v>15368</v>
       </c>
       <c r="N419" t="n">
-        <v>703.79500789654</v>
+        <v>703.7949766627</v>
       </c>
       <c r="O419" t="n">
-        <v>10815921.68135403</v>
+        <v>10815921.20135237</v>
       </c>
       <c r="P419" t="n">
         <v>900</v>
@@ -19386,10 +19386,10 @@
         <v>569</v>
       </c>
       <c r="N432" t="n">
-        <v>1595.5001480385</v>
+        <v>1595.4999702159</v>
       </c>
       <c r="O432" t="n">
-        <v>907839.5842339065</v>
+        <v>907839.4830528471</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
@@ -20263,10 +20263,10 @@
         <v>1976</v>
       </c>
       <c r="N451" t="n">
-        <v>7046.9398275119</v>
+        <v>7049.9805782093</v>
       </c>
       <c r="O451" t="n">
-        <v>13924753.09916352</v>
+        <v>13930761.62254158</v>
       </c>
       <c r="P451" t="n">
         <v>9900</v>
@@ -21754,10 +21754,10 @@
         <v>481</v>
       </c>
       <c r="N485" t="n">
-        <v>2181.4247724621</v>
+        <v>2181.4247663551</v>
       </c>
       <c r="O485" t="n">
-        <v>1049265.31555427</v>
+        <v>1049265.312616803</v>
       </c>
       <c r="P485" t="n">
         <v>2900</v>
@@ -21798,10 +21798,10 @@
         <v>1440</v>
       </c>
       <c r="N486" t="n">
-        <v>1727.31</v>
+        <v>1728.3970421649</v>
       </c>
       <c r="O486" t="n">
-        <v>2487326.4</v>
+        <v>2488891.740717456</v>
       </c>
       <c r="P486" t="n">
         <v>2850</v>
@@ -22393,10 +22393,10 @@
         <v>1</v>
       </c>
       <c r="N500" t="n">
-        <v>4985.40591133</v>
+        <v>4985.4060913706</v>
       </c>
       <c r="O500" t="n">
-        <v>4985.40591133</v>
+        <v>4985.4060913706</v>
       </c>
       <c r="P500" t="n">
         <v>7900</v>
@@ -22664,10 +22664,10 @@
         <v>5</v>
       </c>
       <c r="N506" t="n">
-        <v>21664.371666667</v>
+        <v>21664.371818182</v>
       </c>
       <c r="O506" t="n">
-        <v>108321.858333335</v>
+        <v>108321.85909091</v>
       </c>
       <c r="P506" t="n">
         <v>30000</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -798,10 +798,10 @@
         <v>60</v>
       </c>
       <c r="N10" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>1622148.54111408</v>
+        <v>1620000</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
@@ -4655,10 +4655,10 @@
         <v>101</v>
       </c>
       <c r="N103" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O103" t="n">
-        <v>1740720.257543888</v>
+        <v>1737948.41</v>
       </c>
       <c r="P103" t="n">
         <v>20000</v>
@@ -5384,10 +5384,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O119" t="n">
-        <v>1268308.340425526</v>
+        <v>1266624</v>
       </c>
       <c r="P119" t="n">
         <v>14900</v>
@@ -5750,10 +5750,10 @@
         <v>95</v>
       </c>
       <c r="N127" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="O127" t="n">
-        <v>564880.0000000005</v>
+        <v>559360</v>
       </c>
       <c r="P127" t="n">
         <v>9500</v>
@@ -6640,10 +6640,10 @@
         <v>180</v>
       </c>
       <c r="N147" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O147" t="n">
-        <v>480068.338480542</v>
+        <v>479772</v>
       </c>
       <c r="P147" t="n">
         <v>20900</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O152" t="n">
-        <v>3537371.471350867</v>
+        <v>3537118.530998287</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7259,10 +7259,10 @@
         <v>4579</v>
       </c>
       <c r="N161" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O161" t="n">
-        <v>80013234.65312298</v>
+        <v>80008454.89</v>
       </c>
       <c r="P161" t="n">
         <v>2900</v>
@@ -7347,10 +7347,10 @@
         <v>5378</v>
       </c>
       <c r="N163" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O163" t="n">
-        <v>8232192.134596441</v>
+        <v>8231728.140000001</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -9402,10 +9402,10 @@
         <v>864</v>
       </c>
       <c r="N210" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O210" t="n">
-        <v>2220244.113314419</v>
+        <v>2217888</v>
       </c>
       <c r="P210" t="n">
         <v>4500</v>
@@ -11720,10 +11720,10 @@
         <v>480</v>
       </c>
       <c r="N264" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O264" t="n">
-        <v>3831416.654656512</v>
+        <v>3825576.080610672</v>
       </c>
       <c r="P264" t="n">
         <v>12900</v>
@@ -11802,10 +11802,10 @@
         <v>12</v>
       </c>
       <c r="N266" t="n">
-        <v>10148.474923077</v>
+        <v>9994.710153846199</v>
       </c>
       <c r="O266" t="n">
-        <v>121781.699076924</v>
+        <v>119936.5218461544</v>
       </c>
       <c r="P266" t="n">
         <v>20800</v>
@@ -12891,10 +12891,10 @@
         <v>108</v>
       </c>
       <c r="N290" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O290" t="n">
-        <v>1560348.42352938</v>
+        <v>1553040</v>
       </c>
       <c r="P290" t="n">
         <v>23000</v>
@@ -14271,10 +14271,10 @@
         <v>36</v>
       </c>
       <c r="N320" t="n">
-        <v>23400.84</v>
+        <v>22942</v>
       </c>
       <c r="O320" t="n">
-        <v>842430.24</v>
+        <v>825912</v>
       </c>
       <c r="P320" t="n">
         <v>36900</v>
@@ -16007,10 +16007,10 @@
         <v>355</v>
       </c>
       <c r="N358" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O358" t="n">
-        <v>21285276.18106137</v>
+        <v>21241070</v>
       </c>
       <c r="P358" t="n">
         <v>7900</v>
@@ -16562,10 +16562,10 @@
         <v>528</v>
       </c>
       <c r="N370" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O370" t="n">
-        <v>2017832.281228685</v>
+        <v>2017488</v>
       </c>
       <c r="P370" t="n">
         <v>5900</v>
@@ -16608,10 +16608,10 @@
         <v>180</v>
       </c>
       <c r="N371" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O371" t="n">
-        <v>2792212.50000006</v>
+        <v>2784960</v>
       </c>
       <c r="P371" t="n">
         <v>25900</v>
@@ -16746,10 +16746,10 @@
         <v>576</v>
       </c>
       <c r="N374" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O374" t="n">
-        <v>3160471.760479066</v>
+        <v>3154176</v>
       </c>
       <c r="P374" t="n">
         <v>8900</v>
@@ -18189,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="N405" t="n">
-        <v>2407.2030769231</v>
+        <v>2357.74</v>
       </c>
       <c r="O405" t="n">
-        <v>2407.2030769231</v>
+        <v>2357.74</v>
       </c>
       <c r="P405" t="n">
         <v>3000</v>
@@ -20263,10 +20263,10 @@
         <v>1976</v>
       </c>
       <c r="N451" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O451" t="n">
-        <v>13930761.62254158</v>
+        <v>13924753.09894279</v>
       </c>
       <c r="P451" t="n">
         <v>9900</v>
@@ -21798,10 +21798,10 @@
         <v>1440</v>
       </c>
       <c r="N486" t="n">
-        <v>1728.3970421649</v>
+        <v>1727.31</v>
       </c>
       <c r="O486" t="n">
-        <v>2488891.740717456</v>
+        <v>2487326.4</v>
       </c>
       <c r="P486" t="n">
         <v>2850</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.34986176</v>
+        <v>754174.346915904</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2878,10 +2878,10 @@
         <v>28</v>
       </c>
       <c r="N62" t="n">
-        <v>56906.803962264</v>
+        <v>56906.805744681</v>
       </c>
       <c r="O62" t="n">
-        <v>1593390.510943392</v>
+        <v>1593390.560851068</v>
       </c>
       <c r="P62" t="n">
         <v>95900</v>
@@ -2925,10 +2925,10 @@
         <v>6</v>
       </c>
       <c r="N63" t="n">
-        <v>62349.656875</v>
+        <v>62349.656129032</v>
       </c>
       <c r="O63" t="n">
-        <v>374097.94125</v>
+        <v>374097.936774192</v>
       </c>
       <c r="P63" t="n">
         <v>109900</v>
@@ -3019,10 +3019,10 @@
         <v>111</v>
       </c>
       <c r="N65" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O65" t="n">
-        <v>15697274.18950776</v>
+        <v>15697274.19118386</v>
       </c>
       <c r="P65" t="n">
         <v>251900</v>
@@ -3061,10 +3061,10 @@
         <v>27</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O66" t="n">
-        <v>5401949.44954122</v>
+        <v>5401949.45249988</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.79954545</v>
+        <v>174389.80095238</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.7972727</v>
+        <v>1046338.80571428</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3197,10 +3197,10 @@
         <v>16</v>
       </c>
       <c r="N69" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O69" t="n">
-        <v>5513586.85617024</v>
+        <v>5513586.85511104</v>
       </c>
       <c r="P69" t="n">
         <v>532900</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.30260992</v>
+        <v>5241684.3035813</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.914986336</v>
+        <v>2788835.910545484</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -6239,10 +6239,10 @@
         <v>168</v>
       </c>
       <c r="N138" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O138" t="n">
-        <v>603834.606231696</v>
+        <v>603834.6048</v>
       </c>
       <c r="P138" t="n">
         <v>6500</v>
@@ -6464,10 +6464,10 @@
         <v>361</v>
       </c>
       <c r="N143" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O143" t="n">
-        <v>5350878.760181548</v>
+        <v>5350878.759927404</v>
       </c>
       <c r="P143" t="n">
         <v>24900</v>
@@ -8060,10 +8060,10 @@
         <v>384</v>
       </c>
       <c r="N179" t="n">
-        <v>1690.5922846782</v>
+        <v>1690.591979835</v>
       </c>
       <c r="O179" t="n">
-        <v>649187.4373164289</v>
+        <v>649187.32025664</v>
       </c>
       <c r="P179" t="n">
         <v>2900</v>
@@ -8106,10 +8106,10 @@
         <v>4608</v>
       </c>
       <c r="N180" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O180" t="n">
-        <v>7143294.099191501</v>
+        <v>7143294.12344663</v>
       </c>
       <c r="P180" t="n">
         <v>2500</v>
@@ -8152,10 +8152,10 @@
         <v>1632</v>
       </c>
       <c r="N181" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O181" t="n">
-        <v>3922534.875991901</v>
+        <v>3922535.168804525</v>
       </c>
       <c r="P181" t="n">
         <v>3500</v>
@@ -10222,10 +10222,10 @@
         <v>150</v>
       </c>
       <c r="N229" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O229" t="n">
-        <v>642779.37788019</v>
+        <v>642779.378892735</v>
       </c>
       <c r="P229" t="n">
         <v>6900</v>
@@ -13397,10 +13397,10 @@
         <v>1145</v>
       </c>
       <c r="N301" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O301" t="n">
-        <v>2036351.238475253</v>
+        <v>2036351.238952375</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -15782,10 +15782,10 @@
         <v>192</v>
       </c>
       <c r="N353" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O353" t="n">
-        <v>3278589.98819136</v>
+        <v>3278589.988063872</v>
       </c>
       <c r="P353" t="n">
         <v>27500</v>
@@ -17206,10 +17206,10 @@
         <v>396</v>
       </c>
       <c r="N384" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O384" t="n">
-        <v>814208.754917052</v>
+        <v>814208.75287884</v>
       </c>
       <c r="P384" t="n">
         <v>2900</v>
@@ -17252,10 +17252,10 @@
         <v>714</v>
       </c>
       <c r="N385" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O385" t="n">
-        <v>2302342.246315805</v>
+        <v>2302342.25274459</v>
       </c>
       <c r="P385" t="n">
         <v>4500</v>
@@ -18677,10 +18677,10 @@
         <v>6996</v>
       </c>
       <c r="N416" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O416" t="n">
-        <v>3618977.530964453</v>
+        <v>3618977.663121481</v>
       </c>
       <c r="P416" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.904982944</v>
+        <v>2788835.898291156</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -5335,10 +5335,10 @@
         <v>360</v>
       </c>
       <c r="N118" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O118" t="n">
-        <v>2702660.4</v>
+        <v>2706551.919654444</v>
       </c>
       <c r="P118" t="n">
         <v>13500</v>
@@ -5384,10 +5384,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O119" t="n">
-        <v>1266624</v>
+        <v>1271697.260347123</v>
       </c>
       <c r="P119" t="n">
         <v>14900</v>
@@ -8060,10 +8060,10 @@
         <v>4224</v>
       </c>
       <c r="N179" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O179" t="n">
-        <v>6548019.745904948</v>
+        <v>6548019.75344521</v>
       </c>
       <c r="P179" t="n">
         <v>2500</v>
@@ -8106,10 +8106,10 @@
         <v>1632</v>
       </c>
       <c r="N180" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O180" t="n">
-        <v>3922535.328773328</v>
+        <v>3922535.344891776</v>
       </c>
       <c r="P180" t="n">
         <v>3500</v>
@@ -12845,10 +12845,10 @@
         <v>30</v>
       </c>
       <c r="N289" t="n">
-        <v>15502</v>
+        <v>15634.495726496</v>
       </c>
       <c r="O289" t="n">
-        <v>465060</v>
+        <v>469034.87179488</v>
       </c>
       <c r="P289" t="n">
         <v>25900</v>
@@ -13305,10 +13305,10 @@
         <v>1145</v>
       </c>
       <c r="N299" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O299" t="n">
-        <v>2036351.242297034</v>
+        <v>2036351.242775416</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
@@ -16010,10 +16010,10 @@
         <v>209</v>
       </c>
       <c r="N358" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O358" t="n">
-        <v>2247795</v>
+        <v>2255695.861160005</v>
       </c>
       <c r="P358" t="n">
         <v>17900</v>
@@ -17022,10 +17022,10 @@
         <v>864</v>
       </c>
       <c r="N380" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O380" t="n">
-        <v>1557805.76235049</v>
+        <v>1557805.765936262</v>
       </c>
       <c r="P380" t="n">
         <v>2500</v>
@@ -18717,10 +18717,10 @@
         <v>15368</v>
       </c>
       <c r="N417" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O417" t="n">
-        <v>10815921.10656731</v>
+        <v>10815921.09785089</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8550526316</v>
+        <v>6272.8550704225</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.691368426</v>
+        <v>1354936.69521126</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -3933,10 +3933,10 @@
         <v>2130</v>
       </c>
       <c r="N86" t="n">
-        <v>2834.5536057033</v>
+        <v>2833</v>
       </c>
       <c r="O86" t="n">
-        <v>6037599.180148029</v>
+        <v>6034290</v>
       </c>
       <c r="P86" t="n">
         <v>3500</v>
@@ -4783,10 +4783,10 @@
         <v>708</v>
       </c>
       <c r="N106" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O106" t="n">
-        <v>1988279.242701916</v>
+        <v>1985465.64</v>
       </c>
       <c r="P106" t="n">
         <v>4900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O108" t="n">
-        <v>2790764.056234152</v>
+        <v>2788835.841806832</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.629231596</v>
+        <v>9901668.625887131</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O112" t="n">
-        <v>19910209.12320404</v>
+        <v>19894505.52160119</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5384,10 +5384,10 @@
         <v>144</v>
       </c>
       <c r="N119" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O119" t="n">
-        <v>1268319.614457831</v>
+        <v>1266624</v>
       </c>
       <c r="P119" t="n">
         <v>14900</v>
@@ -5609,10 +5609,10 @@
         <v>1260</v>
       </c>
       <c r="N124" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O124" t="n">
-        <v>5497031.218836528</v>
+        <v>5490513</v>
       </c>
       <c r="P124" t="n">
         <v>7500</v>
@@ -5655,10 +5655,10 @@
         <v>64</v>
       </c>
       <c r="N125" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O125" t="n">
-        <v>313019.5231781504</v>
+        <v>313019.5231820992</v>
       </c>
       <c r="P125" t="n">
         <v>8200</v>
@@ -6062,10 +6062,10 @@
         <v>539</v>
       </c>
       <c r="N134" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O134" t="n">
-        <v>4673646.146845914</v>
+        <v>4668818</v>
       </c>
       <c r="P134" t="n">
         <v>14200</v>
@@ -6239,10 +6239,10 @@
         <v>168</v>
       </c>
       <c r="N138" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O138" t="n">
-        <v>603834.6012040104</v>
+        <v>603834.6004819296</v>
       </c>
       <c r="P138" t="n">
         <v>6500</v>
@@ -6464,10 +6464,10 @@
         <v>361</v>
       </c>
       <c r="N143" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O143" t="n">
-        <v>5360625.351475398</v>
+        <v>5350878.759162084</v>
       </c>
       <c r="P143" t="n">
         <v>24900</v>
@@ -6640,10 +6640,10 @@
         <v>180</v>
       </c>
       <c r="N147" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O147" t="n">
-        <v>480961.026022302</v>
+        <v>479772</v>
       </c>
       <c r="P147" t="n">
         <v>20900</v>
@@ -6823,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O151" t="n">
-        <v>237249.4810706904</v>
+        <v>237249.4810736388</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O152" t="n">
-        <v>3537118.531273428</v>
+        <v>3539144.082329313</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7345,10 +7345,10 @@
         <v>377</v>
       </c>
       <c r="N163" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O163" t="n">
-        <v>3552327.433874681</v>
+        <v>3549194.87</v>
       </c>
       <c r="P163" t="n">
         <v>16900</v>
@@ -7703,10 +7703,10 @@
         <v>541</v>
       </c>
       <c r="N171" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O171" t="n">
-        <v>6459384.431336235</v>
+        <v>6449477.399999999</v>
       </c>
       <c r="P171" t="n">
         <v>19900</v>
@@ -7878,10 +7878,10 @@
         <v>457</v>
       </c>
       <c r="N175" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O175" t="n">
-        <v>4536212.159161481</v>
+        <v>4525671</v>
       </c>
       <c r="P175" t="n">
         <v>15900</v>
@@ -7970,10 +7970,10 @@
         <v>384</v>
       </c>
       <c r="N177" t="n">
-        <v>1690.5907183908</v>
+        <v>1830.8887033195</v>
       </c>
       <c r="O177" t="n">
-        <v>649186.8358620672</v>
+        <v>703061.262074688</v>
       </c>
       <c r="P177" t="n">
         <v>2900</v>
@@ -8016,10 +8016,10 @@
         <v>4224</v>
       </c>
       <c r="N178" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O178" t="n">
-        <v>6548019.922942081</v>
+        <v>6548020.612820544</v>
       </c>
       <c r="P178" t="n">
         <v>2500</v>
@@ -8062,10 +8062,10 @@
         <v>1632</v>
       </c>
       <c r="N179" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O179" t="n">
-        <v>3922535.822213913</v>
+        <v>4161154.306536969</v>
       </c>
       <c r="P179" t="n">
         <v>3500</v>
@@ -9266,10 +9266,10 @@
         <v>576</v>
       </c>
       <c r="N207" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O207" t="n">
-        <v>5068479.182302483</v>
+        <v>5065620.48</v>
       </c>
       <c r="P207" t="n">
         <v>14500</v>
@@ -9435,10 +9435,10 @@
         <v>216</v>
       </c>
       <c r="N211" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O211" t="n">
-        <v>545091.3943145568</v>
+        <v>543719.5199999999</v>
       </c>
       <c r="P211" t="n">
         <v>4200</v>
@@ -10086,10 +10086,10 @@
         <v>150</v>
       </c>
       <c r="N226" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O226" t="n">
-        <v>642779.37990762</v>
+        <v>642779.395417155</v>
       </c>
       <c r="P226" t="n">
         <v>6900</v>
@@ -10637,10 +10637,10 @@
         <v>150</v>
       </c>
       <c r="N239" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O239" t="n">
-        <v>1739191.1323944</v>
+        <v>1734305.76338025</v>
       </c>
       <c r="P239" t="n">
         <v>18500</v>
@@ -11323,10 +11323,10 @@
         <v>34</v>
       </c>
       <c r="N255" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O255" t="n">
-        <v>947623.194724414</v>
+        <v>922208.00866142</v>
       </c>
       <c r="P255" t="n">
         <v>44500</v>
@@ -11369,10 +11369,10 @@
         <v>30</v>
       </c>
       <c r="N256" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O256" t="n">
-        <v>512109.66169014</v>
+        <v>509240.7</v>
       </c>
       <c r="P256" t="n">
         <v>26900</v>
@@ -11410,10 +11410,10 @@
         <v>51</v>
       </c>
       <c r="N257" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O257" t="n">
-        <v>209630.5299757287</v>
+        <v>209122.95</v>
       </c>
       <c r="P257" t="n">
         <v>26900</v>
@@ -12985,10 +12985,10 @@
         <v>123</v>
       </c>
       <c r="N292" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O292" t="n">
-        <v>1951699.120879179</v>
+        <v>1946352</v>
       </c>
       <c r="P292" t="n">
         <v>26900</v>
@@ -13215,10 +13215,10 @@
         <v>156</v>
       </c>
       <c r="N297" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O297" t="n">
-        <v>545138.3489361731</v>
+        <v>543816</v>
       </c>
       <c r="P297" t="n">
         <v>6900</v>
@@ -13261,10 +13261,10 @@
         <v>1145</v>
       </c>
       <c r="N298" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O298" t="n">
-        <v>2036351.266884993</v>
+        <v>2036351.268343495</v>
       </c>
       <c r="P298" t="n">
         <v>4900</v>
@@ -13629,10 +13629,10 @@
         <v>216</v>
       </c>
       <c r="N306" t="n">
-        <v>32376.967005076</v>
+        <v>32295</v>
       </c>
       <c r="O306" t="n">
-        <v>6993424.873096416</v>
+        <v>6975720</v>
       </c>
       <c r="P306" t="n">
         <v>51900</v>
@@ -13905,10 +13905,10 @@
         <v>624</v>
       </c>
       <c r="N312" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O312" t="n">
-        <v>5536340.546254002</v>
+        <v>5527491.84</v>
       </c>
       <c r="P312" t="n">
         <v>15500</v>
@@ -13997,10 +13997,10 @@
         <v>48</v>
       </c>
       <c r="N314" t="n">
-        <v>5040.7413333333</v>
+        <v>5014</v>
       </c>
       <c r="O314" t="n">
-        <v>241955.5839999984</v>
+        <v>240672</v>
       </c>
       <c r="P314" t="n">
         <v>8200</v>
@@ -14225,10 +14225,10 @@
         <v>864</v>
       </c>
       <c r="N319" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O319" t="n">
-        <v>2019037.6494</v>
+        <v>2011494.5406</v>
       </c>
       <c r="P319" t="n">
         <v>4500</v>
@@ -14363,10 +14363,10 @@
         <v>1</v>
       </c>
       <c r="N322" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="O322" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="P322" t="n">
         <v>56900</v>
@@ -15140,10 +15140,10 @@
         <v>10</v>
       </c>
       <c r="N339" t="n">
-        <v>9751.4516129032</v>
+        <v>8637</v>
       </c>
       <c r="O339" t="n">
-        <v>97514.516129032</v>
+        <v>86370</v>
       </c>
       <c r="P339" t="n">
         <v>14500</v>
@@ -15370,10 +15370,10 @@
         <v>480</v>
       </c>
       <c r="N344" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O344" t="n">
-        <v>1872555.012145728</v>
+        <v>1871040</v>
       </c>
       <c r="P344" t="n">
         <v>6900</v>
@@ -15416,10 +15416,10 @@
         <v>425</v>
       </c>
       <c r="N345" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O345" t="n">
-        <v>5782782.3506892</v>
+        <v>5765125</v>
       </c>
       <c r="P345" t="n">
         <v>22500</v>
@@ -15462,10 +15462,10 @@
         <v>750</v>
       </c>
       <c r="N346" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O346" t="n">
-        <v>5735847.067039125</v>
+        <v>5726250</v>
       </c>
       <c r="P346" t="n">
         <v>13900</v>
@@ -16242,10 +16242,10 @@
         <v>2</v>
       </c>
       <c r="N363" t="n">
-        <v>14348.936170213</v>
+        <v>14050</v>
       </c>
       <c r="O363" t="n">
-        <v>28697.872340426</v>
+        <v>28100</v>
       </c>
       <c r="P363" t="n">
         <v>23900</v>
@@ -16288,10 +16288,10 @@
         <v>356</v>
       </c>
       <c r="N364" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O364" t="n">
-        <v>3104699.273607761</v>
+        <v>3097200</v>
       </c>
       <c r="P364" t="n">
         <v>14900</v>
@@ -16380,10 +16380,10 @@
         <v>103</v>
       </c>
       <c r="N366" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O366" t="n">
-        <v>2247695.102493028</v>
+        <v>2241486</v>
       </c>
       <c r="P366" t="n">
         <v>35900</v>
@@ -16472,10 +16472,10 @@
         <v>180</v>
       </c>
       <c r="N368" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O368" t="n">
-        <v>2792231.43603138</v>
+        <v>2784960</v>
       </c>
       <c r="P368" t="n">
         <v>25900</v>
@@ -16610,10 +16610,10 @@
         <v>576</v>
       </c>
       <c r="N371" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O371" t="n">
-        <v>3158378.766155923</v>
+        <v>3154176</v>
       </c>
       <c r="P371" t="n">
         <v>8900</v>
@@ -16702,10 +16702,10 @@
         <v>24</v>
       </c>
       <c r="N373" t="n">
-        <v>38558.016</v>
+        <v>38252</v>
       </c>
       <c r="O373" t="n">
-        <v>925392.3840000001</v>
+        <v>918048</v>
       </c>
       <c r="P373" t="n">
         <v>61900</v>
@@ -20173,10 +20173,10 @@
         <v>56</v>
       </c>
       <c r="N449" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O449" t="n">
-        <v>1371446.247227392</v>
+        <v>1362954.32</v>
       </c>
       <c r="P449" t="n">
         <v>27900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.408196721</v>
+        <v>16486.408099174</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.226229492</v>
+        <v>857293.221157048</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.96478022</v>
+        <v>15711.964751381</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.30945056</v>
+        <v>754174.308066288</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2878,10 +2878,10 @@
         <v>28</v>
       </c>
       <c r="N62" t="n">
-        <v>56906.805744681</v>
+        <v>56906.806444444</v>
       </c>
       <c r="O62" t="n">
-        <v>1593390.560851068</v>
+        <v>1593390.580444432</v>
       </c>
       <c r="P62" t="n">
         <v>95900</v>
@@ -3019,10 +3019,10 @@
         <v>111</v>
       </c>
       <c r="N65" t="n">
-        <v>141416.88460526</v>
+        <v>141416.88462046</v>
       </c>
       <c r="O65" t="n">
-        <v>15697274.19118386</v>
+        <v>15697274.19287106</v>
       </c>
       <c r="P65" t="n">
         <v>251900</v>
@@ -3061,10 +3061,10 @@
         <v>27</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20205607</v>
+        <v>200072.20216981</v>
       </c>
       <c r="O66" t="n">
-        <v>5401949.45551389</v>
+        <v>5401949.45858487</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.80095238</v>
+        <v>174389.8025</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.80571428</v>
+        <v>1046338.815</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3892,10 +3892,10 @@
         <v>1440</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2145369407</v>
+        <v>1950.214488189</v>
       </c>
       <c r="O85" t="n">
-        <v>2808308.933194608</v>
+        <v>2808308.86299216</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2554090804</v>
+        <v>2582.2554027233</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.841806832</v>
+        <v>2788835.834941164</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8960094242</v>
+        <v>5216.8960047177</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.625887131</v>
+        <v>9901668.616954194</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608322644</v>
+        <v>3158.8608345701</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.52160119</v>
+        <v>19894505.53612249</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5151,10 +5151,10 @@
         <v>144</v>
       </c>
       <c r="N114" t="n">
-        <v>3841.6249390244</v>
+        <v>3841.6250103093</v>
       </c>
       <c r="O114" t="n">
-        <v>553193.9912195136</v>
+        <v>553194.0014845391</v>
       </c>
       <c r="P114" t="n">
         <v>6900</v>
@@ -5243,10 +5243,10 @@
         <v>224</v>
       </c>
       <c r="N116" t="n">
-        <v>2694.8231444759</v>
+        <v>2694.8231379962</v>
       </c>
       <c r="O116" t="n">
-        <v>603640.3843626016</v>
+        <v>603640.3829111487</v>
       </c>
       <c r="P116" t="n">
         <v>4900</v>
@@ -5655,10 +5655,10 @@
         <v>64</v>
       </c>
       <c r="N125" t="n">
-        <v>4890.9300497203</v>
+        <v>4890.9300498132</v>
       </c>
       <c r="O125" t="n">
-        <v>313019.5231820992</v>
+        <v>313019.5231880448</v>
       </c>
       <c r="P125" t="n">
         <v>8200</v>
@@ -5883,10 +5883,10 @@
         <v>24</v>
       </c>
       <c r="N130" t="n">
-        <v>2267.0481239389</v>
+        <v>2267.0481103035</v>
       </c>
       <c r="O130" t="n">
-        <v>54409.1549745336</v>
+        <v>54409.154647284</v>
       </c>
       <c r="P130" t="n">
         <v>3900</v>
@@ -6239,10 +6239,10 @@
         <v>168</v>
       </c>
       <c r="N138" t="n">
-        <v>3594.2535742972</v>
+        <v>3594.2535483871</v>
       </c>
       <c r="O138" t="n">
-        <v>603834.6004819296</v>
+        <v>603834.5961290328</v>
       </c>
       <c r="P138" t="n">
         <v>6500</v>
@@ -6464,10 +6464,10 @@
         <v>361</v>
       </c>
       <c r="N143" t="n">
-        <v>14822.378834244</v>
+        <v>14822.378831406</v>
       </c>
       <c r="O143" t="n">
-        <v>5350878.759162084</v>
+        <v>5350878.758137566</v>
       </c>
       <c r="P143" t="n">
         <v>24900</v>
@@ -6823,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600137646</v>
+        <v>3041.6600137931</v>
       </c>
       <c r="O151" t="n">
-        <v>237249.4810736388</v>
+        <v>237249.4810758618</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4374.7145640659</v>
+        <v>4372.2107930714</v>
       </c>
       <c r="O152" t="n">
-        <v>3539144.082329313</v>
+        <v>3537118.531594763</v>
       </c>
       <c r="P152" t="n">
         <v>7500</v>
@@ -7172,10 +7172,10 @@
         <v>10357</v>
       </c>
       <c r="N159" t="n">
-        <v>1532.6290265229</v>
+        <v>1532.6290255288</v>
       </c>
       <c r="O159" t="n">
-        <v>15873438.82769768</v>
+        <v>15873438.81740178</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -7924,10 +7924,10 @@
         <v>1152</v>
       </c>
       <c r="N176" t="n">
-        <v>1630.9239968815</v>
+        <v>1630.9240698598</v>
       </c>
       <c r="O176" t="n">
-        <v>1878824.444407488</v>
+        <v>1878824.52847849</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>384</v>
       </c>
       <c r="N177" t="n">
-        <v>1830.8887033195</v>
+        <v>1690.5903203883</v>
       </c>
       <c r="O177" t="n">
-        <v>703061.262074688</v>
+        <v>649186.6830291072</v>
       </c>
       <c r="P177" t="n">
         <v>2900</v>
@@ -8016,10 +8016,10 @@
         <v>4224</v>
       </c>
       <c r="N178" t="n">
-        <v>1550.1942738685</v>
+        <v>1550.1941645158</v>
       </c>
       <c r="O178" t="n">
-        <v>6548020.612820544</v>
+        <v>6548020.150914739</v>
       </c>
       <c r="P178" t="n">
         <v>2500</v>
@@ -8062,10 +8062,10 @@
         <v>1632</v>
       </c>
       <c r="N179" t="n">
-        <v>2549.7269035153</v>
+        <v>2403.5147075539</v>
       </c>
       <c r="O179" t="n">
-        <v>4161154.306536969</v>
+        <v>3922536.002727964</v>
       </c>
       <c r="P179" t="n">
         <v>3500</v>
@@ -8897,10 +8897,10 @@
         <v>1415</v>
       </c>
       <c r="N198" t="n">
-        <v>4196.8725389755</v>
+        <v>4196.8725410978</v>
       </c>
       <c r="O198" t="n">
-        <v>5938574.642650332</v>
+        <v>5938574.645653388</v>
       </c>
       <c r="P198" t="n">
         <v>5900</v>
@@ -9648,10 +9648,10 @@
         <v>1254</v>
       </c>
       <c r="N216" t="n">
-        <v>880.32965533864</v>
+        <v>880.32968334542</v>
       </c>
       <c r="O216" t="n">
-        <v>1103933.387794655</v>
+        <v>1103933.422915157</v>
       </c>
       <c r="P216" t="n">
         <v>1200</v>
@@ -10086,10 +10086,10 @@
         <v>150</v>
       </c>
       <c r="N226" t="n">
-        <v>4285.1959694477</v>
+        <v>4285.1960260973</v>
       </c>
       <c r="O226" t="n">
-        <v>642779.395417155</v>
+        <v>642779.403914595</v>
       </c>
       <c r="P226" t="n">
         <v>6900</v>
@@ -10550,10 +10550,10 @@
         <v>1</v>
       </c>
       <c r="N237" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034924</v>
       </c>
       <c r="O237" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034924</v>
       </c>
       <c r="P237" t="n">
         <v>48900</v>
@@ -13261,10 +13261,10 @@
         <v>1145</v>
       </c>
       <c r="N298" t="n">
-        <v>1778.4727234441</v>
+        <v>1778.4727448514</v>
       </c>
       <c r="O298" t="n">
-        <v>2036351.268343495</v>
+        <v>2036351.292854853</v>
       </c>
       <c r="P298" t="n">
         <v>4900</v>
@@ -16748,10 +16748,10 @@
         <v>4224</v>
       </c>
       <c r="N374" t="n">
-        <v>1516.0387724372</v>
+        <v>1516.0387635597</v>
       </c>
       <c r="O374" t="n">
-        <v>6403747.774774732</v>
+        <v>6403747.737276173</v>
       </c>
       <c r="P374" t="n">
         <v>2300</v>
@@ -16794,10 +16794,10 @@
         <v>864</v>
       </c>
       <c r="N375" t="n">
-        <v>2458.5128114246</v>
+        <v>2458.5127187173</v>
       </c>
       <c r="O375" t="n">
-        <v>2124155.069070854</v>
+        <v>2124154.988971747</v>
       </c>
       <c r="P375" t="n">
         <v>3500</v>
@@ -16840,10 +16840,10 @@
         <v>240</v>
       </c>
       <c r="N376" t="n">
-        <v>1907.3928289474</v>
+        <v>1907.3928131868</v>
       </c>
       <c r="O376" t="n">
-        <v>457774.278947376</v>
+        <v>457774.275164832</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -16932,10 +16932,10 @@
         <v>720</v>
       </c>
       <c r="N378" t="n">
-        <v>2079.3837709497</v>
+        <v>2079.3836916549</v>
       </c>
       <c r="O378" t="n">
-        <v>1497156.315083784</v>
+        <v>1497156.257991528</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
@@ -16978,10 +16978,10 @@
         <v>864</v>
       </c>
       <c r="N379" t="n">
-        <v>1803.0159704121</v>
+        <v>1803.0161346363</v>
       </c>
       <c r="O379" t="n">
-        <v>1557805.798436054</v>
+        <v>1557805.940325763</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
@@ -17024,10 +17024,10 @@
         <v>1440</v>
       </c>
       <c r="N380" t="n">
-        <v>2122.1637267479</v>
+        <v>2122.1636203523</v>
       </c>
       <c r="O380" t="n">
-        <v>3055915.766516976</v>
+        <v>3055915.613307312</v>
       </c>
       <c r="P380" t="n">
         <v>2900</v>
@@ -17070,10 +17070,10 @@
         <v>396</v>
       </c>
       <c r="N381" t="n">
-        <v>2056.0826834456</v>
+        <v>2056.0824863487</v>
       </c>
       <c r="O381" t="n">
-        <v>814208.7426444577</v>
+        <v>814208.6645940852</v>
       </c>
       <c r="P381" t="n">
         <v>2900</v>
@@ -17116,10 +17116,10 @@
         <v>714</v>
       </c>
       <c r="N382" t="n">
-        <v>3224.5691001525</v>
+        <v>3224.5693083723</v>
       </c>
       <c r="O382" t="n">
-        <v>2302342.337508885</v>
+        <v>2302342.486177822</v>
       </c>
       <c r="P382" t="n">
         <v>4500</v>
@@ -17162,10 +17162,10 @@
         <v>864</v>
       </c>
       <c r="N383" t="n">
-        <v>1655.9302708407</v>
+        <v>1655.9298420859</v>
       </c>
       <c r="O383" t="n">
-        <v>1430723.754006365</v>
+        <v>1430723.383562217</v>
       </c>
       <c r="P383" t="n">
         <v>2500</v>
@@ -18185,10 +18185,10 @@
         <v>216</v>
       </c>
       <c r="N405" t="n">
-        <v>2286.1645697897</v>
+        <v>2286.1645384615</v>
       </c>
       <c r="O405" t="n">
-        <v>493811.5470745752</v>
+        <v>493811.540307684</v>
       </c>
       <c r="P405" t="n">
         <v>3000</v>
@@ -18541,10 +18541,10 @@
         <v>6996</v>
       </c>
       <c r="N413" t="n">
-        <v>517.29272348033</v>
+        <v>517.29287307808</v>
       </c>
       <c r="O413" t="n">
-        <v>3618979.893468388</v>
+        <v>3618980.940054248</v>
       </c>
       <c r="P413" t="n">
         <v>900</v>
@@ -18673,10 +18673,10 @@
         <v>15368</v>
       </c>
       <c r="N416" t="n">
-        <v>703.7949437622</v>
+        <v>703.79492130965</v>
       </c>
       <c r="O416" t="n">
-        <v>10815920.69573749</v>
+        <v>10815920.3506867</v>
       </c>
       <c r="P416" t="n">
         <v>900</v>
@@ -20353,10 +20353,10 @@
         <v>40</v>
       </c>
       <c r="N453" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="O453" t="n">
-        <v>1764544.15813952</v>
+        <v>1764544.16385544</v>
       </c>
       <c r="P453" t="n">
         <v>71900</v>
@@ -22208,10 +22208,10 @@
         <v>1</v>
       </c>
       <c r="N496" t="n">
-        <v>4985.4060913706</v>
+        <v>4985.4063157895</v>
       </c>
       <c r="O496" t="n">
-        <v>4985.4060913706</v>
+        <v>4985.4063157895</v>
       </c>
       <c r="P496" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.834941164</v>
+        <v>2788835.831501148</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -7703,10 +7703,10 @@
         <v>541</v>
       </c>
       <c r="N171" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O171" t="n">
-        <v>6449477.399999999</v>
+        <v>6464569.780811408</v>
       </c>
       <c r="P171" t="n">
         <v>19900</v>
@@ -7924,10 +7924,10 @@
         <v>1152</v>
       </c>
       <c r="N176" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O176" t="n">
-        <v>1878824.52847849</v>
+        <v>1878824.53096105</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>4224</v>
       </c>
       <c r="N178" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O178" t="n">
-        <v>6548020.150914739</v>
+        <v>6548020.160790451</v>
       </c>
       <c r="P178" t="n">
         <v>2500</v>
@@ -8062,10 +8062,10 @@
         <v>1632</v>
       </c>
       <c r="N179" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O179" t="n">
-        <v>3922536.002727964</v>
+        <v>3922536.03687936</v>
       </c>
       <c r="P179" t="n">
         <v>3500</v>
@@ -18541,10 +18541,10 @@
         <v>6996</v>
       </c>
       <c r="N413" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O413" t="n">
-        <v>3618980.940054248</v>
+        <v>3618981.431439855</v>
       </c>
       <c r="P413" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -8016,10 +8016,10 @@
         <v>1632</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O178" t="n">
-        <v>3922537.366246176</v>
+        <v>3922537.429884547</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -18627,10 +18627,10 @@
         <v>15368</v>
       </c>
       <c r="N415" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O415" t="n">
-        <v>10815919.79078344</v>
+        <v>10815919.77074572</v>
       </c>
       <c r="P415" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -798,10 +798,10 @@
         <v>60</v>
       </c>
       <c r="N10" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>1626488.65153536</v>
+        <v>1620000</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
@@ -960,10 +960,10 @@
         <v>48</v>
       </c>
       <c r="N14" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>1301634.782608704</v>
+        <v>1296000</v>
       </c>
       <c r="P14" t="n">
         <v>30000</v>
@@ -3387,10 +3387,10 @@
         <v>66</v>
       </c>
       <c r="N73" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O73" t="n">
-        <v>1797165.957446838</v>
+        <v>1782000</v>
       </c>
       <c r="P73" t="n">
         <v>20000</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O110" t="n">
-        <v>9916307.383648783</v>
+        <v>9901668.59565351</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5609,10 +5609,10 @@
         <v>64</v>
       </c>
       <c r="N124" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O124" t="n">
-        <v>313814.49346032</v>
+        <v>313019.5232507968</v>
       </c>
       <c r="P124" t="n">
         <v>8200</v>
@@ -5704,10 +5704,10 @@
         <v>95</v>
       </c>
       <c r="N126" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="O126" t="n">
-        <v>563231.0034602085</v>
+        <v>559360</v>
       </c>
       <c r="P126" t="n">
         <v>9500</v>
@@ -6372,10 +6372,10 @@
         <v>48</v>
       </c>
       <c r="N141" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O141" t="n">
-        <v>392845.1881188096</v>
+        <v>391392</v>
       </c>
       <c r="P141" t="n">
         <v>13500</v>
@@ -6418,10 +6418,10 @@
         <v>361</v>
       </c>
       <c r="N142" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O142" t="n">
-        <v>5354139.500572647</v>
+        <v>5350878.757623502</v>
       </c>
       <c r="P142" t="n">
         <v>24900</v>
@@ -7657,10 +7657,10 @@
         <v>505</v>
       </c>
       <c r="N170" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O170" t="n">
-        <v>6039328.507109055</v>
+        <v>6020307</v>
       </c>
       <c r="P170" t="n">
         <v>19900</v>
@@ -8635,10 +8635,10 @@
         <v>63</v>
       </c>
       <c r="N192" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O192" t="n">
-        <v>687162.645000027</v>
+        <v>682729.339090932</v>
       </c>
       <c r="P192" t="n">
         <v>19900</v>
@@ -9430,10 +9430,10 @@
         <v>30</v>
       </c>
       <c r="N211" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O211" t="n">
-        <v>676257.2925</v>
+        <v>674570.865</v>
       </c>
       <c r="P211" t="n">
         <v>36500</v>
@@ -9520,10 +9520,10 @@
         <v>249</v>
       </c>
       <c r="N213" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O213" t="n">
-        <v>6118899.680263254</v>
+        <v>6109966.98</v>
       </c>
       <c r="P213" t="n">
         <v>52900</v>
@@ -10591,10 +10591,10 @@
         <v>150</v>
       </c>
       <c r="N238" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O238" t="n">
-        <v>1739204.93220345</v>
+        <v>1734305.76271185</v>
       </c>
       <c r="P238" t="n">
         <v>18500</v>
@@ -10637,10 +10637,10 @@
         <v>95</v>
       </c>
       <c r="N239" t="n">
-        <v>12056.245617021</v>
+        <v>12005.159829787</v>
       </c>
       <c r="O239" t="n">
-        <v>1145343.333616995</v>
+        <v>1140490.183829765</v>
       </c>
       <c r="P239" t="n">
         <v>19500</v>
@@ -11277,10 +11277,10 @@
         <v>34</v>
       </c>
       <c r="N254" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O254" t="n">
-        <v>925896.83864</v>
+        <v>922208.0059199999</v>
       </c>
       <c r="P254" t="n">
         <v>44500</v>
@@ -11620,10 +11620,10 @@
         <v>12</v>
       </c>
       <c r="N262" t="n">
-        <v>10317.12016129</v>
+        <v>9994.710161290301</v>
       </c>
       <c r="O262" t="n">
-        <v>123805.44193548</v>
+        <v>119936.5219354836</v>
       </c>
       <c r="P262" t="n">
         <v>20800</v>
@@ -11707,10 +11707,10 @@
         <v>78</v>
       </c>
       <c r="N264" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O264" t="n">
-        <v>1020206.012603778</v>
+        <v>1012564.02</v>
       </c>
       <c r="P264" t="n">
         <v>21900</v>
@@ -11753,10 +11753,10 @@
         <v>84</v>
       </c>
       <c r="N265" t="n">
-        <v>13974.031438356</v>
+        <v>13878.97</v>
       </c>
       <c r="O265" t="n">
-        <v>1173818.640821904</v>
+        <v>1165833.48</v>
       </c>
       <c r="P265" t="n">
         <v>21900</v>
@@ -14002,10 +14002,10 @@
         <v>41</v>
       </c>
       <c r="N314" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O314" t="n">
-        <v>1123741.762237776</v>
+        <v>1115938</v>
       </c>
       <c r="P314" t="n">
         <v>43900</v>
@@ -14048,10 +14048,10 @@
         <v>36</v>
       </c>
       <c r="N315" t="n">
-        <v>23419.958333333</v>
+        <v>22942</v>
       </c>
       <c r="O315" t="n">
-        <v>843118.499999988</v>
+        <v>825912</v>
       </c>
       <c r="P315" t="n">
         <v>36900</v>
@@ -14368,10 +14368,10 @@
         <v>108</v>
       </c>
       <c r="N322" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O322" t="n">
-        <v>993419.4019933584</v>
+        <v>991224</v>
       </c>
       <c r="P322" t="n">
         <v>14900</v>
@@ -14414,10 +14414,10 @@
         <v>960</v>
       </c>
       <c r="N323" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O323" t="n">
-        <v>4385179.035933408</v>
+        <v>4362240</v>
       </c>
       <c r="P323" t="n">
         <v>7900</v>
@@ -14460,10 +14460,10 @@
         <v>24</v>
       </c>
       <c r="N324" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O324" t="n">
-        <v>606249.176470584</v>
+        <v>601824</v>
       </c>
       <c r="P324" t="n">
         <v>40900</v>
@@ -15099,10 +15099,10 @@
         <v>72</v>
       </c>
       <c r="N338" t="n">
-        <v>14306.769230769</v>
+        <v>14090</v>
       </c>
       <c r="O338" t="n">
-        <v>1030087.384615368</v>
+        <v>1014480</v>
       </c>
       <c r="P338" t="n">
         <v>22900</v>
@@ -15191,10 +15191,10 @@
         <v>624</v>
       </c>
       <c r="N340" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O340" t="n">
-        <v>8188093.776965232</v>
+        <v>8173152</v>
       </c>
       <c r="P340" t="n">
         <v>21200</v>
@@ -15559,10 +15559,10 @@
         <v>192</v>
       </c>
       <c r="N348" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O348" t="n">
-        <v>3287735.287698816</v>
+        <v>3278589.987614976</v>
       </c>
       <c r="P348" t="n">
         <v>27500</v>
@@ -15925,10 +15925,10 @@
         <v>28</v>
       </c>
       <c r="N356" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O356" t="n">
-        <v>485127.656441708</v>
+        <v>480704</v>
       </c>
       <c r="P356" t="n">
         <v>27900</v>
@@ -15971,10 +15971,10 @@
         <v>301</v>
       </c>
       <c r="N357" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O357" t="n">
-        <v>8214011.855855877</v>
+        <v>8203454</v>
       </c>
       <c r="P357" t="n">
         <v>43900</v>
@@ -16017,10 +16017,10 @@
         <v>60</v>
       </c>
       <c r="N358" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O358" t="n">
-        <v>2418996.29179332</v>
+        <v>2404380</v>
       </c>
       <c r="P358" t="n">
         <v>64900</v>
@@ -16201,10 +16201,10 @@
         <v>356</v>
       </c>
       <c r="N362" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O362" t="n">
-        <v>3104781.884944933</v>
+        <v>3097200</v>
       </c>
       <c r="P362" t="n">
         <v>14900</v>
@@ -19307,10 +19307,10 @@
         <v>35</v>
       </c>
       <c r="N430" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="O430" t="n">
-        <v>372389.415517245</v>
+        <v>369206.6</v>
       </c>
       <c r="P430" t="n">
         <v>35900</v>
@@ -19761,10 +19761,10 @@
         <v>1</v>
       </c>
       <c r="N440" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="O440" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="P440" t="n">
         <v>6500</v>
@@ -20086,10 +20086,10 @@
         <v>56</v>
       </c>
       <c r="N447" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O447" t="n">
-        <v>1371580.613164552</v>
+        <v>1362954.32</v>
       </c>
       <c r="P447" t="n">
         <v>27900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087042532</v>
+        <v>1811.3087824351</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.566765576</v>
+        <v>326035.580838318</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.964632768</v>
+        <v>15711.964602273</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.302372864</v>
+        <v>754174.3009091039</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2714,10 +2714,10 @@
         <v>136</v>
       </c>
       <c r="N58" t="n">
-        <v>7407.7300555556</v>
+        <v>7407.7300557103</v>
       </c>
       <c r="O58" t="n">
-        <v>1007451.287555562</v>
+        <v>1007451.287576601</v>
       </c>
       <c r="P58" t="n">
         <v>10900</v>
@@ -3892,10 +3892,10 @@
         <v>1440</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2144503171</v>
+        <v>1950.2144208289</v>
       </c>
       <c r="O85" t="n">
-        <v>2808308.808456624</v>
+        <v>2808308.765993616</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2551814224</v>
+        <v>2582.2551438323</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.595936192</v>
+        <v>2788835.555338884</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.895993495</v>
+        <v>5216.8959816133</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.59565351</v>
+        <v>9901668.573102044</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608347353</v>
+        <v>3158.8608348592</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.53716292</v>
+        <v>19894505.53794324</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5197,10 +5197,10 @@
         <v>224</v>
       </c>
       <c r="N115" t="n">
-        <v>2694.8231282537</v>
+        <v>2694.823125</v>
       </c>
       <c r="O115" t="n">
-        <v>603640.3807288287</v>
+        <v>603640.38</v>
       </c>
       <c r="P115" t="n">
         <v>4900</v>
@@ -5471,10 +5471,10 @@
         <v>3024</v>
       </c>
       <c r="N121" t="n">
-        <v>3795.7100076132</v>
+        <v>3795.7100076147</v>
       </c>
       <c r="O121" t="n">
-        <v>11478227.06302232</v>
+        <v>11478227.06302685</v>
       </c>
       <c r="P121" t="n">
         <v>6200</v>
@@ -5609,10 +5609,10 @@
         <v>64</v>
       </c>
       <c r="N124" t="n">
-        <v>4890.9300507937</v>
+        <v>4890.9300509879</v>
       </c>
       <c r="O124" t="n">
-        <v>313019.5232507968</v>
+        <v>313019.5232632256</v>
       </c>
       <c r="P124" t="n">
         <v>8200</v>
@@ -6193,10 +6193,10 @@
         <v>168</v>
       </c>
       <c r="N137" t="n">
-        <v>3594.2534111187</v>
+        <v>3594.2533147632</v>
       </c>
       <c r="O137" t="n">
-        <v>603834.5730679416</v>
+        <v>603834.5568802175</v>
       </c>
       <c r="P137" t="n">
         <v>6500</v>
@@ -6418,10 +6418,10 @@
         <v>361</v>
       </c>
       <c r="N142" t="n">
-        <v>14822.378829982</v>
+        <v>14822.378829268</v>
       </c>
       <c r="O142" t="n">
-        <v>5350878.757623502</v>
+        <v>5350878.757365748</v>
       </c>
       <c r="P142" t="n">
         <v>24900</v>
@@ -6777,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.66001386</v>
+        <v>3041.6600138793</v>
       </c>
       <c r="O150" t="n">
-        <v>237249.48108108</v>
+        <v>237249.4810825854</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -6823,10 +6823,10 @@
         <v>809</v>
       </c>
       <c r="N151" t="n">
-        <v>4371.171261065</v>
+        <v>4371.1712612367</v>
       </c>
       <c r="O151" t="n">
-        <v>3536277.550201585</v>
+        <v>3536277.55034049</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -7878,10 +7878,10 @@
         <v>1152</v>
       </c>
       <c r="N175" t="n">
-        <v>1630.9241816204</v>
+        <v>1630.9242252747</v>
       </c>
       <c r="O175" t="n">
-        <v>1878824.657226701</v>
+        <v>1878824.707516454</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -7924,10 +7924,10 @@
         <v>384</v>
       </c>
       <c r="N176" t="n">
-        <v>1690.5861086474</v>
+        <v>1690.5858435754</v>
       </c>
       <c r="O176" t="n">
-        <v>649185.0657206016</v>
+        <v>649184.9639329537</v>
       </c>
       <c r="P176" t="n">
         <v>2900</v>
@@ -7970,10 +7970,10 @@
         <v>4224</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1943423824</v>
+        <v>1550.1943880809</v>
       </c>
       <c r="O177" t="n">
-        <v>6548020.902223257</v>
+        <v>6548021.095253721</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1632</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5162209454</v>
+        <v>2403.5165803524</v>
       </c>
       <c r="O178" t="n">
-        <v>3922538.472582893</v>
+        <v>3922539.059135117</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -8851,10 +8851,10 @@
         <v>1415</v>
       </c>
       <c r="N197" t="n">
-        <v>4196.8725410978</v>
+        <v>4196.872541806</v>
       </c>
       <c r="O197" t="n">
-        <v>5938574.645653388</v>
+        <v>5938574.646655491</v>
       </c>
       <c r="P197" t="n">
         <v>5900</v>
@@ -9430,10 +9430,10 @@
         <v>30</v>
       </c>
       <c r="N211" t="n">
-        <v>22485.6955</v>
+        <v>22485.695494368</v>
       </c>
       <c r="O211" t="n">
-        <v>674570.865</v>
+        <v>674570.86483104</v>
       </c>
       <c r="P211" t="n">
         <v>36500</v>
@@ -9730,10 +9730,10 @@
         <v>2738</v>
       </c>
       <c r="N218" t="n">
-        <v>1732.9153651597</v>
+        <v>1732.9153592909</v>
       </c>
       <c r="O218" t="n">
-        <v>4744722.269807259</v>
+        <v>4744722.253738484</v>
       </c>
       <c r="P218" t="n">
         <v>1900</v>
@@ -9863,10 +9863,10 @@
         <v>523</v>
       </c>
       <c r="N221" t="n">
-        <v>998.76126091703</v>
+        <v>998.76126229508</v>
       </c>
       <c r="O221" t="n">
-        <v>522352.1394596067</v>
+        <v>522352.1401803268</v>
       </c>
       <c r="P221" t="n">
         <v>1600</v>
@@ -10040,10 +10040,10 @@
         <v>150</v>
       </c>
       <c r="N225" t="n">
-        <v>4285.1960620525</v>
+        <v>4285.1961426844</v>
       </c>
       <c r="O225" t="n">
-        <v>642779.409307875</v>
+        <v>642779.42140266</v>
       </c>
       <c r="P225" t="n">
         <v>6900</v>
@@ -11277,10 +11277,10 @@
         <v>34</v>
       </c>
       <c r="N254" t="n">
-        <v>27123.76488</v>
+        <v>27123.764869739</v>
       </c>
       <c r="O254" t="n">
-        <v>922208.0059199999</v>
+        <v>922208.005571126</v>
       </c>
       <c r="P254" t="n">
         <v>44500</v>
@@ -11538,10 +11538,10 @@
         <v>480</v>
       </c>
       <c r="N260" t="n">
-        <v>7969.9501692308</v>
+        <v>7969.950169361</v>
       </c>
       <c r="O260" t="n">
-        <v>3825576.081230784</v>
+        <v>3825576.08129328</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>
@@ -12254,10 +12254,10 @@
         <v>399</v>
       </c>
       <c r="N276" t="n">
-        <v>5218.1705789474</v>
+        <v>5218.1705812417</v>
       </c>
       <c r="O276" t="n">
-        <v>2082050.061000013</v>
+        <v>2082050.061915438</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -13174,10 +13174,10 @@
         <v>1145</v>
       </c>
       <c r="N296" t="n">
-        <v>1778.4727487406</v>
+        <v>1778.4727855775</v>
       </c>
       <c r="O296" t="n">
-        <v>2036351.297307987</v>
+        <v>2036351.339486237</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
@@ -13956,10 +13956,10 @@
         <v>28</v>
       </c>
       <c r="N313" t="n">
-        <v>2252.2977023121</v>
+        <v>2252.2978962963</v>
       </c>
       <c r="O313" t="n">
-        <v>63064.33566473879</v>
+        <v>63064.3410962964</v>
       </c>
       <c r="P313" t="n">
         <v>3900</v>
@@ -14138,10 +14138,10 @@
         <v>864</v>
       </c>
       <c r="N317" t="n">
-        <v>2328.1186779449</v>
+        <v>2328.1186767012</v>
       </c>
       <c r="O317" t="n">
-        <v>2011494.537744394</v>
+        <v>2011494.536669837</v>
       </c>
       <c r="P317" t="n">
         <v>4500</v>
@@ -16661,10 +16661,10 @@
         <v>4224</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0387603223</v>
+        <v>1516.0387548048</v>
       </c>
       <c r="O372" t="n">
-        <v>6403747.723601395</v>
+        <v>6403747.700295475</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -16707,10 +16707,10 @@
         <v>864</v>
       </c>
       <c r="N373" t="n">
-        <v>2458.5126727464</v>
+        <v>2458.5126365879</v>
       </c>
       <c r="O373" t="n">
-        <v>2124154.949252889</v>
+        <v>2124154.918011946</v>
       </c>
       <c r="P373" t="n">
         <v>3500</v>
@@ -16753,10 +16753,10 @@
         <v>240</v>
       </c>
       <c r="N374" t="n">
-        <v>1907.3927734807</v>
+        <v>1907.3927252503</v>
       </c>
       <c r="O374" t="n">
-        <v>457774.265635368</v>
+        <v>457774.254060072</v>
       </c>
       <c r="P374" t="n">
         <v>2500</v>
@@ -16799,10 +16799,10 @@
         <v>288</v>
       </c>
       <c r="N375" t="n">
-        <v>1771.0894683176</v>
+        <v>1771.0894375457</v>
       </c>
       <c r="O375" t="n">
-        <v>510073.7668754688</v>
+        <v>510073.7580131616</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16845,10 +16845,10 @@
         <v>720</v>
       </c>
       <c r="N376" t="n">
-        <v>2079.383486674</v>
+        <v>2079.3834819145</v>
       </c>
       <c r="O376" t="n">
-        <v>1497156.11040528</v>
+        <v>1497156.10697844</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16891,10 +16891,10 @@
         <v>864</v>
       </c>
       <c r="N377" t="n">
-        <v>1803.0162940958</v>
+        <v>1803.0163011152</v>
       </c>
       <c r="O377" t="n">
-        <v>1557806.078098771</v>
+        <v>1557806.084163533</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -16937,10 +16937,10 @@
         <v>1440</v>
       </c>
       <c r="N378" t="n">
-        <v>2122.1635509397</v>
+        <v>2122.1635338843</v>
       </c>
       <c r="O378" t="n">
-        <v>3055915.513353168</v>
+        <v>3055915.488793392</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
@@ -16983,10 +16983,10 @@
         <v>396</v>
       </c>
       <c r="N379" t="n">
-        <v>2056.0823949889</v>
+        <v>2056.0823271375</v>
       </c>
       <c r="O379" t="n">
-        <v>814208.6284156044</v>
+        <v>814208.6015464501</v>
       </c>
       <c r="P379" t="n">
         <v>2900</v>
@@ -17029,10 +17029,10 @@
         <v>714</v>
       </c>
       <c r="N380" t="n">
-        <v>3224.5693375065</v>
+        <v>3224.5693668237</v>
       </c>
       <c r="O380" t="n">
-        <v>2302342.506979641</v>
+        <v>2302342.527912122</v>
       </c>
       <c r="P380" t="n">
         <v>4500</v>
@@ -17075,10 +17075,10 @@
         <v>864</v>
       </c>
       <c r="N381" t="n">
-        <v>1655.9297403561</v>
+        <v>1655.9297327394</v>
       </c>
       <c r="O381" t="n">
-        <v>1430723.29566767</v>
+        <v>1430723.289086842</v>
       </c>
       <c r="P381" t="n">
         <v>2500</v>
@@ -17492,10 +17492,10 @@
         <v>1400</v>
       </c>
       <c r="N390" t="n">
-        <v>1185.3195700703</v>
+        <v>1185.319565762</v>
       </c>
       <c r="O390" t="n">
-        <v>1659447.39809842</v>
+        <v>1659447.3920668</v>
       </c>
       <c r="P390" t="n">
         <v>1900</v>
@@ -18098,10 +18098,10 @@
         <v>17</v>
       </c>
       <c r="N403" t="n">
-        <v>2286.1616470588</v>
+        <v>2286.1645384615</v>
       </c>
       <c r="O403" t="n">
-        <v>38864.7479999996</v>
+        <v>38864.79715384549</v>
       </c>
       <c r="P403" t="n">
         <v>3000</v>
@@ -18454,10 +18454,10 @@
         <v>6996</v>
       </c>
       <c r="N411" t="n">
-        <v>517.29385463984</v>
+        <v>517.2940518305199</v>
       </c>
       <c r="O411" t="n">
-        <v>3618987.80706032</v>
+        <v>3618989.186606318</v>
       </c>
       <c r="P411" t="n">
         <v>900</v>
@@ -18586,10 +18586,10 @@
         <v>14792</v>
       </c>
       <c r="N414" t="n">
-        <v>703.79485280542</v>
+        <v>703.79483731577</v>
       </c>
       <c r="O414" t="n">
-        <v>10410533.46269777</v>
+        <v>10410533.23357487</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -18635,10 +18635,10 @@
         <v>127</v>
       </c>
       <c r="N415" t="n">
-        <v>3182.251119403</v>
+        <v>3182.2511257036</v>
       </c>
       <c r="O415" t="n">
-        <v>404145.892164181</v>
+        <v>404145.8929643572</v>
       </c>
       <c r="P415" t="n">
         <v>6900</v>
@@ -19163,10 +19163,10 @@
         <v>569</v>
       </c>
       <c r="N427" t="n">
-        <v>1595.4997222222</v>
+        <v>1595.4994469697</v>
       </c>
       <c r="O427" t="n">
-        <v>907839.3419444318</v>
+        <v>907839.1853257593</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
@@ -20266,10 +20266,10 @@
         <v>40</v>
       </c>
       <c r="N451" t="n">
-        <v>44113.604387097</v>
+        <v>44113.604121212</v>
       </c>
       <c r="O451" t="n">
-        <v>1764544.17548388</v>
+        <v>1764544.16484848</v>
       </c>
       <c r="P451" t="n">
         <v>71900</v>
@@ -21995,10 +21995,10 @@
         <v>5</v>
       </c>
       <c r="N491" t="n">
-        <v>3683.6327400468</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O491" t="n">
-        <v>18418.163700234</v>
+        <v>18418.1637323945</v>
       </c>
       <c r="P491" t="n">
         <v>3600</v>
@@ -22121,10 +22121,10 @@
         <v>1</v>
       </c>
       <c r="N494" t="n">
-        <v>4985.4064864865</v>
+        <v>4985.4066666667</v>
       </c>
       <c r="O494" t="n">
-        <v>4985.4064864865</v>
+        <v>4985.4066666667</v>
       </c>
       <c r="P494" t="n">
         <v>7900</v>
